--- a/справка  ЦППД-1.xlsx
+++ b/справка  ЦППД-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лот 2" sheetId="1" state="hidden" r:id="rId1"/>
-    <sheet name="Справка ЦППД-1 октябрь" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лот 2" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка ЦППД-1 октябрь" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Лот 2'!$16:$18</definedName>
@@ -432,9 +432,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -479,11 +476,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="26">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -825,8 +825,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Лот2"/>
       <sheetName val="Лот2 (2)"/>
@@ -1179,713 +1179,713 @@
   <dimension ref="A1:L231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.7109375" customWidth="1" style="83" min="1" max="1"/>
-    <col width="5.85546875" customWidth="1" style="83" min="2" max="2"/>
-    <col width="41.85546875" customWidth="1" style="83" min="3" max="3"/>
-    <col width="14.28515625" customWidth="1" style="83" min="4" max="4"/>
-    <col width="21.5703125" customWidth="1" style="83" min="5" max="5"/>
-    <col width="24.28515625" customWidth="1" style="83" min="6" max="6"/>
-    <col width="4.28515625" customWidth="1" style="83" min="7" max="7"/>
-    <col width="14.7109375" customWidth="1" style="83" min="8" max="8"/>
-    <col width="23" customWidth="1" style="83" min="9" max="9"/>
-    <col width="12.85546875" customWidth="1" style="83" min="10" max="10"/>
-    <col width="16.140625" customWidth="1" style="83" min="11" max="11"/>
-    <col width="14.140625" customWidth="1" style="83" min="12" max="12"/>
-    <col width="11" bestFit="1" customWidth="1" style="83" min="13" max="14"/>
-    <col width="9.140625" customWidth="1" style="83" min="15" max="256"/>
-    <col width="2" customWidth="1" style="83" min="257" max="257"/>
-    <col width="5.85546875" customWidth="1" style="83" min="258" max="258"/>
-    <col width="38.5703125" customWidth="1" style="83" min="259" max="259"/>
-    <col width="10" customWidth="1" style="83" min="260" max="260"/>
-    <col width="21.5703125" customWidth="1" style="83" min="261" max="261"/>
-    <col width="22.7109375" customWidth="1" style="83" min="262" max="262"/>
-    <col width="0.28515625" customWidth="1" style="83" min="263" max="263"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="264" max="264"/>
-    <col width="9.140625" customWidth="1" style="83" min="265" max="267"/>
-    <col width="14.140625" customWidth="1" style="83" min="268" max="268"/>
-    <col width="9.140625" customWidth="1" style="83" min="269" max="512"/>
-    <col width="2" customWidth="1" style="83" min="513" max="513"/>
-    <col width="5.85546875" customWidth="1" style="83" min="514" max="514"/>
-    <col width="38.5703125" customWidth="1" style="83" min="515" max="515"/>
-    <col width="10" customWidth="1" style="83" min="516" max="516"/>
-    <col width="21.5703125" customWidth="1" style="83" min="517" max="517"/>
-    <col width="22.7109375" customWidth="1" style="83" min="518" max="518"/>
-    <col width="0.28515625" customWidth="1" style="83" min="519" max="519"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="520" max="520"/>
-    <col width="9.140625" customWidth="1" style="83" min="521" max="523"/>
-    <col width="14.140625" customWidth="1" style="83" min="524" max="524"/>
-    <col width="9.140625" customWidth="1" style="83" min="525" max="768"/>
-    <col width="2" customWidth="1" style="83" min="769" max="769"/>
-    <col width="5.85546875" customWidth="1" style="83" min="770" max="770"/>
-    <col width="38.5703125" customWidth="1" style="83" min="771" max="771"/>
-    <col width="10" customWidth="1" style="83" min="772" max="772"/>
-    <col width="21.5703125" customWidth="1" style="83" min="773" max="773"/>
-    <col width="22.7109375" customWidth="1" style="83" min="774" max="774"/>
-    <col width="0.28515625" customWidth="1" style="83" min="775" max="775"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="776" max="776"/>
-    <col width="9.140625" customWidth="1" style="83" min="777" max="779"/>
-    <col width="14.140625" customWidth="1" style="83" min="780" max="780"/>
-    <col width="9.140625" customWidth="1" style="83" min="781" max="1024"/>
-    <col width="2" customWidth="1" style="83" min="1025" max="1025"/>
-    <col width="5.85546875" customWidth="1" style="83" min="1026" max="1026"/>
-    <col width="38.5703125" customWidth="1" style="83" min="1027" max="1027"/>
-    <col width="10" customWidth="1" style="83" min="1028" max="1028"/>
-    <col width="21.5703125" customWidth="1" style="83" min="1029" max="1029"/>
-    <col width="22.7109375" customWidth="1" style="83" min="1030" max="1030"/>
-    <col width="0.28515625" customWidth="1" style="83" min="1031" max="1031"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="1032" max="1032"/>
-    <col width="9.140625" customWidth="1" style="83" min="1033" max="1035"/>
-    <col width="14.140625" customWidth="1" style="83" min="1036" max="1036"/>
-    <col width="9.140625" customWidth="1" style="83" min="1037" max="1280"/>
-    <col width="2" customWidth="1" style="83" min="1281" max="1281"/>
-    <col width="5.85546875" customWidth="1" style="83" min="1282" max="1282"/>
-    <col width="38.5703125" customWidth="1" style="83" min="1283" max="1283"/>
-    <col width="10" customWidth="1" style="83" min="1284" max="1284"/>
-    <col width="21.5703125" customWidth="1" style="83" min="1285" max="1285"/>
-    <col width="22.7109375" customWidth="1" style="83" min="1286" max="1286"/>
-    <col width="0.28515625" customWidth="1" style="83" min="1287" max="1287"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="1288" max="1288"/>
-    <col width="9.140625" customWidth="1" style="83" min="1289" max="1291"/>
-    <col width="14.140625" customWidth="1" style="83" min="1292" max="1292"/>
-    <col width="9.140625" customWidth="1" style="83" min="1293" max="1536"/>
-    <col width="2" customWidth="1" style="83" min="1537" max="1537"/>
-    <col width="5.85546875" customWidth="1" style="83" min="1538" max="1538"/>
-    <col width="38.5703125" customWidth="1" style="83" min="1539" max="1539"/>
-    <col width="10" customWidth="1" style="83" min="1540" max="1540"/>
-    <col width="21.5703125" customWidth="1" style="83" min="1541" max="1541"/>
-    <col width="22.7109375" customWidth="1" style="83" min="1542" max="1542"/>
-    <col width="0.28515625" customWidth="1" style="83" min="1543" max="1543"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="1544" max="1544"/>
-    <col width="9.140625" customWidth="1" style="83" min="1545" max="1547"/>
-    <col width="14.140625" customWidth="1" style="83" min="1548" max="1548"/>
-    <col width="9.140625" customWidth="1" style="83" min="1549" max="1792"/>
-    <col width="2" customWidth="1" style="83" min="1793" max="1793"/>
-    <col width="5.85546875" customWidth="1" style="83" min="1794" max="1794"/>
-    <col width="38.5703125" customWidth="1" style="83" min="1795" max="1795"/>
-    <col width="10" customWidth="1" style="83" min="1796" max="1796"/>
-    <col width="21.5703125" customWidth="1" style="83" min="1797" max="1797"/>
-    <col width="22.7109375" customWidth="1" style="83" min="1798" max="1798"/>
-    <col width="0.28515625" customWidth="1" style="83" min="1799" max="1799"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="1800" max="1800"/>
-    <col width="9.140625" customWidth="1" style="83" min="1801" max="1803"/>
-    <col width="14.140625" customWidth="1" style="83" min="1804" max="1804"/>
-    <col width="9.140625" customWidth="1" style="83" min="1805" max="2048"/>
-    <col width="2" customWidth="1" style="83" min="2049" max="2049"/>
-    <col width="5.85546875" customWidth="1" style="83" min="2050" max="2050"/>
-    <col width="38.5703125" customWidth="1" style="83" min="2051" max="2051"/>
-    <col width="10" customWidth="1" style="83" min="2052" max="2052"/>
-    <col width="21.5703125" customWidth="1" style="83" min="2053" max="2053"/>
-    <col width="22.7109375" customWidth="1" style="83" min="2054" max="2054"/>
-    <col width="0.28515625" customWidth="1" style="83" min="2055" max="2055"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="2056" max="2056"/>
-    <col width="9.140625" customWidth="1" style="83" min="2057" max="2059"/>
-    <col width="14.140625" customWidth="1" style="83" min="2060" max="2060"/>
-    <col width="9.140625" customWidth="1" style="83" min="2061" max="2304"/>
-    <col width="2" customWidth="1" style="83" min="2305" max="2305"/>
-    <col width="5.85546875" customWidth="1" style="83" min="2306" max="2306"/>
-    <col width="38.5703125" customWidth="1" style="83" min="2307" max="2307"/>
-    <col width="10" customWidth="1" style="83" min="2308" max="2308"/>
-    <col width="21.5703125" customWidth="1" style="83" min="2309" max="2309"/>
-    <col width="22.7109375" customWidth="1" style="83" min="2310" max="2310"/>
-    <col width="0.28515625" customWidth="1" style="83" min="2311" max="2311"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="2312" max="2312"/>
-    <col width="9.140625" customWidth="1" style="83" min="2313" max="2315"/>
-    <col width="14.140625" customWidth="1" style="83" min="2316" max="2316"/>
-    <col width="9.140625" customWidth="1" style="83" min="2317" max="2560"/>
-    <col width="2" customWidth="1" style="83" min="2561" max="2561"/>
-    <col width="5.85546875" customWidth="1" style="83" min="2562" max="2562"/>
-    <col width="38.5703125" customWidth="1" style="83" min="2563" max="2563"/>
-    <col width="10" customWidth="1" style="83" min="2564" max="2564"/>
-    <col width="21.5703125" customWidth="1" style="83" min="2565" max="2565"/>
-    <col width="22.7109375" customWidth="1" style="83" min="2566" max="2566"/>
-    <col width="0.28515625" customWidth="1" style="83" min="2567" max="2567"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="2568" max="2568"/>
-    <col width="9.140625" customWidth="1" style="83" min="2569" max="2571"/>
-    <col width="14.140625" customWidth="1" style="83" min="2572" max="2572"/>
-    <col width="9.140625" customWidth="1" style="83" min="2573" max="2816"/>
-    <col width="2" customWidth="1" style="83" min="2817" max="2817"/>
-    <col width="5.85546875" customWidth="1" style="83" min="2818" max="2818"/>
-    <col width="38.5703125" customWidth="1" style="83" min="2819" max="2819"/>
-    <col width="10" customWidth="1" style="83" min="2820" max="2820"/>
-    <col width="21.5703125" customWidth="1" style="83" min="2821" max="2821"/>
-    <col width="22.7109375" customWidth="1" style="83" min="2822" max="2822"/>
-    <col width="0.28515625" customWidth="1" style="83" min="2823" max="2823"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="2824" max="2824"/>
-    <col width="9.140625" customWidth="1" style="83" min="2825" max="2827"/>
-    <col width="14.140625" customWidth="1" style="83" min="2828" max="2828"/>
-    <col width="9.140625" customWidth="1" style="83" min="2829" max="3072"/>
-    <col width="2" customWidth="1" style="83" min="3073" max="3073"/>
-    <col width="5.85546875" customWidth="1" style="83" min="3074" max="3074"/>
-    <col width="38.5703125" customWidth="1" style="83" min="3075" max="3075"/>
-    <col width="10" customWidth="1" style="83" min="3076" max="3076"/>
-    <col width="21.5703125" customWidth="1" style="83" min="3077" max="3077"/>
-    <col width="22.7109375" customWidth="1" style="83" min="3078" max="3078"/>
-    <col width="0.28515625" customWidth="1" style="83" min="3079" max="3079"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="3080" max="3080"/>
-    <col width="9.140625" customWidth="1" style="83" min="3081" max="3083"/>
-    <col width="14.140625" customWidth="1" style="83" min="3084" max="3084"/>
-    <col width="9.140625" customWidth="1" style="83" min="3085" max="3328"/>
-    <col width="2" customWidth="1" style="83" min="3329" max="3329"/>
-    <col width="5.85546875" customWidth="1" style="83" min="3330" max="3330"/>
-    <col width="38.5703125" customWidth="1" style="83" min="3331" max="3331"/>
-    <col width="10" customWidth="1" style="83" min="3332" max="3332"/>
-    <col width="21.5703125" customWidth="1" style="83" min="3333" max="3333"/>
-    <col width="22.7109375" customWidth="1" style="83" min="3334" max="3334"/>
-    <col width="0.28515625" customWidth="1" style="83" min="3335" max="3335"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="3336" max="3336"/>
-    <col width="9.140625" customWidth="1" style="83" min="3337" max="3339"/>
-    <col width="14.140625" customWidth="1" style="83" min="3340" max="3340"/>
-    <col width="9.140625" customWidth="1" style="83" min="3341" max="3584"/>
-    <col width="2" customWidth="1" style="83" min="3585" max="3585"/>
-    <col width="5.85546875" customWidth="1" style="83" min="3586" max="3586"/>
-    <col width="38.5703125" customWidth="1" style="83" min="3587" max="3587"/>
-    <col width="10" customWidth="1" style="83" min="3588" max="3588"/>
-    <col width="21.5703125" customWidth="1" style="83" min="3589" max="3589"/>
-    <col width="22.7109375" customWidth="1" style="83" min="3590" max="3590"/>
-    <col width="0.28515625" customWidth="1" style="83" min="3591" max="3591"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="3592" max="3592"/>
-    <col width="9.140625" customWidth="1" style="83" min="3593" max="3595"/>
-    <col width="14.140625" customWidth="1" style="83" min="3596" max="3596"/>
-    <col width="9.140625" customWidth="1" style="83" min="3597" max="3840"/>
-    <col width="2" customWidth="1" style="83" min="3841" max="3841"/>
-    <col width="5.85546875" customWidth="1" style="83" min="3842" max="3842"/>
-    <col width="38.5703125" customWidth="1" style="83" min="3843" max="3843"/>
-    <col width="10" customWidth="1" style="83" min="3844" max="3844"/>
-    <col width="21.5703125" customWidth="1" style="83" min="3845" max="3845"/>
-    <col width="22.7109375" customWidth="1" style="83" min="3846" max="3846"/>
-    <col width="0.28515625" customWidth="1" style="83" min="3847" max="3847"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="3848" max="3848"/>
-    <col width="9.140625" customWidth="1" style="83" min="3849" max="3851"/>
-    <col width="14.140625" customWidth="1" style="83" min="3852" max="3852"/>
-    <col width="9.140625" customWidth="1" style="83" min="3853" max="4096"/>
-    <col width="2" customWidth="1" style="83" min="4097" max="4097"/>
-    <col width="5.85546875" customWidth="1" style="83" min="4098" max="4098"/>
-    <col width="38.5703125" customWidth="1" style="83" min="4099" max="4099"/>
-    <col width="10" customWidth="1" style="83" min="4100" max="4100"/>
-    <col width="21.5703125" customWidth="1" style="83" min="4101" max="4101"/>
-    <col width="22.7109375" customWidth="1" style="83" min="4102" max="4102"/>
-    <col width="0.28515625" customWidth="1" style="83" min="4103" max="4103"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="4104" max="4104"/>
-    <col width="9.140625" customWidth="1" style="83" min="4105" max="4107"/>
-    <col width="14.140625" customWidth="1" style="83" min="4108" max="4108"/>
-    <col width="9.140625" customWidth="1" style="83" min="4109" max="4352"/>
-    <col width="2" customWidth="1" style="83" min="4353" max="4353"/>
-    <col width="5.85546875" customWidth="1" style="83" min="4354" max="4354"/>
-    <col width="38.5703125" customWidth="1" style="83" min="4355" max="4355"/>
-    <col width="10" customWidth="1" style="83" min="4356" max="4356"/>
-    <col width="21.5703125" customWidth="1" style="83" min="4357" max="4357"/>
-    <col width="22.7109375" customWidth="1" style="83" min="4358" max="4358"/>
-    <col width="0.28515625" customWidth="1" style="83" min="4359" max="4359"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="4360" max="4360"/>
-    <col width="9.140625" customWidth="1" style="83" min="4361" max="4363"/>
-    <col width="14.140625" customWidth="1" style="83" min="4364" max="4364"/>
-    <col width="9.140625" customWidth="1" style="83" min="4365" max="4608"/>
-    <col width="2" customWidth="1" style="83" min="4609" max="4609"/>
-    <col width="5.85546875" customWidth="1" style="83" min="4610" max="4610"/>
-    <col width="38.5703125" customWidth="1" style="83" min="4611" max="4611"/>
-    <col width="10" customWidth="1" style="83" min="4612" max="4612"/>
-    <col width="21.5703125" customWidth="1" style="83" min="4613" max="4613"/>
-    <col width="22.7109375" customWidth="1" style="83" min="4614" max="4614"/>
-    <col width="0.28515625" customWidth="1" style="83" min="4615" max="4615"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="4616" max="4616"/>
-    <col width="9.140625" customWidth="1" style="83" min="4617" max="4619"/>
-    <col width="14.140625" customWidth="1" style="83" min="4620" max="4620"/>
-    <col width="9.140625" customWidth="1" style="83" min="4621" max="4864"/>
-    <col width="2" customWidth="1" style="83" min="4865" max="4865"/>
-    <col width="5.85546875" customWidth="1" style="83" min="4866" max="4866"/>
-    <col width="38.5703125" customWidth="1" style="83" min="4867" max="4867"/>
-    <col width="10" customWidth="1" style="83" min="4868" max="4868"/>
-    <col width="21.5703125" customWidth="1" style="83" min="4869" max="4869"/>
-    <col width="22.7109375" customWidth="1" style="83" min="4870" max="4870"/>
-    <col width="0.28515625" customWidth="1" style="83" min="4871" max="4871"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="4872" max="4872"/>
-    <col width="9.140625" customWidth="1" style="83" min="4873" max="4875"/>
-    <col width="14.140625" customWidth="1" style="83" min="4876" max="4876"/>
-    <col width="9.140625" customWidth="1" style="83" min="4877" max="5120"/>
-    <col width="2" customWidth="1" style="83" min="5121" max="5121"/>
-    <col width="5.85546875" customWidth="1" style="83" min="5122" max="5122"/>
-    <col width="38.5703125" customWidth="1" style="83" min="5123" max="5123"/>
-    <col width="10" customWidth="1" style="83" min="5124" max="5124"/>
-    <col width="21.5703125" customWidth="1" style="83" min="5125" max="5125"/>
-    <col width="22.7109375" customWidth="1" style="83" min="5126" max="5126"/>
-    <col width="0.28515625" customWidth="1" style="83" min="5127" max="5127"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="5128" max="5128"/>
-    <col width="9.140625" customWidth="1" style="83" min="5129" max="5131"/>
-    <col width="14.140625" customWidth="1" style="83" min="5132" max="5132"/>
-    <col width="9.140625" customWidth="1" style="83" min="5133" max="5376"/>
-    <col width="2" customWidth="1" style="83" min="5377" max="5377"/>
-    <col width="5.85546875" customWidth="1" style="83" min="5378" max="5378"/>
-    <col width="38.5703125" customWidth="1" style="83" min="5379" max="5379"/>
-    <col width="10" customWidth="1" style="83" min="5380" max="5380"/>
-    <col width="21.5703125" customWidth="1" style="83" min="5381" max="5381"/>
-    <col width="22.7109375" customWidth="1" style="83" min="5382" max="5382"/>
-    <col width="0.28515625" customWidth="1" style="83" min="5383" max="5383"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="5384" max="5384"/>
-    <col width="9.140625" customWidth="1" style="83" min="5385" max="5387"/>
-    <col width="14.140625" customWidth="1" style="83" min="5388" max="5388"/>
-    <col width="9.140625" customWidth="1" style="83" min="5389" max="5632"/>
-    <col width="2" customWidth="1" style="83" min="5633" max="5633"/>
-    <col width="5.85546875" customWidth="1" style="83" min="5634" max="5634"/>
-    <col width="38.5703125" customWidth="1" style="83" min="5635" max="5635"/>
-    <col width="10" customWidth="1" style="83" min="5636" max="5636"/>
-    <col width="21.5703125" customWidth="1" style="83" min="5637" max="5637"/>
-    <col width="22.7109375" customWidth="1" style="83" min="5638" max="5638"/>
-    <col width="0.28515625" customWidth="1" style="83" min="5639" max="5639"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="5640" max="5640"/>
-    <col width="9.140625" customWidth="1" style="83" min="5641" max="5643"/>
-    <col width="14.140625" customWidth="1" style="83" min="5644" max="5644"/>
-    <col width="9.140625" customWidth="1" style="83" min="5645" max="5888"/>
-    <col width="2" customWidth="1" style="83" min="5889" max="5889"/>
-    <col width="5.85546875" customWidth="1" style="83" min="5890" max="5890"/>
-    <col width="38.5703125" customWidth="1" style="83" min="5891" max="5891"/>
-    <col width="10" customWidth="1" style="83" min="5892" max="5892"/>
-    <col width="21.5703125" customWidth="1" style="83" min="5893" max="5893"/>
-    <col width="22.7109375" customWidth="1" style="83" min="5894" max="5894"/>
-    <col width="0.28515625" customWidth="1" style="83" min="5895" max="5895"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="5896" max="5896"/>
-    <col width="9.140625" customWidth="1" style="83" min="5897" max="5899"/>
-    <col width="14.140625" customWidth="1" style="83" min="5900" max="5900"/>
-    <col width="9.140625" customWidth="1" style="83" min="5901" max="6144"/>
-    <col width="2" customWidth="1" style="83" min="6145" max="6145"/>
-    <col width="5.85546875" customWidth="1" style="83" min="6146" max="6146"/>
-    <col width="38.5703125" customWidth="1" style="83" min="6147" max="6147"/>
-    <col width="10" customWidth="1" style="83" min="6148" max="6148"/>
-    <col width="21.5703125" customWidth="1" style="83" min="6149" max="6149"/>
-    <col width="22.7109375" customWidth="1" style="83" min="6150" max="6150"/>
-    <col width="0.28515625" customWidth="1" style="83" min="6151" max="6151"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="6152" max="6152"/>
-    <col width="9.140625" customWidth="1" style="83" min="6153" max="6155"/>
-    <col width="14.140625" customWidth="1" style="83" min="6156" max="6156"/>
-    <col width="9.140625" customWidth="1" style="83" min="6157" max="6400"/>
-    <col width="2" customWidth="1" style="83" min="6401" max="6401"/>
-    <col width="5.85546875" customWidth="1" style="83" min="6402" max="6402"/>
-    <col width="38.5703125" customWidth="1" style="83" min="6403" max="6403"/>
-    <col width="10" customWidth="1" style="83" min="6404" max="6404"/>
-    <col width="21.5703125" customWidth="1" style="83" min="6405" max="6405"/>
-    <col width="22.7109375" customWidth="1" style="83" min="6406" max="6406"/>
-    <col width="0.28515625" customWidth="1" style="83" min="6407" max="6407"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="6408" max="6408"/>
-    <col width="9.140625" customWidth="1" style="83" min="6409" max="6411"/>
-    <col width="14.140625" customWidth="1" style="83" min="6412" max="6412"/>
-    <col width="9.140625" customWidth="1" style="83" min="6413" max="6656"/>
-    <col width="2" customWidth="1" style="83" min="6657" max="6657"/>
-    <col width="5.85546875" customWidth="1" style="83" min="6658" max="6658"/>
-    <col width="38.5703125" customWidth="1" style="83" min="6659" max="6659"/>
-    <col width="10" customWidth="1" style="83" min="6660" max="6660"/>
-    <col width="21.5703125" customWidth="1" style="83" min="6661" max="6661"/>
-    <col width="22.7109375" customWidth="1" style="83" min="6662" max="6662"/>
-    <col width="0.28515625" customWidth="1" style="83" min="6663" max="6663"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="6664" max="6664"/>
-    <col width="9.140625" customWidth="1" style="83" min="6665" max="6667"/>
-    <col width="14.140625" customWidth="1" style="83" min="6668" max="6668"/>
-    <col width="9.140625" customWidth="1" style="83" min="6669" max="6912"/>
-    <col width="2" customWidth="1" style="83" min="6913" max="6913"/>
-    <col width="5.85546875" customWidth="1" style="83" min="6914" max="6914"/>
-    <col width="38.5703125" customWidth="1" style="83" min="6915" max="6915"/>
-    <col width="10" customWidth="1" style="83" min="6916" max="6916"/>
-    <col width="21.5703125" customWidth="1" style="83" min="6917" max="6917"/>
-    <col width="22.7109375" customWidth="1" style="83" min="6918" max="6918"/>
-    <col width="0.28515625" customWidth="1" style="83" min="6919" max="6919"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="6920" max="6920"/>
-    <col width="9.140625" customWidth="1" style="83" min="6921" max="6923"/>
-    <col width="14.140625" customWidth="1" style="83" min="6924" max="6924"/>
-    <col width="9.140625" customWidth="1" style="83" min="6925" max="7168"/>
-    <col width="2" customWidth="1" style="83" min="7169" max="7169"/>
-    <col width="5.85546875" customWidth="1" style="83" min="7170" max="7170"/>
-    <col width="38.5703125" customWidth="1" style="83" min="7171" max="7171"/>
-    <col width="10" customWidth="1" style="83" min="7172" max="7172"/>
-    <col width="21.5703125" customWidth="1" style="83" min="7173" max="7173"/>
-    <col width="22.7109375" customWidth="1" style="83" min="7174" max="7174"/>
-    <col width="0.28515625" customWidth="1" style="83" min="7175" max="7175"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="7176" max="7176"/>
-    <col width="9.140625" customWidth="1" style="83" min="7177" max="7179"/>
-    <col width="14.140625" customWidth="1" style="83" min="7180" max="7180"/>
-    <col width="9.140625" customWidth="1" style="83" min="7181" max="7424"/>
-    <col width="2" customWidth="1" style="83" min="7425" max="7425"/>
-    <col width="5.85546875" customWidth="1" style="83" min="7426" max="7426"/>
-    <col width="38.5703125" customWidth="1" style="83" min="7427" max="7427"/>
-    <col width="10" customWidth="1" style="83" min="7428" max="7428"/>
-    <col width="21.5703125" customWidth="1" style="83" min="7429" max="7429"/>
-    <col width="22.7109375" customWidth="1" style="83" min="7430" max="7430"/>
-    <col width="0.28515625" customWidth="1" style="83" min="7431" max="7431"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="7432" max="7432"/>
-    <col width="9.140625" customWidth="1" style="83" min="7433" max="7435"/>
-    <col width="14.140625" customWidth="1" style="83" min="7436" max="7436"/>
-    <col width="9.140625" customWidth="1" style="83" min="7437" max="7680"/>
-    <col width="2" customWidth="1" style="83" min="7681" max="7681"/>
-    <col width="5.85546875" customWidth="1" style="83" min="7682" max="7682"/>
-    <col width="38.5703125" customWidth="1" style="83" min="7683" max="7683"/>
-    <col width="10" customWidth="1" style="83" min="7684" max="7684"/>
-    <col width="21.5703125" customWidth="1" style="83" min="7685" max="7685"/>
-    <col width="22.7109375" customWidth="1" style="83" min="7686" max="7686"/>
-    <col width="0.28515625" customWidth="1" style="83" min="7687" max="7687"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="7688" max="7688"/>
-    <col width="9.140625" customWidth="1" style="83" min="7689" max="7691"/>
-    <col width="14.140625" customWidth="1" style="83" min="7692" max="7692"/>
-    <col width="9.140625" customWidth="1" style="83" min="7693" max="7936"/>
-    <col width="2" customWidth="1" style="83" min="7937" max="7937"/>
-    <col width="5.85546875" customWidth="1" style="83" min="7938" max="7938"/>
-    <col width="38.5703125" customWidth="1" style="83" min="7939" max="7939"/>
-    <col width="10" customWidth="1" style="83" min="7940" max="7940"/>
-    <col width="21.5703125" customWidth="1" style="83" min="7941" max="7941"/>
-    <col width="22.7109375" customWidth="1" style="83" min="7942" max="7942"/>
-    <col width="0.28515625" customWidth="1" style="83" min="7943" max="7943"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="7944" max="7944"/>
-    <col width="9.140625" customWidth="1" style="83" min="7945" max="7947"/>
-    <col width="14.140625" customWidth="1" style="83" min="7948" max="7948"/>
-    <col width="9.140625" customWidth="1" style="83" min="7949" max="8192"/>
-    <col width="2" customWidth="1" style="83" min="8193" max="8193"/>
-    <col width="5.85546875" customWidth="1" style="83" min="8194" max="8194"/>
-    <col width="38.5703125" customWidth="1" style="83" min="8195" max="8195"/>
-    <col width="10" customWidth="1" style="83" min="8196" max="8196"/>
-    <col width="21.5703125" customWidth="1" style="83" min="8197" max="8197"/>
-    <col width="22.7109375" customWidth="1" style="83" min="8198" max="8198"/>
-    <col width="0.28515625" customWidth="1" style="83" min="8199" max="8199"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="8200" max="8200"/>
-    <col width="9.140625" customWidth="1" style="83" min="8201" max="8203"/>
-    <col width="14.140625" customWidth="1" style="83" min="8204" max="8204"/>
-    <col width="9.140625" customWidth="1" style="83" min="8205" max="8448"/>
-    <col width="2" customWidth="1" style="83" min="8449" max="8449"/>
-    <col width="5.85546875" customWidth="1" style="83" min="8450" max="8450"/>
-    <col width="38.5703125" customWidth="1" style="83" min="8451" max="8451"/>
-    <col width="10" customWidth="1" style="83" min="8452" max="8452"/>
-    <col width="21.5703125" customWidth="1" style="83" min="8453" max="8453"/>
-    <col width="22.7109375" customWidth="1" style="83" min="8454" max="8454"/>
-    <col width="0.28515625" customWidth="1" style="83" min="8455" max="8455"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="8456" max="8456"/>
-    <col width="9.140625" customWidth="1" style="83" min="8457" max="8459"/>
-    <col width="14.140625" customWidth="1" style="83" min="8460" max="8460"/>
-    <col width="9.140625" customWidth="1" style="83" min="8461" max="8704"/>
-    <col width="2" customWidth="1" style="83" min="8705" max="8705"/>
-    <col width="5.85546875" customWidth="1" style="83" min="8706" max="8706"/>
-    <col width="38.5703125" customWidth="1" style="83" min="8707" max="8707"/>
-    <col width="10" customWidth="1" style="83" min="8708" max="8708"/>
-    <col width="21.5703125" customWidth="1" style="83" min="8709" max="8709"/>
-    <col width="22.7109375" customWidth="1" style="83" min="8710" max="8710"/>
-    <col width="0.28515625" customWidth="1" style="83" min="8711" max="8711"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="8712" max="8712"/>
-    <col width="9.140625" customWidth="1" style="83" min="8713" max="8715"/>
-    <col width="14.140625" customWidth="1" style="83" min="8716" max="8716"/>
-    <col width="9.140625" customWidth="1" style="83" min="8717" max="8960"/>
-    <col width="2" customWidth="1" style="83" min="8961" max="8961"/>
-    <col width="5.85546875" customWidth="1" style="83" min="8962" max="8962"/>
-    <col width="38.5703125" customWidth="1" style="83" min="8963" max="8963"/>
-    <col width="10" customWidth="1" style="83" min="8964" max="8964"/>
-    <col width="21.5703125" customWidth="1" style="83" min="8965" max="8965"/>
-    <col width="22.7109375" customWidth="1" style="83" min="8966" max="8966"/>
-    <col width="0.28515625" customWidth="1" style="83" min="8967" max="8967"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="8968" max="8968"/>
-    <col width="9.140625" customWidth="1" style="83" min="8969" max="8971"/>
-    <col width="14.140625" customWidth="1" style="83" min="8972" max="8972"/>
-    <col width="9.140625" customWidth="1" style="83" min="8973" max="9216"/>
-    <col width="2" customWidth="1" style="83" min="9217" max="9217"/>
-    <col width="5.85546875" customWidth="1" style="83" min="9218" max="9218"/>
-    <col width="38.5703125" customWidth="1" style="83" min="9219" max="9219"/>
-    <col width="10" customWidth="1" style="83" min="9220" max="9220"/>
-    <col width="21.5703125" customWidth="1" style="83" min="9221" max="9221"/>
-    <col width="22.7109375" customWidth="1" style="83" min="9222" max="9222"/>
-    <col width="0.28515625" customWidth="1" style="83" min="9223" max="9223"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="9224" max="9224"/>
-    <col width="9.140625" customWidth="1" style="83" min="9225" max="9227"/>
-    <col width="14.140625" customWidth="1" style="83" min="9228" max="9228"/>
-    <col width="9.140625" customWidth="1" style="83" min="9229" max="9472"/>
-    <col width="2" customWidth="1" style="83" min="9473" max="9473"/>
-    <col width="5.85546875" customWidth="1" style="83" min="9474" max="9474"/>
-    <col width="38.5703125" customWidth="1" style="83" min="9475" max="9475"/>
-    <col width="10" customWidth="1" style="83" min="9476" max="9476"/>
-    <col width="21.5703125" customWidth="1" style="83" min="9477" max="9477"/>
-    <col width="22.7109375" customWidth="1" style="83" min="9478" max="9478"/>
-    <col width="0.28515625" customWidth="1" style="83" min="9479" max="9479"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="9480" max="9480"/>
-    <col width="9.140625" customWidth="1" style="83" min="9481" max="9483"/>
-    <col width="14.140625" customWidth="1" style="83" min="9484" max="9484"/>
-    <col width="9.140625" customWidth="1" style="83" min="9485" max="9728"/>
-    <col width="2" customWidth="1" style="83" min="9729" max="9729"/>
-    <col width="5.85546875" customWidth="1" style="83" min="9730" max="9730"/>
-    <col width="38.5703125" customWidth="1" style="83" min="9731" max="9731"/>
-    <col width="10" customWidth="1" style="83" min="9732" max="9732"/>
-    <col width="21.5703125" customWidth="1" style="83" min="9733" max="9733"/>
-    <col width="22.7109375" customWidth="1" style="83" min="9734" max="9734"/>
-    <col width="0.28515625" customWidth="1" style="83" min="9735" max="9735"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="9736" max="9736"/>
-    <col width="9.140625" customWidth="1" style="83" min="9737" max="9739"/>
-    <col width="14.140625" customWidth="1" style="83" min="9740" max="9740"/>
-    <col width="9.140625" customWidth="1" style="83" min="9741" max="9984"/>
-    <col width="2" customWidth="1" style="83" min="9985" max="9985"/>
-    <col width="5.85546875" customWidth="1" style="83" min="9986" max="9986"/>
-    <col width="38.5703125" customWidth="1" style="83" min="9987" max="9987"/>
-    <col width="10" customWidth="1" style="83" min="9988" max="9988"/>
-    <col width="21.5703125" customWidth="1" style="83" min="9989" max="9989"/>
-    <col width="22.7109375" customWidth="1" style="83" min="9990" max="9990"/>
-    <col width="0.28515625" customWidth="1" style="83" min="9991" max="9991"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="9992" max="9992"/>
-    <col width="9.140625" customWidth="1" style="83" min="9993" max="9995"/>
-    <col width="14.140625" customWidth="1" style="83" min="9996" max="9996"/>
-    <col width="9.140625" customWidth="1" style="83" min="9997" max="10240"/>
-    <col width="2" customWidth="1" style="83" min="10241" max="10241"/>
-    <col width="5.85546875" customWidth="1" style="83" min="10242" max="10242"/>
-    <col width="38.5703125" customWidth="1" style="83" min="10243" max="10243"/>
-    <col width="10" customWidth="1" style="83" min="10244" max="10244"/>
-    <col width="21.5703125" customWidth="1" style="83" min="10245" max="10245"/>
-    <col width="22.7109375" customWidth="1" style="83" min="10246" max="10246"/>
-    <col width="0.28515625" customWidth="1" style="83" min="10247" max="10247"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="10248" max="10248"/>
-    <col width="9.140625" customWidth="1" style="83" min="10249" max="10251"/>
-    <col width="14.140625" customWidth="1" style="83" min="10252" max="10252"/>
-    <col width="9.140625" customWidth="1" style="83" min="10253" max="10496"/>
-    <col width="2" customWidth="1" style="83" min="10497" max="10497"/>
-    <col width="5.85546875" customWidth="1" style="83" min="10498" max="10498"/>
-    <col width="38.5703125" customWidth="1" style="83" min="10499" max="10499"/>
-    <col width="10" customWidth="1" style="83" min="10500" max="10500"/>
-    <col width="21.5703125" customWidth="1" style="83" min="10501" max="10501"/>
-    <col width="22.7109375" customWidth="1" style="83" min="10502" max="10502"/>
-    <col width="0.28515625" customWidth="1" style="83" min="10503" max="10503"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="10504" max="10504"/>
-    <col width="9.140625" customWidth="1" style="83" min="10505" max="10507"/>
-    <col width="14.140625" customWidth="1" style="83" min="10508" max="10508"/>
-    <col width="9.140625" customWidth="1" style="83" min="10509" max="10752"/>
-    <col width="2" customWidth="1" style="83" min="10753" max="10753"/>
-    <col width="5.85546875" customWidth="1" style="83" min="10754" max="10754"/>
-    <col width="38.5703125" customWidth="1" style="83" min="10755" max="10755"/>
-    <col width="10" customWidth="1" style="83" min="10756" max="10756"/>
-    <col width="21.5703125" customWidth="1" style="83" min="10757" max="10757"/>
-    <col width="22.7109375" customWidth="1" style="83" min="10758" max="10758"/>
-    <col width="0.28515625" customWidth="1" style="83" min="10759" max="10759"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="10760" max="10760"/>
-    <col width="9.140625" customWidth="1" style="83" min="10761" max="10763"/>
-    <col width="14.140625" customWidth="1" style="83" min="10764" max="10764"/>
-    <col width="9.140625" customWidth="1" style="83" min="10765" max="11008"/>
-    <col width="2" customWidth="1" style="83" min="11009" max="11009"/>
-    <col width="5.85546875" customWidth="1" style="83" min="11010" max="11010"/>
-    <col width="38.5703125" customWidth="1" style="83" min="11011" max="11011"/>
-    <col width="10" customWidth="1" style="83" min="11012" max="11012"/>
-    <col width="21.5703125" customWidth="1" style="83" min="11013" max="11013"/>
-    <col width="22.7109375" customWidth="1" style="83" min="11014" max="11014"/>
-    <col width="0.28515625" customWidth="1" style="83" min="11015" max="11015"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="11016" max="11016"/>
-    <col width="9.140625" customWidth="1" style="83" min="11017" max="11019"/>
-    <col width="14.140625" customWidth="1" style="83" min="11020" max="11020"/>
-    <col width="9.140625" customWidth="1" style="83" min="11021" max="11264"/>
-    <col width="2" customWidth="1" style="83" min="11265" max="11265"/>
-    <col width="5.85546875" customWidth="1" style="83" min="11266" max="11266"/>
-    <col width="38.5703125" customWidth="1" style="83" min="11267" max="11267"/>
-    <col width="10" customWidth="1" style="83" min="11268" max="11268"/>
-    <col width="21.5703125" customWidth="1" style="83" min="11269" max="11269"/>
-    <col width="22.7109375" customWidth="1" style="83" min="11270" max="11270"/>
-    <col width="0.28515625" customWidth="1" style="83" min="11271" max="11271"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="11272" max="11272"/>
-    <col width="9.140625" customWidth="1" style="83" min="11273" max="11275"/>
-    <col width="14.140625" customWidth="1" style="83" min="11276" max="11276"/>
-    <col width="9.140625" customWidth="1" style="83" min="11277" max="11520"/>
-    <col width="2" customWidth="1" style="83" min="11521" max="11521"/>
-    <col width="5.85546875" customWidth="1" style="83" min="11522" max="11522"/>
-    <col width="38.5703125" customWidth="1" style="83" min="11523" max="11523"/>
-    <col width="10" customWidth="1" style="83" min="11524" max="11524"/>
-    <col width="21.5703125" customWidth="1" style="83" min="11525" max="11525"/>
-    <col width="22.7109375" customWidth="1" style="83" min="11526" max="11526"/>
-    <col width="0.28515625" customWidth="1" style="83" min="11527" max="11527"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="11528" max="11528"/>
-    <col width="9.140625" customWidth="1" style="83" min="11529" max="11531"/>
-    <col width="14.140625" customWidth="1" style="83" min="11532" max="11532"/>
-    <col width="9.140625" customWidth="1" style="83" min="11533" max="11776"/>
-    <col width="2" customWidth="1" style="83" min="11777" max="11777"/>
-    <col width="5.85546875" customWidth="1" style="83" min="11778" max="11778"/>
-    <col width="38.5703125" customWidth="1" style="83" min="11779" max="11779"/>
-    <col width="10" customWidth="1" style="83" min="11780" max="11780"/>
-    <col width="21.5703125" customWidth="1" style="83" min="11781" max="11781"/>
-    <col width="22.7109375" customWidth="1" style="83" min="11782" max="11782"/>
-    <col width="0.28515625" customWidth="1" style="83" min="11783" max="11783"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="11784" max="11784"/>
-    <col width="9.140625" customWidth="1" style="83" min="11785" max="11787"/>
-    <col width="14.140625" customWidth="1" style="83" min="11788" max="11788"/>
-    <col width="9.140625" customWidth="1" style="83" min="11789" max="12032"/>
-    <col width="2" customWidth="1" style="83" min="12033" max="12033"/>
-    <col width="5.85546875" customWidth="1" style="83" min="12034" max="12034"/>
-    <col width="38.5703125" customWidth="1" style="83" min="12035" max="12035"/>
-    <col width="10" customWidth="1" style="83" min="12036" max="12036"/>
-    <col width="21.5703125" customWidth="1" style="83" min="12037" max="12037"/>
-    <col width="22.7109375" customWidth="1" style="83" min="12038" max="12038"/>
-    <col width="0.28515625" customWidth="1" style="83" min="12039" max="12039"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="12040" max="12040"/>
-    <col width="9.140625" customWidth="1" style="83" min="12041" max="12043"/>
-    <col width="14.140625" customWidth="1" style="83" min="12044" max="12044"/>
-    <col width="9.140625" customWidth="1" style="83" min="12045" max="12288"/>
-    <col width="2" customWidth="1" style="83" min="12289" max="12289"/>
-    <col width="5.85546875" customWidth="1" style="83" min="12290" max="12290"/>
-    <col width="38.5703125" customWidth="1" style="83" min="12291" max="12291"/>
-    <col width="10" customWidth="1" style="83" min="12292" max="12292"/>
-    <col width="21.5703125" customWidth="1" style="83" min="12293" max="12293"/>
-    <col width="22.7109375" customWidth="1" style="83" min="12294" max="12294"/>
-    <col width="0.28515625" customWidth="1" style="83" min="12295" max="12295"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="12296" max="12296"/>
-    <col width="9.140625" customWidth="1" style="83" min="12297" max="12299"/>
-    <col width="14.140625" customWidth="1" style="83" min="12300" max="12300"/>
-    <col width="9.140625" customWidth="1" style="83" min="12301" max="12544"/>
-    <col width="2" customWidth="1" style="83" min="12545" max="12545"/>
-    <col width="5.85546875" customWidth="1" style="83" min="12546" max="12546"/>
-    <col width="38.5703125" customWidth="1" style="83" min="12547" max="12547"/>
-    <col width="10" customWidth="1" style="83" min="12548" max="12548"/>
-    <col width="21.5703125" customWidth="1" style="83" min="12549" max="12549"/>
-    <col width="22.7109375" customWidth="1" style="83" min="12550" max="12550"/>
-    <col width="0.28515625" customWidth="1" style="83" min="12551" max="12551"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="12552" max="12552"/>
-    <col width="9.140625" customWidth="1" style="83" min="12553" max="12555"/>
-    <col width="14.140625" customWidth="1" style="83" min="12556" max="12556"/>
-    <col width="9.140625" customWidth="1" style="83" min="12557" max="12800"/>
-    <col width="2" customWidth="1" style="83" min="12801" max="12801"/>
-    <col width="5.85546875" customWidth="1" style="83" min="12802" max="12802"/>
-    <col width="38.5703125" customWidth="1" style="83" min="12803" max="12803"/>
-    <col width="10" customWidth="1" style="83" min="12804" max="12804"/>
-    <col width="21.5703125" customWidth="1" style="83" min="12805" max="12805"/>
-    <col width="22.7109375" customWidth="1" style="83" min="12806" max="12806"/>
-    <col width="0.28515625" customWidth="1" style="83" min="12807" max="12807"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="12808" max="12808"/>
-    <col width="9.140625" customWidth="1" style="83" min="12809" max="12811"/>
-    <col width="14.140625" customWidth="1" style="83" min="12812" max="12812"/>
-    <col width="9.140625" customWidth="1" style="83" min="12813" max="13056"/>
-    <col width="2" customWidth="1" style="83" min="13057" max="13057"/>
-    <col width="5.85546875" customWidth="1" style="83" min="13058" max="13058"/>
-    <col width="38.5703125" customWidth="1" style="83" min="13059" max="13059"/>
-    <col width="10" customWidth="1" style="83" min="13060" max="13060"/>
-    <col width="21.5703125" customWidth="1" style="83" min="13061" max="13061"/>
-    <col width="22.7109375" customWidth="1" style="83" min="13062" max="13062"/>
-    <col width="0.28515625" customWidth="1" style="83" min="13063" max="13063"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="13064" max="13064"/>
-    <col width="9.140625" customWidth="1" style="83" min="13065" max="13067"/>
-    <col width="14.140625" customWidth="1" style="83" min="13068" max="13068"/>
-    <col width="9.140625" customWidth="1" style="83" min="13069" max="13312"/>
-    <col width="2" customWidth="1" style="83" min="13313" max="13313"/>
-    <col width="5.85546875" customWidth="1" style="83" min="13314" max="13314"/>
-    <col width="38.5703125" customWidth="1" style="83" min="13315" max="13315"/>
-    <col width="10" customWidth="1" style="83" min="13316" max="13316"/>
-    <col width="21.5703125" customWidth="1" style="83" min="13317" max="13317"/>
-    <col width="22.7109375" customWidth="1" style="83" min="13318" max="13318"/>
-    <col width="0.28515625" customWidth="1" style="83" min="13319" max="13319"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="13320" max="13320"/>
-    <col width="9.140625" customWidth="1" style="83" min="13321" max="13323"/>
-    <col width="14.140625" customWidth="1" style="83" min="13324" max="13324"/>
-    <col width="9.140625" customWidth="1" style="83" min="13325" max="13568"/>
-    <col width="2" customWidth="1" style="83" min="13569" max="13569"/>
-    <col width="5.85546875" customWidth="1" style="83" min="13570" max="13570"/>
-    <col width="38.5703125" customWidth="1" style="83" min="13571" max="13571"/>
-    <col width="10" customWidth="1" style="83" min="13572" max="13572"/>
-    <col width="21.5703125" customWidth="1" style="83" min="13573" max="13573"/>
-    <col width="22.7109375" customWidth="1" style="83" min="13574" max="13574"/>
-    <col width="0.28515625" customWidth="1" style="83" min="13575" max="13575"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="13576" max="13576"/>
-    <col width="9.140625" customWidth="1" style="83" min="13577" max="13579"/>
-    <col width="14.140625" customWidth="1" style="83" min="13580" max="13580"/>
-    <col width="9.140625" customWidth="1" style="83" min="13581" max="13824"/>
-    <col width="2" customWidth="1" style="83" min="13825" max="13825"/>
-    <col width="5.85546875" customWidth="1" style="83" min="13826" max="13826"/>
-    <col width="38.5703125" customWidth="1" style="83" min="13827" max="13827"/>
-    <col width="10" customWidth="1" style="83" min="13828" max="13828"/>
-    <col width="21.5703125" customWidth="1" style="83" min="13829" max="13829"/>
-    <col width="22.7109375" customWidth="1" style="83" min="13830" max="13830"/>
-    <col width="0.28515625" customWidth="1" style="83" min="13831" max="13831"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="13832" max="13832"/>
-    <col width="9.140625" customWidth="1" style="83" min="13833" max="13835"/>
-    <col width="14.140625" customWidth="1" style="83" min="13836" max="13836"/>
-    <col width="9.140625" customWidth="1" style="83" min="13837" max="14080"/>
-    <col width="2" customWidth="1" style="83" min="14081" max="14081"/>
-    <col width="5.85546875" customWidth="1" style="83" min="14082" max="14082"/>
-    <col width="38.5703125" customWidth="1" style="83" min="14083" max="14083"/>
-    <col width="10" customWidth="1" style="83" min="14084" max="14084"/>
-    <col width="21.5703125" customWidth="1" style="83" min="14085" max="14085"/>
-    <col width="22.7109375" customWidth="1" style="83" min="14086" max="14086"/>
-    <col width="0.28515625" customWidth="1" style="83" min="14087" max="14087"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="14088" max="14088"/>
-    <col width="9.140625" customWidth="1" style="83" min="14089" max="14091"/>
-    <col width="14.140625" customWidth="1" style="83" min="14092" max="14092"/>
-    <col width="9.140625" customWidth="1" style="83" min="14093" max="14336"/>
-    <col width="2" customWidth="1" style="83" min="14337" max="14337"/>
-    <col width="5.85546875" customWidth="1" style="83" min="14338" max="14338"/>
-    <col width="38.5703125" customWidth="1" style="83" min="14339" max="14339"/>
-    <col width="10" customWidth="1" style="83" min="14340" max="14340"/>
-    <col width="21.5703125" customWidth="1" style="83" min="14341" max="14341"/>
-    <col width="22.7109375" customWidth="1" style="83" min="14342" max="14342"/>
-    <col width="0.28515625" customWidth="1" style="83" min="14343" max="14343"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="14344" max="14344"/>
-    <col width="9.140625" customWidth="1" style="83" min="14345" max="14347"/>
-    <col width="14.140625" customWidth="1" style="83" min="14348" max="14348"/>
-    <col width="9.140625" customWidth="1" style="83" min="14349" max="14592"/>
-    <col width="2" customWidth="1" style="83" min="14593" max="14593"/>
-    <col width="5.85546875" customWidth="1" style="83" min="14594" max="14594"/>
-    <col width="38.5703125" customWidth="1" style="83" min="14595" max="14595"/>
-    <col width="10" customWidth="1" style="83" min="14596" max="14596"/>
-    <col width="21.5703125" customWidth="1" style="83" min="14597" max="14597"/>
-    <col width="22.7109375" customWidth="1" style="83" min="14598" max="14598"/>
-    <col width="0.28515625" customWidth="1" style="83" min="14599" max="14599"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="14600" max="14600"/>
-    <col width="9.140625" customWidth="1" style="83" min="14601" max="14603"/>
-    <col width="14.140625" customWidth="1" style="83" min="14604" max="14604"/>
-    <col width="9.140625" customWidth="1" style="83" min="14605" max="14848"/>
-    <col width="2" customWidth="1" style="83" min="14849" max="14849"/>
-    <col width="5.85546875" customWidth="1" style="83" min="14850" max="14850"/>
-    <col width="38.5703125" customWidth="1" style="83" min="14851" max="14851"/>
-    <col width="10" customWidth="1" style="83" min="14852" max="14852"/>
-    <col width="21.5703125" customWidth="1" style="83" min="14853" max="14853"/>
-    <col width="22.7109375" customWidth="1" style="83" min="14854" max="14854"/>
-    <col width="0.28515625" customWidth="1" style="83" min="14855" max="14855"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="14856" max="14856"/>
-    <col width="9.140625" customWidth="1" style="83" min="14857" max="14859"/>
-    <col width="14.140625" customWidth="1" style="83" min="14860" max="14860"/>
-    <col width="9.140625" customWidth="1" style="83" min="14861" max="15104"/>
-    <col width="2" customWidth="1" style="83" min="15105" max="15105"/>
-    <col width="5.85546875" customWidth="1" style="83" min="15106" max="15106"/>
-    <col width="38.5703125" customWidth="1" style="83" min="15107" max="15107"/>
-    <col width="10" customWidth="1" style="83" min="15108" max="15108"/>
-    <col width="21.5703125" customWidth="1" style="83" min="15109" max="15109"/>
-    <col width="22.7109375" customWidth="1" style="83" min="15110" max="15110"/>
-    <col width="0.28515625" customWidth="1" style="83" min="15111" max="15111"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="15112" max="15112"/>
-    <col width="9.140625" customWidth="1" style="83" min="15113" max="15115"/>
-    <col width="14.140625" customWidth="1" style="83" min="15116" max="15116"/>
-    <col width="9.140625" customWidth="1" style="83" min="15117" max="15360"/>
-    <col width="2" customWidth="1" style="83" min="15361" max="15361"/>
-    <col width="5.85546875" customWidth="1" style="83" min="15362" max="15362"/>
-    <col width="38.5703125" customWidth="1" style="83" min="15363" max="15363"/>
-    <col width="10" customWidth="1" style="83" min="15364" max="15364"/>
-    <col width="21.5703125" customWidth="1" style="83" min="15365" max="15365"/>
-    <col width="22.7109375" customWidth="1" style="83" min="15366" max="15366"/>
-    <col width="0.28515625" customWidth="1" style="83" min="15367" max="15367"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="15368" max="15368"/>
-    <col width="9.140625" customWidth="1" style="83" min="15369" max="15371"/>
-    <col width="14.140625" customWidth="1" style="83" min="15372" max="15372"/>
-    <col width="9.140625" customWidth="1" style="83" min="15373" max="15616"/>
-    <col width="2" customWidth="1" style="83" min="15617" max="15617"/>
-    <col width="5.85546875" customWidth="1" style="83" min="15618" max="15618"/>
-    <col width="38.5703125" customWidth="1" style="83" min="15619" max="15619"/>
-    <col width="10" customWidth="1" style="83" min="15620" max="15620"/>
-    <col width="21.5703125" customWidth="1" style="83" min="15621" max="15621"/>
-    <col width="22.7109375" customWidth="1" style="83" min="15622" max="15622"/>
-    <col width="0.28515625" customWidth="1" style="83" min="15623" max="15623"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="15624" max="15624"/>
-    <col width="9.140625" customWidth="1" style="83" min="15625" max="15627"/>
-    <col width="14.140625" customWidth="1" style="83" min="15628" max="15628"/>
-    <col width="9.140625" customWidth="1" style="83" min="15629" max="15872"/>
-    <col width="2" customWidth="1" style="83" min="15873" max="15873"/>
-    <col width="5.85546875" customWidth="1" style="83" min="15874" max="15874"/>
-    <col width="38.5703125" customWidth="1" style="83" min="15875" max="15875"/>
-    <col width="10" customWidth="1" style="83" min="15876" max="15876"/>
-    <col width="21.5703125" customWidth="1" style="83" min="15877" max="15877"/>
-    <col width="22.7109375" customWidth="1" style="83" min="15878" max="15878"/>
-    <col width="0.28515625" customWidth="1" style="83" min="15879" max="15879"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="15880" max="15880"/>
-    <col width="9.140625" customWidth="1" style="83" min="15881" max="15883"/>
-    <col width="14.140625" customWidth="1" style="83" min="15884" max="15884"/>
-    <col width="9.140625" customWidth="1" style="83" min="15885" max="16128"/>
-    <col width="2" customWidth="1" style="83" min="16129" max="16129"/>
-    <col width="5.85546875" customWidth="1" style="83" min="16130" max="16130"/>
-    <col width="38.5703125" customWidth="1" style="83" min="16131" max="16131"/>
-    <col width="10" customWidth="1" style="83" min="16132" max="16132"/>
-    <col width="21.5703125" customWidth="1" style="83" min="16133" max="16133"/>
-    <col width="22.7109375" customWidth="1" style="83" min="16134" max="16134"/>
-    <col width="0.28515625" customWidth="1" style="83" min="16135" max="16135"/>
-    <col hidden="1" width="13" customWidth="1" style="83" min="16136" max="16136"/>
-    <col width="9.140625" customWidth="1" style="83" min="16137" max="16139"/>
-    <col width="14.140625" customWidth="1" style="83" min="16140" max="16140"/>
-    <col width="9.140625" customWidth="1" style="83" min="16141" max="16384"/>
+    <col width="3.7109375" customWidth="1" style="82" min="1" max="1"/>
+    <col width="5.85546875" customWidth="1" style="82" min="2" max="2"/>
+    <col width="41.85546875" customWidth="1" style="82" min="3" max="3"/>
+    <col width="14.28515625" customWidth="1" style="82" min="4" max="4"/>
+    <col width="21.5703125" customWidth="1" style="82" min="5" max="5"/>
+    <col width="24.28515625" customWidth="1" style="82" min="6" max="6"/>
+    <col width="4.28515625" customWidth="1" style="82" min="7" max="7"/>
+    <col width="14.7109375" customWidth="1" style="82" min="8" max="8"/>
+    <col width="23" customWidth="1" style="82" min="9" max="9"/>
+    <col width="12.85546875" customWidth="1" style="82" min="10" max="10"/>
+    <col width="16.140625" customWidth="1" style="82" min="11" max="11"/>
+    <col width="14.140625" customWidth="1" style="82" min="12" max="12"/>
+    <col width="11" bestFit="1" customWidth="1" style="82" min="13" max="14"/>
+    <col width="9.140625" customWidth="1" style="82" min="15" max="256"/>
+    <col width="2" customWidth="1" style="82" min="257" max="257"/>
+    <col width="5.85546875" customWidth="1" style="82" min="258" max="258"/>
+    <col width="38.5703125" customWidth="1" style="82" min="259" max="259"/>
+    <col width="10" customWidth="1" style="82" min="260" max="260"/>
+    <col width="21.5703125" customWidth="1" style="82" min="261" max="261"/>
+    <col width="22.7109375" customWidth="1" style="82" min="262" max="262"/>
+    <col width="0.28515625" customWidth="1" style="82" min="263" max="263"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="264" max="264"/>
+    <col width="9.140625" customWidth="1" style="82" min="265" max="267"/>
+    <col width="14.140625" customWidth="1" style="82" min="268" max="268"/>
+    <col width="9.140625" customWidth="1" style="82" min="269" max="512"/>
+    <col width="2" customWidth="1" style="82" min="513" max="513"/>
+    <col width="5.85546875" customWidth="1" style="82" min="514" max="514"/>
+    <col width="38.5703125" customWidth="1" style="82" min="515" max="515"/>
+    <col width="10" customWidth="1" style="82" min="516" max="516"/>
+    <col width="21.5703125" customWidth="1" style="82" min="517" max="517"/>
+    <col width="22.7109375" customWidth="1" style="82" min="518" max="518"/>
+    <col width="0.28515625" customWidth="1" style="82" min="519" max="519"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="520" max="520"/>
+    <col width="9.140625" customWidth="1" style="82" min="521" max="523"/>
+    <col width="14.140625" customWidth="1" style="82" min="524" max="524"/>
+    <col width="9.140625" customWidth="1" style="82" min="525" max="768"/>
+    <col width="2" customWidth="1" style="82" min="769" max="769"/>
+    <col width="5.85546875" customWidth="1" style="82" min="770" max="770"/>
+    <col width="38.5703125" customWidth="1" style="82" min="771" max="771"/>
+    <col width="10" customWidth="1" style="82" min="772" max="772"/>
+    <col width="21.5703125" customWidth="1" style="82" min="773" max="773"/>
+    <col width="22.7109375" customWidth="1" style="82" min="774" max="774"/>
+    <col width="0.28515625" customWidth="1" style="82" min="775" max="775"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="776" max="776"/>
+    <col width="9.140625" customWidth="1" style="82" min="777" max="779"/>
+    <col width="14.140625" customWidth="1" style="82" min="780" max="780"/>
+    <col width="9.140625" customWidth="1" style="82" min="781" max="1024"/>
+    <col width="2" customWidth="1" style="82" min="1025" max="1025"/>
+    <col width="5.85546875" customWidth="1" style="82" min="1026" max="1026"/>
+    <col width="38.5703125" customWidth="1" style="82" min="1027" max="1027"/>
+    <col width="10" customWidth="1" style="82" min="1028" max="1028"/>
+    <col width="21.5703125" customWidth="1" style="82" min="1029" max="1029"/>
+    <col width="22.7109375" customWidth="1" style="82" min="1030" max="1030"/>
+    <col width="0.28515625" customWidth="1" style="82" min="1031" max="1031"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="1032" max="1032"/>
+    <col width="9.140625" customWidth="1" style="82" min="1033" max="1035"/>
+    <col width="14.140625" customWidth="1" style="82" min="1036" max="1036"/>
+    <col width="9.140625" customWidth="1" style="82" min="1037" max="1280"/>
+    <col width="2" customWidth="1" style="82" min="1281" max="1281"/>
+    <col width="5.85546875" customWidth="1" style="82" min="1282" max="1282"/>
+    <col width="38.5703125" customWidth="1" style="82" min="1283" max="1283"/>
+    <col width="10" customWidth="1" style="82" min="1284" max="1284"/>
+    <col width="21.5703125" customWidth="1" style="82" min="1285" max="1285"/>
+    <col width="22.7109375" customWidth="1" style="82" min="1286" max="1286"/>
+    <col width="0.28515625" customWidth="1" style="82" min="1287" max="1287"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="1288" max="1288"/>
+    <col width="9.140625" customWidth="1" style="82" min="1289" max="1291"/>
+    <col width="14.140625" customWidth="1" style="82" min="1292" max="1292"/>
+    <col width="9.140625" customWidth="1" style="82" min="1293" max="1536"/>
+    <col width="2" customWidth="1" style="82" min="1537" max="1537"/>
+    <col width="5.85546875" customWidth="1" style="82" min="1538" max="1538"/>
+    <col width="38.5703125" customWidth="1" style="82" min="1539" max="1539"/>
+    <col width="10" customWidth="1" style="82" min="1540" max="1540"/>
+    <col width="21.5703125" customWidth="1" style="82" min="1541" max="1541"/>
+    <col width="22.7109375" customWidth="1" style="82" min="1542" max="1542"/>
+    <col width="0.28515625" customWidth="1" style="82" min="1543" max="1543"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="1544" max="1544"/>
+    <col width="9.140625" customWidth="1" style="82" min="1545" max="1547"/>
+    <col width="14.140625" customWidth="1" style="82" min="1548" max="1548"/>
+    <col width="9.140625" customWidth="1" style="82" min="1549" max="1792"/>
+    <col width="2" customWidth="1" style="82" min="1793" max="1793"/>
+    <col width="5.85546875" customWidth="1" style="82" min="1794" max="1794"/>
+    <col width="38.5703125" customWidth="1" style="82" min="1795" max="1795"/>
+    <col width="10" customWidth="1" style="82" min="1796" max="1796"/>
+    <col width="21.5703125" customWidth="1" style="82" min="1797" max="1797"/>
+    <col width="22.7109375" customWidth="1" style="82" min="1798" max="1798"/>
+    <col width="0.28515625" customWidth="1" style="82" min="1799" max="1799"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="1800" max="1800"/>
+    <col width="9.140625" customWidth="1" style="82" min="1801" max="1803"/>
+    <col width="14.140625" customWidth="1" style="82" min="1804" max="1804"/>
+    <col width="9.140625" customWidth="1" style="82" min="1805" max="2048"/>
+    <col width="2" customWidth="1" style="82" min="2049" max="2049"/>
+    <col width="5.85546875" customWidth="1" style="82" min="2050" max="2050"/>
+    <col width="38.5703125" customWidth="1" style="82" min="2051" max="2051"/>
+    <col width="10" customWidth="1" style="82" min="2052" max="2052"/>
+    <col width="21.5703125" customWidth="1" style="82" min="2053" max="2053"/>
+    <col width="22.7109375" customWidth="1" style="82" min="2054" max="2054"/>
+    <col width="0.28515625" customWidth="1" style="82" min="2055" max="2055"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="2056" max="2056"/>
+    <col width="9.140625" customWidth="1" style="82" min="2057" max="2059"/>
+    <col width="14.140625" customWidth="1" style="82" min="2060" max="2060"/>
+    <col width="9.140625" customWidth="1" style="82" min="2061" max="2304"/>
+    <col width="2" customWidth="1" style="82" min="2305" max="2305"/>
+    <col width="5.85546875" customWidth="1" style="82" min="2306" max="2306"/>
+    <col width="38.5703125" customWidth="1" style="82" min="2307" max="2307"/>
+    <col width="10" customWidth="1" style="82" min="2308" max="2308"/>
+    <col width="21.5703125" customWidth="1" style="82" min="2309" max="2309"/>
+    <col width="22.7109375" customWidth="1" style="82" min="2310" max="2310"/>
+    <col width="0.28515625" customWidth="1" style="82" min="2311" max="2311"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="2312" max="2312"/>
+    <col width="9.140625" customWidth="1" style="82" min="2313" max="2315"/>
+    <col width="14.140625" customWidth="1" style="82" min="2316" max="2316"/>
+    <col width="9.140625" customWidth="1" style="82" min="2317" max="2560"/>
+    <col width="2" customWidth="1" style="82" min="2561" max="2561"/>
+    <col width="5.85546875" customWidth="1" style="82" min="2562" max="2562"/>
+    <col width="38.5703125" customWidth="1" style="82" min="2563" max="2563"/>
+    <col width="10" customWidth="1" style="82" min="2564" max="2564"/>
+    <col width="21.5703125" customWidth="1" style="82" min="2565" max="2565"/>
+    <col width="22.7109375" customWidth="1" style="82" min="2566" max="2566"/>
+    <col width="0.28515625" customWidth="1" style="82" min="2567" max="2567"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="2568" max="2568"/>
+    <col width="9.140625" customWidth="1" style="82" min="2569" max="2571"/>
+    <col width="14.140625" customWidth="1" style="82" min="2572" max="2572"/>
+    <col width="9.140625" customWidth="1" style="82" min="2573" max="2816"/>
+    <col width="2" customWidth="1" style="82" min="2817" max="2817"/>
+    <col width="5.85546875" customWidth="1" style="82" min="2818" max="2818"/>
+    <col width="38.5703125" customWidth="1" style="82" min="2819" max="2819"/>
+    <col width="10" customWidth="1" style="82" min="2820" max="2820"/>
+    <col width="21.5703125" customWidth="1" style="82" min="2821" max="2821"/>
+    <col width="22.7109375" customWidth="1" style="82" min="2822" max="2822"/>
+    <col width="0.28515625" customWidth="1" style="82" min="2823" max="2823"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="2824" max="2824"/>
+    <col width="9.140625" customWidth="1" style="82" min="2825" max="2827"/>
+    <col width="14.140625" customWidth="1" style="82" min="2828" max="2828"/>
+    <col width="9.140625" customWidth="1" style="82" min="2829" max="3072"/>
+    <col width="2" customWidth="1" style="82" min="3073" max="3073"/>
+    <col width="5.85546875" customWidth="1" style="82" min="3074" max="3074"/>
+    <col width="38.5703125" customWidth="1" style="82" min="3075" max="3075"/>
+    <col width="10" customWidth="1" style="82" min="3076" max="3076"/>
+    <col width="21.5703125" customWidth="1" style="82" min="3077" max="3077"/>
+    <col width="22.7109375" customWidth="1" style="82" min="3078" max="3078"/>
+    <col width="0.28515625" customWidth="1" style="82" min="3079" max="3079"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="3080" max="3080"/>
+    <col width="9.140625" customWidth="1" style="82" min="3081" max="3083"/>
+    <col width="14.140625" customWidth="1" style="82" min="3084" max="3084"/>
+    <col width="9.140625" customWidth="1" style="82" min="3085" max="3328"/>
+    <col width="2" customWidth="1" style="82" min="3329" max="3329"/>
+    <col width="5.85546875" customWidth="1" style="82" min="3330" max="3330"/>
+    <col width="38.5703125" customWidth="1" style="82" min="3331" max="3331"/>
+    <col width="10" customWidth="1" style="82" min="3332" max="3332"/>
+    <col width="21.5703125" customWidth="1" style="82" min="3333" max="3333"/>
+    <col width="22.7109375" customWidth="1" style="82" min="3334" max="3334"/>
+    <col width="0.28515625" customWidth="1" style="82" min="3335" max="3335"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="3336" max="3336"/>
+    <col width="9.140625" customWidth="1" style="82" min="3337" max="3339"/>
+    <col width="14.140625" customWidth="1" style="82" min="3340" max="3340"/>
+    <col width="9.140625" customWidth="1" style="82" min="3341" max="3584"/>
+    <col width="2" customWidth="1" style="82" min="3585" max="3585"/>
+    <col width="5.85546875" customWidth="1" style="82" min="3586" max="3586"/>
+    <col width="38.5703125" customWidth="1" style="82" min="3587" max="3587"/>
+    <col width="10" customWidth="1" style="82" min="3588" max="3588"/>
+    <col width="21.5703125" customWidth="1" style="82" min="3589" max="3589"/>
+    <col width="22.7109375" customWidth="1" style="82" min="3590" max="3590"/>
+    <col width="0.28515625" customWidth="1" style="82" min="3591" max="3591"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="3592" max="3592"/>
+    <col width="9.140625" customWidth="1" style="82" min="3593" max="3595"/>
+    <col width="14.140625" customWidth="1" style="82" min="3596" max="3596"/>
+    <col width="9.140625" customWidth="1" style="82" min="3597" max="3840"/>
+    <col width="2" customWidth="1" style="82" min="3841" max="3841"/>
+    <col width="5.85546875" customWidth="1" style="82" min="3842" max="3842"/>
+    <col width="38.5703125" customWidth="1" style="82" min="3843" max="3843"/>
+    <col width="10" customWidth="1" style="82" min="3844" max="3844"/>
+    <col width="21.5703125" customWidth="1" style="82" min="3845" max="3845"/>
+    <col width="22.7109375" customWidth="1" style="82" min="3846" max="3846"/>
+    <col width="0.28515625" customWidth="1" style="82" min="3847" max="3847"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="3848" max="3848"/>
+    <col width="9.140625" customWidth="1" style="82" min="3849" max="3851"/>
+    <col width="14.140625" customWidth="1" style="82" min="3852" max="3852"/>
+    <col width="9.140625" customWidth="1" style="82" min="3853" max="4096"/>
+    <col width="2" customWidth="1" style="82" min="4097" max="4097"/>
+    <col width="5.85546875" customWidth="1" style="82" min="4098" max="4098"/>
+    <col width="38.5703125" customWidth="1" style="82" min="4099" max="4099"/>
+    <col width="10" customWidth="1" style="82" min="4100" max="4100"/>
+    <col width="21.5703125" customWidth="1" style="82" min="4101" max="4101"/>
+    <col width="22.7109375" customWidth="1" style="82" min="4102" max="4102"/>
+    <col width="0.28515625" customWidth="1" style="82" min="4103" max="4103"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="4104" max="4104"/>
+    <col width="9.140625" customWidth="1" style="82" min="4105" max="4107"/>
+    <col width="14.140625" customWidth="1" style="82" min="4108" max="4108"/>
+    <col width="9.140625" customWidth="1" style="82" min="4109" max="4352"/>
+    <col width="2" customWidth="1" style="82" min="4353" max="4353"/>
+    <col width="5.85546875" customWidth="1" style="82" min="4354" max="4354"/>
+    <col width="38.5703125" customWidth="1" style="82" min="4355" max="4355"/>
+    <col width="10" customWidth="1" style="82" min="4356" max="4356"/>
+    <col width="21.5703125" customWidth="1" style="82" min="4357" max="4357"/>
+    <col width="22.7109375" customWidth="1" style="82" min="4358" max="4358"/>
+    <col width="0.28515625" customWidth="1" style="82" min="4359" max="4359"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="4360" max="4360"/>
+    <col width="9.140625" customWidth="1" style="82" min="4361" max="4363"/>
+    <col width="14.140625" customWidth="1" style="82" min="4364" max="4364"/>
+    <col width="9.140625" customWidth="1" style="82" min="4365" max="4608"/>
+    <col width="2" customWidth="1" style="82" min="4609" max="4609"/>
+    <col width="5.85546875" customWidth="1" style="82" min="4610" max="4610"/>
+    <col width="38.5703125" customWidth="1" style="82" min="4611" max="4611"/>
+    <col width="10" customWidth="1" style="82" min="4612" max="4612"/>
+    <col width="21.5703125" customWidth="1" style="82" min="4613" max="4613"/>
+    <col width="22.7109375" customWidth="1" style="82" min="4614" max="4614"/>
+    <col width="0.28515625" customWidth="1" style="82" min="4615" max="4615"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="4616" max="4616"/>
+    <col width="9.140625" customWidth="1" style="82" min="4617" max="4619"/>
+    <col width="14.140625" customWidth="1" style="82" min="4620" max="4620"/>
+    <col width="9.140625" customWidth="1" style="82" min="4621" max="4864"/>
+    <col width="2" customWidth="1" style="82" min="4865" max="4865"/>
+    <col width="5.85546875" customWidth="1" style="82" min="4866" max="4866"/>
+    <col width="38.5703125" customWidth="1" style="82" min="4867" max="4867"/>
+    <col width="10" customWidth="1" style="82" min="4868" max="4868"/>
+    <col width="21.5703125" customWidth="1" style="82" min="4869" max="4869"/>
+    <col width="22.7109375" customWidth="1" style="82" min="4870" max="4870"/>
+    <col width="0.28515625" customWidth="1" style="82" min="4871" max="4871"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="4872" max="4872"/>
+    <col width="9.140625" customWidth="1" style="82" min="4873" max="4875"/>
+    <col width="14.140625" customWidth="1" style="82" min="4876" max="4876"/>
+    <col width="9.140625" customWidth="1" style="82" min="4877" max="5120"/>
+    <col width="2" customWidth="1" style="82" min="5121" max="5121"/>
+    <col width="5.85546875" customWidth="1" style="82" min="5122" max="5122"/>
+    <col width="38.5703125" customWidth="1" style="82" min="5123" max="5123"/>
+    <col width="10" customWidth="1" style="82" min="5124" max="5124"/>
+    <col width="21.5703125" customWidth="1" style="82" min="5125" max="5125"/>
+    <col width="22.7109375" customWidth="1" style="82" min="5126" max="5126"/>
+    <col width="0.28515625" customWidth="1" style="82" min="5127" max="5127"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="5128" max="5128"/>
+    <col width="9.140625" customWidth="1" style="82" min="5129" max="5131"/>
+    <col width="14.140625" customWidth="1" style="82" min="5132" max="5132"/>
+    <col width="9.140625" customWidth="1" style="82" min="5133" max="5376"/>
+    <col width="2" customWidth="1" style="82" min="5377" max="5377"/>
+    <col width="5.85546875" customWidth="1" style="82" min="5378" max="5378"/>
+    <col width="38.5703125" customWidth="1" style="82" min="5379" max="5379"/>
+    <col width="10" customWidth="1" style="82" min="5380" max="5380"/>
+    <col width="21.5703125" customWidth="1" style="82" min="5381" max="5381"/>
+    <col width="22.7109375" customWidth="1" style="82" min="5382" max="5382"/>
+    <col width="0.28515625" customWidth="1" style="82" min="5383" max="5383"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="5384" max="5384"/>
+    <col width="9.140625" customWidth="1" style="82" min="5385" max="5387"/>
+    <col width="14.140625" customWidth="1" style="82" min="5388" max="5388"/>
+    <col width="9.140625" customWidth="1" style="82" min="5389" max="5632"/>
+    <col width="2" customWidth="1" style="82" min="5633" max="5633"/>
+    <col width="5.85546875" customWidth="1" style="82" min="5634" max="5634"/>
+    <col width="38.5703125" customWidth="1" style="82" min="5635" max="5635"/>
+    <col width="10" customWidth="1" style="82" min="5636" max="5636"/>
+    <col width="21.5703125" customWidth="1" style="82" min="5637" max="5637"/>
+    <col width="22.7109375" customWidth="1" style="82" min="5638" max="5638"/>
+    <col width="0.28515625" customWidth="1" style="82" min="5639" max="5639"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="5640" max="5640"/>
+    <col width="9.140625" customWidth="1" style="82" min="5641" max="5643"/>
+    <col width="14.140625" customWidth="1" style="82" min="5644" max="5644"/>
+    <col width="9.140625" customWidth="1" style="82" min="5645" max="5888"/>
+    <col width="2" customWidth="1" style="82" min="5889" max="5889"/>
+    <col width="5.85546875" customWidth="1" style="82" min="5890" max="5890"/>
+    <col width="38.5703125" customWidth="1" style="82" min="5891" max="5891"/>
+    <col width="10" customWidth="1" style="82" min="5892" max="5892"/>
+    <col width="21.5703125" customWidth="1" style="82" min="5893" max="5893"/>
+    <col width="22.7109375" customWidth="1" style="82" min="5894" max="5894"/>
+    <col width="0.28515625" customWidth="1" style="82" min="5895" max="5895"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="5896" max="5896"/>
+    <col width="9.140625" customWidth="1" style="82" min="5897" max="5899"/>
+    <col width="14.140625" customWidth="1" style="82" min="5900" max="5900"/>
+    <col width="9.140625" customWidth="1" style="82" min="5901" max="6144"/>
+    <col width="2" customWidth="1" style="82" min="6145" max="6145"/>
+    <col width="5.85546875" customWidth="1" style="82" min="6146" max="6146"/>
+    <col width="38.5703125" customWidth="1" style="82" min="6147" max="6147"/>
+    <col width="10" customWidth="1" style="82" min="6148" max="6148"/>
+    <col width="21.5703125" customWidth="1" style="82" min="6149" max="6149"/>
+    <col width="22.7109375" customWidth="1" style="82" min="6150" max="6150"/>
+    <col width="0.28515625" customWidth="1" style="82" min="6151" max="6151"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="6152" max="6152"/>
+    <col width="9.140625" customWidth="1" style="82" min="6153" max="6155"/>
+    <col width="14.140625" customWidth="1" style="82" min="6156" max="6156"/>
+    <col width="9.140625" customWidth="1" style="82" min="6157" max="6400"/>
+    <col width="2" customWidth="1" style="82" min="6401" max="6401"/>
+    <col width="5.85546875" customWidth="1" style="82" min="6402" max="6402"/>
+    <col width="38.5703125" customWidth="1" style="82" min="6403" max="6403"/>
+    <col width="10" customWidth="1" style="82" min="6404" max="6404"/>
+    <col width="21.5703125" customWidth="1" style="82" min="6405" max="6405"/>
+    <col width="22.7109375" customWidth="1" style="82" min="6406" max="6406"/>
+    <col width="0.28515625" customWidth="1" style="82" min="6407" max="6407"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="6408" max="6408"/>
+    <col width="9.140625" customWidth="1" style="82" min="6409" max="6411"/>
+    <col width="14.140625" customWidth="1" style="82" min="6412" max="6412"/>
+    <col width="9.140625" customWidth="1" style="82" min="6413" max="6656"/>
+    <col width="2" customWidth="1" style="82" min="6657" max="6657"/>
+    <col width="5.85546875" customWidth="1" style="82" min="6658" max="6658"/>
+    <col width="38.5703125" customWidth="1" style="82" min="6659" max="6659"/>
+    <col width="10" customWidth="1" style="82" min="6660" max="6660"/>
+    <col width="21.5703125" customWidth="1" style="82" min="6661" max="6661"/>
+    <col width="22.7109375" customWidth="1" style="82" min="6662" max="6662"/>
+    <col width="0.28515625" customWidth="1" style="82" min="6663" max="6663"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="6664" max="6664"/>
+    <col width="9.140625" customWidth="1" style="82" min="6665" max="6667"/>
+    <col width="14.140625" customWidth="1" style="82" min="6668" max="6668"/>
+    <col width="9.140625" customWidth="1" style="82" min="6669" max="6912"/>
+    <col width="2" customWidth="1" style="82" min="6913" max="6913"/>
+    <col width="5.85546875" customWidth="1" style="82" min="6914" max="6914"/>
+    <col width="38.5703125" customWidth="1" style="82" min="6915" max="6915"/>
+    <col width="10" customWidth="1" style="82" min="6916" max="6916"/>
+    <col width="21.5703125" customWidth="1" style="82" min="6917" max="6917"/>
+    <col width="22.7109375" customWidth="1" style="82" min="6918" max="6918"/>
+    <col width="0.28515625" customWidth="1" style="82" min="6919" max="6919"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="6920" max="6920"/>
+    <col width="9.140625" customWidth="1" style="82" min="6921" max="6923"/>
+    <col width="14.140625" customWidth="1" style="82" min="6924" max="6924"/>
+    <col width="9.140625" customWidth="1" style="82" min="6925" max="7168"/>
+    <col width="2" customWidth="1" style="82" min="7169" max="7169"/>
+    <col width="5.85546875" customWidth="1" style="82" min="7170" max="7170"/>
+    <col width="38.5703125" customWidth="1" style="82" min="7171" max="7171"/>
+    <col width="10" customWidth="1" style="82" min="7172" max="7172"/>
+    <col width="21.5703125" customWidth="1" style="82" min="7173" max="7173"/>
+    <col width="22.7109375" customWidth="1" style="82" min="7174" max="7174"/>
+    <col width="0.28515625" customWidth="1" style="82" min="7175" max="7175"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="7176" max="7176"/>
+    <col width="9.140625" customWidth="1" style="82" min="7177" max="7179"/>
+    <col width="14.140625" customWidth="1" style="82" min="7180" max="7180"/>
+    <col width="9.140625" customWidth="1" style="82" min="7181" max="7424"/>
+    <col width="2" customWidth="1" style="82" min="7425" max="7425"/>
+    <col width="5.85546875" customWidth="1" style="82" min="7426" max="7426"/>
+    <col width="38.5703125" customWidth="1" style="82" min="7427" max="7427"/>
+    <col width="10" customWidth="1" style="82" min="7428" max="7428"/>
+    <col width="21.5703125" customWidth="1" style="82" min="7429" max="7429"/>
+    <col width="22.7109375" customWidth="1" style="82" min="7430" max="7430"/>
+    <col width="0.28515625" customWidth="1" style="82" min="7431" max="7431"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="7432" max="7432"/>
+    <col width="9.140625" customWidth="1" style="82" min="7433" max="7435"/>
+    <col width="14.140625" customWidth="1" style="82" min="7436" max="7436"/>
+    <col width="9.140625" customWidth="1" style="82" min="7437" max="7680"/>
+    <col width="2" customWidth="1" style="82" min="7681" max="7681"/>
+    <col width="5.85546875" customWidth="1" style="82" min="7682" max="7682"/>
+    <col width="38.5703125" customWidth="1" style="82" min="7683" max="7683"/>
+    <col width="10" customWidth="1" style="82" min="7684" max="7684"/>
+    <col width="21.5703125" customWidth="1" style="82" min="7685" max="7685"/>
+    <col width="22.7109375" customWidth="1" style="82" min="7686" max="7686"/>
+    <col width="0.28515625" customWidth="1" style="82" min="7687" max="7687"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="7688" max="7688"/>
+    <col width="9.140625" customWidth="1" style="82" min="7689" max="7691"/>
+    <col width="14.140625" customWidth="1" style="82" min="7692" max="7692"/>
+    <col width="9.140625" customWidth="1" style="82" min="7693" max="7936"/>
+    <col width="2" customWidth="1" style="82" min="7937" max="7937"/>
+    <col width="5.85546875" customWidth="1" style="82" min="7938" max="7938"/>
+    <col width="38.5703125" customWidth="1" style="82" min="7939" max="7939"/>
+    <col width="10" customWidth="1" style="82" min="7940" max="7940"/>
+    <col width="21.5703125" customWidth="1" style="82" min="7941" max="7941"/>
+    <col width="22.7109375" customWidth="1" style="82" min="7942" max="7942"/>
+    <col width="0.28515625" customWidth="1" style="82" min="7943" max="7943"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="7944" max="7944"/>
+    <col width="9.140625" customWidth="1" style="82" min="7945" max="7947"/>
+    <col width="14.140625" customWidth="1" style="82" min="7948" max="7948"/>
+    <col width="9.140625" customWidth="1" style="82" min="7949" max="8192"/>
+    <col width="2" customWidth="1" style="82" min="8193" max="8193"/>
+    <col width="5.85546875" customWidth="1" style="82" min="8194" max="8194"/>
+    <col width="38.5703125" customWidth="1" style="82" min="8195" max="8195"/>
+    <col width="10" customWidth="1" style="82" min="8196" max="8196"/>
+    <col width="21.5703125" customWidth="1" style="82" min="8197" max="8197"/>
+    <col width="22.7109375" customWidth="1" style="82" min="8198" max="8198"/>
+    <col width="0.28515625" customWidth="1" style="82" min="8199" max="8199"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="8200" max="8200"/>
+    <col width="9.140625" customWidth="1" style="82" min="8201" max="8203"/>
+    <col width="14.140625" customWidth="1" style="82" min="8204" max="8204"/>
+    <col width="9.140625" customWidth="1" style="82" min="8205" max="8448"/>
+    <col width="2" customWidth="1" style="82" min="8449" max="8449"/>
+    <col width="5.85546875" customWidth="1" style="82" min="8450" max="8450"/>
+    <col width="38.5703125" customWidth="1" style="82" min="8451" max="8451"/>
+    <col width="10" customWidth="1" style="82" min="8452" max="8452"/>
+    <col width="21.5703125" customWidth="1" style="82" min="8453" max="8453"/>
+    <col width="22.7109375" customWidth="1" style="82" min="8454" max="8454"/>
+    <col width="0.28515625" customWidth="1" style="82" min="8455" max="8455"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="8456" max="8456"/>
+    <col width="9.140625" customWidth="1" style="82" min="8457" max="8459"/>
+    <col width="14.140625" customWidth="1" style="82" min="8460" max="8460"/>
+    <col width="9.140625" customWidth="1" style="82" min="8461" max="8704"/>
+    <col width="2" customWidth="1" style="82" min="8705" max="8705"/>
+    <col width="5.85546875" customWidth="1" style="82" min="8706" max="8706"/>
+    <col width="38.5703125" customWidth="1" style="82" min="8707" max="8707"/>
+    <col width="10" customWidth="1" style="82" min="8708" max="8708"/>
+    <col width="21.5703125" customWidth="1" style="82" min="8709" max="8709"/>
+    <col width="22.7109375" customWidth="1" style="82" min="8710" max="8710"/>
+    <col width="0.28515625" customWidth="1" style="82" min="8711" max="8711"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="8712" max="8712"/>
+    <col width="9.140625" customWidth="1" style="82" min="8713" max="8715"/>
+    <col width="14.140625" customWidth="1" style="82" min="8716" max="8716"/>
+    <col width="9.140625" customWidth="1" style="82" min="8717" max="8960"/>
+    <col width="2" customWidth="1" style="82" min="8961" max="8961"/>
+    <col width="5.85546875" customWidth="1" style="82" min="8962" max="8962"/>
+    <col width="38.5703125" customWidth="1" style="82" min="8963" max="8963"/>
+    <col width="10" customWidth="1" style="82" min="8964" max="8964"/>
+    <col width="21.5703125" customWidth="1" style="82" min="8965" max="8965"/>
+    <col width="22.7109375" customWidth="1" style="82" min="8966" max="8966"/>
+    <col width="0.28515625" customWidth="1" style="82" min="8967" max="8967"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="8968" max="8968"/>
+    <col width="9.140625" customWidth="1" style="82" min="8969" max="8971"/>
+    <col width="14.140625" customWidth="1" style="82" min="8972" max="8972"/>
+    <col width="9.140625" customWidth="1" style="82" min="8973" max="9216"/>
+    <col width="2" customWidth="1" style="82" min="9217" max="9217"/>
+    <col width="5.85546875" customWidth="1" style="82" min="9218" max="9218"/>
+    <col width="38.5703125" customWidth="1" style="82" min="9219" max="9219"/>
+    <col width="10" customWidth="1" style="82" min="9220" max="9220"/>
+    <col width="21.5703125" customWidth="1" style="82" min="9221" max="9221"/>
+    <col width="22.7109375" customWidth="1" style="82" min="9222" max="9222"/>
+    <col width="0.28515625" customWidth="1" style="82" min="9223" max="9223"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="9224" max="9224"/>
+    <col width="9.140625" customWidth="1" style="82" min="9225" max="9227"/>
+    <col width="14.140625" customWidth="1" style="82" min="9228" max="9228"/>
+    <col width="9.140625" customWidth="1" style="82" min="9229" max="9472"/>
+    <col width="2" customWidth="1" style="82" min="9473" max="9473"/>
+    <col width="5.85546875" customWidth="1" style="82" min="9474" max="9474"/>
+    <col width="38.5703125" customWidth="1" style="82" min="9475" max="9475"/>
+    <col width="10" customWidth="1" style="82" min="9476" max="9476"/>
+    <col width="21.5703125" customWidth="1" style="82" min="9477" max="9477"/>
+    <col width="22.7109375" customWidth="1" style="82" min="9478" max="9478"/>
+    <col width="0.28515625" customWidth="1" style="82" min="9479" max="9479"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="9480" max="9480"/>
+    <col width="9.140625" customWidth="1" style="82" min="9481" max="9483"/>
+    <col width="14.140625" customWidth="1" style="82" min="9484" max="9484"/>
+    <col width="9.140625" customWidth="1" style="82" min="9485" max="9728"/>
+    <col width="2" customWidth="1" style="82" min="9729" max="9729"/>
+    <col width="5.85546875" customWidth="1" style="82" min="9730" max="9730"/>
+    <col width="38.5703125" customWidth="1" style="82" min="9731" max="9731"/>
+    <col width="10" customWidth="1" style="82" min="9732" max="9732"/>
+    <col width="21.5703125" customWidth="1" style="82" min="9733" max="9733"/>
+    <col width="22.7109375" customWidth="1" style="82" min="9734" max="9734"/>
+    <col width="0.28515625" customWidth="1" style="82" min="9735" max="9735"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="9736" max="9736"/>
+    <col width="9.140625" customWidth="1" style="82" min="9737" max="9739"/>
+    <col width="14.140625" customWidth="1" style="82" min="9740" max="9740"/>
+    <col width="9.140625" customWidth="1" style="82" min="9741" max="9984"/>
+    <col width="2" customWidth="1" style="82" min="9985" max="9985"/>
+    <col width="5.85546875" customWidth="1" style="82" min="9986" max="9986"/>
+    <col width="38.5703125" customWidth="1" style="82" min="9987" max="9987"/>
+    <col width="10" customWidth="1" style="82" min="9988" max="9988"/>
+    <col width="21.5703125" customWidth="1" style="82" min="9989" max="9989"/>
+    <col width="22.7109375" customWidth="1" style="82" min="9990" max="9990"/>
+    <col width="0.28515625" customWidth="1" style="82" min="9991" max="9991"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="9992" max="9992"/>
+    <col width="9.140625" customWidth="1" style="82" min="9993" max="9995"/>
+    <col width="14.140625" customWidth="1" style="82" min="9996" max="9996"/>
+    <col width="9.140625" customWidth="1" style="82" min="9997" max="10240"/>
+    <col width="2" customWidth="1" style="82" min="10241" max="10241"/>
+    <col width="5.85546875" customWidth="1" style="82" min="10242" max="10242"/>
+    <col width="38.5703125" customWidth="1" style="82" min="10243" max="10243"/>
+    <col width="10" customWidth="1" style="82" min="10244" max="10244"/>
+    <col width="21.5703125" customWidth="1" style="82" min="10245" max="10245"/>
+    <col width="22.7109375" customWidth="1" style="82" min="10246" max="10246"/>
+    <col width="0.28515625" customWidth="1" style="82" min="10247" max="10247"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="10248" max="10248"/>
+    <col width="9.140625" customWidth="1" style="82" min="10249" max="10251"/>
+    <col width="14.140625" customWidth="1" style="82" min="10252" max="10252"/>
+    <col width="9.140625" customWidth="1" style="82" min="10253" max="10496"/>
+    <col width="2" customWidth="1" style="82" min="10497" max="10497"/>
+    <col width="5.85546875" customWidth="1" style="82" min="10498" max="10498"/>
+    <col width="38.5703125" customWidth="1" style="82" min="10499" max="10499"/>
+    <col width="10" customWidth="1" style="82" min="10500" max="10500"/>
+    <col width="21.5703125" customWidth="1" style="82" min="10501" max="10501"/>
+    <col width="22.7109375" customWidth="1" style="82" min="10502" max="10502"/>
+    <col width="0.28515625" customWidth="1" style="82" min="10503" max="10503"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="10504" max="10504"/>
+    <col width="9.140625" customWidth="1" style="82" min="10505" max="10507"/>
+    <col width="14.140625" customWidth="1" style="82" min="10508" max="10508"/>
+    <col width="9.140625" customWidth="1" style="82" min="10509" max="10752"/>
+    <col width="2" customWidth="1" style="82" min="10753" max="10753"/>
+    <col width="5.85546875" customWidth="1" style="82" min="10754" max="10754"/>
+    <col width="38.5703125" customWidth="1" style="82" min="10755" max="10755"/>
+    <col width="10" customWidth="1" style="82" min="10756" max="10756"/>
+    <col width="21.5703125" customWidth="1" style="82" min="10757" max="10757"/>
+    <col width="22.7109375" customWidth="1" style="82" min="10758" max="10758"/>
+    <col width="0.28515625" customWidth="1" style="82" min="10759" max="10759"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="10760" max="10760"/>
+    <col width="9.140625" customWidth="1" style="82" min="10761" max="10763"/>
+    <col width="14.140625" customWidth="1" style="82" min="10764" max="10764"/>
+    <col width="9.140625" customWidth="1" style="82" min="10765" max="11008"/>
+    <col width="2" customWidth="1" style="82" min="11009" max="11009"/>
+    <col width="5.85546875" customWidth="1" style="82" min="11010" max="11010"/>
+    <col width="38.5703125" customWidth="1" style="82" min="11011" max="11011"/>
+    <col width="10" customWidth="1" style="82" min="11012" max="11012"/>
+    <col width="21.5703125" customWidth="1" style="82" min="11013" max="11013"/>
+    <col width="22.7109375" customWidth="1" style="82" min="11014" max="11014"/>
+    <col width="0.28515625" customWidth="1" style="82" min="11015" max="11015"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="11016" max="11016"/>
+    <col width="9.140625" customWidth="1" style="82" min="11017" max="11019"/>
+    <col width="14.140625" customWidth="1" style="82" min="11020" max="11020"/>
+    <col width="9.140625" customWidth="1" style="82" min="11021" max="11264"/>
+    <col width="2" customWidth="1" style="82" min="11265" max="11265"/>
+    <col width="5.85546875" customWidth="1" style="82" min="11266" max="11266"/>
+    <col width="38.5703125" customWidth="1" style="82" min="11267" max="11267"/>
+    <col width="10" customWidth="1" style="82" min="11268" max="11268"/>
+    <col width="21.5703125" customWidth="1" style="82" min="11269" max="11269"/>
+    <col width="22.7109375" customWidth="1" style="82" min="11270" max="11270"/>
+    <col width="0.28515625" customWidth="1" style="82" min="11271" max="11271"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="11272" max="11272"/>
+    <col width="9.140625" customWidth="1" style="82" min="11273" max="11275"/>
+    <col width="14.140625" customWidth="1" style="82" min="11276" max="11276"/>
+    <col width="9.140625" customWidth="1" style="82" min="11277" max="11520"/>
+    <col width="2" customWidth="1" style="82" min="11521" max="11521"/>
+    <col width="5.85546875" customWidth="1" style="82" min="11522" max="11522"/>
+    <col width="38.5703125" customWidth="1" style="82" min="11523" max="11523"/>
+    <col width="10" customWidth="1" style="82" min="11524" max="11524"/>
+    <col width="21.5703125" customWidth="1" style="82" min="11525" max="11525"/>
+    <col width="22.7109375" customWidth="1" style="82" min="11526" max="11526"/>
+    <col width="0.28515625" customWidth="1" style="82" min="11527" max="11527"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="11528" max="11528"/>
+    <col width="9.140625" customWidth="1" style="82" min="11529" max="11531"/>
+    <col width="14.140625" customWidth="1" style="82" min="11532" max="11532"/>
+    <col width="9.140625" customWidth="1" style="82" min="11533" max="11776"/>
+    <col width="2" customWidth="1" style="82" min="11777" max="11777"/>
+    <col width="5.85546875" customWidth="1" style="82" min="11778" max="11778"/>
+    <col width="38.5703125" customWidth="1" style="82" min="11779" max="11779"/>
+    <col width="10" customWidth="1" style="82" min="11780" max="11780"/>
+    <col width="21.5703125" customWidth="1" style="82" min="11781" max="11781"/>
+    <col width="22.7109375" customWidth="1" style="82" min="11782" max="11782"/>
+    <col width="0.28515625" customWidth="1" style="82" min="11783" max="11783"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="11784" max="11784"/>
+    <col width="9.140625" customWidth="1" style="82" min="11785" max="11787"/>
+    <col width="14.140625" customWidth="1" style="82" min="11788" max="11788"/>
+    <col width="9.140625" customWidth="1" style="82" min="11789" max="12032"/>
+    <col width="2" customWidth="1" style="82" min="12033" max="12033"/>
+    <col width="5.85546875" customWidth="1" style="82" min="12034" max="12034"/>
+    <col width="38.5703125" customWidth="1" style="82" min="12035" max="12035"/>
+    <col width="10" customWidth="1" style="82" min="12036" max="12036"/>
+    <col width="21.5703125" customWidth="1" style="82" min="12037" max="12037"/>
+    <col width="22.7109375" customWidth="1" style="82" min="12038" max="12038"/>
+    <col width="0.28515625" customWidth="1" style="82" min="12039" max="12039"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="12040" max="12040"/>
+    <col width="9.140625" customWidth="1" style="82" min="12041" max="12043"/>
+    <col width="14.140625" customWidth="1" style="82" min="12044" max="12044"/>
+    <col width="9.140625" customWidth="1" style="82" min="12045" max="12288"/>
+    <col width="2" customWidth="1" style="82" min="12289" max="12289"/>
+    <col width="5.85546875" customWidth="1" style="82" min="12290" max="12290"/>
+    <col width="38.5703125" customWidth="1" style="82" min="12291" max="12291"/>
+    <col width="10" customWidth="1" style="82" min="12292" max="12292"/>
+    <col width="21.5703125" customWidth="1" style="82" min="12293" max="12293"/>
+    <col width="22.7109375" customWidth="1" style="82" min="12294" max="12294"/>
+    <col width="0.28515625" customWidth="1" style="82" min="12295" max="12295"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="12296" max="12296"/>
+    <col width="9.140625" customWidth="1" style="82" min="12297" max="12299"/>
+    <col width="14.140625" customWidth="1" style="82" min="12300" max="12300"/>
+    <col width="9.140625" customWidth="1" style="82" min="12301" max="12544"/>
+    <col width="2" customWidth="1" style="82" min="12545" max="12545"/>
+    <col width="5.85546875" customWidth="1" style="82" min="12546" max="12546"/>
+    <col width="38.5703125" customWidth="1" style="82" min="12547" max="12547"/>
+    <col width="10" customWidth="1" style="82" min="12548" max="12548"/>
+    <col width="21.5703125" customWidth="1" style="82" min="12549" max="12549"/>
+    <col width="22.7109375" customWidth="1" style="82" min="12550" max="12550"/>
+    <col width="0.28515625" customWidth="1" style="82" min="12551" max="12551"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="12552" max="12552"/>
+    <col width="9.140625" customWidth="1" style="82" min="12553" max="12555"/>
+    <col width="14.140625" customWidth="1" style="82" min="12556" max="12556"/>
+    <col width="9.140625" customWidth="1" style="82" min="12557" max="12800"/>
+    <col width="2" customWidth="1" style="82" min="12801" max="12801"/>
+    <col width="5.85546875" customWidth="1" style="82" min="12802" max="12802"/>
+    <col width="38.5703125" customWidth="1" style="82" min="12803" max="12803"/>
+    <col width="10" customWidth="1" style="82" min="12804" max="12804"/>
+    <col width="21.5703125" customWidth="1" style="82" min="12805" max="12805"/>
+    <col width="22.7109375" customWidth="1" style="82" min="12806" max="12806"/>
+    <col width="0.28515625" customWidth="1" style="82" min="12807" max="12807"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="12808" max="12808"/>
+    <col width="9.140625" customWidth="1" style="82" min="12809" max="12811"/>
+    <col width="14.140625" customWidth="1" style="82" min="12812" max="12812"/>
+    <col width="9.140625" customWidth="1" style="82" min="12813" max="13056"/>
+    <col width="2" customWidth="1" style="82" min="13057" max="13057"/>
+    <col width="5.85546875" customWidth="1" style="82" min="13058" max="13058"/>
+    <col width="38.5703125" customWidth="1" style="82" min="13059" max="13059"/>
+    <col width="10" customWidth="1" style="82" min="13060" max="13060"/>
+    <col width="21.5703125" customWidth="1" style="82" min="13061" max="13061"/>
+    <col width="22.7109375" customWidth="1" style="82" min="13062" max="13062"/>
+    <col width="0.28515625" customWidth="1" style="82" min="13063" max="13063"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="13064" max="13064"/>
+    <col width="9.140625" customWidth="1" style="82" min="13065" max="13067"/>
+    <col width="14.140625" customWidth="1" style="82" min="13068" max="13068"/>
+    <col width="9.140625" customWidth="1" style="82" min="13069" max="13312"/>
+    <col width="2" customWidth="1" style="82" min="13313" max="13313"/>
+    <col width="5.85546875" customWidth="1" style="82" min="13314" max="13314"/>
+    <col width="38.5703125" customWidth="1" style="82" min="13315" max="13315"/>
+    <col width="10" customWidth="1" style="82" min="13316" max="13316"/>
+    <col width="21.5703125" customWidth="1" style="82" min="13317" max="13317"/>
+    <col width="22.7109375" customWidth="1" style="82" min="13318" max="13318"/>
+    <col width="0.28515625" customWidth="1" style="82" min="13319" max="13319"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="13320" max="13320"/>
+    <col width="9.140625" customWidth="1" style="82" min="13321" max="13323"/>
+    <col width="14.140625" customWidth="1" style="82" min="13324" max="13324"/>
+    <col width="9.140625" customWidth="1" style="82" min="13325" max="13568"/>
+    <col width="2" customWidth="1" style="82" min="13569" max="13569"/>
+    <col width="5.85546875" customWidth="1" style="82" min="13570" max="13570"/>
+    <col width="38.5703125" customWidth="1" style="82" min="13571" max="13571"/>
+    <col width="10" customWidth="1" style="82" min="13572" max="13572"/>
+    <col width="21.5703125" customWidth="1" style="82" min="13573" max="13573"/>
+    <col width="22.7109375" customWidth="1" style="82" min="13574" max="13574"/>
+    <col width="0.28515625" customWidth="1" style="82" min="13575" max="13575"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="13576" max="13576"/>
+    <col width="9.140625" customWidth="1" style="82" min="13577" max="13579"/>
+    <col width="14.140625" customWidth="1" style="82" min="13580" max="13580"/>
+    <col width="9.140625" customWidth="1" style="82" min="13581" max="13824"/>
+    <col width="2" customWidth="1" style="82" min="13825" max="13825"/>
+    <col width="5.85546875" customWidth="1" style="82" min="13826" max="13826"/>
+    <col width="38.5703125" customWidth="1" style="82" min="13827" max="13827"/>
+    <col width="10" customWidth="1" style="82" min="13828" max="13828"/>
+    <col width="21.5703125" customWidth="1" style="82" min="13829" max="13829"/>
+    <col width="22.7109375" customWidth="1" style="82" min="13830" max="13830"/>
+    <col width="0.28515625" customWidth="1" style="82" min="13831" max="13831"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="13832" max="13832"/>
+    <col width="9.140625" customWidth="1" style="82" min="13833" max="13835"/>
+    <col width="14.140625" customWidth="1" style="82" min="13836" max="13836"/>
+    <col width="9.140625" customWidth="1" style="82" min="13837" max="14080"/>
+    <col width="2" customWidth="1" style="82" min="14081" max="14081"/>
+    <col width="5.85546875" customWidth="1" style="82" min="14082" max="14082"/>
+    <col width="38.5703125" customWidth="1" style="82" min="14083" max="14083"/>
+    <col width="10" customWidth="1" style="82" min="14084" max="14084"/>
+    <col width="21.5703125" customWidth="1" style="82" min="14085" max="14085"/>
+    <col width="22.7109375" customWidth="1" style="82" min="14086" max="14086"/>
+    <col width="0.28515625" customWidth="1" style="82" min="14087" max="14087"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="14088" max="14088"/>
+    <col width="9.140625" customWidth="1" style="82" min="14089" max="14091"/>
+    <col width="14.140625" customWidth="1" style="82" min="14092" max="14092"/>
+    <col width="9.140625" customWidth="1" style="82" min="14093" max="14336"/>
+    <col width="2" customWidth="1" style="82" min="14337" max="14337"/>
+    <col width="5.85546875" customWidth="1" style="82" min="14338" max="14338"/>
+    <col width="38.5703125" customWidth="1" style="82" min="14339" max="14339"/>
+    <col width="10" customWidth="1" style="82" min="14340" max="14340"/>
+    <col width="21.5703125" customWidth="1" style="82" min="14341" max="14341"/>
+    <col width="22.7109375" customWidth="1" style="82" min="14342" max="14342"/>
+    <col width="0.28515625" customWidth="1" style="82" min="14343" max="14343"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="14344" max="14344"/>
+    <col width="9.140625" customWidth="1" style="82" min="14345" max="14347"/>
+    <col width="14.140625" customWidth="1" style="82" min="14348" max="14348"/>
+    <col width="9.140625" customWidth="1" style="82" min="14349" max="14592"/>
+    <col width="2" customWidth="1" style="82" min="14593" max="14593"/>
+    <col width="5.85546875" customWidth="1" style="82" min="14594" max="14594"/>
+    <col width="38.5703125" customWidth="1" style="82" min="14595" max="14595"/>
+    <col width="10" customWidth="1" style="82" min="14596" max="14596"/>
+    <col width="21.5703125" customWidth="1" style="82" min="14597" max="14597"/>
+    <col width="22.7109375" customWidth="1" style="82" min="14598" max="14598"/>
+    <col width="0.28515625" customWidth="1" style="82" min="14599" max="14599"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="14600" max="14600"/>
+    <col width="9.140625" customWidth="1" style="82" min="14601" max="14603"/>
+    <col width="14.140625" customWidth="1" style="82" min="14604" max="14604"/>
+    <col width="9.140625" customWidth="1" style="82" min="14605" max="14848"/>
+    <col width="2" customWidth="1" style="82" min="14849" max="14849"/>
+    <col width="5.85546875" customWidth="1" style="82" min="14850" max="14850"/>
+    <col width="38.5703125" customWidth="1" style="82" min="14851" max="14851"/>
+    <col width="10" customWidth="1" style="82" min="14852" max="14852"/>
+    <col width="21.5703125" customWidth="1" style="82" min="14853" max="14853"/>
+    <col width="22.7109375" customWidth="1" style="82" min="14854" max="14854"/>
+    <col width="0.28515625" customWidth="1" style="82" min="14855" max="14855"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="14856" max="14856"/>
+    <col width="9.140625" customWidth="1" style="82" min="14857" max="14859"/>
+    <col width="14.140625" customWidth="1" style="82" min="14860" max="14860"/>
+    <col width="9.140625" customWidth="1" style="82" min="14861" max="15104"/>
+    <col width="2" customWidth="1" style="82" min="15105" max="15105"/>
+    <col width="5.85546875" customWidth="1" style="82" min="15106" max="15106"/>
+    <col width="38.5703125" customWidth="1" style="82" min="15107" max="15107"/>
+    <col width="10" customWidth="1" style="82" min="15108" max="15108"/>
+    <col width="21.5703125" customWidth="1" style="82" min="15109" max="15109"/>
+    <col width="22.7109375" customWidth="1" style="82" min="15110" max="15110"/>
+    <col width="0.28515625" customWidth="1" style="82" min="15111" max="15111"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="15112" max="15112"/>
+    <col width="9.140625" customWidth="1" style="82" min="15113" max="15115"/>
+    <col width="14.140625" customWidth="1" style="82" min="15116" max="15116"/>
+    <col width="9.140625" customWidth="1" style="82" min="15117" max="15360"/>
+    <col width="2" customWidth="1" style="82" min="15361" max="15361"/>
+    <col width="5.85546875" customWidth="1" style="82" min="15362" max="15362"/>
+    <col width="38.5703125" customWidth="1" style="82" min="15363" max="15363"/>
+    <col width="10" customWidth="1" style="82" min="15364" max="15364"/>
+    <col width="21.5703125" customWidth="1" style="82" min="15365" max="15365"/>
+    <col width="22.7109375" customWidth="1" style="82" min="15366" max="15366"/>
+    <col width="0.28515625" customWidth="1" style="82" min="15367" max="15367"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="15368" max="15368"/>
+    <col width="9.140625" customWidth="1" style="82" min="15369" max="15371"/>
+    <col width="14.140625" customWidth="1" style="82" min="15372" max="15372"/>
+    <col width="9.140625" customWidth="1" style="82" min="15373" max="15616"/>
+    <col width="2" customWidth="1" style="82" min="15617" max="15617"/>
+    <col width="5.85546875" customWidth="1" style="82" min="15618" max="15618"/>
+    <col width="38.5703125" customWidth="1" style="82" min="15619" max="15619"/>
+    <col width="10" customWidth="1" style="82" min="15620" max="15620"/>
+    <col width="21.5703125" customWidth="1" style="82" min="15621" max="15621"/>
+    <col width="22.7109375" customWidth="1" style="82" min="15622" max="15622"/>
+    <col width="0.28515625" customWidth="1" style="82" min="15623" max="15623"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="15624" max="15624"/>
+    <col width="9.140625" customWidth="1" style="82" min="15625" max="15627"/>
+    <col width="14.140625" customWidth="1" style="82" min="15628" max="15628"/>
+    <col width="9.140625" customWidth="1" style="82" min="15629" max="15872"/>
+    <col width="2" customWidth="1" style="82" min="15873" max="15873"/>
+    <col width="5.85546875" customWidth="1" style="82" min="15874" max="15874"/>
+    <col width="38.5703125" customWidth="1" style="82" min="15875" max="15875"/>
+    <col width="10" customWidth="1" style="82" min="15876" max="15876"/>
+    <col width="21.5703125" customWidth="1" style="82" min="15877" max="15877"/>
+    <col width="22.7109375" customWidth="1" style="82" min="15878" max="15878"/>
+    <col width="0.28515625" customWidth="1" style="82" min="15879" max="15879"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="15880" max="15880"/>
+    <col width="9.140625" customWidth="1" style="82" min="15881" max="15883"/>
+    <col width="14.140625" customWidth="1" style="82" min="15884" max="15884"/>
+    <col width="9.140625" customWidth="1" style="82" min="15885" max="16128"/>
+    <col width="2" customWidth="1" style="82" min="16129" max="16129"/>
+    <col width="5.85546875" customWidth="1" style="82" min="16130" max="16130"/>
+    <col width="38.5703125" customWidth="1" style="82" min="16131" max="16131"/>
+    <col width="10" customWidth="1" style="82" min="16132" max="16132"/>
+    <col width="21.5703125" customWidth="1" style="82" min="16133" max="16133"/>
+    <col width="22.7109375" customWidth="1" style="82" min="16134" max="16134"/>
+    <col width="0.28515625" customWidth="1" style="82" min="16135" max="16135"/>
+    <col hidden="1" width="13" customWidth="1" style="82" min="16136" max="16136"/>
+    <col width="9.140625" customWidth="1" style="82" min="16137" max="16139"/>
+    <col width="14.140625" customWidth="1" style="82" min="16140" max="16140"/>
+    <col width="9.140625" customWidth="1" style="82" min="16141" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1" s="95">
@@ -1896,21 +1896,21 @@
       </c>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="8" t="n"/>
-      <c r="E1" s="87" t="inlineStr">
+      <c r="E1" s="86" t="inlineStr">
         <is>
           <t>Заказчик: АО "Газпромнефть-ННГ"</t>
         </is>
       </c>
       <c r="F1" s="24" t="n"/>
     </row>
-    <row r="2" ht="39" customFormat="1" customHeight="1" s="78">
-      <c r="B2" s="79" t="inlineStr">
+    <row r="2" ht="39" customFormat="1" customHeight="1" s="77">
+      <c r="B2" s="78" t="inlineStr">
         <is>
           <t>Адрес: 629800, Автономный округ Ямало-Ненецкий, город Ноябрьск, Промзона  Юго-Восточный промузел,  
 панель 1-А</t>
         </is>
       </c>
-      <c r="E2" s="79" t="inlineStr">
+      <c r="E2" s="78" t="inlineStr">
         <is>
           <t>Адрес: 629807, Ямало-Ненецкий автономный округ , 
  г. Ноябрьск, ул. Ленина, д. 59/87</t>
@@ -1919,14 +1919,14 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="15" t="n"/>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="78">
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="77">
       <c r="B3" s="20" t="inlineStr">
         <is>
           <t>ИНН: 8905050637</t>
         </is>
       </c>
       <c r="C3" s="22" t="n"/>
-      <c r="E3" s="87" t="inlineStr">
+      <c r="E3" s="86" t="inlineStr">
         <is>
           <t>ИНН: 8905000428</t>
         </is>
@@ -1937,7 +1937,7 @@
       <c r="I3" s="16" t="n"/>
       <c r="J3" s="15" t="n"/>
     </row>
-    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="78">
+    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="77">
       <c r="B4" s="20" t="inlineStr">
         <is>
           <t>КПП: 890501001</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C4" s="22" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="87" t="inlineStr">
+      <c r="E4" s="86" t="inlineStr">
         <is>
           <t>КПП: 890501001</t>
         </is>
@@ -1954,8 +1954,8 @@
       <c r="G4" s="17" t="n"/>
       <c r="H4" s="17" t="n"/>
     </row>
-    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="78">
-      <c r="B5" s="86" t="inlineStr">
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="77">
+      <c r="B5" s="85" t="inlineStr">
         <is>
           <t>Банковские реквизиты: р/с 40702810500020010172 
 в ф-ле № 6602 Банка ВТБ  (ПАО) г. Екатеринбург,  
@@ -1963,8 +1963,8 @@
 ОКПО 37991345;ОГРН 1118905006868</t>
         </is>
       </c>
-      <c r="D5" s="79" t="n"/>
-      <c r="E5" s="85" t="inlineStr">
+      <c r="D5" s="78" t="n"/>
+      <c r="E5" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">Банковские реквизиты: р/с 40702810100489000321  </t>
         </is>
@@ -1972,29 +1972,29 @@
       <c r="G5" s="17" t="n"/>
       <c r="H5" s="17" t="n"/>
     </row>
-    <row r="6" ht="45.75" customFormat="1" customHeight="1" s="78">
-      <c r="D6" s="79" t="n"/>
-      <c r="E6" s="80" t="inlineStr">
+    <row r="6" ht="45.75" customFormat="1" customHeight="1" s="77">
+      <c r="D6" s="78" t="n"/>
+      <c r="E6" s="79" t="inlineStr">
         <is>
           <t>Ф-л Банка"ГПБ" (АО) в г. Сургуте, к/с 30101810400000000721,
  ОКПО 05778425, БИК 047144721, ОГРН 10289007003963</t>
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" ht="21" customFormat="1" customHeight="1" s="78">
+    <row r="7" hidden="1" ht="21" customFormat="1" customHeight="1" s="77">
       <c r="B7" s="48" t="n"/>
       <c r="C7" s="48" t="n"/>
-      <c r="D7" s="79" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="80" t="n"/>
-    </row>
-    <row r="8" ht="6" customFormat="1" customHeight="1" s="78">
-      <c r="B8" s="85" t="n"/>
+      <c r="D7" s="78" t="n"/>
+      <c r="E7" s="79" t="n"/>
+      <c r="F7" s="79" t="n"/>
+      <c r="G7" s="79" t="n"/>
+      <c r="H7" s="79" t="n"/>
+      <c r="I7" s="79" t="n"/>
+    </row>
+    <row r="8" ht="6" customFormat="1" customHeight="1" s="77">
+      <c r="B8" s="84" t="n"/>
       <c r="D8" s="23" t="n"/>
-      <c r="E8" s="80" t="n"/>
+      <c r="E8" s="79" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="27" t="n"/>
       <c r="H8" s="27" t="n"/>
@@ -2002,14 +2002,14 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="23" t="n"/>
     </row>
-    <row r="9" ht="13.5" customFormat="1" customHeight="1" s="78">
-      <c r="B9" s="85" t="n"/>
+    <row r="9" ht="13.5" customFormat="1" customHeight="1" s="77">
+      <c r="B9" s="84" t="n"/>
       <c r="D9" s="39" t="inlineStr">
         <is>
           <t>АКТ № 509</t>
         </is>
       </c>
-      <c r="E9" s="80" t="n"/>
+      <c r="E9" s="79" t="n"/>
       <c r="F9" s="26" t="n"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
@@ -2017,8 +2017,8 @@
       <c r="J9" s="23" t="n"/>
       <c r="K9" s="23" t="n"/>
     </row>
-    <row r="10" ht="20.25" customFormat="1" customHeight="1" s="78">
-      <c r="B10" s="85" t="n"/>
+    <row r="10" ht="20.25" customFormat="1" customHeight="1" s="77">
+      <c r="B10" s="84" t="n"/>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="29" t="inlineStr">
         <is>
@@ -2033,8 +2033,8 @@
       <c r="J10" s="23" t="n"/>
       <c r="K10" s="23" t="n"/>
     </row>
-    <row r="11" ht="13.5" customFormat="1" customHeight="1" s="78">
-      <c r="B11" s="85" t="n"/>
+    <row r="11" ht="13.5" customFormat="1" customHeight="1" s="77">
+      <c r="B11" s="84" t="n"/>
       <c r="C11" s="30" t="n"/>
       <c r="D11" s="30" t="inlineStr">
         <is>
@@ -2049,8 +2049,8 @@
       <c r="J11" s="23" t="n"/>
       <c r="K11" s="23" t="n"/>
     </row>
-    <row r="12" ht="10.5" customFormat="1" customHeight="1" s="78">
-      <c r="B12" s="85" t="n"/>
+    <row r="12" ht="10.5" customFormat="1" customHeight="1" s="77">
+      <c r="B12" s="84" t="n"/>
       <c r="C12" s="30" t="n"/>
       <c r="D12" s="30" t="n"/>
       <c r="E12" s="30" t="n"/>
@@ -2061,7 +2061,7 @@
       <c r="J12" s="23" t="n"/>
       <c r="K12" s="23" t="n"/>
     </row>
-    <row r="13" ht="14.25" customFormat="1" customHeight="1" s="78">
+    <row r="13" ht="14.25" customFormat="1" customHeight="1" s="77">
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>составлен в том, что "Исполнитель" согласно договору №  ННГ-15/11301/00251/Р  от 22.10.2015 г.</t>
@@ -2077,7 +2077,7 @@
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
     </row>
-    <row r="14" customFormat="1" s="78">
+    <row r="14" customFormat="1" s="77">
       <c r="B14" s="31" t="inlineStr">
         <is>
           <t>оказал услуги для АО "Газпромнефть-ННГ"</t>
@@ -2088,98 +2088,98 @@
       <c r="E14" s="22" t="n"/>
       <c r="F14" s="22" t="n"/>
     </row>
-    <row r="15" ht="2.25" customFormat="1" customHeight="1" s="78">
+    <row r="15" ht="2.25" customFormat="1" customHeight="1" s="77">
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
     </row>
     <row r="16" ht="12.75" customHeight="1" s="95">
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>№ п\п</t>
         </is>
       </c>
-      <c r="C16" s="82" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>Наименование услуги</t>
         </is>
       </c>
-      <c r="D16" s="82" t="inlineStr">
+      <c r="D16" s="81" t="inlineStr">
         <is>
           <t>Кол-во оборудования ед</t>
         </is>
       </c>
-      <c r="E16" s="82" t="inlineStr">
+      <c r="E16" s="81" t="inlineStr">
         <is>
           <t>Цена 
 за ед., руб.</t>
         </is>
       </c>
-      <c r="F16" s="82" t="inlineStr">
+      <c r="F16" s="81" t="inlineStr">
         <is>
           <t>Стоимость услуг
 руб.</t>
         </is>
       </c>
-      <c r="G16" s="82" t="n"/>
+      <c r="G16" s="81" t="n"/>
       <c r="J16" s="3" t="n"/>
     </row>
     <row r="17" ht="12.75" customHeight="1" s="95">
-      <c r="G17" s="82" t="n"/>
+      <c r="G17" s="81" t="n"/>
       <c r="J17" s="3" t="n"/>
     </row>
     <row r="18" ht="27.75" customHeight="1" s="95">
-      <c r="G18" s="82" t="n"/>
+      <c r="G18" s="81" t="n"/>
       <c r="J18" s="3" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="95">
-      <c r="B19" s="82" t="n">
+      <c r="B19" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="82" t="n">
+      <c r="C19" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="82" t="n">
+      <c r="D19" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="82" t="n">
+      <c r="E19" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="82" t="n">
+      <c r="F19" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="82" t="n"/>
-      <c r="J19" s="82" t="n"/>
+      <c r="G19" s="81" t="n"/>
+      <c r="J19" s="81" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="95">
-      <c r="B20" s="85" t="inlineStr">
+      <c r="B20" s="84" t="inlineStr">
         <is>
           <t>Западно-Ноябрьское, Средне-Итурское, Спорышевское месторождения</t>
         </is>
       </c>
-      <c r="C20" s="82" t="n"/>
-      <c r="D20" s="82" t="n"/>
-      <c r="E20" s="82" t="n"/>
-      <c r="F20" s="82" t="n"/>
-      <c r="G20" s="82" t="n"/>
-      <c r="J20" s="82" t="n"/>
+      <c r="C20" s="81" t="n"/>
+      <c r="D20" s="81" t="n"/>
+      <c r="E20" s="81" t="n"/>
+      <c r="F20" s="81" t="n"/>
+      <c r="G20" s="81" t="n"/>
+      <c r="J20" s="81" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1" s="95">
-      <c r="B21" s="83" t="inlineStr">
+      <c r="B21" s="82" t="inlineStr">
         <is>
           <t>Сервисное обслуживание</t>
         </is>
       </c>
       <c r="C21" s="41" t="n"/>
-      <c r="D21" s="82" t="n"/>
+      <c r="D21" s="81" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="82" t="n"/>
+      <c r="F21" s="81" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="95">
-      <c r="B22" s="82" t="n">
+      <c r="B22" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="79" t="inlineStr">
+      <c r="C22" s="78" t="inlineStr">
         <is>
           <t>Насос 12НА9/4; 12НА22/6</t>
         </is>
@@ -2188,106 +2188,106 @@
       <c r="E22" s="45" t="n">
         <v>1300.55</v>
       </c>
-      <c r="F22" s="82">
+      <c r="F22" s="81">
         <f>E22*D22</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="95">
-      <c r="B23" s="82" t="n">
+      <c r="B23" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="79" t="inlineStr">
+      <c r="C23" s="78" t="inlineStr">
         <is>
           <t>Насос дозировочный типа ДП,НД</t>
         </is>
       </c>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="82" t="n">
+      <c r="D23" s="81" t="n"/>
+      <c r="E23" s="81" t="n">
         <v>1388.2</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="81">
         <f>E23*D23</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1" s="95">
-      <c r="B24" s="82" t="n">
+      <c r="B24" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="79" t="inlineStr">
+      <c r="C24" s="78" t="inlineStr">
         <is>
           <t>Насос НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80</t>
         </is>
       </c>
-      <c r="D24" s="82" t="n"/>
-      <c r="E24" s="82" t="n">
+      <c r="D24" s="81" t="n"/>
+      <c r="E24" s="81" t="n">
         <v>1022.97</v>
       </c>
-      <c r="F24" s="82">
+      <c r="F24" s="81">
         <f>E24*D24</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="95">
-      <c r="B25" s="82" t="n">
+      <c r="B25" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="79" t="inlineStr">
+      <c r="C25" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D25" s="82" t="n"/>
-      <c r="E25" s="82" t="n">
+      <c r="D25" s="81" t="n"/>
+      <c r="E25" s="81" t="n">
         <v>13437.21</v>
       </c>
-      <c r="F25" s="82">
+      <c r="F25" s="81">
         <f>E25*D25</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="95">
-      <c r="B26" s="82" t="n">
+      <c r="B26" s="81" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="79" t="inlineStr">
+      <c r="C26" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-38/44…220</t>
         </is>
       </c>
-      <c r="D26" s="82" t="n"/>
-      <c r="E26" s="82" t="n">
+      <c r="D26" s="81" t="n"/>
+      <c r="E26" s="81" t="n">
         <v>6070.81</v>
       </c>
-      <c r="F26" s="82">
+      <c r="F26" s="81">
         <f>E26*D26</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1" s="95">
-      <c r="B27" s="82" t="n">
+      <c r="B27" s="81" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="79" t="inlineStr">
+      <c r="C27" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д630/90</t>
         </is>
       </c>
-      <c r="D27" s="82" t="n"/>
-      <c r="E27" s="82" t="n">
+      <c r="D27" s="81" t="n"/>
+      <c r="E27" s="81" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="81">
         <f>E27*D27</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="45.75" customHeight="1" s="95">
-      <c r="B28" s="82" t="n">
+      <c r="B28" s="81" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="79" t="inlineStr">
+      <c r="C28" s="78" t="inlineStr">
         <is>
           <t>Насос К 8-18; К 20-30; К 50-30;К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175; К 100-80-160; К 100-65-200; КМ 160-65-200; 3Т13Н</t>
         </is>
@@ -2296,16 +2296,16 @@
       <c r="E28" s="45" t="n">
         <v>778.17</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="81">
         <f>E28*D28</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="95">
-      <c r="B29" s="82" t="n">
+      <c r="B29" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="79" t="inlineStr">
+      <c r="C29" s="78" t="inlineStr">
         <is>
           <t>Насос НМШ 5/25</t>
         </is>
@@ -2314,34 +2314,34 @@
       <c r="E29" s="45" t="n">
         <v>576.9</v>
       </c>
-      <c r="F29" s="82">
+      <c r="F29" s="81">
         <f>E29*D29</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="95">
-      <c r="B30" s="82" t="n">
+      <c r="B30" s="81" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="79" t="inlineStr">
+      <c r="C30" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д630/125</t>
         </is>
       </c>
-      <c r="D30" s="82" t="n"/>
-      <c r="E30" s="82" t="n">
+      <c r="D30" s="81" t="n"/>
+      <c r="E30" s="81" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="81">
         <f>E30*D30</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="95">
-      <c r="B31" s="82" t="n">
+      <c r="B31" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="79" t="inlineStr">
+      <c r="C31" s="78" t="inlineStr">
         <is>
           <t>Насос АХП 45/31</t>
         </is>
@@ -2350,16 +2350,16 @@
       <c r="E31" s="45" t="n">
         <v>969.65</v>
       </c>
-      <c r="F31" s="82">
+      <c r="F31" s="81">
         <f>E31*D31</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="95">
-      <c r="B32" s="82" t="n">
+      <c r="B32" s="81" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="79" t="inlineStr">
+      <c r="C32" s="78" t="inlineStr">
         <is>
           <t>Насос дозировочный типа PAX 32/12; PIAX 32/28</t>
         </is>
@@ -2368,13 +2368,13 @@
       <c r="E32" s="45" t="n">
         <v>2321.79</v>
       </c>
-      <c r="F32" s="82" t="n"/>
+      <c r="F32" s="81" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="95">
-      <c r="B33" s="82" t="n">
+      <c r="B33" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="C33" s="79" t="inlineStr">
+      <c r="C33" s="78" t="inlineStr">
         <is>
           <t>Насос НМШ 8/25</t>
         </is>
@@ -2383,13 +2383,13 @@
       <c r="E33" s="45" t="n">
         <v>576.9</v>
       </c>
-      <c r="F33" s="82" t="n"/>
+      <c r="F33" s="81" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="95">
-      <c r="B34" s="82" t="n">
+      <c r="B34" s="81" t="n">
         <v>13</v>
       </c>
-      <c r="C34" s="79" t="inlineStr">
+      <c r="C34" s="78" t="inlineStr">
         <is>
           <t>Насос ЦВК 6,3/160</t>
         </is>
@@ -2398,13 +2398,13 @@
       <c r="E34" s="45" t="n">
         <v>1210.41</v>
       </c>
-      <c r="F34" s="82" t="n"/>
+      <c r="F34" s="81" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="95">
-      <c r="B35" s="82" t="n">
+      <c r="B35" s="81" t="n">
         <v>14</v>
       </c>
-      <c r="C35" s="79" t="inlineStr">
+      <c r="C35" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 40/1400</t>
         </is>
@@ -2413,13 +2413,13 @@
       <c r="E35" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F35" s="82" t="n"/>
+      <c r="F35" s="81" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="95">
-      <c r="B36" s="82" t="n">
+      <c r="B36" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="78" t="inlineStr">
         <is>
           <t>Насос ЦГ 6,3/32</t>
         </is>
@@ -2428,13 +2428,13 @@
       <c r="E36" s="45" t="n">
         <v>2017.99</v>
       </c>
-      <c r="F36" s="82" t="n"/>
+      <c r="F36" s="81" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="95">
-      <c r="B37" s="82" t="n">
+      <c r="B37" s="81" t="n">
         <v>16</v>
       </c>
-      <c r="C37" s="79" t="inlineStr">
+      <c r="C37" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-105/98…490</t>
         </is>
@@ -2443,13 +2443,13 @@
       <c r="E37" s="45" t="n">
         <v>11244.09</v>
       </c>
-      <c r="F37" s="82" t="n"/>
+      <c r="F37" s="81" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="95">
-      <c r="B38" s="82" t="n">
+      <c r="B38" s="81" t="n">
         <v>17</v>
       </c>
-      <c r="C38" s="79" t="inlineStr">
+      <c r="C38" s="78" t="inlineStr">
         <is>
           <t>Насос НПВ  1250/60</t>
         </is>
@@ -2458,13 +2458,13 @@
       <c r="E38" s="45" t="n">
         <v>7812.42</v>
       </c>
-      <c r="F38" s="82" t="n"/>
+      <c r="F38" s="81" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="95">
-      <c r="B39" s="82" t="n">
+      <c r="B39" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="C39" s="79" t="inlineStr">
+      <c r="C39" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 180/1422...1900 2 ТМ</t>
         </is>
@@ -2473,13 +2473,13 @@
       <c r="E39" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F39" s="82" t="n"/>
+      <c r="F39" s="81" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="95">
-      <c r="B40" s="82" t="n">
+      <c r="B40" s="81" t="n">
         <v>19</v>
       </c>
-      <c r="C40" s="79" t="inlineStr">
+      <c r="C40" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1422…1900 ЗК</t>
         </is>
@@ -2488,13 +2488,13 @@
       <c r="E40" s="45" t="n">
         <v>16393.97</v>
       </c>
-      <c r="F40" s="82" t="n"/>
+      <c r="F40" s="81" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="95">
-      <c r="B41" s="82" t="n">
+      <c r="B41" s="81" t="n">
         <v>20</v>
       </c>
-      <c r="C41" s="79" t="inlineStr">
+      <c r="C41" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-180/1422…1900</t>
         </is>
@@ -2503,13 +2503,13 @@
       <c r="E41" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F41" s="82" t="n"/>
+      <c r="F41" s="81" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="95">
-      <c r="B42" s="82" t="n">
+      <c r="B42" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="C42" s="79" t="inlineStr">
+      <c r="C42" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1422...1900 2 ТМ</t>
         </is>
@@ -2518,13 +2518,13 @@
       <c r="E42" s="45" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F42" s="82" t="n"/>
+      <c r="F42" s="81" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="95">
-      <c r="B43" s="82" t="n">
+      <c r="B43" s="81" t="n">
         <v>22</v>
       </c>
-      <c r="C43" s="79" t="inlineStr">
+      <c r="C43" s="78" t="inlineStr">
         <is>
           <t>Насос ВКС 2/26</t>
         </is>
@@ -2533,13 +2533,13 @@
       <c r="E43" s="45" t="n">
         <v>863.15</v>
       </c>
-      <c r="F43" s="82" t="n"/>
+      <c r="F43" s="81" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="95">
-      <c r="B44" s="82" t="n">
+      <c r="B44" s="81" t="n">
         <v>23</v>
       </c>
-      <c r="C44" s="79" t="inlineStr">
+      <c r="C44" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д200/90; 4Д200/90; 1Д250/125</t>
         </is>
@@ -2548,13 +2548,13 @@
       <c r="E44" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F44" s="82" t="n"/>
+      <c r="F44" s="81" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="95">
-      <c r="B45" s="82" t="n">
+      <c r="B45" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="C45" s="79" t="inlineStr">
+      <c r="C45" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-60/66…330</t>
         </is>
@@ -2563,13 +2563,13 @@
       <c r="E45" s="45" t="n">
         <v>7879.33</v>
       </c>
-      <c r="F45" s="82" t="n"/>
+      <c r="F45" s="81" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="95">
-      <c r="B46" s="82" t="n">
+      <c r="B46" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="C46" s="79" t="inlineStr">
+      <c r="C46" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve"> Насос 1Д315/71; 1Д320/70</t>
         </is>
@@ -2578,13 +2578,13 @@
       <c r="E46" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F46" s="82" t="n"/>
+      <c r="F46" s="81" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="95">
-      <c r="B47" s="82" t="n">
+      <c r="B47" s="81" t="n">
         <v>26</v>
       </c>
-      <c r="C47" s="79" t="inlineStr">
+      <c r="C47" s="78" t="inlineStr">
         <is>
           <t>Насос НВД 50/50; НВД 50/80; НВД 35/90</t>
         </is>
@@ -2593,13 +2593,13 @@
       <c r="E47" s="45" t="n">
         <v>1332.63</v>
       </c>
-      <c r="F47" s="82" t="n"/>
+      <c r="F47" s="81" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="95">
-      <c r="B48" s="82" t="n">
+      <c r="B48" s="81" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="79" t="inlineStr">
+      <c r="C48" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д1250/90-125</t>
         </is>
@@ -2608,13 +2608,13 @@
       <c r="E48" s="45" t="n">
         <v>5292.31</v>
       </c>
-      <c r="F48" s="82" t="n"/>
+      <c r="F48" s="81" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="95">
-      <c r="B49" s="82" t="n">
+      <c r="B49" s="81" t="n">
         <v>28</v>
       </c>
-      <c r="C49" s="79" t="inlineStr">
+      <c r="C49" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-180/85…425</t>
         </is>
@@ -2623,13 +2623,13 @@
       <c r="E49" s="45" t="n">
         <v>11898.95</v>
       </c>
-      <c r="F49" s="82" t="n"/>
+      <c r="F49" s="81" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="95">
-      <c r="B50" s="82" t="n">
+      <c r="B50" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="C50" s="79" t="inlineStr">
+      <c r="C50" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1900 3ТМ</t>
         </is>
@@ -2638,13 +2638,13 @@
       <c r="E50" s="45" t="n">
         <v>44289.38</v>
       </c>
-      <c r="F50" s="82" t="n"/>
+      <c r="F50" s="81" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="95">
-      <c r="B51" s="82" t="n">
+      <c r="B51" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="C51" s="79" t="inlineStr">
+      <c r="C51" s="78" t="inlineStr">
         <is>
           <t>Насос BUL 6,3/64</t>
         </is>
@@ -2653,13 +2653,13 @@
       <c r="E51" s="45" t="n">
         <v>639.91</v>
       </c>
-      <c r="F51" s="82" t="n"/>
+      <c r="F51" s="81" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="95">
-      <c r="B52" s="82" t="n">
+      <c r="B52" s="81" t="n">
         <v>31</v>
       </c>
-      <c r="C52" s="79" t="inlineStr">
+      <c r="C52" s="78" t="inlineStr">
         <is>
           <t>Насос 200Д90(200Д/60)</t>
         </is>
@@ -2668,13 +2668,13 @@
       <c r="E52" s="45" t="n">
         <v>3722.29</v>
       </c>
-      <c r="F52" s="82" t="n"/>
+      <c r="F52" s="81" t="n"/>
     </row>
     <row r="53" ht="25.5" customHeight="1" s="95">
-      <c r="B53" s="82" t="n">
+      <c r="B53" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="C53" s="79" t="inlineStr">
+      <c r="C53" s="78" t="inlineStr">
         <is>
           <t>Насос KRGH 80/315;KRGH 200/500; KRGH 125/80/315</t>
         </is>
@@ -2683,13 +2683,13 @@
       <c r="E53" s="45" t="n">
         <v>4297.48</v>
       </c>
-      <c r="F53" s="82" t="n"/>
+      <c r="F53" s="81" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="95">
-      <c r="B54" s="82" t="n">
+      <c r="B54" s="81" t="n">
         <v>33</v>
       </c>
-      <c r="C54" s="79" t="inlineStr">
+      <c r="C54" s="78" t="inlineStr">
         <is>
           <t>Насос ГХИ 6,3/32</t>
         </is>
@@ -2698,13 +2698,13 @@
       <c r="E54" s="45" t="n">
         <v>2017.99</v>
       </c>
-      <c r="F54" s="82" t="n"/>
+      <c r="F54" s="81" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="95">
-      <c r="B55" s="82" t="n">
+      <c r="B55" s="81" t="n">
         <v>34</v>
       </c>
-      <c r="C55" s="79" t="inlineStr">
+      <c r="C55" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 180/1422…1900 ЗК</t>
         </is>
@@ -2713,10 +2713,10 @@
       <c r="E55" s="45" t="n">
         <v>16393.97</v>
       </c>
-      <c r="F55" s="82" t="n"/>
+      <c r="F55" s="81" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="95">
-      <c r="B56" s="82" t="n">
+      <c r="B56" s="81" t="n">
         <v>35</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
@@ -2728,13 +2728,13 @@
       <c r="E56" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F56" s="82">
+      <c r="F56" s="81">
         <f>E56*D56</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1" s="95">
-      <c r="B57" s="82" t="n">
+      <c r="B57" s="81" t="n">
         <v>36</v>
       </c>
       <c r="C57" s="51" t="inlineStr">
@@ -2746,13 +2746,13 @@
       <c r="E57" s="45" t="n">
         <v>5556.93</v>
       </c>
-      <c r="F57" s="82">
+      <c r="F57" s="81">
         <f>E57*D57</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="95">
-      <c r="B58" s="82" t="n">
+      <c r="B58" s="81" t="n">
         <v>37</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
@@ -2764,13 +2764,13 @@
       <c r="E58" s="45" t="n">
         <v>5556.93</v>
       </c>
-      <c r="F58" s="82">
+      <c r="F58" s="81">
         <f>E58*D58</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="95">
-      <c r="B59" s="82" t="n">
+      <c r="B59" s="81" t="n">
         <v>38</v>
       </c>
       <c r="C59" s="51" t="inlineStr">
@@ -2778,17 +2778,17 @@
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D59" s="82" t="n"/>
-      <c r="E59" s="82" t="n">
+      <c r="D59" s="81" t="n"/>
+      <c r="E59" s="81" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F59" s="82">
+      <c r="F59" s="81">
         <f>E59*D59</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="95">
-      <c r="B60" s="82" t="n">
+      <c r="B60" s="81" t="n">
         <v>39</v>
       </c>
       <c r="C60" s="51" t="inlineStr">
@@ -2796,17 +2796,17 @@
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D60" s="82" t="n"/>
-      <c r="E60" s="82" t="n">
+      <c r="D60" s="81" t="n"/>
+      <c r="E60" s="81" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F60" s="82">
+      <c r="F60" s="81">
         <f>E60*D60</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="95">
-      <c r="B61" s="82" t="n">
+      <c r="B61" s="81" t="n">
         <v>40</v>
       </c>
       <c r="C61" s="51" t="inlineStr">
@@ -2814,17 +2814,17 @@
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D61" s="82" t="n"/>
-      <c r="E61" s="82" t="n">
+      <c r="D61" s="81" t="n"/>
+      <c r="E61" s="81" t="n">
         <v>6070.81</v>
       </c>
-      <c r="F61" s="82">
+      <c r="F61" s="81">
         <f>E61*D61</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="95">
-      <c r="B62" s="82" t="n">
+      <c r="B62" s="81" t="n">
         <v>41</v>
       </c>
       <c r="C62" s="51" t="inlineStr">
@@ -2836,13 +2836,13 @@
       <c r="E62" s="45" t="n">
         <v>45915.64</v>
       </c>
-      <c r="F62" s="82">
+      <c r="F62" s="81">
         <f>E62*D62</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1" s="95">
-      <c r="B63" s="82" t="n">
+      <c r="B63" s="81" t="n">
         <v>42</v>
       </c>
       <c r="C63" s="51" t="inlineStr">
@@ -2854,46 +2854,46 @@
       <c r="E63" s="45" t="n">
         <v>45915.64</v>
       </c>
-      <c r="F63" s="82">
+      <c r="F63" s="81">
         <f>E63*D63</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1" s="95">
-      <c r="B64" s="82" t="n"/>
-      <c r="C64" s="79" t="inlineStr">
+      <c r="B64" s="81" t="n"/>
+      <c r="C64" s="78" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
       <c r="D64" s="45" t="n"/>
       <c r="E64" s="45" t="n"/>
-      <c r="F64" s="82">
+      <c r="F64" s="81">
         <f>SUM(F22:F63)</f>
         <v/>
       </c>
-      <c r="I64" s="83">
+      <c r="I64" s="82">
         <f>F64-H64</f>
         <v/>
       </c>
-      <c r="J64" s="83">
+      <c r="J64" s="82">
         <f>I64-[1]Лот2!$AN$4</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="95">
-      <c r="B65" s="81" t="inlineStr">
+      <c r="B65" s="80" t="inlineStr">
         <is>
           <t>Текущий ремонт</t>
         </is>
       </c>
-      <c r="C65" s="79" t="n"/>
-      <c r="D65" s="82" t="n"/>
-      <c r="E65" s="82" t="n"/>
-      <c r="F65" s="82" t="n"/>
+      <c r="C65" s="78" t="n"/>
+      <c r="D65" s="81" t="n"/>
+      <c r="E65" s="81" t="n"/>
+      <c r="F65" s="81" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="95">
-      <c r="B66" s="82" t="inlineStr">
+      <c r="B66" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2913,7 +2913,7 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="95">
-      <c r="B67" s="82" t="inlineStr">
+      <c r="B67" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2930,7 +2930,7 @@
       <c r="F67" s="18" t="n"/>
     </row>
     <row r="68" ht="20.25" customHeight="1" s="95">
-      <c r="B68" s="82" t="inlineStr">
+      <c r="B68" s="81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2947,7 +2947,7 @@
       <c r="F68" s="18" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="95">
-      <c r="B69" s="82" t="inlineStr">
+      <c r="B69" s="81" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2964,7 +2964,7 @@
       <c r="F69" s="18" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1" s="95">
-      <c r="B70" s="82" t="inlineStr">
+      <c r="B70" s="81" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2981,7 +2981,7 @@
       <c r="F70" s="18" t="n"/>
     </row>
     <row r="71" ht="38.25" customHeight="1" s="95">
-      <c r="B71" s="82" t="inlineStr">
+      <c r="B71" s="81" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2998,7 +2998,7 @@
       <c r="F71" s="18" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="95">
-      <c r="B72" s="82" t="inlineStr">
+      <c r="B72" s="81" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3015,7 +3015,7 @@
       <c r="F72" s="18" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="95">
-      <c r="B73" s="82" t="inlineStr">
+      <c r="B73" s="81" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3032,7 +3032,7 @@
       <c r="F73" s="18" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1" s="95">
-      <c r="B74" s="82" t="inlineStr">
+      <c r="B74" s="81" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3049,7 +3049,7 @@
       <c r="F74" s="18" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1" s="95">
-      <c r="B75" s="82" t="inlineStr">
+      <c r="B75" s="81" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3066,7 +3066,7 @@
       <c r="F75" s="18" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1" s="95">
-      <c r="B76" s="82" t="inlineStr">
+      <c r="B76" s="81" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3083,7 +3083,7 @@
       <c r="F76" s="18" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="95">
-      <c r="B77" s="82" t="inlineStr">
+      <c r="B77" s="81" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3100,7 +3100,7 @@
       <c r="F77" s="18" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1" s="95">
-      <c r="B78" s="82" t="inlineStr">
+      <c r="B78" s="81" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -3117,7 +3117,7 @@
       <c r="F78" s="18" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1" s="95">
-      <c r="B79" s="82" t="inlineStr">
+      <c r="B79" s="81" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -3134,7 +3134,7 @@
       <c r="F79" s="18" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1" s="95">
-      <c r="B80" s="82" t="inlineStr">
+      <c r="B80" s="81" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -3151,7 +3151,7 @@
       <c r="F80" s="18" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1" s="95">
-      <c r="B81" s="82" t="inlineStr">
+      <c r="B81" s="81" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -3168,7 +3168,7 @@
       <c r="F81" s="18" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="95">
-      <c r="B82" s="82" t="inlineStr">
+      <c r="B82" s="81" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -3185,7 +3185,7 @@
       <c r="F82" s="18" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1" s="95">
-      <c r="B83" s="82" t="inlineStr">
+      <c r="B83" s="81" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -3202,7 +3202,7 @@
       <c r="F83" s="18" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="95">
-      <c r="B84" s="82" t="inlineStr">
+      <c r="B84" s="81" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -3219,7 +3219,7 @@
       <c r="F84" s="18" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="95">
-      <c r="B85" s="82" t="inlineStr">
+      <c r="B85" s="81" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3236,7 +3236,7 @@
       <c r="F85" s="18" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1" s="95">
-      <c r="B86" s="82" t="inlineStr">
+      <c r="B86" s="81" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -3253,7 +3253,7 @@
       <c r="F86" s="18" t="n"/>
     </row>
     <row r="87" ht="12.75" customHeight="1" s="95">
-      <c r="B87" s="82" t="inlineStr">
+      <c r="B87" s="81" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -3273,7 +3273,7 @@
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1" s="95">
-      <c r="B88" s="82" t="inlineStr">
+      <c r="B88" s="81" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3290,7 +3290,7 @@
       <c r="F88" s="18" t="n"/>
     </row>
     <row r="89" ht="12.75" customHeight="1" s="95">
-      <c r="B89" s="82" t="inlineStr">
+      <c r="B89" s="81" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -3307,7 +3307,7 @@
       <c r="F89" s="18" t="n"/>
     </row>
     <row r="90" ht="12.75" customHeight="1" s="95">
-      <c r="B90" s="82" t="inlineStr">
+      <c r="B90" s="81" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3324,7 +3324,7 @@
       <c r="F90" s="18" t="n"/>
     </row>
     <row r="91" ht="12.75" customHeight="1" s="95">
-      <c r="B91" s="82" t="inlineStr">
+      <c r="B91" s="81" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3341,7 +3341,7 @@
       <c r="F91" s="18" t="n"/>
     </row>
     <row r="92" ht="12.75" customHeight="1" s="95">
-      <c r="B92" s="82" t="inlineStr">
+      <c r="B92" s="81" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -3358,7 +3358,7 @@
       <c r="F92" s="18" t="n"/>
     </row>
     <row r="93" ht="12.75" customHeight="1" s="95">
-      <c r="B93" s="82" t="inlineStr">
+      <c r="B93" s="81" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -3375,7 +3375,7 @@
       <c r="F93" s="18" t="n"/>
     </row>
     <row r="94" ht="12.75" customHeight="1" s="95">
-      <c r="B94" s="82" t="inlineStr">
+      <c r="B94" s="81" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -3392,7 +3392,7 @@
       <c r="F94" s="18" t="n"/>
     </row>
     <row r="95" ht="12.75" customHeight="1" s="95">
-      <c r="B95" s="82" t="inlineStr">
+      <c r="B95" s="81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -3409,7 +3409,7 @@
       <c r="F95" s="18" t="n"/>
     </row>
     <row r="96" ht="12.75" customHeight="1" s="95">
-      <c r="B96" s="82" t="inlineStr">
+      <c r="B96" s="81" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -3426,7 +3426,7 @@
       <c r="F96" s="18" t="n"/>
     </row>
     <row r="97" ht="12.75" customHeight="1" s="95">
-      <c r="B97" s="82" t="inlineStr">
+      <c r="B97" s="81" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -3443,7 +3443,7 @@
       <c r="F97" s="18" t="n"/>
     </row>
     <row r="98" ht="12.75" customHeight="1" s="95">
-      <c r="B98" s="82" t="n">
+      <c r="B98" s="81" t="n">
         <v>33</v>
       </c>
       <c r="C98" s="52" t="inlineStr">
@@ -3458,7 +3458,7 @@
       <c r="F98" s="18" t="n"/>
     </row>
     <row r="99" ht="12.75" customHeight="1" s="95">
-      <c r="B99" s="82" t="inlineStr">
+      <c r="B99" s="81" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -3475,7 +3475,7 @@
       <c r="F99" s="18" t="n"/>
     </row>
     <row r="100" ht="12.75" customHeight="1" s="95">
-      <c r="B100" s="82" t="inlineStr">
+      <c r="B100" s="81" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -3492,7 +3492,7 @@
       <c r="F100" s="18" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="95">
-      <c r="B101" s="82" t="inlineStr">
+      <c r="B101" s="81" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -3512,7 +3512,7 @@
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="95">
-      <c r="B102" s="82" t="inlineStr">
+      <c r="B102" s="81" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -3532,7 +3532,7 @@
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="95">
-      <c r="B103" s="82" t="inlineStr">
+      <c r="B103" s="81" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -3552,7 +3552,7 @@
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" s="95">
-      <c r="B104" s="82" t="inlineStr">
+      <c r="B104" s="81" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -3572,7 +3572,7 @@
       </c>
     </row>
     <row r="105" ht="12.75" customHeight="1" s="95">
-      <c r="B105" s="82" t="inlineStr">
+      <c r="B105" s="81" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3592,7 +3592,7 @@
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="95">
-      <c r="B106" s="82" t="inlineStr">
+      <c r="B106" s="81" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -3612,7 +3612,7 @@
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="95">
-      <c r="B107" s="82" t="inlineStr">
+      <c r="B107" s="81" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -3632,7 +3632,7 @@
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" s="95">
-      <c r="B108" s="82" t="inlineStr">
+      <c r="B108" s="81" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -3652,7 +3652,7 @@
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="95">
-      <c r="B109" s="82" t="inlineStr">
+      <c r="B109" s="81" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -3672,7 +3672,7 @@
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" s="95">
-      <c r="B110" s="82" t="inlineStr">
+      <c r="B110" s="81" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -3692,7 +3692,7 @@
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" s="95">
-      <c r="B111" s="82" t="inlineStr">
+      <c r="B111" s="81" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -3712,37 +3712,37 @@
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1" s="95">
-      <c r="B112" s="82" t="n"/>
+      <c r="B112" s="81" t="n"/>
       <c r="C112" s="46" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D112" s="82" t="n"/>
-      <c r="E112" s="82" t="n"/>
-      <c r="F112" s="82">
+      <c r="D112" s="81" t="n"/>
+      <c r="E112" s="81" t="n"/>
+      <c r="F112" s="81">
         <f>SUM(F66:F111)</f>
         <v/>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" s="95">
-      <c r="B113" s="78" t="inlineStr">
+      <c r="B113" s="77" t="inlineStr">
         <is>
           <t>Пуско-наладка насосного  оборудования</t>
         </is>
       </c>
-      <c r="C113" s="79" t="n"/>
-      <c r="D113" s="82" t="n"/>
-      <c r="E113" s="82" t="n"/>
+      <c r="C113" s="78" t="n"/>
+      <c r="D113" s="81" t="n"/>
+      <c r="E113" s="81" t="n"/>
       <c r="F113" s="18" t="n"/>
-      <c r="G113" s="82" t="n"/>
-      <c r="H113" s="78" t="n"/>
-      <c r="J113" s="83" t="n">
+      <c r="G113" s="81" t="n"/>
+      <c r="H113" s="77" t="n"/>
+      <c r="J113" s="82" t="n">
         <v>115488.03</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" s="95">
-      <c r="B114" s="82" t="inlineStr">
+      <c r="B114" s="81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3752,22 +3752,22 @@
           <t>Насос 12НА9/4, 12НА22/6</t>
         </is>
       </c>
-      <c r="D114" s="82" t="n"/>
-      <c r="E114" s="82" t="n">
+      <c r="D114" s="81" t="n"/>
+      <c r="E114" s="81" t="n">
         <v>8693.879999999999</v>
       </c>
       <c r="F114" s="18">
         <f>E114*D114</f>
         <v/>
       </c>
-      <c r="G114" s="82" t="n"/>
-      <c r="H114" s="78" t="n"/>
-      <c r="J114" s="83" t="n">
+      <c r="G114" s="81" t="n"/>
+      <c r="H114" s="77" t="n"/>
+      <c r="J114" s="82" t="n">
         <v>20102.27</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" s="95">
-      <c r="B115" s="82" t="inlineStr">
+      <c r="B115" s="81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3785,14 +3785,14 @@
         <f>E115*D115</f>
         <v/>
       </c>
-      <c r="G115" s="82" t="n"/>
-      <c r="H115" s="78" t="n"/>
-      <c r="J115" s="83" t="n">
+      <c r="G115" s="81" t="n"/>
+      <c r="H115" s="77" t="n"/>
+      <c r="J115" s="82" t="n">
         <v>1434.51</v>
       </c>
     </row>
     <row r="116" ht="25.5" customHeight="1" s="95">
-      <c r="B116" s="82" t="inlineStr">
+      <c r="B116" s="81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3810,14 +3810,14 @@
         <f>E116*D116</f>
         <v/>
       </c>
-      <c r="G116" s="82" t="n"/>
-      <c r="H116" s="78" t="n"/>
-      <c r="J116" s="83" t="n">
+      <c r="G116" s="81" t="n"/>
+      <c r="H116" s="77" t="n"/>
+      <c r="J116" s="82" t="n">
         <v>8391.780000000001</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" s="95">
-      <c r="B117" s="82" t="inlineStr">
+      <c r="B117" s="81" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3835,14 +3835,14 @@
         <f>E117*D117</f>
         <v/>
       </c>
-      <c r="G117" s="82" t="n"/>
-      <c r="H117" s="78" t="n"/>
-      <c r="J117" s="83" t="n">
+      <c r="G117" s="81" t="n"/>
+      <c r="H117" s="77" t="n"/>
+      <c r="J117" s="82" t="n">
         <v>38496.01</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" s="95">
-      <c r="B118" s="82" t="inlineStr">
+      <c r="B118" s="81" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3860,11 +3860,11 @@
         <f>E118*D118</f>
         <v/>
       </c>
-      <c r="G118" s="82" t="n"/>
-      <c r="H118" s="78" t="n"/>
+      <c r="G118" s="81" t="n"/>
+      <c r="H118" s="77" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1" s="95">
-      <c r="B119" s="82" t="inlineStr">
+      <c r="B119" s="81" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3882,11 +3882,11 @@
         <f>E119*D119</f>
         <v/>
       </c>
-      <c r="G119" s="82" t="n"/>
-      <c r="H119" s="78" t="n"/>
+      <c r="G119" s="81" t="n"/>
+      <c r="H119" s="77" t="n"/>
     </row>
     <row r="120" ht="38.25" customHeight="1" s="95">
-      <c r="B120" s="82" t="inlineStr">
+      <c r="B120" s="81" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3904,11 +3904,11 @@
         <f>E120*D120</f>
         <v/>
       </c>
-      <c r="G120" s="82" t="n"/>
-      <c r="H120" s="78" t="n"/>
+      <c r="G120" s="81" t="n"/>
+      <c r="H120" s="77" t="n"/>
     </row>
     <row r="121" ht="15" customHeight="1" s="95">
-      <c r="B121" s="82" t="inlineStr">
+      <c r="B121" s="81" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3923,11 +3923,11 @@
         <v>1486.15</v>
       </c>
       <c r="F121" s="18" t="n"/>
-      <c r="G121" s="82" t="n"/>
-      <c r="H121" s="78" t="n"/>
+      <c r="G121" s="81" t="n"/>
+      <c r="H121" s="77" t="n"/>
     </row>
     <row r="122" ht="15" customHeight="1" s="95">
-      <c r="B122" s="82" t="inlineStr">
+      <c r="B122" s="81" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3942,11 +3942,11 @@
         <v>7053.6</v>
       </c>
       <c r="F122" s="18" t="n"/>
-      <c r="G122" s="82" t="n"/>
-      <c r="H122" s="78" t="n"/>
+      <c r="G122" s="81" t="n"/>
+      <c r="H122" s="77" t="n"/>
     </row>
     <row r="123" ht="15" customHeight="1" s="95">
-      <c r="B123" s="82" t="inlineStr">
+      <c r="B123" s="81" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3961,11 +3961,11 @@
         <v>21627.72</v>
       </c>
       <c r="F123" s="18" t="n"/>
-      <c r="G123" s="82" t="n"/>
-      <c r="H123" s="78" t="n"/>
+      <c r="G123" s="81" t="n"/>
+      <c r="H123" s="77" t="n"/>
     </row>
     <row r="124" ht="15" customHeight="1" s="95">
-      <c r="B124" s="82" t="inlineStr">
+      <c r="B124" s="81" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3980,11 +3980,11 @@
         <v>7898.48</v>
       </c>
       <c r="F124" s="18" t="n"/>
-      <c r="G124" s="82" t="n"/>
-      <c r="H124" s="78" t="n"/>
+      <c r="G124" s="81" t="n"/>
+      <c r="H124" s="77" t="n"/>
     </row>
     <row r="125" ht="15" customHeight="1" s="95">
-      <c r="B125" s="82" t="inlineStr">
+      <c r="B125" s="81" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3999,11 +3999,11 @@
         <v>1486.15</v>
       </c>
       <c r="F125" s="18" t="n"/>
-      <c r="G125" s="82" t="n"/>
-      <c r="H125" s="78" t="n"/>
+      <c r="G125" s="81" t="n"/>
+      <c r="H125" s="77" t="n"/>
     </row>
     <row r="126" ht="15" customHeight="1" s="95">
-      <c r="B126" s="82" t="inlineStr">
+      <c r="B126" s="81" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -4018,11 +4018,11 @@
         <v>6515.95</v>
       </c>
       <c r="F126" s="18" t="n"/>
-      <c r="G126" s="82" t="n"/>
-      <c r="H126" s="78" t="n"/>
+      <c r="G126" s="81" t="n"/>
+      <c r="H126" s="77" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1" s="95">
-      <c r="B127" s="82" t="inlineStr">
+      <c r="B127" s="81" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -4037,11 +4037,11 @@
         <v>18106.45</v>
       </c>
       <c r="F127" s="18" t="n"/>
-      <c r="G127" s="82" t="n"/>
-      <c r="H127" s="78" t="n"/>
+      <c r="G127" s="81" t="n"/>
+      <c r="H127" s="77" t="n"/>
     </row>
     <row r="128" ht="15" customHeight="1" s="95">
-      <c r="B128" s="82" t="inlineStr">
+      <c r="B128" s="81" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -4056,11 +4056,11 @@
         <v>21595.33</v>
       </c>
       <c r="F128" s="18" t="n"/>
-      <c r="G128" s="82" t="n"/>
-      <c r="H128" s="78" t="n"/>
+      <c r="G128" s="81" t="n"/>
+      <c r="H128" s="77" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1" s="95">
-      <c r="B129" s="82" t="inlineStr">
+      <c r="B129" s="81" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4075,11 +4075,11 @@
         <v>34381.12</v>
       </c>
       <c r="F129" s="18" t="n"/>
-      <c r="G129" s="82" t="n"/>
-      <c r="H129" s="78" t="n"/>
+      <c r="G129" s="81" t="n"/>
+      <c r="H129" s="77" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1" s="95">
-      <c r="B130" s="82" t="inlineStr">
+      <c r="B130" s="81" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -4094,11 +4094,11 @@
         <v>30532.49</v>
       </c>
       <c r="F130" s="18" t="n"/>
-      <c r="G130" s="82" t="n"/>
-      <c r="H130" s="78" t="n"/>
+      <c r="G130" s="81" t="n"/>
+      <c r="H130" s="77" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1" s="95">
-      <c r="B131" s="82" t="inlineStr">
+      <c r="B131" s="81" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -4113,11 +4113,11 @@
         <v>34381.12</v>
       </c>
       <c r="F131" s="18" t="n"/>
-      <c r="G131" s="82" t="n"/>
-      <c r="H131" s="78" t="n"/>
+      <c r="G131" s="81" t="n"/>
+      <c r="H131" s="77" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1" s="95">
-      <c r="B132" s="82" t="inlineStr">
+      <c r="B132" s="81" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -4132,11 +4132,11 @@
         <v>39881.87</v>
       </c>
       <c r="F132" s="18" t="n"/>
-      <c r="G132" s="82" t="n"/>
-      <c r="H132" s="78" t="n"/>
+      <c r="G132" s="81" t="n"/>
+      <c r="H132" s="77" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1" s="95">
-      <c r="B133" s="82" t="inlineStr">
+      <c r="B133" s="81" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4151,11 +4151,11 @@
         <v>7053.6</v>
       </c>
       <c r="F133" s="18" t="n"/>
-      <c r="G133" s="82" t="n"/>
-      <c r="H133" s="78" t="n"/>
+      <c r="G133" s="81" t="n"/>
+      <c r="H133" s="77" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1" s="95">
-      <c r="B134" s="82" t="inlineStr">
+      <c r="B134" s="81" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -4173,11 +4173,11 @@
         <f>E134*D134</f>
         <v/>
       </c>
-      <c r="G134" s="82" t="n"/>
-      <c r="H134" s="78" t="n"/>
+      <c r="G134" s="81" t="n"/>
+      <c r="H134" s="77" t="n"/>
     </row>
     <row r="135" ht="15" customHeight="1" s="95">
-      <c r="B135" s="82" t="inlineStr">
+      <c r="B135" s="81" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -4195,11 +4195,11 @@
         <f>E135*D135</f>
         <v/>
       </c>
-      <c r="G135" s="82" t="n"/>
-      <c r="H135" s="78" t="n"/>
+      <c r="G135" s="81" t="n"/>
+      <c r="H135" s="77" t="n"/>
     </row>
     <row r="136" ht="15" customHeight="1" s="95">
-      <c r="B136" s="82" t="inlineStr">
+      <c r="B136" s="81" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -4217,11 +4217,11 @@
         <f>E136*D136</f>
         <v/>
       </c>
-      <c r="G136" s="82" t="n"/>
-      <c r="H136" s="78" t="n"/>
+      <c r="G136" s="81" t="n"/>
+      <c r="H136" s="77" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1" s="95">
-      <c r="B137" s="82" t="inlineStr">
+      <c r="B137" s="81" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4239,11 +4239,11 @@
         <f>E137*D137</f>
         <v/>
       </c>
-      <c r="G137" s="82" t="n"/>
-      <c r="H137" s="78" t="n"/>
+      <c r="G137" s="81" t="n"/>
+      <c r="H137" s="77" t="n"/>
     </row>
     <row r="138" ht="15" customHeight="1" s="95">
-      <c r="B138" s="82" t="inlineStr">
+      <c r="B138" s="81" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -4261,11 +4261,11 @@
         <f>E138*D138</f>
         <v/>
       </c>
-      <c r="G138" s="82" t="n"/>
-      <c r="H138" s="78" t="n"/>
+      <c r="G138" s="81" t="n"/>
+      <c r="H138" s="77" t="n"/>
     </row>
     <row r="139" ht="15" customHeight="1" s="95">
-      <c r="B139" s="82" t="inlineStr">
+      <c r="B139" s="81" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -4283,11 +4283,11 @@
         <f>E139*D139</f>
         <v/>
       </c>
-      <c r="G139" s="82" t="n"/>
-      <c r="H139" s="78" t="n"/>
+      <c r="G139" s="81" t="n"/>
+      <c r="H139" s="77" t="n"/>
     </row>
     <row r="140" ht="25.5" customHeight="1" s="95">
-      <c r="B140" s="82" t="inlineStr">
+      <c r="B140" s="81" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -4305,11 +4305,11 @@
         <f>E140*D140</f>
         <v/>
       </c>
-      <c r="G140" s="82" t="n"/>
-      <c r="H140" s="78" t="n"/>
+      <c r="G140" s="81" t="n"/>
+      <c r="H140" s="77" t="n"/>
     </row>
     <row r="141" ht="15" customHeight="1" s="95">
-      <c r="B141" s="82" t="inlineStr">
+      <c r="B141" s="81" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -4327,11 +4327,11 @@
         <f>E141*D141</f>
         <v/>
       </c>
-      <c r="G141" s="82" t="n"/>
-      <c r="H141" s="78" t="n"/>
+      <c r="G141" s="81" t="n"/>
+      <c r="H141" s="77" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1" s="95">
-      <c r="B142" s="82" t="inlineStr">
+      <c r="B142" s="81" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -4349,11 +4349,11 @@
         <f>E142*D142</f>
         <v/>
       </c>
-      <c r="G142" s="82" t="n"/>
-      <c r="H142" s="78" t="n"/>
+      <c r="G142" s="81" t="n"/>
+      <c r="H142" s="77" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1" s="95">
-      <c r="B143" s="82" t="inlineStr">
+      <c r="B143" s="81" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4368,11 +4368,11 @@
         <v>7053.6</v>
       </c>
       <c r="F143" s="18" t="n"/>
-      <c r="G143" s="82" t="n"/>
-      <c r="H143" s="78" t="n"/>
+      <c r="G143" s="81" t="n"/>
+      <c r="H143" s="77" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="95">
-      <c r="B144" s="82" t="inlineStr">
+      <c r="B144" s="81" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -4387,11 +4387,11 @@
         <v>7406.28</v>
       </c>
       <c r="F144" s="18" t="n"/>
-      <c r="G144" s="82" t="n"/>
-      <c r="H144" s="78" t="n"/>
+      <c r="G144" s="81" t="n"/>
+      <c r="H144" s="77" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1" s="95">
-      <c r="B145" s="82" t="inlineStr">
+      <c r="B145" s="81" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -4406,11 +4406,11 @@
         <v>7406.28</v>
       </c>
       <c r="F145" s="18" t="n"/>
-      <c r="G145" s="82" t="n"/>
-      <c r="H145" s="78" t="n"/>
+      <c r="G145" s="81" t="n"/>
+      <c r="H145" s="77" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" s="95">
-      <c r="B146" s="82" t="inlineStr">
+      <c r="B146" s="81" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -4425,11 +4425,11 @@
         <v>39881.87</v>
       </c>
       <c r="F146" s="18" t="n"/>
-      <c r="G146" s="82" t="n"/>
-      <c r="H146" s="78" t="n"/>
+      <c r="G146" s="81" t="n"/>
+      <c r="H146" s="77" t="n"/>
     </row>
     <row r="147" ht="15" customHeight="1" s="95">
-      <c r="B147" s="82" t="inlineStr">
+      <c r="B147" s="81" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -4447,11 +4447,11 @@
         <f>E147*D147</f>
         <v/>
       </c>
-      <c r="G147" s="82" t="n"/>
-      <c r="H147" s="78" t="n"/>
+      <c r="G147" s="81" t="n"/>
+      <c r="H147" s="77" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1" s="95">
-      <c r="B148" s="82" t="inlineStr">
+      <c r="B148" s="81" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -4469,11 +4469,11 @@
         <f>E148*D148</f>
         <v/>
       </c>
-      <c r="G148" s="82" t="n"/>
-      <c r="H148" s="78" t="n"/>
+      <c r="G148" s="81" t="n"/>
+      <c r="H148" s="77" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1" s="95">
-      <c r="B149" s="82" t="inlineStr">
+      <c r="B149" s="81" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -4491,11 +4491,11 @@
         <f>E149*D149</f>
         <v/>
       </c>
-      <c r="G149" s="82" t="n"/>
-      <c r="H149" s="78" t="n"/>
+      <c r="G149" s="81" t="n"/>
+      <c r="H149" s="77" t="n"/>
     </row>
     <row r="150" ht="15" customHeight="1" s="95">
-      <c r="B150" s="82" t="inlineStr">
+      <c r="B150" s="81" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -4513,37 +4513,37 @@
         <f>E150*D150</f>
         <v/>
       </c>
-      <c r="G150" s="82" t="n"/>
-      <c r="H150" s="78" t="n"/>
+      <c r="G150" s="81" t="n"/>
+      <c r="H150" s="77" t="n"/>
     </row>
     <row r="151" ht="14.25" customHeight="1" s="95">
-      <c r="B151" s="78" t="n"/>
-      <c r="C151" s="79" t="inlineStr">
+      <c r="B151" s="77" t="n"/>
+      <c r="C151" s="78" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D151" s="82" t="n"/>
-      <c r="E151" s="82" t="n"/>
+      <c r="D151" s="81" t="n"/>
+      <c r="E151" s="81" t="n"/>
       <c r="F151" s="18">
         <f>SUM(F114:F150)</f>
         <v/>
       </c>
-      <c r="G151" s="82" t="n"/>
-      <c r="H151" s="78" t="n"/>
+      <c r="G151" s="81" t="n"/>
+      <c r="H151" s="77" t="n"/>
     </row>
     <row r="152" ht="14.25" customHeight="1" s="95">
-      <c r="B152" s="78" t="inlineStr">
+      <c r="B152" s="77" t="inlineStr">
         <is>
           <t>Установка оборудования</t>
         </is>
       </c>
-      <c r="C152" s="79" t="n"/>
-      <c r="D152" s="82" t="n"/>
-      <c r="E152" s="82" t="n"/>
+      <c r="C152" s="78" t="n"/>
+      <c r="D152" s="81" t="n"/>
+      <c r="E152" s="81" t="n"/>
       <c r="F152" s="18" t="n"/>
-      <c r="G152" s="82" t="n"/>
-      <c r="H152" s="78" t="n"/>
+      <c r="G152" s="81" t="n"/>
+      <c r="H152" s="77" t="n"/>
     </row>
     <row r="153" ht="40.5" customHeight="1" s="95">
       <c r="B153" s="3" t="n">
@@ -4554,16 +4554,16 @@
           <t>Насос 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D153" s="82" t="n"/>
-      <c r="E153" s="82" t="n">
+      <c r="D153" s="81" t="n"/>
+      <c r="E153" s="81" t="n">
         <v>5519.78</v>
       </c>
       <c r="F153" s="18">
         <f>E153*D153</f>
         <v/>
       </c>
-      <c r="G153" s="82" t="n"/>
-      <c r="H153" s="78" t="n"/>
+      <c r="G153" s="81" t="n"/>
+      <c r="H153" s="77" t="n"/>
     </row>
     <row r="154" ht="25.5" customHeight="1" s="95">
       <c r="B154" s="3" t="n">
@@ -4574,16 +4574,16 @@
           <t>Насос дозировочный типа НД, ДП, PIAX 32/28; PAX 32/12; BUL 6,3/64</t>
         </is>
       </c>
-      <c r="D154" s="82" t="n"/>
-      <c r="E154" s="82" t="n">
+      <c r="D154" s="81" t="n"/>
+      <c r="E154" s="81" t="n">
         <v>1559.69</v>
       </c>
       <c r="F154" s="18">
         <f>E154*D154</f>
         <v/>
       </c>
-      <c r="G154" s="82" t="n"/>
-      <c r="H154" s="78" t="n"/>
+      <c r="G154" s="81" t="n"/>
+      <c r="H154" s="77" t="n"/>
     </row>
     <row r="155" ht="16.5" customHeight="1" s="95">
       <c r="B155" s="3" t="n">
@@ -4594,16 +4594,16 @@
           <t>Насос ЦНС-38/44…220; ЦНС 13/70…350;  ЦГ 6,3/32;</t>
         </is>
       </c>
-      <c r="D155" s="82" t="n"/>
-      <c r="E155" s="82" t="n">
+      <c r="D155" s="81" t="n"/>
+      <c r="E155" s="81" t="n">
         <v>17361.15</v>
       </c>
       <c r="F155" s="18">
         <f>E155*D155</f>
         <v/>
       </c>
-      <c r="G155" s="82" t="n"/>
-      <c r="H155" s="78" t="n"/>
+      <c r="G155" s="81" t="n"/>
+      <c r="H155" s="77" t="n"/>
     </row>
     <row r="156" ht="15" customHeight="1" s="95">
       <c r="B156" s="3" t="n">
@@ -4614,16 +4614,16 @@
           <t>Насос 1Д630/90, Д630/125</t>
         </is>
       </c>
-      <c r="D156" s="82" t="n"/>
-      <c r="E156" s="82" t="n">
+      <c r="D156" s="81" t="n"/>
+      <c r="E156" s="81" t="n">
         <v>12708.86</v>
       </c>
       <c r="F156" s="18">
         <f>E156*D156</f>
         <v/>
       </c>
-      <c r="G156" s="82" t="n"/>
-      <c r="H156" s="78" t="n"/>
+      <c r="G156" s="81" t="n"/>
+      <c r="H156" s="77" t="n"/>
     </row>
     <row r="157" ht="44.25" customHeight="1" s="95">
       <c r="B157" s="3" t="n">
@@ -4634,16 +4634,16 @@
           <t>Насос К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175, К 100-80-160;К 100-65-200, КМ 160-65-200, 3Т13Н; ЦВК 6,3/160;ВКС 2/26;</t>
         </is>
       </c>
-      <c r="D157" s="82" t="n"/>
-      <c r="E157" s="82" t="n">
+      <c r="D157" s="81" t="n"/>
+      <c r="E157" s="81" t="n">
         <v>2047.93</v>
       </c>
       <c r="F157" s="18">
         <f>E157*D157</f>
         <v/>
       </c>
-      <c r="G157" s="82" t="n"/>
-      <c r="H157" s="78" t="n"/>
+      <c r="G157" s="81" t="n"/>
+      <c r="H157" s="77" t="n"/>
     </row>
     <row r="158" ht="15" customHeight="1" s="95">
       <c r="B158" s="3" t="n">
@@ -4654,16 +4654,16 @@
           <t>Насос НМШ 5/25; 8/25;</t>
         </is>
       </c>
-      <c r="D158" s="82" t="n"/>
-      <c r="E158" s="82" t="n">
+      <c r="D158" s="81" t="n"/>
+      <c r="E158" s="81" t="n">
         <v>1373.17</v>
       </c>
       <c r="F158" s="18">
         <f>E158*D158</f>
         <v/>
       </c>
-      <c r="G158" s="82" t="n"/>
-      <c r="H158" s="78" t="n"/>
+      <c r="G158" s="81" t="n"/>
+      <c r="H158" s="77" t="n"/>
     </row>
     <row r="159" ht="51" customHeight="1" s="95">
       <c r="B159" s="3" t="n">
@@ -4674,16 +4674,16 @@
           <t>Насос ЦНС-105/98...490; ЦНС 180/170…425; ЦНС-180/1422…1900; ЦНС 180/240/1422...1900 (2ТМ, 3ТМ); ЦНС 180/240/1422...1900 ЗК; ЦНС 63/1800; ЦНС 40/1400;</t>
         </is>
       </c>
-      <c r="D159" s="82" t="n"/>
-      <c r="E159" s="82" t="n">
+      <c r="D159" s="81" t="n"/>
+      <c r="E159" s="81" t="n">
         <v>40029.98</v>
       </c>
       <c r="F159" s="18">
         <f>E159*D159</f>
         <v/>
       </c>
-      <c r="G159" s="82" t="n"/>
-      <c r="H159" s="78" t="n"/>
+      <c r="G159" s="81" t="n"/>
+      <c r="H159" s="77" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="95">
       <c r="B160" s="3" t="n">
@@ -4694,16 +4694,16 @@
           <t>Насос НПВ1250-60/90</t>
         </is>
       </c>
-      <c r="D160" s="82" t="n"/>
-      <c r="E160" s="82" t="n">
+      <c r="D160" s="81" t="n"/>
+      <c r="E160" s="81" t="n">
         <v>41116.26</v>
       </c>
       <c r="F160" s="18">
         <f>E160*D160</f>
         <v/>
       </c>
-      <c r="G160" s="82" t="n"/>
-      <c r="H160" s="78" t="n"/>
+      <c r="G160" s="81" t="n"/>
+      <c r="H160" s="77" t="n"/>
     </row>
     <row r="161" ht="25.5" customHeight="1" s="95">
       <c r="B161" s="3" t="n">
@@ -4714,16 +4714,16 @@
           <t>Насос 1Д200/90, 1Д315/71, 4Д200/90, 1Д320/70, 1Д250/125</t>
         </is>
       </c>
-      <c r="D161" s="82" t="n"/>
-      <c r="E161" s="82" t="n">
+      <c r="D161" s="81" t="n"/>
+      <c r="E161" s="81" t="n">
         <v>6310.95</v>
       </c>
       <c r="F161" s="18">
         <f>E161*D161</f>
         <v/>
       </c>
-      <c r="G161" s="82" t="n"/>
-      <c r="H161" s="78" t="n"/>
+      <c r="G161" s="81" t="n"/>
+      <c r="H161" s="77" t="n"/>
     </row>
     <row r="162" ht="15" customHeight="1" s="95">
       <c r="B162" s="3" t="n">
@@ -4734,16 +4734,16 @@
           <t>Насос ЦНС-60/66...330;</t>
         </is>
       </c>
-      <c r="D162" s="82" t="n"/>
-      <c r="E162" s="82" t="n">
+      <c r="D162" s="81" t="n"/>
+      <c r="E162" s="81" t="n">
         <v>17988.94</v>
       </c>
       <c r="F162" s="18">
         <f>E162*D162</f>
         <v/>
       </c>
-      <c r="G162" s="82" t="n"/>
-      <c r="H162" s="78" t="n"/>
+      <c r="G162" s="81" t="n"/>
+      <c r="H162" s="77" t="n"/>
     </row>
     <row r="163" ht="15" customHeight="1" s="95">
       <c r="B163" s="3" t="n">
@@ -4754,16 +4754,16 @@
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D163" s="82" t="n"/>
-      <c r="E163" s="82" t="n">
+      <c r="D163" s="81" t="n"/>
+      <c r="E163" s="81" t="n">
         <v>42583.13</v>
       </c>
       <c r="F163" s="18">
         <f>E163*D163</f>
         <v/>
       </c>
-      <c r="G163" s="82" t="n"/>
-      <c r="H163" s="78" t="n"/>
+      <c r="G163" s="81" t="n"/>
+      <c r="H163" s="77" t="n"/>
     </row>
     <row r="164" ht="38.25" customHeight="1" s="95">
       <c r="B164" s="3" t="n">
@@ -4774,16 +4774,16 @@
           <t>Насос АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D164" s="82" t="n"/>
-      <c r="E164" s="82" t="n">
+      <c r="D164" s="81" t="n"/>
+      <c r="E164" s="81" t="n">
         <v>5519.78</v>
       </c>
       <c r="F164" s="18">
         <f>E164*D164</f>
         <v/>
       </c>
-      <c r="G164" s="82" t="n"/>
-      <c r="H164" s="78" t="n"/>
+      <c r="G164" s="81" t="n"/>
+      <c r="H164" s="77" t="n"/>
     </row>
     <row r="165" ht="15" customHeight="1" s="95">
       <c r="B165" s="3" t="n">
@@ -4794,16 +4794,16 @@
           <t>Насос 1Д1250/90-125</t>
         </is>
       </c>
-      <c r="D165" s="82" t="n"/>
-      <c r="E165" s="82" t="n">
+      <c r="D165" s="81" t="n"/>
+      <c r="E165" s="81" t="n">
         <v>15135.48</v>
       </c>
       <c r="F165" s="18">
         <f>E165*D165</f>
         <v/>
       </c>
-      <c r="G165" s="82" t="n"/>
-      <c r="H165" s="78" t="n"/>
+      <c r="G165" s="81" t="n"/>
+      <c r="H165" s="77" t="n"/>
     </row>
     <row r="166" ht="23.25" customHeight="1" s="95">
       <c r="B166" s="3" t="n">
@@ -4814,16 +4814,16 @@
           <t>Насос KRGH 80/315,KRGH 200/500, KRGH 125/80/315</t>
         </is>
       </c>
-      <c r="D166" s="82" t="n"/>
-      <c r="E166" s="82" t="n">
+      <c r="D166" s="81" t="n"/>
+      <c r="E166" s="81" t="n">
         <v>21541.65</v>
       </c>
       <c r="F166" s="18">
         <f>E166*D166</f>
         <v/>
       </c>
-      <c r="G166" s="82" t="n"/>
-      <c r="H166" s="78" t="n"/>
+      <c r="G166" s="81" t="n"/>
+      <c r="H166" s="77" t="n"/>
     </row>
     <row r="167" ht="38.25" customHeight="1" s="95">
       <c r="B167" s="3" t="n">
@@ -4834,16 +4834,16 @@
           <t>Насос  АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D167" s="82" t="n"/>
-      <c r="E167" s="82" t="n">
+      <c r="D167" s="81" t="n"/>
+      <c r="E167" s="81" t="n">
         <v>5519.78</v>
       </c>
       <c r="F167" s="18">
         <f>E167*D167</f>
         <v/>
       </c>
-      <c r="G167" s="82" t="n"/>
-      <c r="H167" s="78" t="n"/>
+      <c r="G167" s="81" t="n"/>
+      <c r="H167" s="77" t="n"/>
     </row>
     <row r="168" ht="15" customHeight="1" s="95">
       <c r="B168" s="3" t="n">
@@ -4854,16 +4854,16 @@
           <t>Насос 1Д500/63б</t>
         </is>
       </c>
-      <c r="D168" s="82" t="n"/>
-      <c r="E168" s="82" t="n">
+      <c r="D168" s="81" t="n"/>
+      <c r="E168" s="81" t="n">
         <v>12708.89</v>
       </c>
       <c r="F168" s="18">
         <f>E168*D168</f>
         <v/>
       </c>
-      <c r="G168" s="82" t="n"/>
-      <c r="H168" s="78" t="n"/>
+      <c r="G168" s="81" t="n"/>
+      <c r="H168" s="77" t="n"/>
     </row>
     <row r="169" ht="15" customHeight="1" s="95">
       <c r="B169" s="3" t="n">
@@ -4874,16 +4874,16 @@
           <t>Насос CRE20-01 G-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D169" s="82" t="n"/>
-      <c r="E169" s="82" t="n">
+      <c r="D169" s="81" t="n"/>
+      <c r="E169" s="81" t="n">
         <v>5519.78</v>
       </c>
       <c r="F169" s="18">
         <f>E169*D169</f>
         <v/>
       </c>
-      <c r="G169" s="82" t="n"/>
-      <c r="H169" s="78" t="n"/>
+      <c r="G169" s="81" t="n"/>
+      <c r="H169" s="77" t="n"/>
     </row>
     <row r="170" ht="15" customHeight="1" s="95">
       <c r="B170" s="3" t="n">
@@ -4894,13 +4894,13 @@
           <t>Насос CR15-02 A-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D170" s="82" t="n"/>
-      <c r="E170" s="82" t="n">
+      <c r="D170" s="81" t="n"/>
+      <c r="E170" s="81" t="n">
         <v>5519.78</v>
       </c>
       <c r="F170" s="18" t="n"/>
-      <c r="G170" s="82" t="n"/>
-      <c r="H170" s="78" t="n"/>
+      <c r="G170" s="81" t="n"/>
+      <c r="H170" s="77" t="n"/>
     </row>
     <row r="171" ht="15" customHeight="1" s="95">
       <c r="B171" s="3" t="n">
@@ -4911,13 +4911,13 @@
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D171" s="82" t="n"/>
-      <c r="E171" s="82" t="n">
+      <c r="D171" s="81" t="n"/>
+      <c r="E171" s="81" t="n">
         <v>37957.98</v>
       </c>
       <c r="F171" s="18" t="n"/>
-      <c r="G171" s="82" t="n"/>
-      <c r="H171" s="78" t="n"/>
+      <c r="G171" s="81" t="n"/>
+      <c r="H171" s="77" t="n"/>
     </row>
     <row r="172" ht="15" customHeight="1" s="95">
       <c r="B172" s="3" t="n">
@@ -4928,13 +4928,13 @@
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D172" s="82" t="n"/>
-      <c r="E172" s="82" t="n">
+      <c r="D172" s="81" t="n"/>
+      <c r="E172" s="81" t="n">
         <v>37957.98</v>
       </c>
       <c r="F172" s="18" t="n"/>
-      <c r="G172" s="82" t="n"/>
-      <c r="H172" s="78" t="n"/>
+      <c r="G172" s="81" t="n"/>
+      <c r="H172" s="77" t="n"/>
     </row>
     <row r="173" ht="15" customHeight="1" s="95">
       <c r="B173" s="3" t="n">
@@ -4945,16 +4945,16 @@
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D173" s="82" t="n"/>
-      <c r="E173" s="82" t="n">
+      <c r="D173" s="81" t="n"/>
+      <c r="E173" s="81" t="n">
         <v>17361.15</v>
       </c>
       <c r="F173" s="18">
         <f>E173*D173</f>
         <v/>
       </c>
-      <c r="G173" s="82" t="n"/>
-      <c r="H173" s="78" t="n"/>
+      <c r="G173" s="81" t="n"/>
+      <c r="H173" s="77" t="n"/>
     </row>
     <row r="174" ht="15" customHeight="1" s="95">
       <c r="B174" s="3" t="n">
@@ -4965,16 +4965,16 @@
           <t>Насос ЦНС 300/1422…1900</t>
         </is>
       </c>
-      <c r="D174" s="82" t="n"/>
-      <c r="E174" s="82" t="n">
+      <c r="D174" s="81" t="n"/>
+      <c r="E174" s="81" t="n">
         <v>37957.96</v>
       </c>
       <c r="F174" s="18">
         <f>E174*D174</f>
         <v/>
       </c>
-      <c r="G174" s="82" t="n"/>
-      <c r="H174" s="78" t="n"/>
+      <c r="G174" s="81" t="n"/>
+      <c r="H174" s="77" t="n"/>
     </row>
     <row r="175" ht="15" customHeight="1" s="95">
       <c r="B175" s="3" t="n">
@@ -4993,621 +4993,621 @@
         <f>E175*D175</f>
         <v/>
       </c>
-      <c r="G175" s="82" t="n"/>
-      <c r="H175" s="78" t="n"/>
+      <c r="G175" s="81" t="n"/>
+      <c r="H175" s="77" t="n"/>
     </row>
     <row r="176" ht="15" customHeight="1" s="95">
-      <c r="B176" s="78" t="n"/>
-      <c r="C176" s="79" t="inlineStr">
+      <c r="B176" s="77" t="n"/>
+      <c r="C176" s="78" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D176" s="82" t="n"/>
-      <c r="E176" s="82" t="n"/>
+      <c r="D176" s="81" t="n"/>
+      <c r="E176" s="81" t="n"/>
       <c r="F176" s="18">
         <f>SUM(F153:F175)</f>
         <v/>
       </c>
-      <c r="G176" s="82" t="n"/>
-      <c r="H176" s="78" t="n"/>
+      <c r="G176" s="81" t="n"/>
+      <c r="H176" s="77" t="n"/>
     </row>
     <row r="177" ht="15" customHeight="1" s="95">
-      <c r="B177" s="78" t="inlineStr">
+      <c r="B177" s="77" t="inlineStr">
         <is>
           <t>Снятие оборудования</t>
         </is>
       </c>
-      <c r="C177" s="79" t="n"/>
-      <c r="D177" s="82" t="n"/>
-      <c r="E177" s="82" t="n"/>
+      <c r="C177" s="78" t="n"/>
+      <c r="D177" s="81" t="n"/>
+      <c r="E177" s="81" t="n"/>
       <c r="F177" s="3" t="n"/>
-      <c r="G177" s="82" t="n"/>
-      <c r="H177" s="78" t="n"/>
+      <c r="G177" s="81" t="n"/>
+      <c r="H177" s="77" t="n"/>
     </row>
     <row r="178" ht="38.25" customHeight="1" s="95">
       <c r="B178" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C178" s="79" t="inlineStr">
+      <c r="C178" s="78" t="inlineStr">
         <is>
           <t>Насос 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D178" s="82" t="n"/>
-      <c r="E178" s="82" t="n">
+      <c r="D178" s="81" t="n"/>
+      <c r="E178" s="81" t="n">
         <v>1204.93</v>
       </c>
       <c r="F178" s="3">
         <f>E178*D178</f>
         <v/>
       </c>
-      <c r="G178" s="82" t="n"/>
-      <c r="H178" s="78" t="n"/>
+      <c r="G178" s="81" t="n"/>
+      <c r="H178" s="77" t="n"/>
     </row>
     <row r="179" ht="25.5" customHeight="1" s="95">
       <c r="B179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C179" s="79" t="inlineStr">
+      <c r="C179" s="78" t="inlineStr">
         <is>
           <t>Насос дозировочный типа НД, ДП, PIAX 32/28; PAX 32/12; BUL 6,3/64</t>
         </is>
       </c>
-      <c r="D179" s="82" t="n"/>
-      <c r="E179" s="82" t="n">
+      <c r="D179" s="81" t="n"/>
+      <c r="E179" s="81" t="n">
         <v>204.01</v>
       </c>
       <c r="F179" s="3">
         <f>E179*D179</f>
         <v/>
       </c>
-      <c r="G179" s="82" t="n"/>
-      <c r="H179" s="78" t="n"/>
+      <c r="G179" s="81" t="n"/>
+      <c r="H179" s="77" t="n"/>
     </row>
     <row r="180" ht="15" customHeight="1" s="95">
       <c r="B180" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C180" s="79" t="inlineStr">
+      <c r="C180" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D180" s="82" t="n"/>
-      <c r="E180" s="82" t="n">
+      <c r="D180" s="81" t="n"/>
+      <c r="E180" s="81" t="n">
         <v>13670.84</v>
       </c>
       <c r="F180" s="3">
         <f>E180*D180</f>
         <v/>
       </c>
-      <c r="G180" s="82" t="n"/>
-      <c r="H180" s="78" t="n"/>
+      <c r="G180" s="81" t="n"/>
+      <c r="H180" s="77" t="n"/>
     </row>
     <row r="181" ht="21.75" customHeight="1" s="95">
       <c r="B181" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C181" s="79" t="inlineStr">
+      <c r="C181" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-38/44…220; ЦНС 13/70…350;  ЦГ 6,3/32;</t>
         </is>
       </c>
-      <c r="D181" s="82" t="n"/>
-      <c r="E181" s="82" t="n">
+      <c r="D181" s="81" t="n"/>
+      <c r="E181" s="81" t="n">
         <v>4657.5</v>
       </c>
       <c r="F181" s="3">
         <f>E181*D181</f>
         <v/>
       </c>
-      <c r="G181" s="82" t="n"/>
-      <c r="H181" s="78" t="n"/>
+      <c r="G181" s="81" t="n"/>
+      <c r="H181" s="77" t="n"/>
     </row>
     <row r="182" ht="15" customHeight="1" s="95">
       <c r="B182" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C182" s="79" t="inlineStr">
+      <c r="C182" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д630/90, Д630/125</t>
         </is>
       </c>
-      <c r="D182" s="82" t="n"/>
-      <c r="E182" s="82" t="n">
+      <c r="D182" s="81" t="n"/>
+      <c r="E182" s="81" t="n">
         <v>4884.74</v>
       </c>
       <c r="F182" s="3">
         <f>E182*D182</f>
         <v/>
       </c>
-      <c r="G182" s="82" t="n"/>
-      <c r="H182" s="78" t="n"/>
+      <c r="G182" s="81" t="n"/>
+      <c r="H182" s="77" t="n"/>
     </row>
     <row r="183" ht="38.25" customHeight="1" s="95">
       <c r="B183" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C183" s="79" t="inlineStr">
+      <c r="C183" s="78" t="inlineStr">
         <is>
           <t>Насос К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175, К 100-80-160;К 100-65-200, КМ 160-65-200, 3Т13Н; ЦВК 6,3/160;ВКС 2/26;</t>
         </is>
       </c>
-      <c r="D183" s="82" t="n"/>
-      <c r="E183" s="82" t="n">
+      <c r="D183" s="81" t="n"/>
+      <c r="E183" s="81" t="n">
         <v>357.91</v>
       </c>
       <c r="F183" s="3">
         <f>E183*D183</f>
         <v/>
       </c>
-      <c r="G183" s="82" t="n"/>
-      <c r="H183" s="78" t="n"/>
+      <c r="G183" s="81" t="n"/>
+      <c r="H183" s="77" t="n"/>
     </row>
     <row r="184" ht="15" customHeight="1" s="95">
       <c r="B184" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="79" t="inlineStr">
+      <c r="C184" s="78" t="inlineStr">
         <is>
           <t>Насос НМШ 5/25; 8/25;</t>
         </is>
       </c>
-      <c r="D184" s="82" t="n"/>
-      <c r="E184" s="82" t="n">
+      <c r="D184" s="81" t="n"/>
+      <c r="E184" s="81" t="n">
         <v>276.95</v>
       </c>
       <c r="F184" s="3">
         <f>E184*D184</f>
         <v/>
       </c>
-      <c r="G184" s="82" t="n"/>
-      <c r="H184" s="78" t="n"/>
+      <c r="G184" s="81" t="n"/>
+      <c r="H184" s="77" t="n"/>
     </row>
     <row r="185" ht="51" customHeight="1" s="95">
       <c r="B185" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C185" s="79" t="inlineStr">
+      <c r="C185" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-105/98...490; ЦНС 180/170…425; ЦНС-180/1422…1900; ЦНС 180/240/1422...1900 (2ТМ, 3ТМ); ЦНС 180/240/1422...1900 ЗК; ЦНС 63/1800; ЦНС 40/1400;</t>
         </is>
       </c>
-      <c r="D185" s="82" t="n"/>
-      <c r="E185" s="82" t="n">
+      <c r="D185" s="81" t="n"/>
+      <c r="E185" s="81" t="n">
         <v>11253.38</v>
       </c>
       <c r="F185" s="3">
         <f>E185*D185</f>
         <v/>
       </c>
-      <c r="G185" s="82" t="n"/>
-      <c r="H185" s="78" t="n"/>
+      <c r="G185" s="81" t="n"/>
+      <c r="H185" s="77" t="n"/>
     </row>
     <row r="186" ht="15" customHeight="1" s="95">
       <c r="B186" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C186" s="79" t="inlineStr">
+      <c r="C186" s="78" t="inlineStr">
         <is>
           <t>Насос НПВ1250-60/90</t>
         </is>
       </c>
-      <c r="D186" s="82" t="n"/>
-      <c r="E186" s="82" t="n">
+      <c r="D186" s="81" t="n"/>
+      <c r="E186" s="81" t="n">
         <v>1226.32</v>
       </c>
       <c r="F186" s="3">
         <f>E186*D186</f>
         <v/>
       </c>
-      <c r="G186" s="82" t="n"/>
-      <c r="H186" s="78" t="n"/>
+      <c r="G186" s="81" t="n"/>
+      <c r="H186" s="77" t="n"/>
     </row>
     <row r="187" ht="25.5" customHeight="1" s="95">
       <c r="B187" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C187" s="79" t="inlineStr">
+      <c r="C187" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д200/90, 1Д315/71, 4Д200/90, 1Д320/70, 1Д250/125</t>
         </is>
       </c>
-      <c r="D187" s="82" t="n"/>
-      <c r="E187" s="82" t="n">
+      <c r="D187" s="81" t="n"/>
+      <c r="E187" s="81" t="n">
         <v>1941.26</v>
       </c>
       <c r="F187" s="3">
         <f>E187*D187</f>
         <v/>
       </c>
-      <c r="G187" s="82" t="n"/>
-      <c r="H187" s="78" t="n"/>
+      <c r="G187" s="81" t="n"/>
+      <c r="H187" s="77" t="n"/>
     </row>
     <row r="188" ht="15" customHeight="1" s="95">
       <c r="B188" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C188" s="79" t="inlineStr">
+      <c r="C188" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС-60/66...330;</t>
         </is>
       </c>
-      <c r="D188" s="82" t="n"/>
-      <c r="E188" s="82" t="n">
+      <c r="D188" s="81" t="n"/>
+      <c r="E188" s="81" t="n">
         <v>6396.48</v>
       </c>
       <c r="F188" s="3">
         <f>E188*D188</f>
         <v/>
       </c>
-      <c r="G188" s="82" t="n"/>
-      <c r="H188" s="78" t="n"/>
+      <c r="G188" s="81" t="n"/>
+      <c r="H188" s="77" t="n"/>
     </row>
     <row r="189" ht="38.25" customHeight="1" s="95">
       <c r="B189" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C189" s="79" t="inlineStr">
+      <c r="C189" s="78" t="inlineStr">
         <is>
           <t>Насос АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D189" s="82" t="n"/>
-      <c r="E189" s="82" t="n">
+      <c r="D189" s="81" t="n"/>
+      <c r="E189" s="81" t="n">
         <v>1204.93</v>
       </c>
       <c r="F189" s="3">
         <f>E189*D189</f>
         <v/>
       </c>
-      <c r="G189" s="82" t="n"/>
-      <c r="H189" s="78" t="n"/>
+      <c r="G189" s="81" t="n"/>
+      <c r="H189" s="77" t="n"/>
     </row>
     <row r="190" ht="15" customHeight="1" s="95">
       <c r="B190" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C190" s="79" t="inlineStr">
+      <c r="C190" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д1250/90-125</t>
         </is>
       </c>
-      <c r="D190" s="82" t="n"/>
-      <c r="E190" s="82" t="n">
+      <c r="D190" s="81" t="n"/>
+      <c r="E190" s="81" t="n">
         <v>6164.09</v>
       </c>
       <c r="F190" s="3">
         <f>E190*D190</f>
         <v/>
       </c>
-      <c r="G190" s="82" t="n"/>
-      <c r="H190" s="78" t="n"/>
+      <c r="G190" s="81" t="n"/>
+      <c r="H190" s="77" t="n"/>
     </row>
     <row r="191" ht="19.5" customHeight="1" s="95">
       <c r="B191" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C191" s="79" t="inlineStr">
+      <c r="C191" s="78" t="inlineStr">
         <is>
           <t>Насос KRGH 80/315,KRGH 200/500, KRGH 125/80/315</t>
         </is>
       </c>
-      <c r="D191" s="82" t="n"/>
-      <c r="E191" s="82" t="n">
+      <c r="D191" s="81" t="n"/>
+      <c r="E191" s="81" t="n">
         <v>9896.059999999999</v>
       </c>
       <c r="F191" s="3" t="n"/>
-      <c r="G191" s="82" t="n"/>
-      <c r="H191" s="78" t="n"/>
+      <c r="G191" s="81" t="n"/>
+      <c r="H191" s="77" t="n"/>
     </row>
     <row r="192" ht="15" customHeight="1" s="95">
       <c r="B192" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C192" s="79" t="inlineStr">
+      <c r="C192" s="78" t="inlineStr">
         <is>
           <t>Станок-качалка (СК)</t>
         </is>
       </c>
-      <c r="D192" s="82" t="n"/>
-      <c r="E192" s="82" t="n">
+      <c r="D192" s="81" t="n"/>
+      <c r="E192" s="81" t="n">
         <v>14097.33</v>
       </c>
       <c r="F192" s="3" t="n"/>
-      <c r="G192" s="82" t="n"/>
-      <c r="H192" s="78" t="n"/>
+      <c r="G192" s="81" t="n"/>
+      <c r="H192" s="77" t="n"/>
     </row>
     <row r="193" ht="15" customHeight="1" s="95">
       <c r="B193" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C193" s="79" t="inlineStr">
+      <c r="C193" s="78" t="inlineStr">
         <is>
           <t>Демонтаж балансира</t>
         </is>
       </c>
-      <c r="D193" s="82" t="n"/>
-      <c r="E193" s="82" t="n">
+      <c r="D193" s="81" t="n"/>
+      <c r="E193" s="81" t="n">
         <v>10520.32</v>
       </c>
       <c r="F193" s="3" t="n"/>
-      <c r="G193" s="82" t="n"/>
-      <c r="H193" s="78" t="n"/>
+      <c r="G193" s="81" t="n"/>
+      <c r="H193" s="77" t="n"/>
     </row>
     <row r="194" ht="15" customHeight="1" s="95">
       <c r="B194" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C194" s="79" t="inlineStr">
+      <c r="C194" s="78" t="inlineStr">
         <is>
           <t>Основание СК (свайное поле)</t>
         </is>
       </c>
-      <c r="D194" s="82" t="n"/>
-      <c r="E194" s="82" t="n">
+      <c r="D194" s="81" t="n"/>
+      <c r="E194" s="81" t="n">
         <v>21359.93</v>
       </c>
       <c r="F194" s="3" t="n"/>
-      <c r="G194" s="82" t="n"/>
-      <c r="H194" s="78" t="n"/>
+      <c r="G194" s="81" t="n"/>
+      <c r="H194" s="77" t="n"/>
     </row>
     <row r="195" ht="15" customHeight="1" s="95">
       <c r="B195" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C195" s="79" t="inlineStr">
+      <c r="C195" s="78" t="inlineStr">
         <is>
           <t>Насос 1Д500/63б</t>
         </is>
       </c>
-      <c r="D195" s="82" t="n"/>
-      <c r="E195" s="82" t="n">
+      <c r="D195" s="81" t="n"/>
+      <c r="E195" s="81" t="n">
         <v>4884.74</v>
       </c>
       <c r="F195" s="3" t="n"/>
-      <c r="G195" s="82" t="n"/>
-      <c r="H195" s="78" t="n"/>
+      <c r="G195" s="81" t="n"/>
+      <c r="H195" s="77" t="n"/>
     </row>
     <row r="196" ht="15" customHeight="1" s="95">
       <c r="B196" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C196" s="79" t="inlineStr">
+      <c r="C196" s="78" t="inlineStr">
         <is>
           <t>Насос CRE20-01 G-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D196" s="82" t="n"/>
-      <c r="E196" s="82" t="n">
+      <c r="D196" s="81" t="n"/>
+      <c r="E196" s="81" t="n">
         <v>2240.93</v>
       </c>
       <c r="F196" s="3" t="n"/>
-      <c r="G196" s="82" t="n"/>
-      <c r="H196" s="78" t="n"/>
+      <c r="G196" s="81" t="n"/>
+      <c r="H196" s="77" t="n"/>
     </row>
     <row r="197" ht="15" customHeight="1" s="95">
       <c r="B197" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C197" s="79" t="inlineStr">
+      <c r="C197" s="78" t="inlineStr">
         <is>
           <t>Насос CR15-02 A-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D197" s="82" t="n"/>
-      <c r="E197" s="82" t="n">
+      <c r="D197" s="81" t="n"/>
+      <c r="E197" s="81" t="n">
         <v>2240.93</v>
       </c>
       <c r="F197" s="3">
         <f>E197*D197</f>
         <v/>
       </c>
-      <c r="G197" s="82" t="n"/>
-      <c r="H197" s="78" t="n"/>
+      <c r="G197" s="81" t="n"/>
+      <c r="H197" s="77" t="n"/>
     </row>
     <row r="198" ht="15" customHeight="1" s="95">
       <c r="B198" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C198" s="79" t="inlineStr">
+      <c r="C198" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D198" s="82" t="n"/>
-      <c r="E198" s="82" t="n">
+      <c r="D198" s="81" t="n"/>
+      <c r="E198" s="81" t="n">
         <v>11253.38</v>
       </c>
       <c r="F198" s="3">
         <f>E198*D198</f>
         <v/>
       </c>
-      <c r="G198" s="82" t="n"/>
-      <c r="H198" s="78" t="n"/>
+      <c r="G198" s="81" t="n"/>
+      <c r="H198" s="77" t="n"/>
     </row>
     <row r="199" ht="15" customHeight="1" s="95">
       <c r="B199" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C199" s="79" t="inlineStr">
+      <c r="C199" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D199" s="82" t="n"/>
-      <c r="E199" s="82" t="n">
+      <c r="D199" s="81" t="n"/>
+      <c r="E199" s="81" t="n">
         <v>11253.38</v>
       </c>
       <c r="F199" s="3">
         <f>E199*D199</f>
         <v/>
       </c>
-      <c r="G199" s="82" t="n"/>
-      <c r="H199" s="78" t="n"/>
+      <c r="G199" s="81" t="n"/>
+      <c r="H199" s="77" t="n"/>
     </row>
     <row r="200" ht="15" customHeight="1" s="95">
       <c r="B200" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C200" s="79" t="inlineStr">
+      <c r="C200" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D200" s="82" t="n"/>
-      <c r="E200" s="82" t="n">
+      <c r="D200" s="81" t="n"/>
+      <c r="E200" s="81" t="n">
         <v>4657.5</v>
       </c>
       <c r="F200" s="3">
         <f>E200*D200</f>
         <v/>
       </c>
-      <c r="G200" s="82" t="n"/>
-      <c r="H200" s="78" t="n"/>
+      <c r="G200" s="81" t="n"/>
+      <c r="H200" s="77" t="n"/>
     </row>
     <row r="201" ht="15" customHeight="1" s="95">
       <c r="B201" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C201" s="79" t="inlineStr">
+      <c r="C201" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 300/1422…1900</t>
         </is>
       </c>
-      <c r="D201" s="82" t="n"/>
-      <c r="E201" s="82" t="n">
+      <c r="D201" s="81" t="n"/>
+      <c r="E201" s="81" t="n">
         <v>11253.38</v>
       </c>
       <c r="F201" s="3">
         <f>E201*D201</f>
         <v/>
       </c>
-      <c r="G201" s="82" t="n"/>
-      <c r="H201" s="78" t="n"/>
+      <c r="G201" s="81" t="n"/>
+      <c r="H201" s="77" t="n"/>
     </row>
     <row r="202" ht="15" customHeight="1" s="95">
       <c r="B202" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C202" s="79" t="inlineStr">
+      <c r="C202" s="78" t="inlineStr">
         <is>
           <t>Насос ЦНС 310/1422…1900</t>
         </is>
       </c>
-      <c r="D202" s="82" t="n"/>
-      <c r="E202" s="82" t="n">
+      <c r="D202" s="81" t="n"/>
+      <c r="E202" s="81" t="n">
         <v>11253.38</v>
       </c>
       <c r="F202" s="3">
         <f>E202*D202</f>
         <v/>
       </c>
-      <c r="G202" s="82" t="n"/>
-      <c r="H202" s="78" t="n"/>
+      <c r="G202" s="81" t="n"/>
+      <c r="H202" s="77" t="n"/>
     </row>
     <row r="203" ht="14.25" customHeight="1" s="95">
       <c r="B203" s="3" t="n"/>
-      <c r="C203" s="79" t="inlineStr">
+      <c r="C203" s="78" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D203" s="82" t="n"/>
-      <c r="E203" s="82" t="n"/>
+      <c r="D203" s="81" t="n"/>
+      <c r="E203" s="81" t="n"/>
       <c r="F203" s="3">
         <f>SUM(F178:F202)</f>
         <v/>
       </c>
-      <c r="G203" s="82" t="n"/>
-      <c r="H203" s="78" t="n"/>
+      <c r="G203" s="81" t="n"/>
+      <c r="H203" s="77" t="n"/>
     </row>
     <row r="204" ht="15" customHeight="1" s="95">
-      <c r="B204" s="78" t="inlineStr">
+      <c r="B204" s="77" t="inlineStr">
         <is>
           <t>Прочие работы</t>
         </is>
       </c>
-      <c r="C204" s="79" t="n"/>
-      <c r="D204" s="82" t="n"/>
-      <c r="E204" s="82" t="n"/>
+      <c r="C204" s="78" t="n"/>
+      <c r="D204" s="81" t="n"/>
+      <c r="E204" s="81" t="n"/>
       <c r="F204" s="3" t="n"/>
-      <c r="G204" s="82" t="n"/>
-      <c r="H204" s="78" t="n"/>
+      <c r="G204" s="81" t="n"/>
+      <c r="H204" s="77" t="n"/>
     </row>
     <row r="205" ht="15" customHeight="1" s="95">
       <c r="B205" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C205" s="79" t="inlineStr">
+      <c r="C205" s="78" t="inlineStr">
         <is>
           <t>Снятие, установка с обвзякой БГ</t>
         </is>
       </c>
-      <c r="D205" s="82" t="n"/>
-      <c r="E205" s="82" t="n">
+      <c r="D205" s="81" t="n"/>
+      <c r="E205" s="81" t="n">
         <v>325283.1</v>
       </c>
       <c r="F205" s="3">
         <f>E205*D205</f>
         <v/>
       </c>
-      <c r="G205" s="82" t="n"/>
-      <c r="H205" s="78" t="n"/>
+      <c r="G205" s="81" t="n"/>
+      <c r="H205" s="77" t="n"/>
     </row>
     <row r="206" ht="15" customHeight="1" s="95">
       <c r="B206" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C206" s="79" t="inlineStr">
+      <c r="C206" s="78" t="inlineStr">
         <is>
           <t>Снятие, установка с обвзякой АГЗУ</t>
         </is>
       </c>
-      <c r="D206" s="82" t="n"/>
-      <c r="E206" s="82" t="n">
+      <c r="D206" s="81" t="n"/>
+      <c r="E206" s="81" t="n">
         <v>379231.49</v>
       </c>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" s="82" t="n"/>
-      <c r="H206" s="78" t="n"/>
+      <c r="G206" s="81" t="n"/>
+      <c r="H206" s="77" t="n"/>
     </row>
     <row r="207" ht="21" customHeight="1" s="95">
       <c r="B207" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C207" s="79" t="inlineStr">
+      <c r="C207" s="78" t="inlineStr">
         <is>
           <t>Установка площадки обслуживания скважин</t>
         </is>
       </c>
-      <c r="D207" s="82" t="n"/>
-      <c r="E207" s="82" t="n">
+      <c r="D207" s="81" t="n"/>
+      <c r="E207" s="81" t="n">
         <v>10115.25</v>
       </c>
       <c r="F207" s="3">
         <f>E207*D207</f>
         <v/>
       </c>
-      <c r="G207" s="82" t="n"/>
-      <c r="H207" s="78" t="n"/>
+      <c r="G207" s="81" t="n"/>
+      <c r="H207" s="77" t="n"/>
     </row>
     <row r="208" ht="14.25" customHeight="1" s="95">
       <c r="B208" s="3" t="n"/>
-      <c r="C208" s="79" t="inlineStr">
+      <c r="C208" s="78" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D208" s="82" t="n"/>
-      <c r="E208" s="82" t="n"/>
+      <c r="D208" s="81" t="n"/>
+      <c r="E208" s="81" t="n"/>
       <c r="F208" s="3">
         <f>SUM(F205:F207)</f>
         <v/>
       </c>
-      <c r="G208" s="82" t="n"/>
-      <c r="H208" s="78" t="n"/>
+      <c r="G208" s="81" t="n"/>
+      <c r="H208" s="77" t="n"/>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="95">
       <c r="B209" s="13" t="inlineStr">
@@ -5615,8 +5615,8 @@
           <t>Итого:</t>
         </is>
       </c>
-      <c r="D209" s="82" t="n"/>
-      <c r="E209" s="82" t="n"/>
+      <c r="D209" s="81" t="n"/>
+      <c r="E209" s="81" t="n"/>
       <c r="F209" s="18">
         <f>F208+F203+F176+F151+F112+F64</f>
         <v/>
@@ -5625,7 +5625,7 @@
         <f>F203+F176+F152+F151+F112+F64</f>
         <v/>
       </c>
-      <c r="I209" s="83">
+      <c r="I209" s="82">
         <f>F203+F176+F151+F112+F64</f>
         <v/>
       </c>
@@ -5636,13 +5636,13 @@
           <t>НДС 18%</t>
         </is>
       </c>
-      <c r="D210" s="82" t="n"/>
-      <c r="E210" s="82" t="n"/>
+      <c r="D210" s="81" t="n"/>
+      <c r="E210" s="81" t="n"/>
       <c r="F210" s="18">
         <f>F209*0.18</f>
         <v/>
       </c>
-      <c r="G210" s="82" t="n"/>
+      <c r="G210" s="81" t="n"/>
     </row>
     <row r="211" ht="14.25" customHeight="1" s="95">
       <c r="B211" s="13" t="inlineStr">
@@ -5650,30 +5650,30 @@
           <t>Всего с НДС</t>
         </is>
       </c>
-      <c r="D211" s="82" t="n"/>
-      <c r="E211" s="82" t="n"/>
+      <c r="D211" s="81" t="n"/>
+      <c r="E211" s="81" t="n"/>
       <c r="F211" s="18">
         <f>F209+F210</f>
         <v/>
       </c>
-      <c r="G211" s="82" t="n"/>
+      <c r="G211" s="81" t="n"/>
     </row>
     <row r="212" ht="24.75" customHeight="1" s="95">
       <c r="B212" s="13" t="n"/>
-      <c r="D212" s="82" t="n"/>
-      <c r="E212" s="82" t="n"/>
+      <c r="D212" s="81" t="n"/>
+      <c r="E212" s="81" t="n"/>
       <c r="F212" s="18" t="n"/>
       <c r="L212" s="3" t="n"/>
     </row>
-    <row r="213" ht="12.75" customFormat="1" customHeight="1" s="78">
-      <c r="B213" s="81" t="inlineStr">
+    <row r="213" ht="12.75" customFormat="1" customHeight="1" s="77">
+      <c r="B213" s="80" t="inlineStr">
         <is>
           <t>ИСПОЛНИТЕЛЬ:</t>
         </is>
       </c>
-      <c r="C213" s="83" t="n"/>
-      <c r="D213" s="81" t="n"/>
-      <c r="E213" s="81" t="inlineStr">
+      <c r="C213" s="82" t="n"/>
+      <c r="D213" s="80" t="n"/>
+      <c r="E213" s="80" t="inlineStr">
         <is>
           <t>ЗАКАЗЧИК:</t>
         </is>
@@ -5681,16 +5681,16 @@
       <c r="G213" s="3" t="n"/>
       <c r="L213" s="3" t="n"/>
     </row>
-    <row r="214" customFormat="1" s="78">
-      <c r="A214" s="83" t="inlineStr">
+    <row r="214" customFormat="1" s="77">
+      <c r="A214" s="82" t="inlineStr">
         <is>
           <t>Генеральный директор</t>
         </is>
       </c>
       <c r="B214" s="8" t="n"/>
       <c r="C214" s="8" t="n"/>
-      <c r="D214" s="81" t="n"/>
-      <c r="E214" s="78" t="inlineStr">
+      <c r="D214" s="80" t="n"/>
+      <c r="E214" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">И.О.Главного инженера – заместителя </t>
         </is>
@@ -5698,11 +5698,11 @@
       <c r="F214" s="44" t="n"/>
       <c r="H214" s="44" t="n"/>
     </row>
-    <row r="215" ht="20.25" customFormat="1" customHeight="1" s="78">
+    <row r="215" ht="20.25" customFormat="1" customHeight="1" s="77">
       <c r="B215" s="8" t="n"/>
       <c r="C215" s="8" t="n"/>
-      <c r="D215" s="81" t="n"/>
-      <c r="E215" s="78" t="inlineStr">
+      <c r="D215" s="80" t="n"/>
+      <c r="E215" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">генерального директора </t>
         </is>
@@ -5710,7 +5710,7 @@
       <c r="F215" s="44" t="n"/>
       <c r="H215" s="44" t="n"/>
     </row>
-    <row r="216" ht="24" customFormat="1" customHeight="1" s="78">
+    <row r="216" ht="24" customFormat="1" customHeight="1" s="77">
       <c r="A216" s="22" t="inlineStr">
         <is>
           <t>ООО "ЯмалСпецЦентр"</t>
@@ -5718,8 +5718,8 @@
       </c>
       <c r="B216" s="8" t="n"/>
       <c r="C216" s="8" t="n"/>
-      <c r="D216" s="81" t="n"/>
-      <c r="E216" s="78" t="inlineStr">
+      <c r="D216" s="80" t="n"/>
+      <c r="E216" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">АО "Газпромнефть-Ноябрьскнефтегаз"                                  </t>
         </is>
@@ -5727,40 +5727,40 @@
       <c r="F216" s="44" t="n"/>
       <c r="H216" s="44" t="n"/>
     </row>
-    <row r="217" ht="26.25" customFormat="1" customHeight="1" s="78">
-      <c r="A217" s="83" t="inlineStr">
+    <row r="217" ht="26.25" customFormat="1" customHeight="1" s="77">
+      <c r="A217" s="82" t="inlineStr">
         <is>
           <t>_________________А.Г. Воронин</t>
         </is>
       </c>
-      <c r="B217" s="87" t="n"/>
-      <c r="C217" s="87" t="n"/>
-      <c r="D217" s="79" t="n"/>
-      <c r="E217" s="83" t="inlineStr">
+      <c r="B217" s="86" t="n"/>
+      <c r="C217" s="86" t="n"/>
+      <c r="D217" s="78" t="n"/>
+      <c r="E217" s="82" t="inlineStr">
         <is>
           <t>_________________ В.В. Климанов</t>
         </is>
       </c>
-      <c r="G217" s="83" t="n"/>
-    </row>
-    <row r="218" customFormat="1" s="78">
-      <c r="A218" s="84" t="inlineStr">
+      <c r="G217" s="82" t="n"/>
+    </row>
+    <row r="218" customFormat="1" s="77">
+      <c r="A218" s="83" t="inlineStr">
         <is>
           <t xml:space="preserve">                        М.П.</t>
         </is>
       </c>
-      <c r="D218" s="81" t="n"/>
+      <c r="D218" s="80" t="n"/>
       <c r="E218" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">                        М.П.</t>
         </is>
       </c>
-      <c r="F218" s="85" t="n"/>
+      <c r="F218" s="84" t="n"/>
       <c r="G218" s="49" t="n"/>
-      <c r="H218" s="85" t="n"/>
-    </row>
-    <row r="219" ht="15" customFormat="1" customHeight="1" s="78">
-      <c r="A219" s="85" t="n"/>
+      <c r="H218" s="84" t="n"/>
+    </row>
+    <row r="219" ht="15" customFormat="1" customHeight="1" s="77">
+      <c r="A219" s="84" t="n"/>
       <c r="D219" s="10" t="n"/>
       <c r="E219" s="11" t="inlineStr">
         <is>
@@ -5771,16 +5771,16 @@
       <c r="G219" s="11" t="n"/>
       <c r="H219" s="11" t="n"/>
     </row>
-    <row r="220" ht="13.5" customFormat="1" customHeight="1" s="78">
+    <row r="220" ht="13.5" customFormat="1" customHeight="1" s="77">
       <c r="A220" s="30" t="n"/>
-      <c r="B220" s="84" t="n"/>
+      <c r="B220" s="83" t="n"/>
       <c r="C220" s="8" t="n"/>
       <c r="D220" s="20" t="n"/>
       <c r="E220" s="20" t="n"/>
       <c r="F220" s="20" t="n"/>
       <c r="G220" s="20" t="n"/>
     </row>
-    <row r="221" customFormat="1" s="78">
+    <row r="221" customFormat="1" s="77">
       <c r="A221" s="35" t="inlineStr">
         <is>
           <t>СОГЛАСОВАНО:</t>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="B221" s="33" t="n"/>
       <c r="C221" s="8" t="n"/>
-      <c r="D221" s="81" t="n"/>
+      <c r="D221" s="80" t="n"/>
       <c r="E221" s="35" t="inlineStr">
         <is>
           <t>СОГЛАСОВАНО:</t>
@@ -5797,40 +5797,40 @@
       <c r="F221" s="36" t="n"/>
       <c r="G221" s="3" t="n"/>
     </row>
-    <row r="222" customFormat="1" s="78">
+    <row r="222" customFormat="1" s="77">
       <c r="A222" s="32" t="n"/>
       <c r="B222" s="33" t="n"/>
       <c r="C222" s="8" t="n"/>
-      <c r="D222" s="81" t="n"/>
+      <c r="D222" s="80" t="n"/>
       <c r="E222" s="35" t="n"/>
       <c r="F222" s="36" t="n"/>
       <c r="G222" s="3" t="n"/>
     </row>
-    <row r="223" ht="18" customFormat="1" customHeight="1" s="78">
-      <c r="A223" s="87" t="inlineStr">
+    <row r="223" ht="18" customFormat="1" customHeight="1" s="77">
+      <c r="A223" s="86" t="inlineStr">
         <is>
           <t>Начальник ПЭО</t>
         </is>
       </c>
-      <c r="D223" s="79" t="n"/>
+      <c r="D223" s="78" t="n"/>
       <c r="E223" s="37" t="inlineStr">
         <is>
           <t>Главный механик - начальник УОРНПО</t>
         </is>
       </c>
-      <c r="F223" s="83" t="n"/>
+      <c r="F223" s="82" t="n"/>
       <c r="G223" s="3" t="n"/>
     </row>
-    <row r="224" customFormat="1" s="78">
-      <c r="A224" s="77" t="n"/>
-      <c r="C224" s="79" t="n"/>
-      <c r="D224" s="81" t="n"/>
+    <row r="224" customFormat="1" s="77">
+      <c r="A224" s="76" t="n"/>
+      <c r="C224" s="78" t="n"/>
+      <c r="D224" s="80" t="n"/>
       <c r="E224" s="37" t="n"/>
       <c r="F224" s="34" t="n"/>
       <c r="G224" s="3" t="n"/>
     </row>
-    <row r="225" customFormat="1" s="78">
-      <c r="A225" s="83" t="n"/>
+    <row r="225" customFormat="1" s="77">
+      <c r="A225" s="82" t="n"/>
       <c r="B225" s="21" t="inlineStr">
         <is>
           <t>_________________А.С. Бойчук</t>
@@ -5847,7 +5847,7 @@
       <c r="G225" s="3" t="n"/>
       <c r="H225" s="19" t="n"/>
     </row>
-    <row r="226" customFormat="1" s="78">
+    <row r="226" customFormat="1" s="77">
       <c r="B226" s="39" t="n"/>
       <c r="C226" s="40" t="n"/>
       <c r="D226" s="12" t="n"/>
@@ -5856,10 +5856,10 @@
       <c r="G226" s="3" t="n"/>
       <c r="H226" s="19" t="n"/>
     </row>
-    <row r="227" ht="12.75" customFormat="1" customHeight="1" s="78">
+    <row r="227" ht="12.75" customFormat="1" customHeight="1" s="77">
       <c r="B227" s="11" t="n"/>
       <c r="C227" s="8" t="n"/>
-      <c r="D227" s="79" t="n"/>
+      <c r="D227" s="78" t="n"/>
       <c r="E227" s="38" t="inlineStr">
         <is>
           <t>Планово-бюджетное управление</t>
@@ -5868,9 +5868,9 @@
       <c r="F227" s="34" t="n"/>
       <c r="G227" s="3" t="n"/>
     </row>
-    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="78">
-      <c r="B228" s="83" t="n"/>
-      <c r="C228" s="83" t="n"/>
+    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="77">
+      <c r="B228" s="82" t="n"/>
+      <c r="C228" s="82" t="n"/>
       <c r="D228" s="13" t="n"/>
       <c r="E228" s="14" t="inlineStr">
         <is>
@@ -5880,29 +5880,29 @@
       <c r="F228" s="34" t="n"/>
       <c r="G228" s="3" t="n"/>
     </row>
-    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="78">
-      <c r="B229" s="83" t="n"/>
-      <c r="C229" s="83" t="n"/>
+    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="77">
+      <c r="B229" s="82" t="n"/>
+      <c r="C229" s="82" t="n"/>
       <c r="D229" s="14" t="n"/>
-      <c r="E229" s="82" t="n"/>
-      <c r="F229" s="82" t="n"/>
+      <c r="E229" s="81" t="n"/>
+      <c r="F229" s="81" t="n"/>
       <c r="G229" s="3" t="n"/>
     </row>
     <row r="230" ht="6" customHeight="1" s="95">
       <c r="B230" s="6" t="n"/>
-      <c r="C230" s="82" t="n"/>
-      <c r="D230" s="82" t="n"/>
-      <c r="E230" s="82" t="n"/>
-      <c r="F230" s="82" t="n"/>
-      <c r="G230" s="82" t="n"/>
+      <c r="C230" s="81" t="n"/>
+      <c r="D230" s="81" t="n"/>
+      <c r="E230" s="81" t="n"/>
+      <c r="F230" s="81" t="n"/>
+      <c r="G230" s="81" t="n"/>
     </row>
     <row r="231" ht="12.75" customHeight="1" s="95">
       <c r="B231" s="6" t="n"/>
-      <c r="C231" s="82" t="n"/>
-      <c r="D231" s="82" t="n"/>
-      <c r="E231" s="82" t="n"/>
-      <c r="F231" s="82" t="n"/>
-      <c r="G231" s="82" t="n"/>
+      <c r="C231" s="81" t="n"/>
+      <c r="D231" s="81" t="n"/>
+      <c r="E231" s="81" t="n"/>
+      <c r="F231" s="81" t="n"/>
+      <c r="G231" s="81" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -5971,44 +5971,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="92" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>на объектах ЦППН-1 Акционерного Общества "Газпромнефть-Ноябрьскнефтегаз"(Ноябрьский регион)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B10" s="91" t="inlineStr">
+      <c r="B10" s="90" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C10" s="91" t="inlineStr">
+      <c r="C10" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve">Работы по  сервисному обслуживанию </t>
         </is>
       </c>
-      <c r="H10" s="90" t="inlineStr">
+      <c r="H10" s="89" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I10" s="90" t="inlineStr">
+      <c r="I10" s="89" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
@@ -6016,27 +6016,27 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="C12" s="91" t="inlineStr">
+      <c r="C12" s="90" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D12" s="91" t="inlineStr">
+      <c r="D12" s="90" t="inlineStr">
         <is>
           <t>Оборудование</t>
         </is>
       </c>
-      <c r="E12" s="91" t="inlineStr">
+      <c r="E12" s="90" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F12" s="91" t="inlineStr">
+      <c r="F12" s="90" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="G12" s="91" t="inlineStr">
+      <c r="G12" s="90" t="inlineStr">
         <is>
           <t>Зав №</t>
         </is>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="42.75" customHeight="1" s="95">
-      <c r="A14" s="91" t="n">
+      <c r="A14" s="90" t="n">
         <v>1</v>
       </c>
       <c r="B14" s="93" t="inlineStr">
@@ -6057,7 +6057,7 @@
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D14" s="91" t="inlineStr">
+      <c r="D14" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6067,37 +6067,37 @@
           <t xml:space="preserve">ЦНС 240-1650-2ТМ </t>
         </is>
       </c>
-      <c r="F14" s="91" t="inlineStr">
+      <c r="F14" s="90" t="inlineStr">
         <is>
           <t>НА-5</t>
         </is>
       </c>
-      <c r="G14" s="91" t="inlineStr">
+      <c r="G14" s="90" t="inlineStr">
         <is>
           <t>20093/002-2</t>
         </is>
       </c>
       <c r="H14" s="71" t="n"/>
       <c r="I14" s="71" t="n"/>
-      <c r="J14" s="94" t="n">
+      <c r="J14" s="92" t="n">
         <v>61000387815</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="91" t="n">
+      <c r="A15" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="91" t="inlineStr">
+      <c r="B15" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C15" s="60" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D15" s="91" t="inlineStr">
+      <c r="D15" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6122,20 +6122,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="91" t="n">
+      <c r="A16" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="91" t="inlineStr">
+      <c r="B16" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C16" s="60" t="inlineStr">
+      <c r="C16" s="94" t="inlineStr">
         <is>
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D16" s="91" t="inlineStr">
+      <c r="D16" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6162,20 +6162,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="91" t="n">
+      <c r="A17" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="91" t="inlineStr">
+      <c r="B17" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="94" t="inlineStr">
         <is>
           <t>КНС-1В Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D17" s="91" t="inlineStr">
+      <c r="D17" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6202,20 +6202,20 @@
       </c>
     </row>
     <row r="18" ht="25.5" customHeight="1" s="95">
-      <c r="A18" s="91" t="n">
+      <c r="A18" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C18" s="60" t="inlineStr">
+      <c r="C18" s="94" t="inlineStr">
         <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D18" s="91" t="inlineStr">
+      <c r="D18" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6240,86 +6240,113 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="94" t="n"/>
-      <c r="B19" s="94" t="n"/>
-      <c r="C19" s="60" t="n"/>
+      <c r="A19" s="92" t="n"/>
+      <c r="B19" s="92" t="n"/>
+      <c r="C19" s="94" t="n"/>
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="62" t="n"/>
       <c r="G19" s="59" t="n"/>
       <c r="J19" s="61" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="n"/>
-      <c r="B20" s="94" t="n"/>
-      <c r="C20" s="60" t="n"/>
-      <c r="E20" s="76" t="inlineStr">
-        <is>
-          <t>Объединённая ячейка!!!!!!</t>
-        </is>
-      </c>
-      <c r="F20" s="62" t="n"/>
-      <c r="G20" s="59" t="n"/>
-      <c r="J20" s="61" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="94" t="n"/>
-      <c r="B21" s="94" t="n"/>
-      <c r="C21" s="60" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="59" t="n"/>
-      <c r="J21" s="61" t="n"/>
-    </row>
+      <c r="A20" s="92" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B20" s="92" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>Работы по текущему ремонту!!!</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J20" s="61" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="94" t="n"/>
-      <c r="B22" s="94" t="n"/>
-      <c r="C22" s="60" t="n"/>
-      <c r="F22" s="62" t="n"/>
-      <c r="G22" s="59" t="n"/>
-      <c r="J22" s="61" t="n"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="62" t="n"/>
-      <c r="G23" s="59" t="n"/>
-      <c r="J23" s="61" t="n"/>
-    </row>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="D24" s="94" t="n"/>
+      <c r="D24" s="92" t="n"/>
       <c r="F24" s="62" t="n"/>
       <c r="G24" s="59" t="n"/>
-      <c r="J24" s="60" t="n"/>
+      <c r="J24" s="94" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="n"/>
-      <c r="B25" s="94" t="n"/>
-      <c r="C25" s="60" t="n"/>
-      <c r="D25" s="94" t="n"/>
+      <c r="A25" s="92" t="n"/>
+      <c r="B25" s="92" t="n"/>
+      <c r="C25" s="94" t="n"/>
+      <c r="D25" s="92" t="n"/>
       <c r="E25" s="58" t="n"/>
       <c r="F25" s="62" t="n"/>
       <c r="G25" s="59" t="n"/>
-      <c r="J25" s="60" t="n"/>
+      <c r="J25" s="94" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="91" t="inlineStr">
+      <c r="A30" s="90" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
+      <c r="B30" s="90" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>Работы по текущему ремонту</t>
         </is>
       </c>
-      <c r="H30" s="90" t="inlineStr">
+      <c r="H30" s="89" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I30" s="90" t="inlineStr">
+      <c r="I30" s="89" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
@@ -6332,27 +6359,27 @@
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="C32" s="91" t="inlineStr">
+      <c r="C32" s="90" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D32" s="91" t="inlineStr">
+      <c r="D32" s="90" t="inlineStr">
         <is>
           <t>Оборудование</t>
         </is>
       </c>
-      <c r="E32" s="91" t="inlineStr">
+      <c r="E32" s="90" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F32" s="91" t="inlineStr">
+      <c r="F32" s="90" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="G32" s="91" t="inlineStr">
+      <c r="G32" s="90" t="inlineStr">
         <is>
           <t>Зав №</t>
         </is>
@@ -6360,10 +6387,10 @@
     </row>
     <row r="33"/>
     <row r="34" ht="16.5" customHeight="1" s="95">
-      <c r="A34" s="91" t="n">
+      <c r="A34" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="91" t="inlineStr">
+      <c r="B34" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
@@ -6391,17 +6418,17 @@
       <c r="G34" s="73" t="n">
         <v>17</v>
       </c>
-      <c r="H34" s="91" t="n"/>
-      <c r="I34" s="91" t="n"/>
+      <c r="H34" s="90" t="n"/>
+      <c r="I34" s="90" t="n"/>
       <c r="J34" s="75" t="n">
         <v>61000329246</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="91" t="n">
+      <c r="A35" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="91" t="inlineStr">
+      <c r="B35" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
@@ -6429,17 +6456,17 @@
       <c r="G35" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="H35" s="91" t="n"/>
-      <c r="I35" s="91" t="n"/>
+      <c r="H35" s="90" t="n"/>
+      <c r="I35" s="90" t="n"/>
       <c r="J35" s="75" t="n">
         <v>61000313869</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="91" t="n">
+      <c r="A36" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="91" t="inlineStr">
+      <c r="B36" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
@@ -6449,7 +6476,7 @@
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D36" s="91" t="inlineStr">
+      <c r="D36" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6467,17 +6494,17 @@
       <c r="G36" s="73" t="n">
         <v>26</v>
       </c>
-      <c r="H36" s="91" t="n"/>
-      <c r="I36" s="91" t="n"/>
+      <c r="H36" s="90" t="n"/>
+      <c r="I36" s="90" t="n"/>
       <c r="J36" s="75" t="n">
         <v>61000235346</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="91" t="n">
+      <c r="A37" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="91" t="inlineStr">
+      <c r="B37" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
@@ -6487,7 +6514,7 @@
           <t>КНС-1Б Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D37" s="91" t="inlineStr">
+      <c r="D37" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6505,169 +6532,169 @@
       <c r="G37" s="73" t="n">
         <v>86</v>
       </c>
-      <c r="H37" s="91" t="n"/>
-      <c r="I37" s="91" t="n"/>
+      <c r="H37" s="90" t="n"/>
+      <c r="I37" s="90" t="n"/>
       <c r="J37" s="75" t="n">
         <v>61000235329</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="91" t="n">
+      <c r="A38" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B38" s="91" t="inlineStr">
+      <c r="B38" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C38" s="91" t="inlineStr">
+      <c r="C38" s="90" t="inlineStr">
         <is>
           <t>КНС-1В Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D38" s="91" t="inlineStr">
+      <c r="D38" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
       </c>
-      <c r="E38" s="91" t="inlineStr">
+      <c r="E38" s="90" t="inlineStr">
         <is>
           <t>ЦНС 240-1050-2ИТ</t>
         </is>
       </c>
-      <c r="F38" s="91" t="inlineStr">
+      <c r="F38" s="90" t="inlineStr">
         <is>
           <t>НА-13</t>
         </is>
       </c>
-      <c r="G38" s="91" t="inlineStr">
+      <c r="G38" s="90" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H38" s="91" t="n"/>
-      <c r="I38" s="91" t="n"/>
-      <c r="J38" s="91" t="n">
+      <c r="H38" s="90" t="n"/>
+      <c r="I38" s="90" t="n"/>
+      <c r="J38" s="90" t="n">
         <v>61000153881</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="91" t="n">
+      <c r="A39" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B39" s="91" t="inlineStr">
+      <c r="B39" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C39" s="91" t="inlineStr">
+      <c r="C39" s="90" t="inlineStr">
         <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D39" s="91" t="inlineStr">
+      <c r="D39" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
       </c>
-      <c r="E39" s="91" t="inlineStr">
+      <c r="E39" s="90" t="inlineStr">
         <is>
           <t>НЦС К 310-1510-УХЛ4</t>
         </is>
       </c>
-      <c r="F39" s="91" t="inlineStr">
+      <c r="F39" s="90" t="inlineStr">
         <is>
           <t>НА-2</t>
         </is>
       </c>
-      <c r="G39" s="91" t="n">
+      <c r="G39" s="90" t="n">
         <v>2070</v>
       </c>
-      <c r="H39" s="91" t="n"/>
-      <c r="I39" s="91" t="n"/>
-      <c r="J39" s="91" t="n">
+      <c r="H39" s="90" t="n"/>
+      <c r="I39" s="90" t="n"/>
+      <c r="J39" s="90" t="n">
         <v>61000113163</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="91" t="n">
+      <c r="A40" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="B40" s="91" t="inlineStr">
+      <c r="B40" s="90" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C40" s="91" t="inlineStr">
+      <c r="C40" s="90" t="inlineStr">
         <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D40" s="91" t="inlineStr">
+      <c r="D40" s="90" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
       </c>
-      <c r="E40" s="91" t="inlineStr">
+      <c r="E40" s="90" t="inlineStr">
         <is>
           <t>ЦНС 310-1510-2И1Т</t>
         </is>
       </c>
-      <c r="F40" s="91" t="inlineStr">
+      <c r="F40" s="90" t="inlineStr">
         <is>
           <t>НА-4</t>
         </is>
       </c>
-      <c r="G40" s="91" t="inlineStr">
+      <c r="G40" s="90" t="inlineStr">
         <is>
           <t>240-28</t>
         </is>
       </c>
-      <c r="H40" s="91" t="n"/>
-      <c r="I40" s="91" t="n"/>
-      <c r="J40" s="91" t="n">
+      <c r="H40" s="90" t="n"/>
+      <c r="I40" s="90" t="n"/>
+      <c r="J40" s="90" t="n">
         <v>61000313869</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="91" t="n"/>
-      <c r="B41" s="91" t="n"/>
-      <c r="C41" s="91" t="n"/>
-      <c r="D41" s="91" t="n"/>
-      <c r="E41" s="91" t="n"/>
-      <c r="F41" s="91" t="n"/>
-      <c r="G41" s="91" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="91" t="n"/>
-      <c r="J41" s="91" t="n"/>
+      <c r="A41" s="90" t="n"/>
+      <c r="B41" s="90" t="n"/>
+      <c r="C41" s="90" t="n"/>
+      <c r="D41" s="90" t="n"/>
+      <c r="E41" s="90" t="n"/>
+      <c r="F41" s="90" t="n"/>
+      <c r="G41" s="90" t="n"/>
+      <c r="H41" s="90" t="n"/>
+      <c r="I41" s="90" t="n"/>
+      <c r="J41" s="90" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="91" t="inlineStr">
+      <c r="A45" s="90" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B45" s="91" t="inlineStr">
+      <c r="B45" s="90" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C45" s="91" t="inlineStr">
+      <c r="C45" s="90" t="inlineStr">
         <is>
           <t>Работы по замене агрегатов</t>
         </is>
       </c>
-      <c r="H45" s="90" t="inlineStr">
+      <c r="H45" s="89" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I45" s="90" t="inlineStr">
+      <c r="I45" s="89" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J45" s="92" t="inlineStr">
+      <c r="J45" s="91" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
@@ -6675,27 +6702,27 @@
     </row>
     <row r="46"/>
     <row r="47">
-      <c r="C47" s="91" t="inlineStr">
+      <c r="C47" s="90" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D47" s="91" t="inlineStr">
+      <c r="D47" s="90" t="inlineStr">
         <is>
           <t>Рег №</t>
         </is>
       </c>
-      <c r="E47" s="91" t="inlineStr">
+      <c r="E47" s="90" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="F47" s="91" t="inlineStr">
+      <c r="F47" s="90" t="inlineStr">
         <is>
           <t>Монтаж/ПНР</t>
         </is>
       </c>
-      <c r="G47" s="91" t="inlineStr">
+      <c r="G47" s="90" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
@@ -6785,7 +6812,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6933,17 +6960,17 @@
       <c r="J62" s="54" t="n"/>
     </row>
     <row r="63" ht="25.5" customHeight="1" s="95">
-      <c r="A63" s="88" t="inlineStr">
+      <c r="A63" s="87" t="inlineStr">
         <is>
           <t xml:space="preserve">№ п/п </t>
         </is>
       </c>
-      <c r="B63" s="88" t="inlineStr">
+      <c r="B63" s="87" t="inlineStr">
         <is>
           <t>Цех</t>
         </is>
       </c>
-      <c r="C63" s="88" t="inlineStr">
+      <c r="C63" s="87" t="inlineStr">
         <is>
           <t>Прочие работы</t>
         </is>
@@ -6960,7 +6987,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="88" t="inlineStr">
+      <c r="C64" s="87" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
@@ -6984,7 +7011,7 @@
       <c r="F65" s="57" t="n"/>
       <c r="G65" s="57" t="n"/>
       <c r="H65" s="57" t="n"/>
-      <c r="I65" s="88" t="n"/>
+      <c r="I65" s="87" t="n"/>
       <c r="J65" s="54" t="n"/>
     </row>
     <row r="66">
@@ -7056,22 +7083,24 @@
       <c r="J70" s="54" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="51">
     <mergeCell ref="C63:H63"/>
     <mergeCell ref="I30:I33"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="H10:H13"/>
-    <mergeCell ref="E20:E23"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="J10:J13"/>
     <mergeCell ref="A45:A48"/>
+    <mergeCell ref="I45:I48"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="I45:I48"/>
+    <mergeCell ref="C22:C23"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="C12:C13"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="D47:D48"/>
+    <mergeCell ref="J20:J23"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="H45:H48"/>
@@ -7079,25 +7108,33 @@
     <mergeCell ref="J45:J48"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C32:C33"/>
+    <mergeCell ref="I20:I23"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="I63:I64"/>
     <mergeCell ref="G32:G33"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="C30:G31"/>
     <mergeCell ref="B63:B64"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="I10:I13"/>
-    <mergeCell ref="C6:H6"/>
     <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C20:G21"/>
     <mergeCell ref="G47:G48"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="C5:H5"/>
-    <mergeCell ref="E12:E13"/>
     <mergeCell ref="C10:G11"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="E22:E23"/>
     <mergeCell ref="C45:G46"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="H20:H23"/>
     <mergeCell ref="B45:B48"/>
     <mergeCell ref="H30:H33"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <conditionalFormatting sqref="J15:J16">
     <cfRule type="duplicateValues" priority="21" dxfId="0"/>

--- a/справка  ЦППД-1.xlsx
+++ b/справка  ЦППД-1.xlsx
@@ -208,7 +208,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -432,6 +432,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="29">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -468,10 +475,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -482,10 +489,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="26">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="30">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1179,716 +1186,716 @@
   <dimension ref="A1:L231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.7109375" customWidth="1" style="82" min="1" max="1"/>
-    <col width="5.85546875" customWidth="1" style="82" min="2" max="2"/>
-    <col width="41.85546875" customWidth="1" style="82" min="3" max="3"/>
-    <col width="14.28515625" customWidth="1" style="82" min="4" max="4"/>
-    <col width="21.5703125" customWidth="1" style="82" min="5" max="5"/>
-    <col width="24.28515625" customWidth="1" style="82" min="6" max="6"/>
-    <col width="4.28515625" customWidth="1" style="82" min="7" max="7"/>
-    <col width="14.7109375" customWidth="1" style="82" min="8" max="8"/>
-    <col width="23" customWidth="1" style="82" min="9" max="9"/>
-    <col width="12.85546875" customWidth="1" style="82" min="10" max="10"/>
-    <col width="16.140625" customWidth="1" style="82" min="11" max="11"/>
-    <col width="14.140625" customWidth="1" style="82" min="12" max="12"/>
-    <col width="11" bestFit="1" customWidth="1" style="82" min="13" max="14"/>
-    <col width="9.140625" customWidth="1" style="82" min="15" max="256"/>
-    <col width="2" customWidth="1" style="82" min="257" max="257"/>
-    <col width="5.85546875" customWidth="1" style="82" min="258" max="258"/>
-    <col width="38.5703125" customWidth="1" style="82" min="259" max="259"/>
-    <col width="10" customWidth="1" style="82" min="260" max="260"/>
-    <col width="21.5703125" customWidth="1" style="82" min="261" max="261"/>
-    <col width="22.7109375" customWidth="1" style="82" min="262" max="262"/>
-    <col width="0.28515625" customWidth="1" style="82" min="263" max="263"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="264" max="264"/>
-    <col width="9.140625" customWidth="1" style="82" min="265" max="267"/>
-    <col width="14.140625" customWidth="1" style="82" min="268" max="268"/>
-    <col width="9.140625" customWidth="1" style="82" min="269" max="512"/>
-    <col width="2" customWidth="1" style="82" min="513" max="513"/>
-    <col width="5.85546875" customWidth="1" style="82" min="514" max="514"/>
-    <col width="38.5703125" customWidth="1" style="82" min="515" max="515"/>
-    <col width="10" customWidth="1" style="82" min="516" max="516"/>
-    <col width="21.5703125" customWidth="1" style="82" min="517" max="517"/>
-    <col width="22.7109375" customWidth="1" style="82" min="518" max="518"/>
-    <col width="0.28515625" customWidth="1" style="82" min="519" max="519"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="520" max="520"/>
-    <col width="9.140625" customWidth="1" style="82" min="521" max="523"/>
-    <col width="14.140625" customWidth="1" style="82" min="524" max="524"/>
-    <col width="9.140625" customWidth="1" style="82" min="525" max="768"/>
-    <col width="2" customWidth="1" style="82" min="769" max="769"/>
-    <col width="5.85546875" customWidth="1" style="82" min="770" max="770"/>
-    <col width="38.5703125" customWidth="1" style="82" min="771" max="771"/>
-    <col width="10" customWidth="1" style="82" min="772" max="772"/>
-    <col width="21.5703125" customWidth="1" style="82" min="773" max="773"/>
-    <col width="22.7109375" customWidth="1" style="82" min="774" max="774"/>
-    <col width="0.28515625" customWidth="1" style="82" min="775" max="775"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="776" max="776"/>
-    <col width="9.140625" customWidth="1" style="82" min="777" max="779"/>
-    <col width="14.140625" customWidth="1" style="82" min="780" max="780"/>
-    <col width="9.140625" customWidth="1" style="82" min="781" max="1024"/>
-    <col width="2" customWidth="1" style="82" min="1025" max="1025"/>
-    <col width="5.85546875" customWidth="1" style="82" min="1026" max="1026"/>
-    <col width="38.5703125" customWidth="1" style="82" min="1027" max="1027"/>
-    <col width="10" customWidth="1" style="82" min="1028" max="1028"/>
-    <col width="21.5703125" customWidth="1" style="82" min="1029" max="1029"/>
-    <col width="22.7109375" customWidth="1" style="82" min="1030" max="1030"/>
-    <col width="0.28515625" customWidth="1" style="82" min="1031" max="1031"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="1032" max="1032"/>
-    <col width="9.140625" customWidth="1" style="82" min="1033" max="1035"/>
-    <col width="14.140625" customWidth="1" style="82" min="1036" max="1036"/>
-    <col width="9.140625" customWidth="1" style="82" min="1037" max="1280"/>
-    <col width="2" customWidth="1" style="82" min="1281" max="1281"/>
-    <col width="5.85546875" customWidth="1" style="82" min="1282" max="1282"/>
-    <col width="38.5703125" customWidth="1" style="82" min="1283" max="1283"/>
-    <col width="10" customWidth="1" style="82" min="1284" max="1284"/>
-    <col width="21.5703125" customWidth="1" style="82" min="1285" max="1285"/>
-    <col width="22.7109375" customWidth="1" style="82" min="1286" max="1286"/>
-    <col width="0.28515625" customWidth="1" style="82" min="1287" max="1287"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="1288" max="1288"/>
-    <col width="9.140625" customWidth="1" style="82" min="1289" max="1291"/>
-    <col width="14.140625" customWidth="1" style="82" min="1292" max="1292"/>
-    <col width="9.140625" customWidth="1" style="82" min="1293" max="1536"/>
-    <col width="2" customWidth="1" style="82" min="1537" max="1537"/>
-    <col width="5.85546875" customWidth="1" style="82" min="1538" max="1538"/>
-    <col width="38.5703125" customWidth="1" style="82" min="1539" max="1539"/>
-    <col width="10" customWidth="1" style="82" min="1540" max="1540"/>
-    <col width="21.5703125" customWidth="1" style="82" min="1541" max="1541"/>
-    <col width="22.7109375" customWidth="1" style="82" min="1542" max="1542"/>
-    <col width="0.28515625" customWidth="1" style="82" min="1543" max="1543"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="1544" max="1544"/>
-    <col width="9.140625" customWidth="1" style="82" min="1545" max="1547"/>
-    <col width="14.140625" customWidth="1" style="82" min="1548" max="1548"/>
-    <col width="9.140625" customWidth="1" style="82" min="1549" max="1792"/>
-    <col width="2" customWidth="1" style="82" min="1793" max="1793"/>
-    <col width="5.85546875" customWidth="1" style="82" min="1794" max="1794"/>
-    <col width="38.5703125" customWidth="1" style="82" min="1795" max="1795"/>
-    <col width="10" customWidth="1" style="82" min="1796" max="1796"/>
-    <col width="21.5703125" customWidth="1" style="82" min="1797" max="1797"/>
-    <col width="22.7109375" customWidth="1" style="82" min="1798" max="1798"/>
-    <col width="0.28515625" customWidth="1" style="82" min="1799" max="1799"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="1800" max="1800"/>
-    <col width="9.140625" customWidth="1" style="82" min="1801" max="1803"/>
-    <col width="14.140625" customWidth="1" style="82" min="1804" max="1804"/>
-    <col width="9.140625" customWidth="1" style="82" min="1805" max="2048"/>
-    <col width="2" customWidth="1" style="82" min="2049" max="2049"/>
-    <col width="5.85546875" customWidth="1" style="82" min="2050" max="2050"/>
-    <col width="38.5703125" customWidth="1" style="82" min="2051" max="2051"/>
-    <col width="10" customWidth="1" style="82" min="2052" max="2052"/>
-    <col width="21.5703125" customWidth="1" style="82" min="2053" max="2053"/>
-    <col width="22.7109375" customWidth="1" style="82" min="2054" max="2054"/>
-    <col width="0.28515625" customWidth="1" style="82" min="2055" max="2055"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="2056" max="2056"/>
-    <col width="9.140625" customWidth="1" style="82" min="2057" max="2059"/>
-    <col width="14.140625" customWidth="1" style="82" min="2060" max="2060"/>
-    <col width="9.140625" customWidth="1" style="82" min="2061" max="2304"/>
-    <col width="2" customWidth="1" style="82" min="2305" max="2305"/>
-    <col width="5.85546875" customWidth="1" style="82" min="2306" max="2306"/>
-    <col width="38.5703125" customWidth="1" style="82" min="2307" max="2307"/>
-    <col width="10" customWidth="1" style="82" min="2308" max="2308"/>
-    <col width="21.5703125" customWidth="1" style="82" min="2309" max="2309"/>
-    <col width="22.7109375" customWidth="1" style="82" min="2310" max="2310"/>
-    <col width="0.28515625" customWidth="1" style="82" min="2311" max="2311"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="2312" max="2312"/>
-    <col width="9.140625" customWidth="1" style="82" min="2313" max="2315"/>
-    <col width="14.140625" customWidth="1" style="82" min="2316" max="2316"/>
-    <col width="9.140625" customWidth="1" style="82" min="2317" max="2560"/>
-    <col width="2" customWidth="1" style="82" min="2561" max="2561"/>
-    <col width="5.85546875" customWidth="1" style="82" min="2562" max="2562"/>
-    <col width="38.5703125" customWidth="1" style="82" min="2563" max="2563"/>
-    <col width="10" customWidth="1" style="82" min="2564" max="2564"/>
-    <col width="21.5703125" customWidth="1" style="82" min="2565" max="2565"/>
-    <col width="22.7109375" customWidth="1" style="82" min="2566" max="2566"/>
-    <col width="0.28515625" customWidth="1" style="82" min="2567" max="2567"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="2568" max="2568"/>
-    <col width="9.140625" customWidth="1" style="82" min="2569" max="2571"/>
-    <col width="14.140625" customWidth="1" style="82" min="2572" max="2572"/>
-    <col width="9.140625" customWidth="1" style="82" min="2573" max="2816"/>
-    <col width="2" customWidth="1" style="82" min="2817" max="2817"/>
-    <col width="5.85546875" customWidth="1" style="82" min="2818" max="2818"/>
-    <col width="38.5703125" customWidth="1" style="82" min="2819" max="2819"/>
-    <col width="10" customWidth="1" style="82" min="2820" max="2820"/>
-    <col width="21.5703125" customWidth="1" style="82" min="2821" max="2821"/>
-    <col width="22.7109375" customWidth="1" style="82" min="2822" max="2822"/>
-    <col width="0.28515625" customWidth="1" style="82" min="2823" max="2823"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="2824" max="2824"/>
-    <col width="9.140625" customWidth="1" style="82" min="2825" max="2827"/>
-    <col width="14.140625" customWidth="1" style="82" min="2828" max="2828"/>
-    <col width="9.140625" customWidth="1" style="82" min="2829" max="3072"/>
-    <col width="2" customWidth="1" style="82" min="3073" max="3073"/>
-    <col width="5.85546875" customWidth="1" style="82" min="3074" max="3074"/>
-    <col width="38.5703125" customWidth="1" style="82" min="3075" max="3075"/>
-    <col width="10" customWidth="1" style="82" min="3076" max="3076"/>
-    <col width="21.5703125" customWidth="1" style="82" min="3077" max="3077"/>
-    <col width="22.7109375" customWidth="1" style="82" min="3078" max="3078"/>
-    <col width="0.28515625" customWidth="1" style="82" min="3079" max="3079"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="3080" max="3080"/>
-    <col width="9.140625" customWidth="1" style="82" min="3081" max="3083"/>
-    <col width="14.140625" customWidth="1" style="82" min="3084" max="3084"/>
-    <col width="9.140625" customWidth="1" style="82" min="3085" max="3328"/>
-    <col width="2" customWidth="1" style="82" min="3329" max="3329"/>
-    <col width="5.85546875" customWidth="1" style="82" min="3330" max="3330"/>
-    <col width="38.5703125" customWidth="1" style="82" min="3331" max="3331"/>
-    <col width="10" customWidth="1" style="82" min="3332" max="3332"/>
-    <col width="21.5703125" customWidth="1" style="82" min="3333" max="3333"/>
-    <col width="22.7109375" customWidth="1" style="82" min="3334" max="3334"/>
-    <col width="0.28515625" customWidth="1" style="82" min="3335" max="3335"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="3336" max="3336"/>
-    <col width="9.140625" customWidth="1" style="82" min="3337" max="3339"/>
-    <col width="14.140625" customWidth="1" style="82" min="3340" max="3340"/>
-    <col width="9.140625" customWidth="1" style="82" min="3341" max="3584"/>
-    <col width="2" customWidth="1" style="82" min="3585" max="3585"/>
-    <col width="5.85546875" customWidth="1" style="82" min="3586" max="3586"/>
-    <col width="38.5703125" customWidth="1" style="82" min="3587" max="3587"/>
-    <col width="10" customWidth="1" style="82" min="3588" max="3588"/>
-    <col width="21.5703125" customWidth="1" style="82" min="3589" max="3589"/>
-    <col width="22.7109375" customWidth="1" style="82" min="3590" max="3590"/>
-    <col width="0.28515625" customWidth="1" style="82" min="3591" max="3591"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="3592" max="3592"/>
-    <col width="9.140625" customWidth="1" style="82" min="3593" max="3595"/>
-    <col width="14.140625" customWidth="1" style="82" min="3596" max="3596"/>
-    <col width="9.140625" customWidth="1" style="82" min="3597" max="3840"/>
-    <col width="2" customWidth="1" style="82" min="3841" max="3841"/>
-    <col width="5.85546875" customWidth="1" style="82" min="3842" max="3842"/>
-    <col width="38.5703125" customWidth="1" style="82" min="3843" max="3843"/>
-    <col width="10" customWidth="1" style="82" min="3844" max="3844"/>
-    <col width="21.5703125" customWidth="1" style="82" min="3845" max="3845"/>
-    <col width="22.7109375" customWidth="1" style="82" min="3846" max="3846"/>
-    <col width="0.28515625" customWidth="1" style="82" min="3847" max="3847"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="3848" max="3848"/>
-    <col width="9.140625" customWidth="1" style="82" min="3849" max="3851"/>
-    <col width="14.140625" customWidth="1" style="82" min="3852" max="3852"/>
-    <col width="9.140625" customWidth="1" style="82" min="3853" max="4096"/>
-    <col width="2" customWidth="1" style="82" min="4097" max="4097"/>
-    <col width="5.85546875" customWidth="1" style="82" min="4098" max="4098"/>
-    <col width="38.5703125" customWidth="1" style="82" min="4099" max="4099"/>
-    <col width="10" customWidth="1" style="82" min="4100" max="4100"/>
-    <col width="21.5703125" customWidth="1" style="82" min="4101" max="4101"/>
-    <col width="22.7109375" customWidth="1" style="82" min="4102" max="4102"/>
-    <col width="0.28515625" customWidth="1" style="82" min="4103" max="4103"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="4104" max="4104"/>
-    <col width="9.140625" customWidth="1" style="82" min="4105" max="4107"/>
-    <col width="14.140625" customWidth="1" style="82" min="4108" max="4108"/>
-    <col width="9.140625" customWidth="1" style="82" min="4109" max="4352"/>
-    <col width="2" customWidth="1" style="82" min="4353" max="4353"/>
-    <col width="5.85546875" customWidth="1" style="82" min="4354" max="4354"/>
-    <col width="38.5703125" customWidth="1" style="82" min="4355" max="4355"/>
-    <col width="10" customWidth="1" style="82" min="4356" max="4356"/>
-    <col width="21.5703125" customWidth="1" style="82" min="4357" max="4357"/>
-    <col width="22.7109375" customWidth="1" style="82" min="4358" max="4358"/>
-    <col width="0.28515625" customWidth="1" style="82" min="4359" max="4359"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="4360" max="4360"/>
-    <col width="9.140625" customWidth="1" style="82" min="4361" max="4363"/>
-    <col width="14.140625" customWidth="1" style="82" min="4364" max="4364"/>
-    <col width="9.140625" customWidth="1" style="82" min="4365" max="4608"/>
-    <col width="2" customWidth="1" style="82" min="4609" max="4609"/>
-    <col width="5.85546875" customWidth="1" style="82" min="4610" max="4610"/>
-    <col width="38.5703125" customWidth="1" style="82" min="4611" max="4611"/>
-    <col width="10" customWidth="1" style="82" min="4612" max="4612"/>
-    <col width="21.5703125" customWidth="1" style="82" min="4613" max="4613"/>
-    <col width="22.7109375" customWidth="1" style="82" min="4614" max="4614"/>
-    <col width="0.28515625" customWidth="1" style="82" min="4615" max="4615"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="4616" max="4616"/>
-    <col width="9.140625" customWidth="1" style="82" min="4617" max="4619"/>
-    <col width="14.140625" customWidth="1" style="82" min="4620" max="4620"/>
-    <col width="9.140625" customWidth="1" style="82" min="4621" max="4864"/>
-    <col width="2" customWidth="1" style="82" min="4865" max="4865"/>
-    <col width="5.85546875" customWidth="1" style="82" min="4866" max="4866"/>
-    <col width="38.5703125" customWidth="1" style="82" min="4867" max="4867"/>
-    <col width="10" customWidth="1" style="82" min="4868" max="4868"/>
-    <col width="21.5703125" customWidth="1" style="82" min="4869" max="4869"/>
-    <col width="22.7109375" customWidth="1" style="82" min="4870" max="4870"/>
-    <col width="0.28515625" customWidth="1" style="82" min="4871" max="4871"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="4872" max="4872"/>
-    <col width="9.140625" customWidth="1" style="82" min="4873" max="4875"/>
-    <col width="14.140625" customWidth="1" style="82" min="4876" max="4876"/>
-    <col width="9.140625" customWidth="1" style="82" min="4877" max="5120"/>
-    <col width="2" customWidth="1" style="82" min="5121" max="5121"/>
-    <col width="5.85546875" customWidth="1" style="82" min="5122" max="5122"/>
-    <col width="38.5703125" customWidth="1" style="82" min="5123" max="5123"/>
-    <col width="10" customWidth="1" style="82" min="5124" max="5124"/>
-    <col width="21.5703125" customWidth="1" style="82" min="5125" max="5125"/>
-    <col width="22.7109375" customWidth="1" style="82" min="5126" max="5126"/>
-    <col width="0.28515625" customWidth="1" style="82" min="5127" max="5127"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="5128" max="5128"/>
-    <col width="9.140625" customWidth="1" style="82" min="5129" max="5131"/>
-    <col width="14.140625" customWidth="1" style="82" min="5132" max="5132"/>
-    <col width="9.140625" customWidth="1" style="82" min="5133" max="5376"/>
-    <col width="2" customWidth="1" style="82" min="5377" max="5377"/>
-    <col width="5.85546875" customWidth="1" style="82" min="5378" max="5378"/>
-    <col width="38.5703125" customWidth="1" style="82" min="5379" max="5379"/>
-    <col width="10" customWidth="1" style="82" min="5380" max="5380"/>
-    <col width="21.5703125" customWidth="1" style="82" min="5381" max="5381"/>
-    <col width="22.7109375" customWidth="1" style="82" min="5382" max="5382"/>
-    <col width="0.28515625" customWidth="1" style="82" min="5383" max="5383"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="5384" max="5384"/>
-    <col width="9.140625" customWidth="1" style="82" min="5385" max="5387"/>
-    <col width="14.140625" customWidth="1" style="82" min="5388" max="5388"/>
-    <col width="9.140625" customWidth="1" style="82" min="5389" max="5632"/>
-    <col width="2" customWidth="1" style="82" min="5633" max="5633"/>
-    <col width="5.85546875" customWidth="1" style="82" min="5634" max="5634"/>
-    <col width="38.5703125" customWidth="1" style="82" min="5635" max="5635"/>
-    <col width="10" customWidth="1" style="82" min="5636" max="5636"/>
-    <col width="21.5703125" customWidth="1" style="82" min="5637" max="5637"/>
-    <col width="22.7109375" customWidth="1" style="82" min="5638" max="5638"/>
-    <col width="0.28515625" customWidth="1" style="82" min="5639" max="5639"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="5640" max="5640"/>
-    <col width="9.140625" customWidth="1" style="82" min="5641" max="5643"/>
-    <col width="14.140625" customWidth="1" style="82" min="5644" max="5644"/>
-    <col width="9.140625" customWidth="1" style="82" min="5645" max="5888"/>
-    <col width="2" customWidth="1" style="82" min="5889" max="5889"/>
-    <col width="5.85546875" customWidth="1" style="82" min="5890" max="5890"/>
-    <col width="38.5703125" customWidth="1" style="82" min="5891" max="5891"/>
-    <col width="10" customWidth="1" style="82" min="5892" max="5892"/>
-    <col width="21.5703125" customWidth="1" style="82" min="5893" max="5893"/>
-    <col width="22.7109375" customWidth="1" style="82" min="5894" max="5894"/>
-    <col width="0.28515625" customWidth="1" style="82" min="5895" max="5895"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="5896" max="5896"/>
-    <col width="9.140625" customWidth="1" style="82" min="5897" max="5899"/>
-    <col width="14.140625" customWidth="1" style="82" min="5900" max="5900"/>
-    <col width="9.140625" customWidth="1" style="82" min="5901" max="6144"/>
-    <col width="2" customWidth="1" style="82" min="6145" max="6145"/>
-    <col width="5.85546875" customWidth="1" style="82" min="6146" max="6146"/>
-    <col width="38.5703125" customWidth="1" style="82" min="6147" max="6147"/>
-    <col width="10" customWidth="1" style="82" min="6148" max="6148"/>
-    <col width="21.5703125" customWidth="1" style="82" min="6149" max="6149"/>
-    <col width="22.7109375" customWidth="1" style="82" min="6150" max="6150"/>
-    <col width="0.28515625" customWidth="1" style="82" min="6151" max="6151"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="6152" max="6152"/>
-    <col width="9.140625" customWidth="1" style="82" min="6153" max="6155"/>
-    <col width="14.140625" customWidth="1" style="82" min="6156" max="6156"/>
-    <col width="9.140625" customWidth="1" style="82" min="6157" max="6400"/>
-    <col width="2" customWidth="1" style="82" min="6401" max="6401"/>
-    <col width="5.85546875" customWidth="1" style="82" min="6402" max="6402"/>
-    <col width="38.5703125" customWidth="1" style="82" min="6403" max="6403"/>
-    <col width="10" customWidth="1" style="82" min="6404" max="6404"/>
-    <col width="21.5703125" customWidth="1" style="82" min="6405" max="6405"/>
-    <col width="22.7109375" customWidth="1" style="82" min="6406" max="6406"/>
-    <col width="0.28515625" customWidth="1" style="82" min="6407" max="6407"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="6408" max="6408"/>
-    <col width="9.140625" customWidth="1" style="82" min="6409" max="6411"/>
-    <col width="14.140625" customWidth="1" style="82" min="6412" max="6412"/>
-    <col width="9.140625" customWidth="1" style="82" min="6413" max="6656"/>
-    <col width="2" customWidth="1" style="82" min="6657" max="6657"/>
-    <col width="5.85546875" customWidth="1" style="82" min="6658" max="6658"/>
-    <col width="38.5703125" customWidth="1" style="82" min="6659" max="6659"/>
-    <col width="10" customWidth="1" style="82" min="6660" max="6660"/>
-    <col width="21.5703125" customWidth="1" style="82" min="6661" max="6661"/>
-    <col width="22.7109375" customWidth="1" style="82" min="6662" max="6662"/>
-    <col width="0.28515625" customWidth="1" style="82" min="6663" max="6663"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="6664" max="6664"/>
-    <col width="9.140625" customWidth="1" style="82" min="6665" max="6667"/>
-    <col width="14.140625" customWidth="1" style="82" min="6668" max="6668"/>
-    <col width="9.140625" customWidth="1" style="82" min="6669" max="6912"/>
-    <col width="2" customWidth="1" style="82" min="6913" max="6913"/>
-    <col width="5.85546875" customWidth="1" style="82" min="6914" max="6914"/>
-    <col width="38.5703125" customWidth="1" style="82" min="6915" max="6915"/>
-    <col width="10" customWidth="1" style="82" min="6916" max="6916"/>
-    <col width="21.5703125" customWidth="1" style="82" min="6917" max="6917"/>
-    <col width="22.7109375" customWidth="1" style="82" min="6918" max="6918"/>
-    <col width="0.28515625" customWidth="1" style="82" min="6919" max="6919"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="6920" max="6920"/>
-    <col width="9.140625" customWidth="1" style="82" min="6921" max="6923"/>
-    <col width="14.140625" customWidth="1" style="82" min="6924" max="6924"/>
-    <col width="9.140625" customWidth="1" style="82" min="6925" max="7168"/>
-    <col width="2" customWidth="1" style="82" min="7169" max="7169"/>
-    <col width="5.85546875" customWidth="1" style="82" min="7170" max="7170"/>
-    <col width="38.5703125" customWidth="1" style="82" min="7171" max="7171"/>
-    <col width="10" customWidth="1" style="82" min="7172" max="7172"/>
-    <col width="21.5703125" customWidth="1" style="82" min="7173" max="7173"/>
-    <col width="22.7109375" customWidth="1" style="82" min="7174" max="7174"/>
-    <col width="0.28515625" customWidth="1" style="82" min="7175" max="7175"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="7176" max="7176"/>
-    <col width="9.140625" customWidth="1" style="82" min="7177" max="7179"/>
-    <col width="14.140625" customWidth="1" style="82" min="7180" max="7180"/>
-    <col width="9.140625" customWidth="1" style="82" min="7181" max="7424"/>
-    <col width="2" customWidth="1" style="82" min="7425" max="7425"/>
-    <col width="5.85546875" customWidth="1" style="82" min="7426" max="7426"/>
-    <col width="38.5703125" customWidth="1" style="82" min="7427" max="7427"/>
-    <col width="10" customWidth="1" style="82" min="7428" max="7428"/>
-    <col width="21.5703125" customWidth="1" style="82" min="7429" max="7429"/>
-    <col width="22.7109375" customWidth="1" style="82" min="7430" max="7430"/>
-    <col width="0.28515625" customWidth="1" style="82" min="7431" max="7431"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="7432" max="7432"/>
-    <col width="9.140625" customWidth="1" style="82" min="7433" max="7435"/>
-    <col width="14.140625" customWidth="1" style="82" min="7436" max="7436"/>
-    <col width="9.140625" customWidth="1" style="82" min="7437" max="7680"/>
-    <col width="2" customWidth="1" style="82" min="7681" max="7681"/>
-    <col width="5.85546875" customWidth="1" style="82" min="7682" max="7682"/>
-    <col width="38.5703125" customWidth="1" style="82" min="7683" max="7683"/>
-    <col width="10" customWidth="1" style="82" min="7684" max="7684"/>
-    <col width="21.5703125" customWidth="1" style="82" min="7685" max="7685"/>
-    <col width="22.7109375" customWidth="1" style="82" min="7686" max="7686"/>
-    <col width="0.28515625" customWidth="1" style="82" min="7687" max="7687"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="7688" max="7688"/>
-    <col width="9.140625" customWidth="1" style="82" min="7689" max="7691"/>
-    <col width="14.140625" customWidth="1" style="82" min="7692" max="7692"/>
-    <col width="9.140625" customWidth="1" style="82" min="7693" max="7936"/>
-    <col width="2" customWidth="1" style="82" min="7937" max="7937"/>
-    <col width="5.85546875" customWidth="1" style="82" min="7938" max="7938"/>
-    <col width="38.5703125" customWidth="1" style="82" min="7939" max="7939"/>
-    <col width="10" customWidth="1" style="82" min="7940" max="7940"/>
-    <col width="21.5703125" customWidth="1" style="82" min="7941" max="7941"/>
-    <col width="22.7109375" customWidth="1" style="82" min="7942" max="7942"/>
-    <col width="0.28515625" customWidth="1" style="82" min="7943" max="7943"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="7944" max="7944"/>
-    <col width="9.140625" customWidth="1" style="82" min="7945" max="7947"/>
-    <col width="14.140625" customWidth="1" style="82" min="7948" max="7948"/>
-    <col width="9.140625" customWidth="1" style="82" min="7949" max="8192"/>
-    <col width="2" customWidth="1" style="82" min="8193" max="8193"/>
-    <col width="5.85546875" customWidth="1" style="82" min="8194" max="8194"/>
-    <col width="38.5703125" customWidth="1" style="82" min="8195" max="8195"/>
-    <col width="10" customWidth="1" style="82" min="8196" max="8196"/>
-    <col width="21.5703125" customWidth="1" style="82" min="8197" max="8197"/>
-    <col width="22.7109375" customWidth="1" style="82" min="8198" max="8198"/>
-    <col width="0.28515625" customWidth="1" style="82" min="8199" max="8199"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="8200" max="8200"/>
-    <col width="9.140625" customWidth="1" style="82" min="8201" max="8203"/>
-    <col width="14.140625" customWidth="1" style="82" min="8204" max="8204"/>
-    <col width="9.140625" customWidth="1" style="82" min="8205" max="8448"/>
-    <col width="2" customWidth="1" style="82" min="8449" max="8449"/>
-    <col width="5.85546875" customWidth="1" style="82" min="8450" max="8450"/>
-    <col width="38.5703125" customWidth="1" style="82" min="8451" max="8451"/>
-    <col width="10" customWidth="1" style="82" min="8452" max="8452"/>
-    <col width="21.5703125" customWidth="1" style="82" min="8453" max="8453"/>
-    <col width="22.7109375" customWidth="1" style="82" min="8454" max="8454"/>
-    <col width="0.28515625" customWidth="1" style="82" min="8455" max="8455"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="8456" max="8456"/>
-    <col width="9.140625" customWidth="1" style="82" min="8457" max="8459"/>
-    <col width="14.140625" customWidth="1" style="82" min="8460" max="8460"/>
-    <col width="9.140625" customWidth="1" style="82" min="8461" max="8704"/>
-    <col width="2" customWidth="1" style="82" min="8705" max="8705"/>
-    <col width="5.85546875" customWidth="1" style="82" min="8706" max="8706"/>
-    <col width="38.5703125" customWidth="1" style="82" min="8707" max="8707"/>
-    <col width="10" customWidth="1" style="82" min="8708" max="8708"/>
-    <col width="21.5703125" customWidth="1" style="82" min="8709" max="8709"/>
-    <col width="22.7109375" customWidth="1" style="82" min="8710" max="8710"/>
-    <col width="0.28515625" customWidth="1" style="82" min="8711" max="8711"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="8712" max="8712"/>
-    <col width="9.140625" customWidth="1" style="82" min="8713" max="8715"/>
-    <col width="14.140625" customWidth="1" style="82" min="8716" max="8716"/>
-    <col width="9.140625" customWidth="1" style="82" min="8717" max="8960"/>
-    <col width="2" customWidth="1" style="82" min="8961" max="8961"/>
-    <col width="5.85546875" customWidth="1" style="82" min="8962" max="8962"/>
-    <col width="38.5703125" customWidth="1" style="82" min="8963" max="8963"/>
-    <col width="10" customWidth="1" style="82" min="8964" max="8964"/>
-    <col width="21.5703125" customWidth="1" style="82" min="8965" max="8965"/>
-    <col width="22.7109375" customWidth="1" style="82" min="8966" max="8966"/>
-    <col width="0.28515625" customWidth="1" style="82" min="8967" max="8967"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="8968" max="8968"/>
-    <col width="9.140625" customWidth="1" style="82" min="8969" max="8971"/>
-    <col width="14.140625" customWidth="1" style="82" min="8972" max="8972"/>
-    <col width="9.140625" customWidth="1" style="82" min="8973" max="9216"/>
-    <col width="2" customWidth="1" style="82" min="9217" max="9217"/>
-    <col width="5.85546875" customWidth="1" style="82" min="9218" max="9218"/>
-    <col width="38.5703125" customWidth="1" style="82" min="9219" max="9219"/>
-    <col width="10" customWidth="1" style="82" min="9220" max="9220"/>
-    <col width="21.5703125" customWidth="1" style="82" min="9221" max="9221"/>
-    <col width="22.7109375" customWidth="1" style="82" min="9222" max="9222"/>
-    <col width="0.28515625" customWidth="1" style="82" min="9223" max="9223"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="9224" max="9224"/>
-    <col width="9.140625" customWidth="1" style="82" min="9225" max="9227"/>
-    <col width="14.140625" customWidth="1" style="82" min="9228" max="9228"/>
-    <col width="9.140625" customWidth="1" style="82" min="9229" max="9472"/>
-    <col width="2" customWidth="1" style="82" min="9473" max="9473"/>
-    <col width="5.85546875" customWidth="1" style="82" min="9474" max="9474"/>
-    <col width="38.5703125" customWidth="1" style="82" min="9475" max="9475"/>
-    <col width="10" customWidth="1" style="82" min="9476" max="9476"/>
-    <col width="21.5703125" customWidth="1" style="82" min="9477" max="9477"/>
-    <col width="22.7109375" customWidth="1" style="82" min="9478" max="9478"/>
-    <col width="0.28515625" customWidth="1" style="82" min="9479" max="9479"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="9480" max="9480"/>
-    <col width="9.140625" customWidth="1" style="82" min="9481" max="9483"/>
-    <col width="14.140625" customWidth="1" style="82" min="9484" max="9484"/>
-    <col width="9.140625" customWidth="1" style="82" min="9485" max="9728"/>
-    <col width="2" customWidth="1" style="82" min="9729" max="9729"/>
-    <col width="5.85546875" customWidth="1" style="82" min="9730" max="9730"/>
-    <col width="38.5703125" customWidth="1" style="82" min="9731" max="9731"/>
-    <col width="10" customWidth="1" style="82" min="9732" max="9732"/>
-    <col width="21.5703125" customWidth="1" style="82" min="9733" max="9733"/>
-    <col width="22.7109375" customWidth="1" style="82" min="9734" max="9734"/>
-    <col width="0.28515625" customWidth="1" style="82" min="9735" max="9735"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="9736" max="9736"/>
-    <col width="9.140625" customWidth="1" style="82" min="9737" max="9739"/>
-    <col width="14.140625" customWidth="1" style="82" min="9740" max="9740"/>
-    <col width="9.140625" customWidth="1" style="82" min="9741" max="9984"/>
-    <col width="2" customWidth="1" style="82" min="9985" max="9985"/>
-    <col width="5.85546875" customWidth="1" style="82" min="9986" max="9986"/>
-    <col width="38.5703125" customWidth="1" style="82" min="9987" max="9987"/>
-    <col width="10" customWidth="1" style="82" min="9988" max="9988"/>
-    <col width="21.5703125" customWidth="1" style="82" min="9989" max="9989"/>
-    <col width="22.7109375" customWidth="1" style="82" min="9990" max="9990"/>
-    <col width="0.28515625" customWidth="1" style="82" min="9991" max="9991"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="9992" max="9992"/>
-    <col width="9.140625" customWidth="1" style="82" min="9993" max="9995"/>
-    <col width="14.140625" customWidth="1" style="82" min="9996" max="9996"/>
-    <col width="9.140625" customWidth="1" style="82" min="9997" max="10240"/>
-    <col width="2" customWidth="1" style="82" min="10241" max="10241"/>
-    <col width="5.85546875" customWidth="1" style="82" min="10242" max="10242"/>
-    <col width="38.5703125" customWidth="1" style="82" min="10243" max="10243"/>
-    <col width="10" customWidth="1" style="82" min="10244" max="10244"/>
-    <col width="21.5703125" customWidth="1" style="82" min="10245" max="10245"/>
-    <col width="22.7109375" customWidth="1" style="82" min="10246" max="10246"/>
-    <col width="0.28515625" customWidth="1" style="82" min="10247" max="10247"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="10248" max="10248"/>
-    <col width="9.140625" customWidth="1" style="82" min="10249" max="10251"/>
-    <col width="14.140625" customWidth="1" style="82" min="10252" max="10252"/>
-    <col width="9.140625" customWidth="1" style="82" min="10253" max="10496"/>
-    <col width="2" customWidth="1" style="82" min="10497" max="10497"/>
-    <col width="5.85546875" customWidth="1" style="82" min="10498" max="10498"/>
-    <col width="38.5703125" customWidth="1" style="82" min="10499" max="10499"/>
-    <col width="10" customWidth="1" style="82" min="10500" max="10500"/>
-    <col width="21.5703125" customWidth="1" style="82" min="10501" max="10501"/>
-    <col width="22.7109375" customWidth="1" style="82" min="10502" max="10502"/>
-    <col width="0.28515625" customWidth="1" style="82" min="10503" max="10503"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="10504" max="10504"/>
-    <col width="9.140625" customWidth="1" style="82" min="10505" max="10507"/>
-    <col width="14.140625" customWidth="1" style="82" min="10508" max="10508"/>
-    <col width="9.140625" customWidth="1" style="82" min="10509" max="10752"/>
-    <col width="2" customWidth="1" style="82" min="10753" max="10753"/>
-    <col width="5.85546875" customWidth="1" style="82" min="10754" max="10754"/>
-    <col width="38.5703125" customWidth="1" style="82" min="10755" max="10755"/>
-    <col width="10" customWidth="1" style="82" min="10756" max="10756"/>
-    <col width="21.5703125" customWidth="1" style="82" min="10757" max="10757"/>
-    <col width="22.7109375" customWidth="1" style="82" min="10758" max="10758"/>
-    <col width="0.28515625" customWidth="1" style="82" min="10759" max="10759"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="10760" max="10760"/>
-    <col width="9.140625" customWidth="1" style="82" min="10761" max="10763"/>
-    <col width="14.140625" customWidth="1" style="82" min="10764" max="10764"/>
-    <col width="9.140625" customWidth="1" style="82" min="10765" max="11008"/>
-    <col width="2" customWidth="1" style="82" min="11009" max="11009"/>
-    <col width="5.85546875" customWidth="1" style="82" min="11010" max="11010"/>
-    <col width="38.5703125" customWidth="1" style="82" min="11011" max="11011"/>
-    <col width="10" customWidth="1" style="82" min="11012" max="11012"/>
-    <col width="21.5703125" customWidth="1" style="82" min="11013" max="11013"/>
-    <col width="22.7109375" customWidth="1" style="82" min="11014" max="11014"/>
-    <col width="0.28515625" customWidth="1" style="82" min="11015" max="11015"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="11016" max="11016"/>
-    <col width="9.140625" customWidth="1" style="82" min="11017" max="11019"/>
-    <col width="14.140625" customWidth="1" style="82" min="11020" max="11020"/>
-    <col width="9.140625" customWidth="1" style="82" min="11021" max="11264"/>
-    <col width="2" customWidth="1" style="82" min="11265" max="11265"/>
-    <col width="5.85546875" customWidth="1" style="82" min="11266" max="11266"/>
-    <col width="38.5703125" customWidth="1" style="82" min="11267" max="11267"/>
-    <col width="10" customWidth="1" style="82" min="11268" max="11268"/>
-    <col width="21.5703125" customWidth="1" style="82" min="11269" max="11269"/>
-    <col width="22.7109375" customWidth="1" style="82" min="11270" max="11270"/>
-    <col width="0.28515625" customWidth="1" style="82" min="11271" max="11271"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="11272" max="11272"/>
-    <col width="9.140625" customWidth="1" style="82" min="11273" max="11275"/>
-    <col width="14.140625" customWidth="1" style="82" min="11276" max="11276"/>
-    <col width="9.140625" customWidth="1" style="82" min="11277" max="11520"/>
-    <col width="2" customWidth="1" style="82" min="11521" max="11521"/>
-    <col width="5.85546875" customWidth="1" style="82" min="11522" max="11522"/>
-    <col width="38.5703125" customWidth="1" style="82" min="11523" max="11523"/>
-    <col width="10" customWidth="1" style="82" min="11524" max="11524"/>
-    <col width="21.5703125" customWidth="1" style="82" min="11525" max="11525"/>
-    <col width="22.7109375" customWidth="1" style="82" min="11526" max="11526"/>
-    <col width="0.28515625" customWidth="1" style="82" min="11527" max="11527"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="11528" max="11528"/>
-    <col width="9.140625" customWidth="1" style="82" min="11529" max="11531"/>
-    <col width="14.140625" customWidth="1" style="82" min="11532" max="11532"/>
-    <col width="9.140625" customWidth="1" style="82" min="11533" max="11776"/>
-    <col width="2" customWidth="1" style="82" min="11777" max="11777"/>
-    <col width="5.85546875" customWidth="1" style="82" min="11778" max="11778"/>
-    <col width="38.5703125" customWidth="1" style="82" min="11779" max="11779"/>
-    <col width="10" customWidth="1" style="82" min="11780" max="11780"/>
-    <col width="21.5703125" customWidth="1" style="82" min="11781" max="11781"/>
-    <col width="22.7109375" customWidth="1" style="82" min="11782" max="11782"/>
-    <col width="0.28515625" customWidth="1" style="82" min="11783" max="11783"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="11784" max="11784"/>
-    <col width="9.140625" customWidth="1" style="82" min="11785" max="11787"/>
-    <col width="14.140625" customWidth="1" style="82" min="11788" max="11788"/>
-    <col width="9.140625" customWidth="1" style="82" min="11789" max="12032"/>
-    <col width="2" customWidth="1" style="82" min="12033" max="12033"/>
-    <col width="5.85546875" customWidth="1" style="82" min="12034" max="12034"/>
-    <col width="38.5703125" customWidth="1" style="82" min="12035" max="12035"/>
-    <col width="10" customWidth="1" style="82" min="12036" max="12036"/>
-    <col width="21.5703125" customWidth="1" style="82" min="12037" max="12037"/>
-    <col width="22.7109375" customWidth="1" style="82" min="12038" max="12038"/>
-    <col width="0.28515625" customWidth="1" style="82" min="12039" max="12039"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="12040" max="12040"/>
-    <col width="9.140625" customWidth="1" style="82" min="12041" max="12043"/>
-    <col width="14.140625" customWidth="1" style="82" min="12044" max="12044"/>
-    <col width="9.140625" customWidth="1" style="82" min="12045" max="12288"/>
-    <col width="2" customWidth="1" style="82" min="12289" max="12289"/>
-    <col width="5.85546875" customWidth="1" style="82" min="12290" max="12290"/>
-    <col width="38.5703125" customWidth="1" style="82" min="12291" max="12291"/>
-    <col width="10" customWidth="1" style="82" min="12292" max="12292"/>
-    <col width="21.5703125" customWidth="1" style="82" min="12293" max="12293"/>
-    <col width="22.7109375" customWidth="1" style="82" min="12294" max="12294"/>
-    <col width="0.28515625" customWidth="1" style="82" min="12295" max="12295"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="12296" max="12296"/>
-    <col width="9.140625" customWidth="1" style="82" min="12297" max="12299"/>
-    <col width="14.140625" customWidth="1" style="82" min="12300" max="12300"/>
-    <col width="9.140625" customWidth="1" style="82" min="12301" max="12544"/>
-    <col width="2" customWidth="1" style="82" min="12545" max="12545"/>
-    <col width="5.85546875" customWidth="1" style="82" min="12546" max="12546"/>
-    <col width="38.5703125" customWidth="1" style="82" min="12547" max="12547"/>
-    <col width="10" customWidth="1" style="82" min="12548" max="12548"/>
-    <col width="21.5703125" customWidth="1" style="82" min="12549" max="12549"/>
-    <col width="22.7109375" customWidth="1" style="82" min="12550" max="12550"/>
-    <col width="0.28515625" customWidth="1" style="82" min="12551" max="12551"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="12552" max="12552"/>
-    <col width="9.140625" customWidth="1" style="82" min="12553" max="12555"/>
-    <col width="14.140625" customWidth="1" style="82" min="12556" max="12556"/>
-    <col width="9.140625" customWidth="1" style="82" min="12557" max="12800"/>
-    <col width="2" customWidth="1" style="82" min="12801" max="12801"/>
-    <col width="5.85546875" customWidth="1" style="82" min="12802" max="12802"/>
-    <col width="38.5703125" customWidth="1" style="82" min="12803" max="12803"/>
-    <col width="10" customWidth="1" style="82" min="12804" max="12804"/>
-    <col width="21.5703125" customWidth="1" style="82" min="12805" max="12805"/>
-    <col width="22.7109375" customWidth="1" style="82" min="12806" max="12806"/>
-    <col width="0.28515625" customWidth="1" style="82" min="12807" max="12807"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="12808" max="12808"/>
-    <col width="9.140625" customWidth="1" style="82" min="12809" max="12811"/>
-    <col width="14.140625" customWidth="1" style="82" min="12812" max="12812"/>
-    <col width="9.140625" customWidth="1" style="82" min="12813" max="13056"/>
-    <col width="2" customWidth="1" style="82" min="13057" max="13057"/>
-    <col width="5.85546875" customWidth="1" style="82" min="13058" max="13058"/>
-    <col width="38.5703125" customWidth="1" style="82" min="13059" max="13059"/>
-    <col width="10" customWidth="1" style="82" min="13060" max="13060"/>
-    <col width="21.5703125" customWidth="1" style="82" min="13061" max="13061"/>
-    <col width="22.7109375" customWidth="1" style="82" min="13062" max="13062"/>
-    <col width="0.28515625" customWidth="1" style="82" min="13063" max="13063"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="13064" max="13064"/>
-    <col width="9.140625" customWidth="1" style="82" min="13065" max="13067"/>
-    <col width="14.140625" customWidth="1" style="82" min="13068" max="13068"/>
-    <col width="9.140625" customWidth="1" style="82" min="13069" max="13312"/>
-    <col width="2" customWidth="1" style="82" min="13313" max="13313"/>
-    <col width="5.85546875" customWidth="1" style="82" min="13314" max="13314"/>
-    <col width="38.5703125" customWidth="1" style="82" min="13315" max="13315"/>
-    <col width="10" customWidth="1" style="82" min="13316" max="13316"/>
-    <col width="21.5703125" customWidth="1" style="82" min="13317" max="13317"/>
-    <col width="22.7109375" customWidth="1" style="82" min="13318" max="13318"/>
-    <col width="0.28515625" customWidth="1" style="82" min="13319" max="13319"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="13320" max="13320"/>
-    <col width="9.140625" customWidth="1" style="82" min="13321" max="13323"/>
-    <col width="14.140625" customWidth="1" style="82" min="13324" max="13324"/>
-    <col width="9.140625" customWidth="1" style="82" min="13325" max="13568"/>
-    <col width="2" customWidth="1" style="82" min="13569" max="13569"/>
-    <col width="5.85546875" customWidth="1" style="82" min="13570" max="13570"/>
-    <col width="38.5703125" customWidth="1" style="82" min="13571" max="13571"/>
-    <col width="10" customWidth="1" style="82" min="13572" max="13572"/>
-    <col width="21.5703125" customWidth="1" style="82" min="13573" max="13573"/>
-    <col width="22.7109375" customWidth="1" style="82" min="13574" max="13574"/>
-    <col width="0.28515625" customWidth="1" style="82" min="13575" max="13575"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="13576" max="13576"/>
-    <col width="9.140625" customWidth="1" style="82" min="13577" max="13579"/>
-    <col width="14.140625" customWidth="1" style="82" min="13580" max="13580"/>
-    <col width="9.140625" customWidth="1" style="82" min="13581" max="13824"/>
-    <col width="2" customWidth="1" style="82" min="13825" max="13825"/>
-    <col width="5.85546875" customWidth="1" style="82" min="13826" max="13826"/>
-    <col width="38.5703125" customWidth="1" style="82" min="13827" max="13827"/>
-    <col width="10" customWidth="1" style="82" min="13828" max="13828"/>
-    <col width="21.5703125" customWidth="1" style="82" min="13829" max="13829"/>
-    <col width="22.7109375" customWidth="1" style="82" min="13830" max="13830"/>
-    <col width="0.28515625" customWidth="1" style="82" min="13831" max="13831"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="13832" max="13832"/>
-    <col width="9.140625" customWidth="1" style="82" min="13833" max="13835"/>
-    <col width="14.140625" customWidth="1" style="82" min="13836" max="13836"/>
-    <col width="9.140625" customWidth="1" style="82" min="13837" max="14080"/>
-    <col width="2" customWidth="1" style="82" min="14081" max="14081"/>
-    <col width="5.85546875" customWidth="1" style="82" min="14082" max="14082"/>
-    <col width="38.5703125" customWidth="1" style="82" min="14083" max="14083"/>
-    <col width="10" customWidth="1" style="82" min="14084" max="14084"/>
-    <col width="21.5703125" customWidth="1" style="82" min="14085" max="14085"/>
-    <col width="22.7109375" customWidth="1" style="82" min="14086" max="14086"/>
-    <col width="0.28515625" customWidth="1" style="82" min="14087" max="14087"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="14088" max="14088"/>
-    <col width="9.140625" customWidth="1" style="82" min="14089" max="14091"/>
-    <col width="14.140625" customWidth="1" style="82" min="14092" max="14092"/>
-    <col width="9.140625" customWidth="1" style="82" min="14093" max="14336"/>
-    <col width="2" customWidth="1" style="82" min="14337" max="14337"/>
-    <col width="5.85546875" customWidth="1" style="82" min="14338" max="14338"/>
-    <col width="38.5703125" customWidth="1" style="82" min="14339" max="14339"/>
-    <col width="10" customWidth="1" style="82" min="14340" max="14340"/>
-    <col width="21.5703125" customWidth="1" style="82" min="14341" max="14341"/>
-    <col width="22.7109375" customWidth="1" style="82" min="14342" max="14342"/>
-    <col width="0.28515625" customWidth="1" style="82" min="14343" max="14343"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="14344" max="14344"/>
-    <col width="9.140625" customWidth="1" style="82" min="14345" max="14347"/>
-    <col width="14.140625" customWidth="1" style="82" min="14348" max="14348"/>
-    <col width="9.140625" customWidth="1" style="82" min="14349" max="14592"/>
-    <col width="2" customWidth="1" style="82" min="14593" max="14593"/>
-    <col width="5.85546875" customWidth="1" style="82" min="14594" max="14594"/>
-    <col width="38.5703125" customWidth="1" style="82" min="14595" max="14595"/>
-    <col width="10" customWidth="1" style="82" min="14596" max="14596"/>
-    <col width="21.5703125" customWidth="1" style="82" min="14597" max="14597"/>
-    <col width="22.7109375" customWidth="1" style="82" min="14598" max="14598"/>
-    <col width="0.28515625" customWidth="1" style="82" min="14599" max="14599"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="14600" max="14600"/>
-    <col width="9.140625" customWidth="1" style="82" min="14601" max="14603"/>
-    <col width="14.140625" customWidth="1" style="82" min="14604" max="14604"/>
-    <col width="9.140625" customWidth="1" style="82" min="14605" max="14848"/>
-    <col width="2" customWidth="1" style="82" min="14849" max="14849"/>
-    <col width="5.85546875" customWidth="1" style="82" min="14850" max="14850"/>
-    <col width="38.5703125" customWidth="1" style="82" min="14851" max="14851"/>
-    <col width="10" customWidth="1" style="82" min="14852" max="14852"/>
-    <col width="21.5703125" customWidth="1" style="82" min="14853" max="14853"/>
-    <col width="22.7109375" customWidth="1" style="82" min="14854" max="14854"/>
-    <col width="0.28515625" customWidth="1" style="82" min="14855" max="14855"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="14856" max="14856"/>
-    <col width="9.140625" customWidth="1" style="82" min="14857" max="14859"/>
-    <col width="14.140625" customWidth="1" style="82" min="14860" max="14860"/>
-    <col width="9.140625" customWidth="1" style="82" min="14861" max="15104"/>
-    <col width="2" customWidth="1" style="82" min="15105" max="15105"/>
-    <col width="5.85546875" customWidth="1" style="82" min="15106" max="15106"/>
-    <col width="38.5703125" customWidth="1" style="82" min="15107" max="15107"/>
-    <col width="10" customWidth="1" style="82" min="15108" max="15108"/>
-    <col width="21.5703125" customWidth="1" style="82" min="15109" max="15109"/>
-    <col width="22.7109375" customWidth="1" style="82" min="15110" max="15110"/>
-    <col width="0.28515625" customWidth="1" style="82" min="15111" max="15111"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="15112" max="15112"/>
-    <col width="9.140625" customWidth="1" style="82" min="15113" max="15115"/>
-    <col width="14.140625" customWidth="1" style="82" min="15116" max="15116"/>
-    <col width="9.140625" customWidth="1" style="82" min="15117" max="15360"/>
-    <col width="2" customWidth="1" style="82" min="15361" max="15361"/>
-    <col width="5.85546875" customWidth="1" style="82" min="15362" max="15362"/>
-    <col width="38.5703125" customWidth="1" style="82" min="15363" max="15363"/>
-    <col width="10" customWidth="1" style="82" min="15364" max="15364"/>
-    <col width="21.5703125" customWidth="1" style="82" min="15365" max="15365"/>
-    <col width="22.7109375" customWidth="1" style="82" min="15366" max="15366"/>
-    <col width="0.28515625" customWidth="1" style="82" min="15367" max="15367"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="15368" max="15368"/>
-    <col width="9.140625" customWidth="1" style="82" min="15369" max="15371"/>
-    <col width="14.140625" customWidth="1" style="82" min="15372" max="15372"/>
-    <col width="9.140625" customWidth="1" style="82" min="15373" max="15616"/>
-    <col width="2" customWidth="1" style="82" min="15617" max="15617"/>
-    <col width="5.85546875" customWidth="1" style="82" min="15618" max="15618"/>
-    <col width="38.5703125" customWidth="1" style="82" min="15619" max="15619"/>
-    <col width="10" customWidth="1" style="82" min="15620" max="15620"/>
-    <col width="21.5703125" customWidth="1" style="82" min="15621" max="15621"/>
-    <col width="22.7109375" customWidth="1" style="82" min="15622" max="15622"/>
-    <col width="0.28515625" customWidth="1" style="82" min="15623" max="15623"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="15624" max="15624"/>
-    <col width="9.140625" customWidth="1" style="82" min="15625" max="15627"/>
-    <col width="14.140625" customWidth="1" style="82" min="15628" max="15628"/>
-    <col width="9.140625" customWidth="1" style="82" min="15629" max="15872"/>
-    <col width="2" customWidth="1" style="82" min="15873" max="15873"/>
-    <col width="5.85546875" customWidth="1" style="82" min="15874" max="15874"/>
-    <col width="38.5703125" customWidth="1" style="82" min="15875" max="15875"/>
-    <col width="10" customWidth="1" style="82" min="15876" max="15876"/>
-    <col width="21.5703125" customWidth="1" style="82" min="15877" max="15877"/>
-    <col width="22.7109375" customWidth="1" style="82" min="15878" max="15878"/>
-    <col width="0.28515625" customWidth="1" style="82" min="15879" max="15879"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="15880" max="15880"/>
-    <col width="9.140625" customWidth="1" style="82" min="15881" max="15883"/>
-    <col width="14.140625" customWidth="1" style="82" min="15884" max="15884"/>
-    <col width="9.140625" customWidth="1" style="82" min="15885" max="16128"/>
-    <col width="2" customWidth="1" style="82" min="16129" max="16129"/>
-    <col width="5.85546875" customWidth="1" style="82" min="16130" max="16130"/>
-    <col width="38.5703125" customWidth="1" style="82" min="16131" max="16131"/>
-    <col width="10" customWidth="1" style="82" min="16132" max="16132"/>
-    <col width="21.5703125" customWidth="1" style="82" min="16133" max="16133"/>
-    <col width="22.7109375" customWidth="1" style="82" min="16134" max="16134"/>
-    <col width="0.28515625" customWidth="1" style="82" min="16135" max="16135"/>
-    <col hidden="1" width="13" customWidth="1" style="82" min="16136" max="16136"/>
-    <col width="9.140625" customWidth="1" style="82" min="16137" max="16139"/>
-    <col width="14.140625" customWidth="1" style="82" min="16140" max="16140"/>
-    <col width="9.140625" customWidth="1" style="82" min="16141" max="16384"/>
+    <col width="3.7109375" customWidth="1" style="84" min="1" max="1"/>
+    <col width="5.85546875" customWidth="1" style="84" min="2" max="2"/>
+    <col width="41.85546875" customWidth="1" style="84" min="3" max="3"/>
+    <col width="14.28515625" customWidth="1" style="84" min="4" max="4"/>
+    <col width="21.5703125" customWidth="1" style="84" min="5" max="5"/>
+    <col width="24.28515625" customWidth="1" style="84" min="6" max="6"/>
+    <col width="4.28515625" customWidth="1" style="84" min="7" max="7"/>
+    <col width="14.7109375" customWidth="1" style="84" min="8" max="8"/>
+    <col width="23" customWidth="1" style="84" min="9" max="9"/>
+    <col width="12.85546875" customWidth="1" style="84" min="10" max="10"/>
+    <col width="16.140625" customWidth="1" style="84" min="11" max="11"/>
+    <col width="14.140625" customWidth="1" style="84" min="12" max="12"/>
+    <col width="11" bestFit="1" customWidth="1" style="84" min="13" max="14"/>
+    <col width="9.140625" customWidth="1" style="84" min="15" max="256"/>
+    <col width="2" customWidth="1" style="84" min="257" max="257"/>
+    <col width="5.85546875" customWidth="1" style="84" min="258" max="258"/>
+    <col width="38.5703125" customWidth="1" style="84" min="259" max="259"/>
+    <col width="10" customWidth="1" style="84" min="260" max="260"/>
+    <col width="21.5703125" customWidth="1" style="84" min="261" max="261"/>
+    <col width="22.7109375" customWidth="1" style="84" min="262" max="262"/>
+    <col width="0.28515625" customWidth="1" style="84" min="263" max="263"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="264" max="264"/>
+    <col width="9.140625" customWidth="1" style="84" min="265" max="267"/>
+    <col width="14.140625" customWidth="1" style="84" min="268" max="268"/>
+    <col width="9.140625" customWidth="1" style="84" min="269" max="512"/>
+    <col width="2" customWidth="1" style="84" min="513" max="513"/>
+    <col width="5.85546875" customWidth="1" style="84" min="514" max="514"/>
+    <col width="38.5703125" customWidth="1" style="84" min="515" max="515"/>
+    <col width="10" customWidth="1" style="84" min="516" max="516"/>
+    <col width="21.5703125" customWidth="1" style="84" min="517" max="517"/>
+    <col width="22.7109375" customWidth="1" style="84" min="518" max="518"/>
+    <col width="0.28515625" customWidth="1" style="84" min="519" max="519"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="520" max="520"/>
+    <col width="9.140625" customWidth="1" style="84" min="521" max="523"/>
+    <col width="14.140625" customWidth="1" style="84" min="524" max="524"/>
+    <col width="9.140625" customWidth="1" style="84" min="525" max="768"/>
+    <col width="2" customWidth="1" style="84" min="769" max="769"/>
+    <col width="5.85546875" customWidth="1" style="84" min="770" max="770"/>
+    <col width="38.5703125" customWidth="1" style="84" min="771" max="771"/>
+    <col width="10" customWidth="1" style="84" min="772" max="772"/>
+    <col width="21.5703125" customWidth="1" style="84" min="773" max="773"/>
+    <col width="22.7109375" customWidth="1" style="84" min="774" max="774"/>
+    <col width="0.28515625" customWidth="1" style="84" min="775" max="775"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="776" max="776"/>
+    <col width="9.140625" customWidth="1" style="84" min="777" max="779"/>
+    <col width="14.140625" customWidth="1" style="84" min="780" max="780"/>
+    <col width="9.140625" customWidth="1" style="84" min="781" max="1024"/>
+    <col width="2" customWidth="1" style="84" min="1025" max="1025"/>
+    <col width="5.85546875" customWidth="1" style="84" min="1026" max="1026"/>
+    <col width="38.5703125" customWidth="1" style="84" min="1027" max="1027"/>
+    <col width="10" customWidth="1" style="84" min="1028" max="1028"/>
+    <col width="21.5703125" customWidth="1" style="84" min="1029" max="1029"/>
+    <col width="22.7109375" customWidth="1" style="84" min="1030" max="1030"/>
+    <col width="0.28515625" customWidth="1" style="84" min="1031" max="1031"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="1032" max="1032"/>
+    <col width="9.140625" customWidth="1" style="84" min="1033" max="1035"/>
+    <col width="14.140625" customWidth="1" style="84" min="1036" max="1036"/>
+    <col width="9.140625" customWidth="1" style="84" min="1037" max="1280"/>
+    <col width="2" customWidth="1" style="84" min="1281" max="1281"/>
+    <col width="5.85546875" customWidth="1" style="84" min="1282" max="1282"/>
+    <col width="38.5703125" customWidth="1" style="84" min="1283" max="1283"/>
+    <col width="10" customWidth="1" style="84" min="1284" max="1284"/>
+    <col width="21.5703125" customWidth="1" style="84" min="1285" max="1285"/>
+    <col width="22.7109375" customWidth="1" style="84" min="1286" max="1286"/>
+    <col width="0.28515625" customWidth="1" style="84" min="1287" max="1287"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="1288" max="1288"/>
+    <col width="9.140625" customWidth="1" style="84" min="1289" max="1291"/>
+    <col width="14.140625" customWidth="1" style="84" min="1292" max="1292"/>
+    <col width="9.140625" customWidth="1" style="84" min="1293" max="1536"/>
+    <col width="2" customWidth="1" style="84" min="1537" max="1537"/>
+    <col width="5.85546875" customWidth="1" style="84" min="1538" max="1538"/>
+    <col width="38.5703125" customWidth="1" style="84" min="1539" max="1539"/>
+    <col width="10" customWidth="1" style="84" min="1540" max="1540"/>
+    <col width="21.5703125" customWidth="1" style="84" min="1541" max="1541"/>
+    <col width="22.7109375" customWidth="1" style="84" min="1542" max="1542"/>
+    <col width="0.28515625" customWidth="1" style="84" min="1543" max="1543"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="1544" max="1544"/>
+    <col width="9.140625" customWidth="1" style="84" min="1545" max="1547"/>
+    <col width="14.140625" customWidth="1" style="84" min="1548" max="1548"/>
+    <col width="9.140625" customWidth="1" style="84" min="1549" max="1792"/>
+    <col width="2" customWidth="1" style="84" min="1793" max="1793"/>
+    <col width="5.85546875" customWidth="1" style="84" min="1794" max="1794"/>
+    <col width="38.5703125" customWidth="1" style="84" min="1795" max="1795"/>
+    <col width="10" customWidth="1" style="84" min="1796" max="1796"/>
+    <col width="21.5703125" customWidth="1" style="84" min="1797" max="1797"/>
+    <col width="22.7109375" customWidth="1" style="84" min="1798" max="1798"/>
+    <col width="0.28515625" customWidth="1" style="84" min="1799" max="1799"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="1800" max="1800"/>
+    <col width="9.140625" customWidth="1" style="84" min="1801" max="1803"/>
+    <col width="14.140625" customWidth="1" style="84" min="1804" max="1804"/>
+    <col width="9.140625" customWidth="1" style="84" min="1805" max="2048"/>
+    <col width="2" customWidth="1" style="84" min="2049" max="2049"/>
+    <col width="5.85546875" customWidth="1" style="84" min="2050" max="2050"/>
+    <col width="38.5703125" customWidth="1" style="84" min="2051" max="2051"/>
+    <col width="10" customWidth="1" style="84" min="2052" max="2052"/>
+    <col width="21.5703125" customWidth="1" style="84" min="2053" max="2053"/>
+    <col width="22.7109375" customWidth="1" style="84" min="2054" max="2054"/>
+    <col width="0.28515625" customWidth="1" style="84" min="2055" max="2055"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="2056" max="2056"/>
+    <col width="9.140625" customWidth="1" style="84" min="2057" max="2059"/>
+    <col width="14.140625" customWidth="1" style="84" min="2060" max="2060"/>
+    <col width="9.140625" customWidth="1" style="84" min="2061" max="2304"/>
+    <col width="2" customWidth="1" style="84" min="2305" max="2305"/>
+    <col width="5.85546875" customWidth="1" style="84" min="2306" max="2306"/>
+    <col width="38.5703125" customWidth="1" style="84" min="2307" max="2307"/>
+    <col width="10" customWidth="1" style="84" min="2308" max="2308"/>
+    <col width="21.5703125" customWidth="1" style="84" min="2309" max="2309"/>
+    <col width="22.7109375" customWidth="1" style="84" min="2310" max="2310"/>
+    <col width="0.28515625" customWidth="1" style="84" min="2311" max="2311"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="2312" max="2312"/>
+    <col width="9.140625" customWidth="1" style="84" min="2313" max="2315"/>
+    <col width="14.140625" customWidth="1" style="84" min="2316" max="2316"/>
+    <col width="9.140625" customWidth="1" style="84" min="2317" max="2560"/>
+    <col width="2" customWidth="1" style="84" min="2561" max="2561"/>
+    <col width="5.85546875" customWidth="1" style="84" min="2562" max="2562"/>
+    <col width="38.5703125" customWidth="1" style="84" min="2563" max="2563"/>
+    <col width="10" customWidth="1" style="84" min="2564" max="2564"/>
+    <col width="21.5703125" customWidth="1" style="84" min="2565" max="2565"/>
+    <col width="22.7109375" customWidth="1" style="84" min="2566" max="2566"/>
+    <col width="0.28515625" customWidth="1" style="84" min="2567" max="2567"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="2568" max="2568"/>
+    <col width="9.140625" customWidth="1" style="84" min="2569" max="2571"/>
+    <col width="14.140625" customWidth="1" style="84" min="2572" max="2572"/>
+    <col width="9.140625" customWidth="1" style="84" min="2573" max="2816"/>
+    <col width="2" customWidth="1" style="84" min="2817" max="2817"/>
+    <col width="5.85546875" customWidth="1" style="84" min="2818" max="2818"/>
+    <col width="38.5703125" customWidth="1" style="84" min="2819" max="2819"/>
+    <col width="10" customWidth="1" style="84" min="2820" max="2820"/>
+    <col width="21.5703125" customWidth="1" style="84" min="2821" max="2821"/>
+    <col width="22.7109375" customWidth="1" style="84" min="2822" max="2822"/>
+    <col width="0.28515625" customWidth="1" style="84" min="2823" max="2823"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="2824" max="2824"/>
+    <col width="9.140625" customWidth="1" style="84" min="2825" max="2827"/>
+    <col width="14.140625" customWidth="1" style="84" min="2828" max="2828"/>
+    <col width="9.140625" customWidth="1" style="84" min="2829" max="3072"/>
+    <col width="2" customWidth="1" style="84" min="3073" max="3073"/>
+    <col width="5.85546875" customWidth="1" style="84" min="3074" max="3074"/>
+    <col width="38.5703125" customWidth="1" style="84" min="3075" max="3075"/>
+    <col width="10" customWidth="1" style="84" min="3076" max="3076"/>
+    <col width="21.5703125" customWidth="1" style="84" min="3077" max="3077"/>
+    <col width="22.7109375" customWidth="1" style="84" min="3078" max="3078"/>
+    <col width="0.28515625" customWidth="1" style="84" min="3079" max="3079"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="3080" max="3080"/>
+    <col width="9.140625" customWidth="1" style="84" min="3081" max="3083"/>
+    <col width="14.140625" customWidth="1" style="84" min="3084" max="3084"/>
+    <col width="9.140625" customWidth="1" style="84" min="3085" max="3328"/>
+    <col width="2" customWidth="1" style="84" min="3329" max="3329"/>
+    <col width="5.85546875" customWidth="1" style="84" min="3330" max="3330"/>
+    <col width="38.5703125" customWidth="1" style="84" min="3331" max="3331"/>
+    <col width="10" customWidth="1" style="84" min="3332" max="3332"/>
+    <col width="21.5703125" customWidth="1" style="84" min="3333" max="3333"/>
+    <col width="22.7109375" customWidth="1" style="84" min="3334" max="3334"/>
+    <col width="0.28515625" customWidth="1" style="84" min="3335" max="3335"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="3336" max="3336"/>
+    <col width="9.140625" customWidth="1" style="84" min="3337" max="3339"/>
+    <col width="14.140625" customWidth="1" style="84" min="3340" max="3340"/>
+    <col width="9.140625" customWidth="1" style="84" min="3341" max="3584"/>
+    <col width="2" customWidth="1" style="84" min="3585" max="3585"/>
+    <col width="5.85546875" customWidth="1" style="84" min="3586" max="3586"/>
+    <col width="38.5703125" customWidth="1" style="84" min="3587" max="3587"/>
+    <col width="10" customWidth="1" style="84" min="3588" max="3588"/>
+    <col width="21.5703125" customWidth="1" style="84" min="3589" max="3589"/>
+    <col width="22.7109375" customWidth="1" style="84" min="3590" max="3590"/>
+    <col width="0.28515625" customWidth="1" style="84" min="3591" max="3591"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="3592" max="3592"/>
+    <col width="9.140625" customWidth="1" style="84" min="3593" max="3595"/>
+    <col width="14.140625" customWidth="1" style="84" min="3596" max="3596"/>
+    <col width="9.140625" customWidth="1" style="84" min="3597" max="3840"/>
+    <col width="2" customWidth="1" style="84" min="3841" max="3841"/>
+    <col width="5.85546875" customWidth="1" style="84" min="3842" max="3842"/>
+    <col width="38.5703125" customWidth="1" style="84" min="3843" max="3843"/>
+    <col width="10" customWidth="1" style="84" min="3844" max="3844"/>
+    <col width="21.5703125" customWidth="1" style="84" min="3845" max="3845"/>
+    <col width="22.7109375" customWidth="1" style="84" min="3846" max="3846"/>
+    <col width="0.28515625" customWidth="1" style="84" min="3847" max="3847"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="3848" max="3848"/>
+    <col width="9.140625" customWidth="1" style="84" min="3849" max="3851"/>
+    <col width="14.140625" customWidth="1" style="84" min="3852" max="3852"/>
+    <col width="9.140625" customWidth="1" style="84" min="3853" max="4096"/>
+    <col width="2" customWidth="1" style="84" min="4097" max="4097"/>
+    <col width="5.85546875" customWidth="1" style="84" min="4098" max="4098"/>
+    <col width="38.5703125" customWidth="1" style="84" min="4099" max="4099"/>
+    <col width="10" customWidth="1" style="84" min="4100" max="4100"/>
+    <col width="21.5703125" customWidth="1" style="84" min="4101" max="4101"/>
+    <col width="22.7109375" customWidth="1" style="84" min="4102" max="4102"/>
+    <col width="0.28515625" customWidth="1" style="84" min="4103" max="4103"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="4104" max="4104"/>
+    <col width="9.140625" customWidth="1" style="84" min="4105" max="4107"/>
+    <col width="14.140625" customWidth="1" style="84" min="4108" max="4108"/>
+    <col width="9.140625" customWidth="1" style="84" min="4109" max="4352"/>
+    <col width="2" customWidth="1" style="84" min="4353" max="4353"/>
+    <col width="5.85546875" customWidth="1" style="84" min="4354" max="4354"/>
+    <col width="38.5703125" customWidth="1" style="84" min="4355" max="4355"/>
+    <col width="10" customWidth="1" style="84" min="4356" max="4356"/>
+    <col width="21.5703125" customWidth="1" style="84" min="4357" max="4357"/>
+    <col width="22.7109375" customWidth="1" style="84" min="4358" max="4358"/>
+    <col width="0.28515625" customWidth="1" style="84" min="4359" max="4359"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="4360" max="4360"/>
+    <col width="9.140625" customWidth="1" style="84" min="4361" max="4363"/>
+    <col width="14.140625" customWidth="1" style="84" min="4364" max="4364"/>
+    <col width="9.140625" customWidth="1" style="84" min="4365" max="4608"/>
+    <col width="2" customWidth="1" style="84" min="4609" max="4609"/>
+    <col width="5.85546875" customWidth="1" style="84" min="4610" max="4610"/>
+    <col width="38.5703125" customWidth="1" style="84" min="4611" max="4611"/>
+    <col width="10" customWidth="1" style="84" min="4612" max="4612"/>
+    <col width="21.5703125" customWidth="1" style="84" min="4613" max="4613"/>
+    <col width="22.7109375" customWidth="1" style="84" min="4614" max="4614"/>
+    <col width="0.28515625" customWidth="1" style="84" min="4615" max="4615"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="4616" max="4616"/>
+    <col width="9.140625" customWidth="1" style="84" min="4617" max="4619"/>
+    <col width="14.140625" customWidth="1" style="84" min="4620" max="4620"/>
+    <col width="9.140625" customWidth="1" style="84" min="4621" max="4864"/>
+    <col width="2" customWidth="1" style="84" min="4865" max="4865"/>
+    <col width="5.85546875" customWidth="1" style="84" min="4866" max="4866"/>
+    <col width="38.5703125" customWidth="1" style="84" min="4867" max="4867"/>
+    <col width="10" customWidth="1" style="84" min="4868" max="4868"/>
+    <col width="21.5703125" customWidth="1" style="84" min="4869" max="4869"/>
+    <col width="22.7109375" customWidth="1" style="84" min="4870" max="4870"/>
+    <col width="0.28515625" customWidth="1" style="84" min="4871" max="4871"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="4872" max="4872"/>
+    <col width="9.140625" customWidth="1" style="84" min="4873" max="4875"/>
+    <col width="14.140625" customWidth="1" style="84" min="4876" max="4876"/>
+    <col width="9.140625" customWidth="1" style="84" min="4877" max="5120"/>
+    <col width="2" customWidth="1" style="84" min="5121" max="5121"/>
+    <col width="5.85546875" customWidth="1" style="84" min="5122" max="5122"/>
+    <col width="38.5703125" customWidth="1" style="84" min="5123" max="5123"/>
+    <col width="10" customWidth="1" style="84" min="5124" max="5124"/>
+    <col width="21.5703125" customWidth="1" style="84" min="5125" max="5125"/>
+    <col width="22.7109375" customWidth="1" style="84" min="5126" max="5126"/>
+    <col width="0.28515625" customWidth="1" style="84" min="5127" max="5127"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="5128" max="5128"/>
+    <col width="9.140625" customWidth="1" style="84" min="5129" max="5131"/>
+    <col width="14.140625" customWidth="1" style="84" min="5132" max="5132"/>
+    <col width="9.140625" customWidth="1" style="84" min="5133" max="5376"/>
+    <col width="2" customWidth="1" style="84" min="5377" max="5377"/>
+    <col width="5.85546875" customWidth="1" style="84" min="5378" max="5378"/>
+    <col width="38.5703125" customWidth="1" style="84" min="5379" max="5379"/>
+    <col width="10" customWidth="1" style="84" min="5380" max="5380"/>
+    <col width="21.5703125" customWidth="1" style="84" min="5381" max="5381"/>
+    <col width="22.7109375" customWidth="1" style="84" min="5382" max="5382"/>
+    <col width="0.28515625" customWidth="1" style="84" min="5383" max="5383"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="5384" max="5384"/>
+    <col width="9.140625" customWidth="1" style="84" min="5385" max="5387"/>
+    <col width="14.140625" customWidth="1" style="84" min="5388" max="5388"/>
+    <col width="9.140625" customWidth="1" style="84" min="5389" max="5632"/>
+    <col width="2" customWidth="1" style="84" min="5633" max="5633"/>
+    <col width="5.85546875" customWidth="1" style="84" min="5634" max="5634"/>
+    <col width="38.5703125" customWidth="1" style="84" min="5635" max="5635"/>
+    <col width="10" customWidth="1" style="84" min="5636" max="5636"/>
+    <col width="21.5703125" customWidth="1" style="84" min="5637" max="5637"/>
+    <col width="22.7109375" customWidth="1" style="84" min="5638" max="5638"/>
+    <col width="0.28515625" customWidth="1" style="84" min="5639" max="5639"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="5640" max="5640"/>
+    <col width="9.140625" customWidth="1" style="84" min="5641" max="5643"/>
+    <col width="14.140625" customWidth="1" style="84" min="5644" max="5644"/>
+    <col width="9.140625" customWidth="1" style="84" min="5645" max="5888"/>
+    <col width="2" customWidth="1" style="84" min="5889" max="5889"/>
+    <col width="5.85546875" customWidth="1" style="84" min="5890" max="5890"/>
+    <col width="38.5703125" customWidth="1" style="84" min="5891" max="5891"/>
+    <col width="10" customWidth="1" style="84" min="5892" max="5892"/>
+    <col width="21.5703125" customWidth="1" style="84" min="5893" max="5893"/>
+    <col width="22.7109375" customWidth="1" style="84" min="5894" max="5894"/>
+    <col width="0.28515625" customWidth="1" style="84" min="5895" max="5895"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="5896" max="5896"/>
+    <col width="9.140625" customWidth="1" style="84" min="5897" max="5899"/>
+    <col width="14.140625" customWidth="1" style="84" min="5900" max="5900"/>
+    <col width="9.140625" customWidth="1" style="84" min="5901" max="6144"/>
+    <col width="2" customWidth="1" style="84" min="6145" max="6145"/>
+    <col width="5.85546875" customWidth="1" style="84" min="6146" max="6146"/>
+    <col width="38.5703125" customWidth="1" style="84" min="6147" max="6147"/>
+    <col width="10" customWidth="1" style="84" min="6148" max="6148"/>
+    <col width="21.5703125" customWidth="1" style="84" min="6149" max="6149"/>
+    <col width="22.7109375" customWidth="1" style="84" min="6150" max="6150"/>
+    <col width="0.28515625" customWidth="1" style="84" min="6151" max="6151"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="6152" max="6152"/>
+    <col width="9.140625" customWidth="1" style="84" min="6153" max="6155"/>
+    <col width="14.140625" customWidth="1" style="84" min="6156" max="6156"/>
+    <col width="9.140625" customWidth="1" style="84" min="6157" max="6400"/>
+    <col width="2" customWidth="1" style="84" min="6401" max="6401"/>
+    <col width="5.85546875" customWidth="1" style="84" min="6402" max="6402"/>
+    <col width="38.5703125" customWidth="1" style="84" min="6403" max="6403"/>
+    <col width="10" customWidth="1" style="84" min="6404" max="6404"/>
+    <col width="21.5703125" customWidth="1" style="84" min="6405" max="6405"/>
+    <col width="22.7109375" customWidth="1" style="84" min="6406" max="6406"/>
+    <col width="0.28515625" customWidth="1" style="84" min="6407" max="6407"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="6408" max="6408"/>
+    <col width="9.140625" customWidth="1" style="84" min="6409" max="6411"/>
+    <col width="14.140625" customWidth="1" style="84" min="6412" max="6412"/>
+    <col width="9.140625" customWidth="1" style="84" min="6413" max="6656"/>
+    <col width="2" customWidth="1" style="84" min="6657" max="6657"/>
+    <col width="5.85546875" customWidth="1" style="84" min="6658" max="6658"/>
+    <col width="38.5703125" customWidth="1" style="84" min="6659" max="6659"/>
+    <col width="10" customWidth="1" style="84" min="6660" max="6660"/>
+    <col width="21.5703125" customWidth="1" style="84" min="6661" max="6661"/>
+    <col width="22.7109375" customWidth="1" style="84" min="6662" max="6662"/>
+    <col width="0.28515625" customWidth="1" style="84" min="6663" max="6663"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="6664" max="6664"/>
+    <col width="9.140625" customWidth="1" style="84" min="6665" max="6667"/>
+    <col width="14.140625" customWidth="1" style="84" min="6668" max="6668"/>
+    <col width="9.140625" customWidth="1" style="84" min="6669" max="6912"/>
+    <col width="2" customWidth="1" style="84" min="6913" max="6913"/>
+    <col width="5.85546875" customWidth="1" style="84" min="6914" max="6914"/>
+    <col width="38.5703125" customWidth="1" style="84" min="6915" max="6915"/>
+    <col width="10" customWidth="1" style="84" min="6916" max="6916"/>
+    <col width="21.5703125" customWidth="1" style="84" min="6917" max="6917"/>
+    <col width="22.7109375" customWidth="1" style="84" min="6918" max="6918"/>
+    <col width="0.28515625" customWidth="1" style="84" min="6919" max="6919"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="6920" max="6920"/>
+    <col width="9.140625" customWidth="1" style="84" min="6921" max="6923"/>
+    <col width="14.140625" customWidth="1" style="84" min="6924" max="6924"/>
+    <col width="9.140625" customWidth="1" style="84" min="6925" max="7168"/>
+    <col width="2" customWidth="1" style="84" min="7169" max="7169"/>
+    <col width="5.85546875" customWidth="1" style="84" min="7170" max="7170"/>
+    <col width="38.5703125" customWidth="1" style="84" min="7171" max="7171"/>
+    <col width="10" customWidth="1" style="84" min="7172" max="7172"/>
+    <col width="21.5703125" customWidth="1" style="84" min="7173" max="7173"/>
+    <col width="22.7109375" customWidth="1" style="84" min="7174" max="7174"/>
+    <col width="0.28515625" customWidth="1" style="84" min="7175" max="7175"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="7176" max="7176"/>
+    <col width="9.140625" customWidth="1" style="84" min="7177" max="7179"/>
+    <col width="14.140625" customWidth="1" style="84" min="7180" max="7180"/>
+    <col width="9.140625" customWidth="1" style="84" min="7181" max="7424"/>
+    <col width="2" customWidth="1" style="84" min="7425" max="7425"/>
+    <col width="5.85546875" customWidth="1" style="84" min="7426" max="7426"/>
+    <col width="38.5703125" customWidth="1" style="84" min="7427" max="7427"/>
+    <col width="10" customWidth="1" style="84" min="7428" max="7428"/>
+    <col width="21.5703125" customWidth="1" style="84" min="7429" max="7429"/>
+    <col width="22.7109375" customWidth="1" style="84" min="7430" max="7430"/>
+    <col width="0.28515625" customWidth="1" style="84" min="7431" max="7431"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="7432" max="7432"/>
+    <col width="9.140625" customWidth="1" style="84" min="7433" max="7435"/>
+    <col width="14.140625" customWidth="1" style="84" min="7436" max="7436"/>
+    <col width="9.140625" customWidth="1" style="84" min="7437" max="7680"/>
+    <col width="2" customWidth="1" style="84" min="7681" max="7681"/>
+    <col width="5.85546875" customWidth="1" style="84" min="7682" max="7682"/>
+    <col width="38.5703125" customWidth="1" style="84" min="7683" max="7683"/>
+    <col width="10" customWidth="1" style="84" min="7684" max="7684"/>
+    <col width="21.5703125" customWidth="1" style="84" min="7685" max="7685"/>
+    <col width="22.7109375" customWidth="1" style="84" min="7686" max="7686"/>
+    <col width="0.28515625" customWidth="1" style="84" min="7687" max="7687"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="7688" max="7688"/>
+    <col width="9.140625" customWidth="1" style="84" min="7689" max="7691"/>
+    <col width="14.140625" customWidth="1" style="84" min="7692" max="7692"/>
+    <col width="9.140625" customWidth="1" style="84" min="7693" max="7936"/>
+    <col width="2" customWidth="1" style="84" min="7937" max="7937"/>
+    <col width="5.85546875" customWidth="1" style="84" min="7938" max="7938"/>
+    <col width="38.5703125" customWidth="1" style="84" min="7939" max="7939"/>
+    <col width="10" customWidth="1" style="84" min="7940" max="7940"/>
+    <col width="21.5703125" customWidth="1" style="84" min="7941" max="7941"/>
+    <col width="22.7109375" customWidth="1" style="84" min="7942" max="7942"/>
+    <col width="0.28515625" customWidth="1" style="84" min="7943" max="7943"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="7944" max="7944"/>
+    <col width="9.140625" customWidth="1" style="84" min="7945" max="7947"/>
+    <col width="14.140625" customWidth="1" style="84" min="7948" max="7948"/>
+    <col width="9.140625" customWidth="1" style="84" min="7949" max="8192"/>
+    <col width="2" customWidth="1" style="84" min="8193" max="8193"/>
+    <col width="5.85546875" customWidth="1" style="84" min="8194" max="8194"/>
+    <col width="38.5703125" customWidth="1" style="84" min="8195" max="8195"/>
+    <col width="10" customWidth="1" style="84" min="8196" max="8196"/>
+    <col width="21.5703125" customWidth="1" style="84" min="8197" max="8197"/>
+    <col width="22.7109375" customWidth="1" style="84" min="8198" max="8198"/>
+    <col width="0.28515625" customWidth="1" style="84" min="8199" max="8199"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="8200" max="8200"/>
+    <col width="9.140625" customWidth="1" style="84" min="8201" max="8203"/>
+    <col width="14.140625" customWidth="1" style="84" min="8204" max="8204"/>
+    <col width="9.140625" customWidth="1" style="84" min="8205" max="8448"/>
+    <col width="2" customWidth="1" style="84" min="8449" max="8449"/>
+    <col width="5.85546875" customWidth="1" style="84" min="8450" max="8450"/>
+    <col width="38.5703125" customWidth="1" style="84" min="8451" max="8451"/>
+    <col width="10" customWidth="1" style="84" min="8452" max="8452"/>
+    <col width="21.5703125" customWidth="1" style="84" min="8453" max="8453"/>
+    <col width="22.7109375" customWidth="1" style="84" min="8454" max="8454"/>
+    <col width="0.28515625" customWidth="1" style="84" min="8455" max="8455"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="8456" max="8456"/>
+    <col width="9.140625" customWidth="1" style="84" min="8457" max="8459"/>
+    <col width="14.140625" customWidth="1" style="84" min="8460" max="8460"/>
+    <col width="9.140625" customWidth="1" style="84" min="8461" max="8704"/>
+    <col width="2" customWidth="1" style="84" min="8705" max="8705"/>
+    <col width="5.85546875" customWidth="1" style="84" min="8706" max="8706"/>
+    <col width="38.5703125" customWidth="1" style="84" min="8707" max="8707"/>
+    <col width="10" customWidth="1" style="84" min="8708" max="8708"/>
+    <col width="21.5703125" customWidth="1" style="84" min="8709" max="8709"/>
+    <col width="22.7109375" customWidth="1" style="84" min="8710" max="8710"/>
+    <col width="0.28515625" customWidth="1" style="84" min="8711" max="8711"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="8712" max="8712"/>
+    <col width="9.140625" customWidth="1" style="84" min="8713" max="8715"/>
+    <col width="14.140625" customWidth="1" style="84" min="8716" max="8716"/>
+    <col width="9.140625" customWidth="1" style="84" min="8717" max="8960"/>
+    <col width="2" customWidth="1" style="84" min="8961" max="8961"/>
+    <col width="5.85546875" customWidth="1" style="84" min="8962" max="8962"/>
+    <col width="38.5703125" customWidth="1" style="84" min="8963" max="8963"/>
+    <col width="10" customWidth="1" style="84" min="8964" max="8964"/>
+    <col width="21.5703125" customWidth="1" style="84" min="8965" max="8965"/>
+    <col width="22.7109375" customWidth="1" style="84" min="8966" max="8966"/>
+    <col width="0.28515625" customWidth="1" style="84" min="8967" max="8967"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="8968" max="8968"/>
+    <col width="9.140625" customWidth="1" style="84" min="8969" max="8971"/>
+    <col width="14.140625" customWidth="1" style="84" min="8972" max="8972"/>
+    <col width="9.140625" customWidth="1" style="84" min="8973" max="9216"/>
+    <col width="2" customWidth="1" style="84" min="9217" max="9217"/>
+    <col width="5.85546875" customWidth="1" style="84" min="9218" max="9218"/>
+    <col width="38.5703125" customWidth="1" style="84" min="9219" max="9219"/>
+    <col width="10" customWidth="1" style="84" min="9220" max="9220"/>
+    <col width="21.5703125" customWidth="1" style="84" min="9221" max="9221"/>
+    <col width="22.7109375" customWidth="1" style="84" min="9222" max="9222"/>
+    <col width="0.28515625" customWidth="1" style="84" min="9223" max="9223"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="9224" max="9224"/>
+    <col width="9.140625" customWidth="1" style="84" min="9225" max="9227"/>
+    <col width="14.140625" customWidth="1" style="84" min="9228" max="9228"/>
+    <col width="9.140625" customWidth="1" style="84" min="9229" max="9472"/>
+    <col width="2" customWidth="1" style="84" min="9473" max="9473"/>
+    <col width="5.85546875" customWidth="1" style="84" min="9474" max="9474"/>
+    <col width="38.5703125" customWidth="1" style="84" min="9475" max="9475"/>
+    <col width="10" customWidth="1" style="84" min="9476" max="9476"/>
+    <col width="21.5703125" customWidth="1" style="84" min="9477" max="9477"/>
+    <col width="22.7109375" customWidth="1" style="84" min="9478" max="9478"/>
+    <col width="0.28515625" customWidth="1" style="84" min="9479" max="9479"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="9480" max="9480"/>
+    <col width="9.140625" customWidth="1" style="84" min="9481" max="9483"/>
+    <col width="14.140625" customWidth="1" style="84" min="9484" max="9484"/>
+    <col width="9.140625" customWidth="1" style="84" min="9485" max="9728"/>
+    <col width="2" customWidth="1" style="84" min="9729" max="9729"/>
+    <col width="5.85546875" customWidth="1" style="84" min="9730" max="9730"/>
+    <col width="38.5703125" customWidth="1" style="84" min="9731" max="9731"/>
+    <col width="10" customWidth="1" style="84" min="9732" max="9732"/>
+    <col width="21.5703125" customWidth="1" style="84" min="9733" max="9733"/>
+    <col width="22.7109375" customWidth="1" style="84" min="9734" max="9734"/>
+    <col width="0.28515625" customWidth="1" style="84" min="9735" max="9735"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="9736" max="9736"/>
+    <col width="9.140625" customWidth="1" style="84" min="9737" max="9739"/>
+    <col width="14.140625" customWidth="1" style="84" min="9740" max="9740"/>
+    <col width="9.140625" customWidth="1" style="84" min="9741" max="9984"/>
+    <col width="2" customWidth="1" style="84" min="9985" max="9985"/>
+    <col width="5.85546875" customWidth="1" style="84" min="9986" max="9986"/>
+    <col width="38.5703125" customWidth="1" style="84" min="9987" max="9987"/>
+    <col width="10" customWidth="1" style="84" min="9988" max="9988"/>
+    <col width="21.5703125" customWidth="1" style="84" min="9989" max="9989"/>
+    <col width="22.7109375" customWidth="1" style="84" min="9990" max="9990"/>
+    <col width="0.28515625" customWidth="1" style="84" min="9991" max="9991"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="9992" max="9992"/>
+    <col width="9.140625" customWidth="1" style="84" min="9993" max="9995"/>
+    <col width="14.140625" customWidth="1" style="84" min="9996" max="9996"/>
+    <col width="9.140625" customWidth="1" style="84" min="9997" max="10240"/>
+    <col width="2" customWidth="1" style="84" min="10241" max="10241"/>
+    <col width="5.85546875" customWidth="1" style="84" min="10242" max="10242"/>
+    <col width="38.5703125" customWidth="1" style="84" min="10243" max="10243"/>
+    <col width="10" customWidth="1" style="84" min="10244" max="10244"/>
+    <col width="21.5703125" customWidth="1" style="84" min="10245" max="10245"/>
+    <col width="22.7109375" customWidth="1" style="84" min="10246" max="10246"/>
+    <col width="0.28515625" customWidth="1" style="84" min="10247" max="10247"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="10248" max="10248"/>
+    <col width="9.140625" customWidth="1" style="84" min="10249" max="10251"/>
+    <col width="14.140625" customWidth="1" style="84" min="10252" max="10252"/>
+    <col width="9.140625" customWidth="1" style="84" min="10253" max="10496"/>
+    <col width="2" customWidth="1" style="84" min="10497" max="10497"/>
+    <col width="5.85546875" customWidth="1" style="84" min="10498" max="10498"/>
+    <col width="38.5703125" customWidth="1" style="84" min="10499" max="10499"/>
+    <col width="10" customWidth="1" style="84" min="10500" max="10500"/>
+    <col width="21.5703125" customWidth="1" style="84" min="10501" max="10501"/>
+    <col width="22.7109375" customWidth="1" style="84" min="10502" max="10502"/>
+    <col width="0.28515625" customWidth="1" style="84" min="10503" max="10503"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="10504" max="10504"/>
+    <col width="9.140625" customWidth="1" style="84" min="10505" max="10507"/>
+    <col width="14.140625" customWidth="1" style="84" min="10508" max="10508"/>
+    <col width="9.140625" customWidth="1" style="84" min="10509" max="10752"/>
+    <col width="2" customWidth="1" style="84" min="10753" max="10753"/>
+    <col width="5.85546875" customWidth="1" style="84" min="10754" max="10754"/>
+    <col width="38.5703125" customWidth="1" style="84" min="10755" max="10755"/>
+    <col width="10" customWidth="1" style="84" min="10756" max="10756"/>
+    <col width="21.5703125" customWidth="1" style="84" min="10757" max="10757"/>
+    <col width="22.7109375" customWidth="1" style="84" min="10758" max="10758"/>
+    <col width="0.28515625" customWidth="1" style="84" min="10759" max="10759"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="10760" max="10760"/>
+    <col width="9.140625" customWidth="1" style="84" min="10761" max="10763"/>
+    <col width="14.140625" customWidth="1" style="84" min="10764" max="10764"/>
+    <col width="9.140625" customWidth="1" style="84" min="10765" max="11008"/>
+    <col width="2" customWidth="1" style="84" min="11009" max="11009"/>
+    <col width="5.85546875" customWidth="1" style="84" min="11010" max="11010"/>
+    <col width="38.5703125" customWidth="1" style="84" min="11011" max="11011"/>
+    <col width="10" customWidth="1" style="84" min="11012" max="11012"/>
+    <col width="21.5703125" customWidth="1" style="84" min="11013" max="11013"/>
+    <col width="22.7109375" customWidth="1" style="84" min="11014" max="11014"/>
+    <col width="0.28515625" customWidth="1" style="84" min="11015" max="11015"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="11016" max="11016"/>
+    <col width="9.140625" customWidth="1" style="84" min="11017" max="11019"/>
+    <col width="14.140625" customWidth="1" style="84" min="11020" max="11020"/>
+    <col width="9.140625" customWidth="1" style="84" min="11021" max="11264"/>
+    <col width="2" customWidth="1" style="84" min="11265" max="11265"/>
+    <col width="5.85546875" customWidth="1" style="84" min="11266" max="11266"/>
+    <col width="38.5703125" customWidth="1" style="84" min="11267" max="11267"/>
+    <col width="10" customWidth="1" style="84" min="11268" max="11268"/>
+    <col width="21.5703125" customWidth="1" style="84" min="11269" max="11269"/>
+    <col width="22.7109375" customWidth="1" style="84" min="11270" max="11270"/>
+    <col width="0.28515625" customWidth="1" style="84" min="11271" max="11271"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="11272" max="11272"/>
+    <col width="9.140625" customWidth="1" style="84" min="11273" max="11275"/>
+    <col width="14.140625" customWidth="1" style="84" min="11276" max="11276"/>
+    <col width="9.140625" customWidth="1" style="84" min="11277" max="11520"/>
+    <col width="2" customWidth="1" style="84" min="11521" max="11521"/>
+    <col width="5.85546875" customWidth="1" style="84" min="11522" max="11522"/>
+    <col width="38.5703125" customWidth="1" style="84" min="11523" max="11523"/>
+    <col width="10" customWidth="1" style="84" min="11524" max="11524"/>
+    <col width="21.5703125" customWidth="1" style="84" min="11525" max="11525"/>
+    <col width="22.7109375" customWidth="1" style="84" min="11526" max="11526"/>
+    <col width="0.28515625" customWidth="1" style="84" min="11527" max="11527"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="11528" max="11528"/>
+    <col width="9.140625" customWidth="1" style="84" min="11529" max="11531"/>
+    <col width="14.140625" customWidth="1" style="84" min="11532" max="11532"/>
+    <col width="9.140625" customWidth="1" style="84" min="11533" max="11776"/>
+    <col width="2" customWidth="1" style="84" min="11777" max="11777"/>
+    <col width="5.85546875" customWidth="1" style="84" min="11778" max="11778"/>
+    <col width="38.5703125" customWidth="1" style="84" min="11779" max="11779"/>
+    <col width="10" customWidth="1" style="84" min="11780" max="11780"/>
+    <col width="21.5703125" customWidth="1" style="84" min="11781" max="11781"/>
+    <col width="22.7109375" customWidth="1" style="84" min="11782" max="11782"/>
+    <col width="0.28515625" customWidth="1" style="84" min="11783" max="11783"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="11784" max="11784"/>
+    <col width="9.140625" customWidth="1" style="84" min="11785" max="11787"/>
+    <col width="14.140625" customWidth="1" style="84" min="11788" max="11788"/>
+    <col width="9.140625" customWidth="1" style="84" min="11789" max="12032"/>
+    <col width="2" customWidth="1" style="84" min="12033" max="12033"/>
+    <col width="5.85546875" customWidth="1" style="84" min="12034" max="12034"/>
+    <col width="38.5703125" customWidth="1" style="84" min="12035" max="12035"/>
+    <col width="10" customWidth="1" style="84" min="12036" max="12036"/>
+    <col width="21.5703125" customWidth="1" style="84" min="12037" max="12037"/>
+    <col width="22.7109375" customWidth="1" style="84" min="12038" max="12038"/>
+    <col width="0.28515625" customWidth="1" style="84" min="12039" max="12039"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="12040" max="12040"/>
+    <col width="9.140625" customWidth="1" style="84" min="12041" max="12043"/>
+    <col width="14.140625" customWidth="1" style="84" min="12044" max="12044"/>
+    <col width="9.140625" customWidth="1" style="84" min="12045" max="12288"/>
+    <col width="2" customWidth="1" style="84" min="12289" max="12289"/>
+    <col width="5.85546875" customWidth="1" style="84" min="12290" max="12290"/>
+    <col width="38.5703125" customWidth="1" style="84" min="12291" max="12291"/>
+    <col width="10" customWidth="1" style="84" min="12292" max="12292"/>
+    <col width="21.5703125" customWidth="1" style="84" min="12293" max="12293"/>
+    <col width="22.7109375" customWidth="1" style="84" min="12294" max="12294"/>
+    <col width="0.28515625" customWidth="1" style="84" min="12295" max="12295"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="12296" max="12296"/>
+    <col width="9.140625" customWidth="1" style="84" min="12297" max="12299"/>
+    <col width="14.140625" customWidth="1" style="84" min="12300" max="12300"/>
+    <col width="9.140625" customWidth="1" style="84" min="12301" max="12544"/>
+    <col width="2" customWidth="1" style="84" min="12545" max="12545"/>
+    <col width="5.85546875" customWidth="1" style="84" min="12546" max="12546"/>
+    <col width="38.5703125" customWidth="1" style="84" min="12547" max="12547"/>
+    <col width="10" customWidth="1" style="84" min="12548" max="12548"/>
+    <col width="21.5703125" customWidth="1" style="84" min="12549" max="12549"/>
+    <col width="22.7109375" customWidth="1" style="84" min="12550" max="12550"/>
+    <col width="0.28515625" customWidth="1" style="84" min="12551" max="12551"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="12552" max="12552"/>
+    <col width="9.140625" customWidth="1" style="84" min="12553" max="12555"/>
+    <col width="14.140625" customWidth="1" style="84" min="12556" max="12556"/>
+    <col width="9.140625" customWidth="1" style="84" min="12557" max="12800"/>
+    <col width="2" customWidth="1" style="84" min="12801" max="12801"/>
+    <col width="5.85546875" customWidth="1" style="84" min="12802" max="12802"/>
+    <col width="38.5703125" customWidth="1" style="84" min="12803" max="12803"/>
+    <col width="10" customWidth="1" style="84" min="12804" max="12804"/>
+    <col width="21.5703125" customWidth="1" style="84" min="12805" max="12805"/>
+    <col width="22.7109375" customWidth="1" style="84" min="12806" max="12806"/>
+    <col width="0.28515625" customWidth="1" style="84" min="12807" max="12807"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="12808" max="12808"/>
+    <col width="9.140625" customWidth="1" style="84" min="12809" max="12811"/>
+    <col width="14.140625" customWidth="1" style="84" min="12812" max="12812"/>
+    <col width="9.140625" customWidth="1" style="84" min="12813" max="13056"/>
+    <col width="2" customWidth="1" style="84" min="13057" max="13057"/>
+    <col width="5.85546875" customWidth="1" style="84" min="13058" max="13058"/>
+    <col width="38.5703125" customWidth="1" style="84" min="13059" max="13059"/>
+    <col width="10" customWidth="1" style="84" min="13060" max="13060"/>
+    <col width="21.5703125" customWidth="1" style="84" min="13061" max="13061"/>
+    <col width="22.7109375" customWidth="1" style="84" min="13062" max="13062"/>
+    <col width="0.28515625" customWidth="1" style="84" min="13063" max="13063"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="13064" max="13064"/>
+    <col width="9.140625" customWidth="1" style="84" min="13065" max="13067"/>
+    <col width="14.140625" customWidth="1" style="84" min="13068" max="13068"/>
+    <col width="9.140625" customWidth="1" style="84" min="13069" max="13312"/>
+    <col width="2" customWidth="1" style="84" min="13313" max="13313"/>
+    <col width="5.85546875" customWidth="1" style="84" min="13314" max="13314"/>
+    <col width="38.5703125" customWidth="1" style="84" min="13315" max="13315"/>
+    <col width="10" customWidth="1" style="84" min="13316" max="13316"/>
+    <col width="21.5703125" customWidth="1" style="84" min="13317" max="13317"/>
+    <col width="22.7109375" customWidth="1" style="84" min="13318" max="13318"/>
+    <col width="0.28515625" customWidth="1" style="84" min="13319" max="13319"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="13320" max="13320"/>
+    <col width="9.140625" customWidth="1" style="84" min="13321" max="13323"/>
+    <col width="14.140625" customWidth="1" style="84" min="13324" max="13324"/>
+    <col width="9.140625" customWidth="1" style="84" min="13325" max="13568"/>
+    <col width="2" customWidth="1" style="84" min="13569" max="13569"/>
+    <col width="5.85546875" customWidth="1" style="84" min="13570" max="13570"/>
+    <col width="38.5703125" customWidth="1" style="84" min="13571" max="13571"/>
+    <col width="10" customWidth="1" style="84" min="13572" max="13572"/>
+    <col width="21.5703125" customWidth="1" style="84" min="13573" max="13573"/>
+    <col width="22.7109375" customWidth="1" style="84" min="13574" max="13574"/>
+    <col width="0.28515625" customWidth="1" style="84" min="13575" max="13575"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="13576" max="13576"/>
+    <col width="9.140625" customWidth="1" style="84" min="13577" max="13579"/>
+    <col width="14.140625" customWidth="1" style="84" min="13580" max="13580"/>
+    <col width="9.140625" customWidth="1" style="84" min="13581" max="13824"/>
+    <col width="2" customWidth="1" style="84" min="13825" max="13825"/>
+    <col width="5.85546875" customWidth="1" style="84" min="13826" max="13826"/>
+    <col width="38.5703125" customWidth="1" style="84" min="13827" max="13827"/>
+    <col width="10" customWidth="1" style="84" min="13828" max="13828"/>
+    <col width="21.5703125" customWidth="1" style="84" min="13829" max="13829"/>
+    <col width="22.7109375" customWidth="1" style="84" min="13830" max="13830"/>
+    <col width="0.28515625" customWidth="1" style="84" min="13831" max="13831"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="13832" max="13832"/>
+    <col width="9.140625" customWidth="1" style="84" min="13833" max="13835"/>
+    <col width="14.140625" customWidth="1" style="84" min="13836" max="13836"/>
+    <col width="9.140625" customWidth="1" style="84" min="13837" max="14080"/>
+    <col width="2" customWidth="1" style="84" min="14081" max="14081"/>
+    <col width="5.85546875" customWidth="1" style="84" min="14082" max="14082"/>
+    <col width="38.5703125" customWidth="1" style="84" min="14083" max="14083"/>
+    <col width="10" customWidth="1" style="84" min="14084" max="14084"/>
+    <col width="21.5703125" customWidth="1" style="84" min="14085" max="14085"/>
+    <col width="22.7109375" customWidth="1" style="84" min="14086" max="14086"/>
+    <col width="0.28515625" customWidth="1" style="84" min="14087" max="14087"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="14088" max="14088"/>
+    <col width="9.140625" customWidth="1" style="84" min="14089" max="14091"/>
+    <col width="14.140625" customWidth="1" style="84" min="14092" max="14092"/>
+    <col width="9.140625" customWidth="1" style="84" min="14093" max="14336"/>
+    <col width="2" customWidth="1" style="84" min="14337" max="14337"/>
+    <col width="5.85546875" customWidth="1" style="84" min="14338" max="14338"/>
+    <col width="38.5703125" customWidth="1" style="84" min="14339" max="14339"/>
+    <col width="10" customWidth="1" style="84" min="14340" max="14340"/>
+    <col width="21.5703125" customWidth="1" style="84" min="14341" max="14341"/>
+    <col width="22.7109375" customWidth="1" style="84" min="14342" max="14342"/>
+    <col width="0.28515625" customWidth="1" style="84" min="14343" max="14343"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="14344" max="14344"/>
+    <col width="9.140625" customWidth="1" style="84" min="14345" max="14347"/>
+    <col width="14.140625" customWidth="1" style="84" min="14348" max="14348"/>
+    <col width="9.140625" customWidth="1" style="84" min="14349" max="14592"/>
+    <col width="2" customWidth="1" style="84" min="14593" max="14593"/>
+    <col width="5.85546875" customWidth="1" style="84" min="14594" max="14594"/>
+    <col width="38.5703125" customWidth="1" style="84" min="14595" max="14595"/>
+    <col width="10" customWidth="1" style="84" min="14596" max="14596"/>
+    <col width="21.5703125" customWidth="1" style="84" min="14597" max="14597"/>
+    <col width="22.7109375" customWidth="1" style="84" min="14598" max="14598"/>
+    <col width="0.28515625" customWidth="1" style="84" min="14599" max="14599"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="14600" max="14600"/>
+    <col width="9.140625" customWidth="1" style="84" min="14601" max="14603"/>
+    <col width="14.140625" customWidth="1" style="84" min="14604" max="14604"/>
+    <col width="9.140625" customWidth="1" style="84" min="14605" max="14848"/>
+    <col width="2" customWidth="1" style="84" min="14849" max="14849"/>
+    <col width="5.85546875" customWidth="1" style="84" min="14850" max="14850"/>
+    <col width="38.5703125" customWidth="1" style="84" min="14851" max="14851"/>
+    <col width="10" customWidth="1" style="84" min="14852" max="14852"/>
+    <col width="21.5703125" customWidth="1" style="84" min="14853" max="14853"/>
+    <col width="22.7109375" customWidth="1" style="84" min="14854" max="14854"/>
+    <col width="0.28515625" customWidth="1" style="84" min="14855" max="14855"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="14856" max="14856"/>
+    <col width="9.140625" customWidth="1" style="84" min="14857" max="14859"/>
+    <col width="14.140625" customWidth="1" style="84" min="14860" max="14860"/>
+    <col width="9.140625" customWidth="1" style="84" min="14861" max="15104"/>
+    <col width="2" customWidth="1" style="84" min="15105" max="15105"/>
+    <col width="5.85546875" customWidth="1" style="84" min="15106" max="15106"/>
+    <col width="38.5703125" customWidth="1" style="84" min="15107" max="15107"/>
+    <col width="10" customWidth="1" style="84" min="15108" max="15108"/>
+    <col width="21.5703125" customWidth="1" style="84" min="15109" max="15109"/>
+    <col width="22.7109375" customWidth="1" style="84" min="15110" max="15110"/>
+    <col width="0.28515625" customWidth="1" style="84" min="15111" max="15111"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="15112" max="15112"/>
+    <col width="9.140625" customWidth="1" style="84" min="15113" max="15115"/>
+    <col width="14.140625" customWidth="1" style="84" min="15116" max="15116"/>
+    <col width="9.140625" customWidth="1" style="84" min="15117" max="15360"/>
+    <col width="2" customWidth="1" style="84" min="15361" max="15361"/>
+    <col width="5.85546875" customWidth="1" style="84" min="15362" max="15362"/>
+    <col width="38.5703125" customWidth="1" style="84" min="15363" max="15363"/>
+    <col width="10" customWidth="1" style="84" min="15364" max="15364"/>
+    <col width="21.5703125" customWidth="1" style="84" min="15365" max="15365"/>
+    <col width="22.7109375" customWidth="1" style="84" min="15366" max="15366"/>
+    <col width="0.28515625" customWidth="1" style="84" min="15367" max="15367"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="15368" max="15368"/>
+    <col width="9.140625" customWidth="1" style="84" min="15369" max="15371"/>
+    <col width="14.140625" customWidth="1" style="84" min="15372" max="15372"/>
+    <col width="9.140625" customWidth="1" style="84" min="15373" max="15616"/>
+    <col width="2" customWidth="1" style="84" min="15617" max="15617"/>
+    <col width="5.85546875" customWidth="1" style="84" min="15618" max="15618"/>
+    <col width="38.5703125" customWidth="1" style="84" min="15619" max="15619"/>
+    <col width="10" customWidth="1" style="84" min="15620" max="15620"/>
+    <col width="21.5703125" customWidth="1" style="84" min="15621" max="15621"/>
+    <col width="22.7109375" customWidth="1" style="84" min="15622" max="15622"/>
+    <col width="0.28515625" customWidth="1" style="84" min="15623" max="15623"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="15624" max="15624"/>
+    <col width="9.140625" customWidth="1" style="84" min="15625" max="15627"/>
+    <col width="14.140625" customWidth="1" style="84" min="15628" max="15628"/>
+    <col width="9.140625" customWidth="1" style="84" min="15629" max="15872"/>
+    <col width="2" customWidth="1" style="84" min="15873" max="15873"/>
+    <col width="5.85546875" customWidth="1" style="84" min="15874" max="15874"/>
+    <col width="38.5703125" customWidth="1" style="84" min="15875" max="15875"/>
+    <col width="10" customWidth="1" style="84" min="15876" max="15876"/>
+    <col width="21.5703125" customWidth="1" style="84" min="15877" max="15877"/>
+    <col width="22.7109375" customWidth="1" style="84" min="15878" max="15878"/>
+    <col width="0.28515625" customWidth="1" style="84" min="15879" max="15879"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="15880" max="15880"/>
+    <col width="9.140625" customWidth="1" style="84" min="15881" max="15883"/>
+    <col width="14.140625" customWidth="1" style="84" min="15884" max="15884"/>
+    <col width="9.140625" customWidth="1" style="84" min="15885" max="16128"/>
+    <col width="2" customWidth="1" style="84" min="16129" max="16129"/>
+    <col width="5.85546875" customWidth="1" style="84" min="16130" max="16130"/>
+    <col width="38.5703125" customWidth="1" style="84" min="16131" max="16131"/>
+    <col width="10" customWidth="1" style="84" min="16132" max="16132"/>
+    <col width="21.5703125" customWidth="1" style="84" min="16133" max="16133"/>
+    <col width="22.7109375" customWidth="1" style="84" min="16134" max="16134"/>
+    <col width="0.28515625" customWidth="1" style="84" min="16135" max="16135"/>
+    <col hidden="1" width="13" customWidth="1" style="84" min="16136" max="16136"/>
+    <col width="9.140625" customWidth="1" style="84" min="16137" max="16139"/>
+    <col width="14.140625" customWidth="1" style="84" min="16140" max="16140"/>
+    <col width="9.140625" customWidth="1" style="84" min="16141" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="95">
+    <row r="1" ht="13.5" customHeight="1" s="96">
       <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Исполнитель: ООО "ЯмалСпецЦентр"</t>
@@ -1896,21 +1903,21 @@
       </c>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="8" t="n"/>
-      <c r="E1" s="86" t="inlineStr">
+      <c r="E1" s="88" t="inlineStr">
         <is>
           <t>Заказчик: АО "Газпромнефть-ННГ"</t>
         </is>
       </c>
       <c r="F1" s="24" t="n"/>
     </row>
-    <row r="2" ht="39" customFormat="1" customHeight="1" s="77">
-      <c r="B2" s="78" t="inlineStr">
+    <row r="2" ht="39" customFormat="1" customHeight="1" s="79">
+      <c r="B2" s="80" t="inlineStr">
         <is>
           <t>Адрес: 629800, Автономный округ Ямало-Ненецкий, город Ноябрьск, Промзона  Юго-Восточный промузел,  
 панель 1-А</t>
         </is>
       </c>
-      <c r="E2" s="78" t="inlineStr">
+      <c r="E2" s="80" t="inlineStr">
         <is>
           <t>Адрес: 629807, Ямало-Ненецкий автономный округ , 
  г. Ноябрьск, ул. Ленина, д. 59/87</t>
@@ -1919,14 +1926,14 @@
       <c r="I2" s="16" t="n"/>
       <c r="J2" s="15" t="n"/>
     </row>
-    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="77">
+    <row r="3" ht="15.75" customFormat="1" customHeight="1" s="79">
       <c r="B3" s="20" t="inlineStr">
         <is>
           <t>ИНН: 8905050637</t>
         </is>
       </c>
       <c r="C3" s="22" t="n"/>
-      <c r="E3" s="86" t="inlineStr">
+      <c r="E3" s="88" t="inlineStr">
         <is>
           <t>ИНН: 8905000428</t>
         </is>
@@ -1937,7 +1944,7 @@
       <c r="I3" s="16" t="n"/>
       <c r="J3" s="15" t="n"/>
     </row>
-    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="77">
+    <row r="4" ht="10.5" customFormat="1" customHeight="1" s="79">
       <c r="B4" s="20" t="inlineStr">
         <is>
           <t>КПП: 890501001</t>
@@ -1945,7 +1952,7 @@
       </c>
       <c r="C4" s="22" t="n"/>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="86" t="inlineStr">
+      <c r="E4" s="88" t="inlineStr">
         <is>
           <t>КПП: 890501001</t>
         </is>
@@ -1954,8 +1961,8 @@
       <c r="G4" s="17" t="n"/>
       <c r="H4" s="17" t="n"/>
     </row>
-    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="77">
-      <c r="B5" s="85" t="inlineStr">
+    <row r="5" ht="13.5" customFormat="1" customHeight="1" s="79">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>Банковские реквизиты: р/с 40702810500020010172 
 в ф-ле № 6602 Банка ВТБ  (ПАО) г. Екатеринбург,  
@@ -1963,8 +1970,8 @@
 ОКПО 37991345;ОГРН 1118905006868</t>
         </is>
       </c>
-      <c r="D5" s="78" t="n"/>
-      <c r="E5" s="84" t="inlineStr">
+      <c r="D5" s="80" t="n"/>
+      <c r="E5" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">Банковские реквизиты: р/с 40702810100489000321  </t>
         </is>
@@ -1972,29 +1979,29 @@
       <c r="G5" s="17" t="n"/>
       <c r="H5" s="17" t="n"/>
     </row>
-    <row r="6" ht="45.75" customFormat="1" customHeight="1" s="77">
-      <c r="D6" s="78" t="n"/>
-      <c r="E6" s="79" t="inlineStr">
+    <row r="6" ht="45.75" customFormat="1" customHeight="1" s="79">
+      <c r="D6" s="80" t="n"/>
+      <c r="E6" s="81" t="inlineStr">
         <is>
           <t>Ф-л Банка"ГПБ" (АО) в г. Сургуте, к/с 30101810400000000721,
  ОКПО 05778425, БИК 047144721, ОГРН 10289007003963</t>
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" ht="21" customFormat="1" customHeight="1" s="77">
+    <row r="7" hidden="1" ht="21" customFormat="1" customHeight="1" s="79">
       <c r="B7" s="48" t="n"/>
       <c r="C7" s="48" t="n"/>
-      <c r="D7" s="78" t="n"/>
-      <c r="E7" s="79" t="n"/>
-      <c r="F7" s="79" t="n"/>
-      <c r="G7" s="79" t="n"/>
-      <c r="H7" s="79" t="n"/>
-      <c r="I7" s="79" t="n"/>
-    </row>
-    <row r="8" ht="6" customFormat="1" customHeight="1" s="77">
-      <c r="B8" s="84" t="n"/>
+      <c r="D7" s="80" t="n"/>
+      <c r="E7" s="81" t="n"/>
+      <c r="F7" s="81" t="n"/>
+      <c r="G7" s="81" t="n"/>
+      <c r="H7" s="81" t="n"/>
+      <c r="I7" s="81" t="n"/>
+    </row>
+    <row r="8" ht="6" customFormat="1" customHeight="1" s="79">
+      <c r="B8" s="86" t="n"/>
       <c r="D8" s="23" t="n"/>
-      <c r="E8" s="79" t="n"/>
+      <c r="E8" s="81" t="n"/>
       <c r="F8" s="26" t="n"/>
       <c r="G8" s="27" t="n"/>
       <c r="H8" s="27" t="n"/>
@@ -2002,14 +2009,14 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="23" t="n"/>
     </row>
-    <row r="9" ht="13.5" customFormat="1" customHeight="1" s="77">
-      <c r="B9" s="84" t="n"/>
+    <row r="9" ht="13.5" customFormat="1" customHeight="1" s="79">
+      <c r="B9" s="86" t="n"/>
       <c r="D9" s="39" t="inlineStr">
         <is>
           <t>АКТ № 509</t>
         </is>
       </c>
-      <c r="E9" s="79" t="n"/>
+      <c r="E9" s="81" t="n"/>
       <c r="F9" s="26" t="n"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
@@ -2017,8 +2024,8 @@
       <c r="J9" s="23" t="n"/>
       <c r="K9" s="23" t="n"/>
     </row>
-    <row r="10" ht="20.25" customFormat="1" customHeight="1" s="77">
-      <c r="B10" s="84" t="n"/>
+    <row r="10" ht="20.25" customFormat="1" customHeight="1" s="79">
+      <c r="B10" s="86" t="n"/>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="29" t="inlineStr">
         <is>
@@ -2033,8 +2040,8 @@
       <c r="J10" s="23" t="n"/>
       <c r="K10" s="23" t="n"/>
     </row>
-    <row r="11" ht="13.5" customFormat="1" customHeight="1" s="77">
-      <c r="B11" s="84" t="n"/>
+    <row r="11" ht="13.5" customFormat="1" customHeight="1" s="79">
+      <c r="B11" s="86" t="n"/>
       <c r="C11" s="30" t="n"/>
       <c r="D11" s="30" t="inlineStr">
         <is>
@@ -2049,8 +2056,8 @@
       <c r="J11" s="23" t="n"/>
       <c r="K11" s="23" t="n"/>
     </row>
-    <row r="12" ht="10.5" customFormat="1" customHeight="1" s="77">
-      <c r="B12" s="84" t="n"/>
+    <row r="12" ht="10.5" customFormat="1" customHeight="1" s="79">
+      <c r="B12" s="86" t="n"/>
       <c r="C12" s="30" t="n"/>
       <c r="D12" s="30" t="n"/>
       <c r="E12" s="30" t="n"/>
@@ -2061,7 +2068,7 @@
       <c r="J12" s="23" t="n"/>
       <c r="K12" s="23" t="n"/>
     </row>
-    <row r="13" ht="14.25" customFormat="1" customHeight="1" s="77">
+    <row r="13" ht="14.25" customFormat="1" customHeight="1" s="79">
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>составлен в том, что "Исполнитель" согласно договору №  ННГ-15/11301/00251/Р  от 22.10.2015 г.</t>
@@ -2077,7 +2084,7 @@
       <c r="J13" s="23" t="n"/>
       <c r="K13" s="23" t="n"/>
     </row>
-    <row r="14" customFormat="1" s="77">
+    <row r="14" customFormat="1" s="79">
       <c r="B14" s="31" t="inlineStr">
         <is>
           <t>оказал услуги для АО "Газпромнефть-ННГ"</t>
@@ -2088,98 +2095,98 @@
       <c r="E14" s="22" t="n"/>
       <c r="F14" s="22" t="n"/>
     </row>
-    <row r="15" ht="2.25" customFormat="1" customHeight="1" s="77">
+    <row r="15" ht="2.25" customFormat="1" customHeight="1" s="79">
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
     </row>
-    <row r="16" ht="12.75" customHeight="1" s="95">
-      <c r="B16" s="81" t="inlineStr">
+    <row r="16" ht="12.75" customHeight="1" s="96">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>№ п\п</t>
         </is>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C16" s="83" t="inlineStr">
         <is>
           <t>Наименование услуги</t>
         </is>
       </c>
-      <c r="D16" s="81" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
         <is>
           <t>Кол-во оборудования ед</t>
         </is>
       </c>
-      <c r="E16" s="81" t="inlineStr">
+      <c r="E16" s="83" t="inlineStr">
         <is>
           <t>Цена 
 за ед., руб.</t>
         </is>
       </c>
-      <c r="F16" s="81" t="inlineStr">
+      <c r="F16" s="83" t="inlineStr">
         <is>
           <t>Стоимость услуг
 руб.</t>
         </is>
       </c>
-      <c r="G16" s="81" t="n"/>
+      <c r="G16" s="83" t="n"/>
       <c r="J16" s="3" t="n"/>
     </row>
-    <row r="17" ht="12.75" customHeight="1" s="95">
-      <c r="G17" s="81" t="n"/>
+    <row r="17" ht="12.75" customHeight="1" s="96">
+      <c r="G17" s="83" t="n"/>
       <c r="J17" s="3" t="n"/>
     </row>
-    <row r="18" ht="27.75" customHeight="1" s="95">
-      <c r="G18" s="81" t="n"/>
+    <row r="18" ht="27.75" customHeight="1" s="96">
+      <c r="G18" s="83" t="n"/>
       <c r="J18" s="3" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="95">
-      <c r="B19" s="81" t="n">
+    <row r="19" ht="18" customHeight="1" s="96">
+      <c r="B19" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="81" t="n">
+      <c r="D19" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="81" t="n">
+      <c r="E19" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="81" t="n">
+      <c r="F19" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="81" t="n"/>
-      <c r="J19" s="81" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="95">
-      <c r="B20" s="84" t="inlineStr">
+      <c r="G19" s="83" t="n"/>
+      <c r="J19" s="83" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="96">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>Западно-Ноябрьское, Средне-Итурское, Спорышевское месторождения</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n"/>
-      <c r="D20" s="81" t="n"/>
-      <c r="E20" s="81" t="n"/>
-      <c r="F20" s="81" t="n"/>
-      <c r="G20" s="81" t="n"/>
-      <c r="J20" s="81" t="n"/>
-    </row>
-    <row r="21" ht="14.25" customHeight="1" s="95">
-      <c r="B21" s="82" t="inlineStr">
+      <c r="C20" s="83" t="n"/>
+      <c r="D20" s="83" t="n"/>
+      <c r="E20" s="83" t="n"/>
+      <c r="F20" s="83" t="n"/>
+      <c r="G20" s="83" t="n"/>
+      <c r="J20" s="83" t="n"/>
+    </row>
+    <row r="21" ht="14.25" customHeight="1" s="96">
+      <c r="B21" s="84" t="inlineStr">
         <is>
           <t>Сервисное обслуживание</t>
         </is>
       </c>
       <c r="C21" s="41" t="n"/>
-      <c r="D21" s="81" t="n"/>
+      <c r="D21" s="83" t="n"/>
       <c r="E21" s="8" t="n"/>
-      <c r="F21" s="81" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="95">
-      <c r="B22" s="81" t="n">
+      <c r="F21" s="83" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="96">
+      <c r="B22" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="78" t="inlineStr">
+      <c r="C22" s="80" t="inlineStr">
         <is>
           <t>Насос 12НА9/4; 12НА22/6</t>
         </is>
@@ -2188,106 +2195,106 @@
       <c r="E22" s="45" t="n">
         <v>1300.55</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="83">
         <f>E22*D22</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="95">
-      <c r="B23" s="81" t="n">
+    <row r="23" ht="15" customHeight="1" s="96">
+      <c r="B23" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="78" t="inlineStr">
+      <c r="C23" s="80" t="inlineStr">
         <is>
           <t>Насос дозировочный типа ДП,НД</t>
         </is>
       </c>
-      <c r="D23" s="81" t="n"/>
-      <c r="E23" s="81" t="n">
+      <c r="D23" s="83" t="n"/>
+      <c r="E23" s="83" t="n">
         <v>1388.2</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="83">
         <f>E23*D23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="21" customHeight="1" s="95">
-      <c r="B24" s="81" t="n">
+    <row r="24" ht="21" customHeight="1" s="96">
+      <c r="B24" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="78" t="inlineStr">
+      <c r="C24" s="80" t="inlineStr">
         <is>
           <t>Насос НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80</t>
         </is>
       </c>
-      <c r="D24" s="81" t="n"/>
-      <c r="E24" s="81" t="n">
+      <c r="D24" s="83" t="n"/>
+      <c r="E24" s="83" t="n">
         <v>1022.97</v>
       </c>
-      <c r="F24" s="81">
+      <c r="F24" s="83">
         <f>E24*D24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="95">
-      <c r="B25" s="81" t="n">
+    <row r="25" ht="15" customHeight="1" s="96">
+      <c r="B25" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="78" t="inlineStr">
+      <c r="C25" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D25" s="81" t="n"/>
-      <c r="E25" s="81" t="n">
+      <c r="D25" s="83" t="n"/>
+      <c r="E25" s="83" t="n">
         <v>13437.21</v>
       </c>
-      <c r="F25" s="81">
+      <c r="F25" s="83">
         <f>E25*D25</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="95">
-      <c r="B26" s="81" t="n">
+    <row r="26" ht="15" customHeight="1" s="96">
+      <c r="B26" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="78" t="inlineStr">
+      <c r="C26" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-38/44…220</t>
         </is>
       </c>
-      <c r="D26" s="81" t="n"/>
-      <c r="E26" s="81" t="n">
+      <c r="D26" s="83" t="n"/>
+      <c r="E26" s="83" t="n">
         <v>6070.81</v>
       </c>
-      <c r="F26" s="81">
+      <c r="F26" s="83">
         <f>E26*D26</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" s="95">
-      <c r="B27" s="81" t="n">
+    <row r="27" ht="18.75" customHeight="1" s="96">
+      <c r="B27" s="83" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="78" t="inlineStr">
+      <c r="C27" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д630/90</t>
         </is>
       </c>
-      <c r="D27" s="81" t="n"/>
-      <c r="E27" s="81" t="n">
+      <c r="D27" s="83" t="n"/>
+      <c r="E27" s="83" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F27" s="81">
+      <c r="F27" s="83">
         <f>E27*D27</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="45.75" customHeight="1" s="95">
-      <c r="B28" s="81" t="n">
+    <row r="28" ht="45.75" customHeight="1" s="96">
+      <c r="B28" s="83" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="78" t="inlineStr">
+      <c r="C28" s="80" t="inlineStr">
         <is>
           <t>Насос К 8-18; К 20-30; К 50-30;К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175; К 100-80-160; К 100-65-200; КМ 160-65-200; 3Т13Н</t>
         </is>
@@ -2296,16 +2303,16 @@
       <c r="E28" s="45" t="n">
         <v>778.17</v>
       </c>
-      <c r="F28" s="81">
+      <c r="F28" s="83">
         <f>E28*D28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="95">
-      <c r="B29" s="81" t="n">
+    <row r="29" ht="15" customHeight="1" s="96">
+      <c r="B29" s="83" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="78" t="inlineStr">
+      <c r="C29" s="80" t="inlineStr">
         <is>
           <t>Насос НМШ 5/25</t>
         </is>
@@ -2314,34 +2321,34 @@
       <c r="E29" s="45" t="n">
         <v>576.9</v>
       </c>
-      <c r="F29" s="81">
+      <c r="F29" s="83">
         <f>E29*D29</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="95">
-      <c r="B30" s="81" t="n">
+    <row r="30" ht="15" customHeight="1" s="96">
+      <c r="B30" s="83" t="n">
         <v>9</v>
       </c>
-      <c r="C30" s="78" t="inlineStr">
+      <c r="C30" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д630/125</t>
         </is>
       </c>
-      <c r="D30" s="81" t="n"/>
-      <c r="E30" s="81" t="n">
+      <c r="D30" s="83" t="n"/>
+      <c r="E30" s="83" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F30" s="81">
+      <c r="F30" s="83">
         <f>E30*D30</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="95">
-      <c r="B31" s="81" t="n">
+    <row r="31" ht="15" customHeight="1" s="96">
+      <c r="B31" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="C31" s="78" t="inlineStr">
+      <c r="C31" s="80" t="inlineStr">
         <is>
           <t>Насос АХП 45/31</t>
         </is>
@@ -2350,16 +2357,16 @@
       <c r="E31" s="45" t="n">
         <v>969.65</v>
       </c>
-      <c r="F31" s="81">
+      <c r="F31" s="83">
         <f>E31*D31</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="95">
-      <c r="B32" s="81" t="n">
+    <row r="32" ht="15" customHeight="1" s="96">
+      <c r="B32" s="83" t="n">
         <v>11</v>
       </c>
-      <c r="C32" s="78" t="inlineStr">
+      <c r="C32" s="80" t="inlineStr">
         <is>
           <t>Насос дозировочный типа PAX 32/12; PIAX 32/28</t>
         </is>
@@ -2368,13 +2375,13 @@
       <c r="E32" s="45" t="n">
         <v>2321.79</v>
       </c>
-      <c r="F32" s="81" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="95">
-      <c r="B33" s="81" t="n">
+      <c r="F32" s="83" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="96">
+      <c r="B33" s="83" t="n">
         <v>12</v>
       </c>
-      <c r="C33" s="78" t="inlineStr">
+      <c r="C33" s="80" t="inlineStr">
         <is>
           <t>Насос НМШ 8/25</t>
         </is>
@@ -2383,13 +2390,13 @@
       <c r="E33" s="45" t="n">
         <v>576.9</v>
       </c>
-      <c r="F33" s="81" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="95">
-      <c r="B34" s="81" t="n">
+      <c r="F33" s="83" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="96">
+      <c r="B34" s="83" t="n">
         <v>13</v>
       </c>
-      <c r="C34" s="78" t="inlineStr">
+      <c r="C34" s="80" t="inlineStr">
         <is>
           <t>Насос ЦВК 6,3/160</t>
         </is>
@@ -2398,13 +2405,13 @@
       <c r="E34" s="45" t="n">
         <v>1210.41</v>
       </c>
-      <c r="F34" s="81" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="95">
-      <c r="B35" s="81" t="n">
+      <c r="F34" s="83" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="96">
+      <c r="B35" s="83" t="n">
         <v>14</v>
       </c>
-      <c r="C35" s="78" t="inlineStr">
+      <c r="C35" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 40/1400</t>
         </is>
@@ -2413,13 +2420,13 @@
       <c r="E35" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F35" s="81" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="95">
-      <c r="B36" s="81" t="n">
+      <c r="F35" s="83" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="96">
+      <c r="B36" s="83" t="n">
         <v>15</v>
       </c>
-      <c r="C36" s="78" t="inlineStr">
+      <c r="C36" s="80" t="inlineStr">
         <is>
           <t>Насос ЦГ 6,3/32</t>
         </is>
@@ -2428,13 +2435,13 @@
       <c r="E36" s="45" t="n">
         <v>2017.99</v>
       </c>
-      <c r="F36" s="81" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="95">
-      <c r="B37" s="81" t="n">
+      <c r="F36" s="83" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="96">
+      <c r="B37" s="83" t="n">
         <v>16</v>
       </c>
-      <c r="C37" s="78" t="inlineStr">
+      <c r="C37" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-105/98…490</t>
         </is>
@@ -2443,13 +2450,13 @@
       <c r="E37" s="45" t="n">
         <v>11244.09</v>
       </c>
-      <c r="F37" s="81" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="95">
-      <c r="B38" s="81" t="n">
+      <c r="F37" s="83" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="96">
+      <c r="B38" s="83" t="n">
         <v>17</v>
       </c>
-      <c r="C38" s="78" t="inlineStr">
+      <c r="C38" s="80" t="inlineStr">
         <is>
           <t>Насос НПВ  1250/60</t>
         </is>
@@ -2458,13 +2465,13 @@
       <c r="E38" s="45" t="n">
         <v>7812.42</v>
       </c>
-      <c r="F38" s="81" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="95">
-      <c r="B39" s="81" t="n">
+      <c r="F38" s="83" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="96">
+      <c r="B39" s="83" t="n">
         <v>18</v>
       </c>
-      <c r="C39" s="78" t="inlineStr">
+      <c r="C39" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 180/1422...1900 2 ТМ</t>
         </is>
@@ -2473,13 +2480,13 @@
       <c r="E39" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F39" s="81" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="95">
-      <c r="B40" s="81" t="n">
+      <c r="F39" s="83" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="96">
+      <c r="B40" s="83" t="n">
         <v>19</v>
       </c>
-      <c r="C40" s="78" t="inlineStr">
+      <c r="C40" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1422…1900 ЗК</t>
         </is>
@@ -2488,13 +2495,13 @@
       <c r="E40" s="45" t="n">
         <v>16393.97</v>
       </c>
-      <c r="F40" s="81" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="95">
-      <c r="B41" s="81" t="n">
+      <c r="F40" s="83" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="96">
+      <c r="B41" s="83" t="n">
         <v>20</v>
       </c>
-      <c r="C41" s="78" t="inlineStr">
+      <c r="C41" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-180/1422…1900</t>
         </is>
@@ -2503,13 +2510,13 @@
       <c r="E41" s="45" t="n">
         <v>17894.24</v>
       </c>
-      <c r="F41" s="81" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="95">
-      <c r="B42" s="81" t="n">
+      <c r="F41" s="83" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="96">
+      <c r="B42" s="83" t="n">
         <v>21</v>
       </c>
-      <c r="C42" s="78" t="inlineStr">
+      <c r="C42" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1422...1900 2 ТМ</t>
         </is>
@@ -2518,13 +2525,13 @@
       <c r="E42" s="45" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F42" s="81" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="95">
-      <c r="B43" s="81" t="n">
+      <c r="F42" s="83" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="96">
+      <c r="B43" s="83" t="n">
         <v>22</v>
       </c>
-      <c r="C43" s="78" t="inlineStr">
+      <c r="C43" s="80" t="inlineStr">
         <is>
           <t>Насос ВКС 2/26</t>
         </is>
@@ -2533,13 +2540,13 @@
       <c r="E43" s="45" t="n">
         <v>863.15</v>
       </c>
-      <c r="F43" s="81" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="95">
-      <c r="B44" s="81" t="n">
+      <c r="F43" s="83" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="96">
+      <c r="B44" s="83" t="n">
         <v>23</v>
       </c>
-      <c r="C44" s="78" t="inlineStr">
+      <c r="C44" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д200/90; 4Д200/90; 1Д250/125</t>
         </is>
@@ -2548,13 +2555,13 @@
       <c r="E44" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F44" s="81" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="95">
-      <c r="B45" s="81" t="n">
+      <c r="F44" s="83" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="96">
+      <c r="B45" s="83" t="n">
         <v>24</v>
       </c>
-      <c r="C45" s="78" t="inlineStr">
+      <c r="C45" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-60/66…330</t>
         </is>
@@ -2563,13 +2570,13 @@
       <c r="E45" s="45" t="n">
         <v>7879.33</v>
       </c>
-      <c r="F45" s="81" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="95">
-      <c r="B46" s="81" t="n">
+      <c r="F45" s="83" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="96">
+      <c r="B46" s="83" t="n">
         <v>25</v>
       </c>
-      <c r="C46" s="78" t="inlineStr">
+      <c r="C46" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve"> Насос 1Д315/71; 1Д320/70</t>
         </is>
@@ -2578,13 +2585,13 @@
       <c r="E46" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F46" s="81" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="95">
-      <c r="B47" s="81" t="n">
+      <c r="F46" s="83" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="96">
+      <c r="B47" s="83" t="n">
         <v>26</v>
       </c>
-      <c r="C47" s="78" t="inlineStr">
+      <c r="C47" s="80" t="inlineStr">
         <is>
           <t>Насос НВД 50/50; НВД 50/80; НВД 35/90</t>
         </is>
@@ -2593,13 +2600,13 @@
       <c r="E47" s="45" t="n">
         <v>1332.63</v>
       </c>
-      <c r="F47" s="81" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="95">
-      <c r="B48" s="81" t="n">
+      <c r="F47" s="83" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="96">
+      <c r="B48" s="83" t="n">
         <v>27</v>
       </c>
-      <c r="C48" s="78" t="inlineStr">
+      <c r="C48" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д1250/90-125</t>
         </is>
@@ -2608,13 +2615,13 @@
       <c r="E48" s="45" t="n">
         <v>5292.31</v>
       </c>
-      <c r="F48" s="81" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="95">
-      <c r="B49" s="81" t="n">
+      <c r="F48" s="83" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="96">
+      <c r="B49" s="83" t="n">
         <v>28</v>
       </c>
-      <c r="C49" s="78" t="inlineStr">
+      <c r="C49" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-180/85…425</t>
         </is>
@@ -2623,13 +2630,13 @@
       <c r="E49" s="45" t="n">
         <v>11898.95</v>
       </c>
-      <c r="F49" s="81" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="95">
-      <c r="B50" s="81" t="n">
+      <c r="F49" s="83" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="96">
+      <c r="B50" s="83" t="n">
         <v>29</v>
       </c>
-      <c r="C50" s="78" t="inlineStr">
+      <c r="C50" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 240/1900 3ТМ</t>
         </is>
@@ -2638,13 +2645,13 @@
       <c r="E50" s="45" t="n">
         <v>44289.38</v>
       </c>
-      <c r="F50" s="81" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="95">
-      <c r="B51" s="81" t="n">
+      <c r="F50" s="83" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="96">
+      <c r="B51" s="83" t="n">
         <v>30</v>
       </c>
-      <c r="C51" s="78" t="inlineStr">
+      <c r="C51" s="80" t="inlineStr">
         <is>
           <t>Насос BUL 6,3/64</t>
         </is>
@@ -2653,13 +2660,13 @@
       <c r="E51" s="45" t="n">
         <v>639.91</v>
       </c>
-      <c r="F51" s="81" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="95">
-      <c r="B52" s="81" t="n">
+      <c r="F51" s="83" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="96">
+      <c r="B52" s="83" t="n">
         <v>31</v>
       </c>
-      <c r="C52" s="78" t="inlineStr">
+      <c r="C52" s="80" t="inlineStr">
         <is>
           <t>Насос 200Д90(200Д/60)</t>
         </is>
@@ -2668,13 +2675,13 @@
       <c r="E52" s="45" t="n">
         <v>3722.29</v>
       </c>
-      <c r="F52" s="81" t="n"/>
-    </row>
-    <row r="53" ht="25.5" customHeight="1" s="95">
-      <c r="B53" s="81" t="n">
+      <c r="F52" s="83" t="n"/>
+    </row>
+    <row r="53" ht="25.5" customHeight="1" s="96">
+      <c r="B53" s="83" t="n">
         <v>32</v>
       </c>
-      <c r="C53" s="78" t="inlineStr">
+      <c r="C53" s="80" t="inlineStr">
         <is>
           <t>Насос KRGH 80/315;KRGH 200/500; KRGH 125/80/315</t>
         </is>
@@ -2683,13 +2690,13 @@
       <c r="E53" s="45" t="n">
         <v>4297.48</v>
       </c>
-      <c r="F53" s="81" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="95">
-      <c r="B54" s="81" t="n">
+      <c r="F53" s="83" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="96">
+      <c r="B54" s="83" t="n">
         <v>33</v>
       </c>
-      <c r="C54" s="78" t="inlineStr">
+      <c r="C54" s="80" t="inlineStr">
         <is>
           <t>Насос ГХИ 6,3/32</t>
         </is>
@@ -2698,13 +2705,13 @@
       <c r="E54" s="45" t="n">
         <v>2017.99</v>
       </c>
-      <c r="F54" s="81" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="95">
-      <c r="B55" s="81" t="n">
+      <c r="F54" s="83" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="96">
+      <c r="B55" s="83" t="n">
         <v>34</v>
       </c>
-      <c r="C55" s="78" t="inlineStr">
+      <c r="C55" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 180/1422…1900 ЗК</t>
         </is>
@@ -2713,10 +2720,10 @@
       <c r="E55" s="45" t="n">
         <v>16393.97</v>
       </c>
-      <c r="F55" s="81" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="95">
-      <c r="B56" s="81" t="n">
+      <c r="F55" s="83" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="96">
+      <c r="B56" s="83" t="n">
         <v>35</v>
       </c>
       <c r="C56" s="50" t="inlineStr">
@@ -2728,13 +2735,13 @@
       <c r="E56" s="45" t="n">
         <v>4773.79</v>
       </c>
-      <c r="F56" s="81">
+      <c r="F56" s="83">
         <f>E56*D56</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="12.75" customHeight="1" s="95">
-      <c r="B57" s="81" t="n">
+    <row r="57" ht="12.75" customHeight="1" s="96">
+      <c r="B57" s="83" t="n">
         <v>36</v>
       </c>
       <c r="C57" s="51" t="inlineStr">
@@ -2746,13 +2753,13 @@
       <c r="E57" s="45" t="n">
         <v>5556.93</v>
       </c>
-      <c r="F57" s="81">
+      <c r="F57" s="83">
         <f>E57*D57</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="95">
-      <c r="B58" s="81" t="n">
+    <row r="58" ht="15" customHeight="1" s="96">
+      <c r="B58" s="83" t="n">
         <v>37</v>
       </c>
       <c r="C58" s="50" t="inlineStr">
@@ -2764,13 +2771,13 @@
       <c r="E58" s="45" t="n">
         <v>5556.93</v>
       </c>
-      <c r="F58" s="81">
+      <c r="F58" s="83">
         <f>E58*D58</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="95">
-      <c r="B59" s="81" t="n">
+    <row r="59" ht="15" customHeight="1" s="96">
+      <c r="B59" s="83" t="n">
         <v>38</v>
       </c>
       <c r="C59" s="51" t="inlineStr">
@@ -2778,17 +2785,17 @@
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D59" s="81" t="n"/>
-      <c r="E59" s="81" t="n">
+      <c r="D59" s="83" t="n"/>
+      <c r="E59" s="83" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F59" s="81">
+      <c r="F59" s="83">
         <f>E59*D59</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="95">
-      <c r="B60" s="81" t="n">
+    <row r="60" ht="15" customHeight="1" s="96">
+      <c r="B60" s="83" t="n">
         <v>39</v>
       </c>
       <c r="C60" s="51" t="inlineStr">
@@ -2796,17 +2803,17 @@
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D60" s="81" t="n"/>
-      <c r="E60" s="81" t="n">
+      <c r="D60" s="83" t="n"/>
+      <c r="E60" s="83" t="n">
         <v>41616.5</v>
       </c>
-      <c r="F60" s="81">
+      <c r="F60" s="83">
         <f>E60*D60</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="95">
-      <c r="B61" s="81" t="n">
+    <row r="61" ht="15" customHeight="1" s="96">
+      <c r="B61" s="83" t="n">
         <v>40</v>
       </c>
       <c r="C61" s="51" t="inlineStr">
@@ -2814,17 +2821,17 @@
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D61" s="81" t="n"/>
-      <c r="E61" s="81" t="n">
+      <c r="D61" s="83" t="n"/>
+      <c r="E61" s="83" t="n">
         <v>6070.81</v>
       </c>
-      <c r="F61" s="81">
+      <c r="F61" s="83">
         <f>E61*D61</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="95">
-      <c r="B62" s="81" t="n">
+    <row r="62" ht="15" customHeight="1" s="96">
+      <c r="B62" s="83" t="n">
         <v>41</v>
       </c>
       <c r="C62" s="51" t="inlineStr">
@@ -2836,13 +2843,13 @@
       <c r="E62" s="45" t="n">
         <v>45915.64</v>
       </c>
-      <c r="F62" s="81">
+      <c r="F62" s="83">
         <f>E62*D62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="12.75" customHeight="1" s="95">
-      <c r="B63" s="81" t="n">
+    <row r="63" ht="12.75" customHeight="1" s="96">
+      <c r="B63" s="83" t="n">
         <v>42</v>
       </c>
       <c r="C63" s="51" t="inlineStr">
@@ -2854,46 +2861,46 @@
       <c r="E63" s="45" t="n">
         <v>45915.64</v>
       </c>
-      <c r="F63" s="81">
+      <c r="F63" s="83">
         <f>E63*D63</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="14.25" customHeight="1" s="95">
-      <c r="B64" s="81" t="n"/>
-      <c r="C64" s="78" t="inlineStr">
+    <row r="64" ht="14.25" customHeight="1" s="96">
+      <c r="B64" s="83" t="n"/>
+      <c r="C64" s="80" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
       <c r="D64" s="45" t="n"/>
       <c r="E64" s="45" t="n"/>
-      <c r="F64" s="81">
+      <c r="F64" s="83">
         <f>SUM(F22:F63)</f>
         <v/>
       </c>
-      <c r="I64" s="82">
+      <c r="I64" s="84">
         <f>F64-H64</f>
         <v/>
       </c>
-      <c r="J64" s="82">
+      <c r="J64" s="84">
         <f>I64-[1]Лот2!$AN$4</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="95">
-      <c r="B65" s="80" t="inlineStr">
+    <row r="65" ht="15.75" customHeight="1" s="96">
+      <c r="B65" s="82" t="inlineStr">
         <is>
           <t>Текущий ремонт</t>
         </is>
       </c>
-      <c r="C65" s="78" t="n"/>
-      <c r="D65" s="81" t="n"/>
-      <c r="E65" s="81" t="n"/>
-      <c r="F65" s="81" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="95">
-      <c r="B66" s="81" t="inlineStr">
+      <c r="C65" s="80" t="n"/>
+      <c r="D65" s="83" t="n"/>
+      <c r="E65" s="83" t="n"/>
+      <c r="F65" s="83" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="96">
+      <c r="B66" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2912,8 +2919,8 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="95">
-      <c r="B67" s="81" t="inlineStr">
+    <row r="67" ht="15" customHeight="1" s="96">
+      <c r="B67" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2929,8 +2936,8 @@
       </c>
       <c r="F67" s="18" t="n"/>
     </row>
-    <row r="68" ht="20.25" customHeight="1" s="95">
-      <c r="B68" s="81" t="inlineStr">
+    <row r="68" ht="20.25" customHeight="1" s="96">
+      <c r="B68" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -2946,8 +2953,8 @@
       </c>
       <c r="F68" s="18" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1" s="95">
-      <c r="B69" s="81" t="inlineStr">
+    <row r="69" ht="15" customHeight="1" s="96">
+      <c r="B69" s="83" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2963,8 +2970,8 @@
       </c>
       <c r="F69" s="18" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1" s="95">
-      <c r="B70" s="81" t="inlineStr">
+    <row r="70" ht="15" customHeight="1" s="96">
+      <c r="B70" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -2980,8 +2987,8 @@
       </c>
       <c r="F70" s="18" t="n"/>
     </row>
-    <row r="71" ht="38.25" customHeight="1" s="95">
-      <c r="B71" s="81" t="inlineStr">
+    <row r="71" ht="38.25" customHeight="1" s="96">
+      <c r="B71" s="83" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -2997,8 +3004,8 @@
       </c>
       <c r="F71" s="18" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1" s="95">
-      <c r="B72" s="81" t="inlineStr">
+    <row r="72" ht="15" customHeight="1" s="96">
+      <c r="B72" s="83" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3014,8 +3021,8 @@
       </c>
       <c r="F72" s="18" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1" s="95">
-      <c r="B73" s="81" t="inlineStr">
+    <row r="73" ht="15" customHeight="1" s="96">
+      <c r="B73" s="83" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3031,8 +3038,8 @@
       </c>
       <c r="F73" s="18" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1" s="95">
-      <c r="B74" s="81" t="inlineStr">
+    <row r="74" ht="15" customHeight="1" s="96">
+      <c r="B74" s="83" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3048,8 +3055,8 @@
       </c>
       <c r="F74" s="18" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1" s="95">
-      <c r="B75" s="81" t="inlineStr">
+    <row r="75" ht="15" customHeight="1" s="96">
+      <c r="B75" s="83" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3065,8 +3072,8 @@
       </c>
       <c r="F75" s="18" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1" s="95">
-      <c r="B76" s="81" t="inlineStr">
+    <row r="76" ht="15" customHeight="1" s="96">
+      <c r="B76" s="83" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3082,8 +3089,8 @@
       </c>
       <c r="F76" s="18" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1" s="95">
-      <c r="B77" s="81" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="96">
+      <c r="B77" s="83" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3099,8 +3106,8 @@
       </c>
       <c r="F77" s="18" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1" s="95">
-      <c r="B78" s="81" t="inlineStr">
+    <row r="78" ht="15" customHeight="1" s="96">
+      <c r="B78" s="83" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -3116,8 +3123,8 @@
       </c>
       <c r="F78" s="18" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1" s="95">
-      <c r="B79" s="81" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="96">
+      <c r="B79" s="83" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -3133,8 +3140,8 @@
       </c>
       <c r="F79" s="18" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="95">
-      <c r="B80" s="81" t="inlineStr">
+    <row r="80" ht="15" customHeight="1" s="96">
+      <c r="B80" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -3150,8 +3157,8 @@
       </c>
       <c r="F80" s="18" t="n"/>
     </row>
-    <row r="81" ht="15" customHeight="1" s="95">
-      <c r="B81" s="81" t="inlineStr">
+    <row r="81" ht="15" customHeight="1" s="96">
+      <c r="B81" s="83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -3167,8 +3174,8 @@
       </c>
       <c r="F81" s="18" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1" s="95">
-      <c r="B82" s="81" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="96">
+      <c r="B82" s="83" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -3184,8 +3191,8 @@
       </c>
       <c r="F82" s="18" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1" s="95">
-      <c r="B83" s="81" t="inlineStr">
+    <row r="83" ht="15" customHeight="1" s="96">
+      <c r="B83" s="83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -3201,8 +3208,8 @@
       </c>
       <c r="F83" s="18" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1" s="95">
-      <c r="B84" s="81" t="inlineStr">
+    <row r="84" ht="15" customHeight="1" s="96">
+      <c r="B84" s="83" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -3218,8 +3225,8 @@
       </c>
       <c r="F84" s="18" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1" s="95">
-      <c r="B85" s="81" t="inlineStr">
+    <row r="85" ht="15" customHeight="1" s="96">
+      <c r="B85" s="83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -3235,8 +3242,8 @@
       </c>
       <c r="F85" s="18" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1" s="95">
-      <c r="B86" s="81" t="inlineStr">
+    <row r="86" ht="15" customHeight="1" s="96">
+      <c r="B86" s="83" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -3252,8 +3259,8 @@
       </c>
       <c r="F86" s="18" t="n"/>
     </row>
-    <row r="87" ht="12.75" customHeight="1" s="95">
-      <c r="B87" s="81" t="inlineStr">
+    <row r="87" ht="12.75" customHeight="1" s="96">
+      <c r="B87" s="83" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -3272,8 +3279,8 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="12.75" customHeight="1" s="95">
-      <c r="B88" s="81" t="inlineStr">
+    <row r="88" ht="12.75" customHeight="1" s="96">
+      <c r="B88" s="83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -3289,8 +3296,8 @@
       </c>
       <c r="F88" s="18" t="n"/>
     </row>
-    <row r="89" ht="12.75" customHeight="1" s="95">
-      <c r="B89" s="81" t="inlineStr">
+    <row r="89" ht="12.75" customHeight="1" s="96">
+      <c r="B89" s="83" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -3306,8 +3313,8 @@
       </c>
       <c r="F89" s="18" t="n"/>
     </row>
-    <row r="90" ht="12.75" customHeight="1" s="95">
-      <c r="B90" s="81" t="inlineStr">
+    <row r="90" ht="12.75" customHeight="1" s="96">
+      <c r="B90" s="83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -3323,8 +3330,8 @@
       </c>
       <c r="F90" s="18" t="n"/>
     </row>
-    <row r="91" ht="12.75" customHeight="1" s="95">
-      <c r="B91" s="81" t="inlineStr">
+    <row r="91" ht="12.75" customHeight="1" s="96">
+      <c r="B91" s="83" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -3340,8 +3347,8 @@
       </c>
       <c r="F91" s="18" t="n"/>
     </row>
-    <row r="92" ht="12.75" customHeight="1" s="95">
-      <c r="B92" s="81" t="inlineStr">
+    <row r="92" ht="12.75" customHeight="1" s="96">
+      <c r="B92" s="83" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -3357,8 +3364,8 @@
       </c>
       <c r="F92" s="18" t="n"/>
     </row>
-    <row r="93" ht="12.75" customHeight="1" s="95">
-      <c r="B93" s="81" t="inlineStr">
+    <row r="93" ht="12.75" customHeight="1" s="96">
+      <c r="B93" s="83" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -3374,8 +3381,8 @@
       </c>
       <c r="F93" s="18" t="n"/>
     </row>
-    <row r="94" ht="12.75" customHeight="1" s="95">
-      <c r="B94" s="81" t="inlineStr">
+    <row r="94" ht="12.75" customHeight="1" s="96">
+      <c r="B94" s="83" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -3391,8 +3398,8 @@
       </c>
       <c r="F94" s="18" t="n"/>
     </row>
-    <row r="95" ht="12.75" customHeight="1" s="95">
-      <c r="B95" s="81" t="inlineStr">
+    <row r="95" ht="12.75" customHeight="1" s="96">
+      <c r="B95" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -3408,8 +3415,8 @@
       </c>
       <c r="F95" s="18" t="n"/>
     </row>
-    <row r="96" ht="12.75" customHeight="1" s="95">
-      <c r="B96" s="81" t="inlineStr">
+    <row r="96" ht="12.75" customHeight="1" s="96">
+      <c r="B96" s="83" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -3425,8 +3432,8 @@
       </c>
       <c r="F96" s="18" t="n"/>
     </row>
-    <row r="97" ht="12.75" customHeight="1" s="95">
-      <c r="B97" s="81" t="inlineStr">
+    <row r="97" ht="12.75" customHeight="1" s="96">
+      <c r="B97" s="83" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -3442,8 +3449,8 @@
       </c>
       <c r="F97" s="18" t="n"/>
     </row>
-    <row r="98" ht="12.75" customHeight="1" s="95">
-      <c r="B98" s="81" t="n">
+    <row r="98" ht="12.75" customHeight="1" s="96">
+      <c r="B98" s="83" t="n">
         <v>33</v>
       </c>
       <c r="C98" s="52" t="inlineStr">
@@ -3457,8 +3464,8 @@
       </c>
       <c r="F98" s="18" t="n"/>
     </row>
-    <row r="99" ht="12.75" customHeight="1" s="95">
-      <c r="B99" s="81" t="inlineStr">
+    <row r="99" ht="12.75" customHeight="1" s="96">
+      <c r="B99" s="83" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -3474,8 +3481,8 @@
       </c>
       <c r="F99" s="18" t="n"/>
     </row>
-    <row r="100" ht="12.75" customHeight="1" s="95">
-      <c r="B100" s="81" t="inlineStr">
+    <row r="100" ht="12.75" customHeight="1" s="96">
+      <c r="B100" s="83" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -3491,8 +3498,8 @@
       </c>
       <c r="F100" s="18" t="n"/>
     </row>
-    <row r="101" ht="18" customHeight="1" s="95">
-      <c r="B101" s="81" t="inlineStr">
+    <row r="101" ht="18" customHeight="1" s="96">
+      <c r="B101" s="83" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -3511,8 +3518,8 @@
         <v/>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="95">
-      <c r="B102" s="81" t="inlineStr">
+    <row r="102" ht="15" customHeight="1" s="96">
+      <c r="B102" s="83" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -3531,8 +3538,8 @@
         <v/>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="95">
-      <c r="B103" s="81" t="inlineStr">
+    <row r="103" ht="15" customHeight="1" s="96">
+      <c r="B103" s="83" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -3551,8 +3558,8 @@
         <v/>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" s="95">
-      <c r="B104" s="81" t="inlineStr">
+    <row r="104" ht="15" customHeight="1" s="96">
+      <c r="B104" s="83" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -3571,8 +3578,8 @@
         <v/>
       </c>
     </row>
-    <row r="105" ht="12.75" customHeight="1" s="95">
-      <c r="B105" s="81" t="inlineStr">
+    <row r="105" ht="12.75" customHeight="1" s="96">
+      <c r="B105" s="83" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -3591,8 +3598,8 @@
         <v/>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" s="95">
-      <c r="B106" s="81" t="inlineStr">
+    <row r="106" ht="15" customHeight="1" s="96">
+      <c r="B106" s="83" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -3611,8 +3618,8 @@
         <v/>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1" s="95">
-      <c r="B107" s="81" t="inlineStr">
+    <row r="107" ht="15" customHeight="1" s="96">
+      <c r="B107" s="83" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -3631,8 +3638,8 @@
         <v/>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="95">
-      <c r="B108" s="81" t="inlineStr">
+    <row r="108" ht="15" customHeight="1" s="96">
+      <c r="B108" s="83" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -3651,8 +3658,8 @@
         <v/>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" s="95">
-      <c r="B109" s="81" t="inlineStr">
+    <row r="109" ht="15" customHeight="1" s="96">
+      <c r="B109" s="83" t="inlineStr">
         <is>
           <t>44</t>
         </is>
@@ -3671,8 +3678,8 @@
         <v/>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1" s="95">
-      <c r="B110" s="81" t="inlineStr">
+    <row r="110" ht="15" customHeight="1" s="96">
+      <c r="B110" s="83" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -3691,8 +3698,8 @@
         <v/>
       </c>
     </row>
-    <row r="111" ht="15" customHeight="1" s="95">
-      <c r="B111" s="81" t="inlineStr">
+    <row r="111" ht="15" customHeight="1" s="96">
+      <c r="B111" s="83" t="inlineStr">
         <is>
           <t>46</t>
         </is>
@@ -3711,38 +3718,38 @@
         <v/>
       </c>
     </row>
-    <row r="112" ht="14.25" customHeight="1" s="95">
-      <c r="B112" s="81" t="n"/>
+    <row r="112" ht="14.25" customHeight="1" s="96">
+      <c r="B112" s="83" t="n"/>
       <c r="C112" s="46" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D112" s="81" t="n"/>
-      <c r="E112" s="81" t="n"/>
-      <c r="F112" s="81">
+      <c r="D112" s="83" t="n"/>
+      <c r="E112" s="83" t="n"/>
+      <c r="F112" s="83">
         <f>SUM(F66:F111)</f>
         <v/>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1" s="95">
-      <c r="B113" s="77" t="inlineStr">
+    <row r="113" ht="15" customHeight="1" s="96">
+      <c r="B113" s="79" t="inlineStr">
         <is>
           <t>Пуско-наладка насосного  оборудования</t>
         </is>
       </c>
-      <c r="C113" s="78" t="n"/>
-      <c r="D113" s="81" t="n"/>
-      <c r="E113" s="81" t="n"/>
+      <c r="C113" s="80" t="n"/>
+      <c r="D113" s="83" t="n"/>
+      <c r="E113" s="83" t="n"/>
       <c r="F113" s="18" t="n"/>
-      <c r="G113" s="81" t="n"/>
-      <c r="H113" s="77" t="n"/>
-      <c r="J113" s="82" t="n">
+      <c r="G113" s="83" t="n"/>
+      <c r="H113" s="79" t="n"/>
+      <c r="J113" s="84" t="n">
         <v>115488.03</v>
       </c>
     </row>
-    <row r="114" ht="15" customHeight="1" s="95">
-      <c r="B114" s="81" t="inlineStr">
+    <row r="114" ht="15" customHeight="1" s="96">
+      <c r="B114" s="83" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3752,22 +3759,22 @@
           <t>Насос 12НА9/4, 12НА22/6</t>
         </is>
       </c>
-      <c r="D114" s="81" t="n"/>
-      <c r="E114" s="81" t="n">
+      <c r="D114" s="83" t="n"/>
+      <c r="E114" s="83" t="n">
         <v>8693.879999999999</v>
       </c>
       <c r="F114" s="18">
         <f>E114*D114</f>
         <v/>
       </c>
-      <c r="G114" s="81" t="n"/>
-      <c r="H114" s="77" t="n"/>
-      <c r="J114" s="82" t="n">
+      <c r="G114" s="83" t="n"/>
+      <c r="H114" s="79" t="n"/>
+      <c r="J114" s="84" t="n">
         <v>20102.27</v>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1" s="95">
-      <c r="B115" s="81" t="inlineStr">
+    <row r="115" ht="15" customHeight="1" s="96">
+      <c r="B115" s="83" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3785,14 +3792,14 @@
         <f>E115*D115</f>
         <v/>
       </c>
-      <c r="G115" s="81" t="n"/>
-      <c r="H115" s="77" t="n"/>
-      <c r="J115" s="82" t="n">
+      <c r="G115" s="83" t="n"/>
+      <c r="H115" s="79" t="n"/>
+      <c r="J115" s="84" t="n">
         <v>1434.51</v>
       </c>
     </row>
-    <row r="116" ht="25.5" customHeight="1" s="95">
-      <c r="B116" s="81" t="inlineStr">
+    <row r="116" ht="25.5" customHeight="1" s="96">
+      <c r="B116" s="83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3810,14 +3817,14 @@
         <f>E116*D116</f>
         <v/>
       </c>
-      <c r="G116" s="81" t="n"/>
-      <c r="H116" s="77" t="n"/>
-      <c r="J116" s="82" t="n">
+      <c r="G116" s="83" t="n"/>
+      <c r="H116" s="79" t="n"/>
+      <c r="J116" s="84" t="n">
         <v>8391.780000000001</v>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="95">
-      <c r="B117" s="81" t="inlineStr">
+    <row r="117" ht="15" customHeight="1" s="96">
+      <c r="B117" s="83" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3835,14 +3842,14 @@
         <f>E117*D117</f>
         <v/>
       </c>
-      <c r="G117" s="81" t="n"/>
-      <c r="H117" s="77" t="n"/>
-      <c r="J117" s="82" t="n">
+      <c r="G117" s="83" t="n"/>
+      <c r="H117" s="79" t="n"/>
+      <c r="J117" s="84" t="n">
         <v>38496.01</v>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="95">
-      <c r="B118" s="81" t="inlineStr">
+    <row r="118" ht="15" customHeight="1" s="96">
+      <c r="B118" s="83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3860,11 +3867,11 @@
         <f>E118*D118</f>
         <v/>
       </c>
-      <c r="G118" s="81" t="n"/>
-      <c r="H118" s="77" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="95">
-      <c r="B119" s="81" t="inlineStr">
+      <c r="G118" s="83" t="n"/>
+      <c r="H118" s="79" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="96">
+      <c r="B119" s="83" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3882,11 +3889,11 @@
         <f>E119*D119</f>
         <v/>
       </c>
-      <c r="G119" s="81" t="n"/>
-      <c r="H119" s="77" t="n"/>
-    </row>
-    <row r="120" ht="38.25" customHeight="1" s="95">
-      <c r="B120" s="81" t="inlineStr">
+      <c r="G119" s="83" t="n"/>
+      <c r="H119" s="79" t="n"/>
+    </row>
+    <row r="120" ht="38.25" customHeight="1" s="96">
+      <c r="B120" s="83" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3904,11 +3911,11 @@
         <f>E120*D120</f>
         <v/>
       </c>
-      <c r="G120" s="81" t="n"/>
-      <c r="H120" s="77" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1" s="95">
-      <c r="B121" s="81" t="inlineStr">
+      <c r="G120" s="83" t="n"/>
+      <c r="H120" s="79" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="96">
+      <c r="B121" s="83" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3923,11 +3930,11 @@
         <v>1486.15</v>
       </c>
       <c r="F121" s="18" t="n"/>
-      <c r="G121" s="81" t="n"/>
-      <c r="H121" s="77" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="95">
-      <c r="B122" s="81" t="inlineStr">
+      <c r="G121" s="83" t="n"/>
+      <c r="H121" s="79" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="96">
+      <c r="B122" s="83" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3942,11 +3949,11 @@
         <v>7053.6</v>
       </c>
       <c r="F122" s="18" t="n"/>
-      <c r="G122" s="81" t="n"/>
-      <c r="H122" s="77" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="95">
-      <c r="B123" s="81" t="inlineStr">
+      <c r="G122" s="83" t="n"/>
+      <c r="H122" s="79" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="96">
+      <c r="B123" s="83" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3961,11 +3968,11 @@
         <v>21627.72</v>
       </c>
       <c r="F123" s="18" t="n"/>
-      <c r="G123" s="81" t="n"/>
-      <c r="H123" s="77" t="n"/>
-    </row>
-    <row r="124" ht="15" customHeight="1" s="95">
-      <c r="B124" s="81" t="inlineStr">
+      <c r="G123" s="83" t="n"/>
+      <c r="H123" s="79" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1" s="96">
+      <c r="B124" s="83" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3980,11 +3987,11 @@
         <v>7898.48</v>
       </c>
       <c r="F124" s="18" t="n"/>
-      <c r="G124" s="81" t="n"/>
-      <c r="H124" s="77" t="n"/>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="95">
-      <c r="B125" s="81" t="inlineStr">
+      <c r="G124" s="83" t="n"/>
+      <c r="H124" s="79" t="n"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="96">
+      <c r="B125" s="83" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -3999,11 +4006,11 @@
         <v>1486.15</v>
       </c>
       <c r="F125" s="18" t="n"/>
-      <c r="G125" s="81" t="n"/>
-      <c r="H125" s="77" t="n"/>
-    </row>
-    <row r="126" ht="15" customHeight="1" s="95">
-      <c r="B126" s="81" t="inlineStr">
+      <c r="G125" s="83" t="n"/>
+      <c r="H125" s="79" t="n"/>
+    </row>
+    <row r="126" ht="15" customHeight="1" s="96">
+      <c r="B126" s="83" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -4018,11 +4025,11 @@
         <v>6515.95</v>
       </c>
       <c r="F126" s="18" t="n"/>
-      <c r="G126" s="81" t="n"/>
-      <c r="H126" s="77" t="n"/>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="95">
-      <c r="B127" s="81" t="inlineStr">
+      <c r="G126" s="83" t="n"/>
+      <c r="H126" s="79" t="n"/>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="96">
+      <c r="B127" s="83" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -4037,11 +4044,11 @@
         <v>18106.45</v>
       </c>
       <c r="F127" s="18" t="n"/>
-      <c r="G127" s="81" t="n"/>
-      <c r="H127" s="77" t="n"/>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="95">
-      <c r="B128" s="81" t="inlineStr">
+      <c r="G127" s="83" t="n"/>
+      <c r="H127" s="79" t="n"/>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="96">
+      <c r="B128" s="83" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -4056,11 +4063,11 @@
         <v>21595.33</v>
       </c>
       <c r="F128" s="18" t="n"/>
-      <c r="G128" s="81" t="n"/>
-      <c r="H128" s="77" t="n"/>
-    </row>
-    <row r="129" ht="15" customHeight="1" s="95">
-      <c r="B129" s="81" t="inlineStr">
+      <c r="G128" s="83" t="n"/>
+      <c r="H128" s="79" t="n"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="96">
+      <c r="B129" s="83" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -4075,11 +4082,11 @@
         <v>34381.12</v>
       </c>
       <c r="F129" s="18" t="n"/>
-      <c r="G129" s="81" t="n"/>
-      <c r="H129" s="77" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="95">
-      <c r="B130" s="81" t="inlineStr">
+      <c r="G129" s="83" t="n"/>
+      <c r="H129" s="79" t="n"/>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="96">
+      <c r="B130" s="83" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -4094,11 +4101,11 @@
         <v>30532.49</v>
       </c>
       <c r="F130" s="18" t="n"/>
-      <c r="G130" s="81" t="n"/>
-      <c r="H130" s="77" t="n"/>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="95">
-      <c r="B131" s="81" t="inlineStr">
+      <c r="G130" s="83" t="n"/>
+      <c r="H130" s="79" t="n"/>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="96">
+      <c r="B131" s="83" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -4113,11 +4120,11 @@
         <v>34381.12</v>
       </c>
       <c r="F131" s="18" t="n"/>
-      <c r="G131" s="81" t="n"/>
-      <c r="H131" s="77" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="95">
-      <c r="B132" s="81" t="inlineStr">
+      <c r="G131" s="83" t="n"/>
+      <c r="H131" s="79" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="96">
+      <c r="B132" s="83" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -4132,11 +4139,11 @@
         <v>39881.87</v>
       </c>
       <c r="F132" s="18" t="n"/>
-      <c r="G132" s="81" t="n"/>
-      <c r="H132" s="77" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="95">
-      <c r="B133" s="81" t="inlineStr">
+      <c r="G132" s="83" t="n"/>
+      <c r="H132" s="79" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="96">
+      <c r="B133" s="83" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4151,11 +4158,11 @@
         <v>7053.6</v>
       </c>
       <c r="F133" s="18" t="n"/>
-      <c r="G133" s="81" t="n"/>
-      <c r="H133" s="77" t="n"/>
-    </row>
-    <row r="134" ht="15" customHeight="1" s="95">
-      <c r="B134" s="81" t="inlineStr">
+      <c r="G133" s="83" t="n"/>
+      <c r="H133" s="79" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="96">
+      <c r="B134" s="83" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -4173,11 +4180,11 @@
         <f>E134*D134</f>
         <v/>
       </c>
-      <c r="G134" s="81" t="n"/>
-      <c r="H134" s="77" t="n"/>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="95">
-      <c r="B135" s="81" t="inlineStr">
+      <c r="G134" s="83" t="n"/>
+      <c r="H134" s="79" t="n"/>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="96">
+      <c r="B135" s="83" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -4195,11 +4202,11 @@
         <f>E135*D135</f>
         <v/>
       </c>
-      <c r="G135" s="81" t="n"/>
-      <c r="H135" s="77" t="n"/>
-    </row>
-    <row r="136" ht="15" customHeight="1" s="95">
-      <c r="B136" s="81" t="inlineStr">
+      <c r="G135" s="83" t="n"/>
+      <c r="H135" s="79" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" s="96">
+      <c r="B136" s="83" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -4217,11 +4224,11 @@
         <f>E136*D136</f>
         <v/>
       </c>
-      <c r="G136" s="81" t="n"/>
-      <c r="H136" s="77" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="95">
-      <c r="B137" s="81" t="inlineStr">
+      <c r="G136" s="83" t="n"/>
+      <c r="H136" s="79" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="96">
+      <c r="B137" s="83" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -4239,11 +4246,11 @@
         <f>E137*D137</f>
         <v/>
       </c>
-      <c r="G137" s="81" t="n"/>
-      <c r="H137" s="77" t="n"/>
-    </row>
-    <row r="138" ht="15" customHeight="1" s="95">
-      <c r="B138" s="81" t="inlineStr">
+      <c r="G137" s="83" t="n"/>
+      <c r="H137" s="79" t="n"/>
+    </row>
+    <row r="138" ht="15" customHeight="1" s="96">
+      <c r="B138" s="83" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -4261,11 +4268,11 @@
         <f>E138*D138</f>
         <v/>
       </c>
-      <c r="G138" s="81" t="n"/>
-      <c r="H138" s="77" t="n"/>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="95">
-      <c r="B139" s="81" t="inlineStr">
+      <c r="G138" s="83" t="n"/>
+      <c r="H138" s="79" t="n"/>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="96">
+      <c r="B139" s="83" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -4283,11 +4290,11 @@
         <f>E139*D139</f>
         <v/>
       </c>
-      <c r="G139" s="81" t="n"/>
-      <c r="H139" s="77" t="n"/>
-    </row>
-    <row r="140" ht="25.5" customHeight="1" s="95">
-      <c r="B140" s="81" t="inlineStr">
+      <c r="G139" s="83" t="n"/>
+      <c r="H139" s="79" t="n"/>
+    </row>
+    <row r="140" ht="25.5" customHeight="1" s="96">
+      <c r="B140" s="83" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -4305,11 +4312,11 @@
         <f>E140*D140</f>
         <v/>
       </c>
-      <c r="G140" s="81" t="n"/>
-      <c r="H140" s="77" t="n"/>
-    </row>
-    <row r="141" ht="15" customHeight="1" s="95">
-      <c r="B141" s="81" t="inlineStr">
+      <c r="G140" s="83" t="n"/>
+      <c r="H140" s="79" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="96">
+      <c r="B141" s="83" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -4327,11 +4334,11 @@
         <f>E141*D141</f>
         <v/>
       </c>
-      <c r="G141" s="81" t="n"/>
-      <c r="H141" s="77" t="n"/>
-    </row>
-    <row r="142" ht="15" customHeight="1" s="95">
-      <c r="B142" s="81" t="inlineStr">
+      <c r="G141" s="83" t="n"/>
+      <c r="H141" s="79" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="96">
+      <c r="B142" s="83" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -4349,11 +4356,11 @@
         <f>E142*D142</f>
         <v/>
       </c>
-      <c r="G142" s="81" t="n"/>
-      <c r="H142" s="77" t="n"/>
-    </row>
-    <row r="143" ht="15" customHeight="1" s="95">
-      <c r="B143" s="81" t="inlineStr">
+      <c r="G142" s="83" t="n"/>
+      <c r="H142" s="79" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="96">
+      <c r="B143" s="83" t="inlineStr">
         <is>
           <t>30</t>
         </is>
@@ -4368,11 +4375,11 @@
         <v>7053.6</v>
       </c>
       <c r="F143" s="18" t="n"/>
-      <c r="G143" s="81" t="n"/>
-      <c r="H143" s="77" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="95">
-      <c r="B144" s="81" t="inlineStr">
+      <c r="G143" s="83" t="n"/>
+      <c r="H143" s="79" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="96">
+      <c r="B144" s="83" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -4387,11 +4394,11 @@
         <v>7406.28</v>
       </c>
       <c r="F144" s="18" t="n"/>
-      <c r="G144" s="81" t="n"/>
-      <c r="H144" s="77" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" s="95">
-      <c r="B145" s="81" t="inlineStr">
+      <c r="G144" s="83" t="n"/>
+      <c r="H144" s="79" t="n"/>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="96">
+      <c r="B145" s="83" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -4406,11 +4413,11 @@
         <v>7406.28</v>
       </c>
       <c r="F145" s="18" t="n"/>
-      <c r="G145" s="81" t="n"/>
-      <c r="H145" s="77" t="n"/>
-    </row>
-    <row r="146" ht="15" customHeight="1" s="95">
-      <c r="B146" s="81" t="inlineStr">
+      <c r="G145" s="83" t="n"/>
+      <c r="H145" s="79" t="n"/>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="96">
+      <c r="B146" s="83" t="inlineStr">
         <is>
           <t>33</t>
         </is>
@@ -4425,11 +4432,11 @@
         <v>39881.87</v>
       </c>
       <c r="F146" s="18" t="n"/>
-      <c r="G146" s="81" t="n"/>
-      <c r="H146" s="77" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1" s="95">
-      <c r="B147" s="81" t="inlineStr">
+      <c r="G146" s="83" t="n"/>
+      <c r="H146" s="79" t="n"/>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="96">
+      <c r="B147" s="83" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -4447,11 +4454,11 @@
         <f>E147*D147</f>
         <v/>
       </c>
-      <c r="G147" s="81" t="n"/>
-      <c r="H147" s="77" t="n"/>
-    </row>
-    <row r="148" ht="15" customHeight="1" s="95">
-      <c r="B148" s="81" t="inlineStr">
+      <c r="G147" s="83" t="n"/>
+      <c r="H147" s="79" t="n"/>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="96">
+      <c r="B148" s="83" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -4469,11 +4476,11 @@
         <f>E148*D148</f>
         <v/>
       </c>
-      <c r="G148" s="81" t="n"/>
-      <c r="H148" s="77" t="n"/>
-    </row>
-    <row r="149" ht="15" customHeight="1" s="95">
-      <c r="B149" s="81" t="inlineStr">
+      <c r="G148" s="83" t="n"/>
+      <c r="H148" s="79" t="n"/>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="96">
+      <c r="B149" s="83" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -4491,11 +4498,11 @@
         <f>E149*D149</f>
         <v/>
       </c>
-      <c r="G149" s="81" t="n"/>
-      <c r="H149" s="77" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1" s="95">
-      <c r="B150" s="81" t="inlineStr">
+      <c r="G149" s="83" t="n"/>
+      <c r="H149" s="79" t="n"/>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="96">
+      <c r="B150" s="83" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -4513,39 +4520,39 @@
         <f>E150*D150</f>
         <v/>
       </c>
-      <c r="G150" s="81" t="n"/>
-      <c r="H150" s="77" t="n"/>
-    </row>
-    <row r="151" ht="14.25" customHeight="1" s="95">
-      <c r="B151" s="77" t="n"/>
-      <c r="C151" s="78" t="inlineStr">
+      <c r="G150" s="83" t="n"/>
+      <c r="H150" s="79" t="n"/>
+    </row>
+    <row r="151" ht="14.25" customHeight="1" s="96">
+      <c r="B151" s="79" t="n"/>
+      <c r="C151" s="80" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D151" s="81" t="n"/>
-      <c r="E151" s="81" t="n"/>
+      <c r="D151" s="83" t="n"/>
+      <c r="E151" s="83" t="n"/>
       <c r="F151" s="18">
         <f>SUM(F114:F150)</f>
         <v/>
       </c>
-      <c r="G151" s="81" t="n"/>
-      <c r="H151" s="77" t="n"/>
-    </row>
-    <row r="152" ht="14.25" customHeight="1" s="95">
-      <c r="B152" s="77" t="inlineStr">
+      <c r="G151" s="83" t="n"/>
+      <c r="H151" s="79" t="n"/>
+    </row>
+    <row r="152" ht="14.25" customHeight="1" s="96">
+      <c r="B152" s="79" t="inlineStr">
         <is>
           <t>Установка оборудования</t>
         </is>
       </c>
-      <c r="C152" s="78" t="n"/>
-      <c r="D152" s="81" t="n"/>
-      <c r="E152" s="81" t="n"/>
+      <c r="C152" s="80" t="n"/>
+      <c r="D152" s="83" t="n"/>
+      <c r="E152" s="83" t="n"/>
       <c r="F152" s="18" t="n"/>
-      <c r="G152" s="81" t="n"/>
-      <c r="H152" s="77" t="n"/>
-    </row>
-    <row r="153" ht="40.5" customHeight="1" s="95">
+      <c r="G152" s="83" t="n"/>
+      <c r="H152" s="79" t="n"/>
+    </row>
+    <row r="153" ht="40.5" customHeight="1" s="96">
       <c r="B153" s="3" t="n">
         <v>1</v>
       </c>
@@ -4554,18 +4561,18 @@
           <t>Насос 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D153" s="81" t="n"/>
-      <c r="E153" s="81" t="n">
+      <c r="D153" s="83" t="n"/>
+      <c r="E153" s="83" t="n">
         <v>5519.78</v>
       </c>
       <c r="F153" s="18">
         <f>E153*D153</f>
         <v/>
       </c>
-      <c r="G153" s="81" t="n"/>
-      <c r="H153" s="77" t="n"/>
-    </row>
-    <row r="154" ht="25.5" customHeight="1" s="95">
+      <c r="G153" s="83" t="n"/>
+      <c r="H153" s="79" t="n"/>
+    </row>
+    <row r="154" ht="25.5" customHeight="1" s="96">
       <c r="B154" s="3" t="n">
         <v>2</v>
       </c>
@@ -4574,18 +4581,18 @@
           <t>Насос дозировочный типа НД, ДП, PIAX 32/28; PAX 32/12; BUL 6,3/64</t>
         </is>
       </c>
-      <c r="D154" s="81" t="n"/>
-      <c r="E154" s="81" t="n">
+      <c r="D154" s="83" t="n"/>
+      <c r="E154" s="83" t="n">
         <v>1559.69</v>
       </c>
       <c r="F154" s="18">
         <f>E154*D154</f>
         <v/>
       </c>
-      <c r="G154" s="81" t="n"/>
-      <c r="H154" s="77" t="n"/>
-    </row>
-    <row r="155" ht="16.5" customHeight="1" s="95">
+      <c r="G154" s="83" t="n"/>
+      <c r="H154" s="79" t="n"/>
+    </row>
+    <row r="155" ht="16.5" customHeight="1" s="96">
       <c r="B155" s="3" t="n">
         <v>3</v>
       </c>
@@ -4594,18 +4601,18 @@
           <t>Насос ЦНС-38/44…220; ЦНС 13/70…350;  ЦГ 6,3/32;</t>
         </is>
       </c>
-      <c r="D155" s="81" t="n"/>
-      <c r="E155" s="81" t="n">
+      <c r="D155" s="83" t="n"/>
+      <c r="E155" s="83" t="n">
         <v>17361.15</v>
       </c>
       <c r="F155" s="18">
         <f>E155*D155</f>
         <v/>
       </c>
-      <c r="G155" s="81" t="n"/>
-      <c r="H155" s="77" t="n"/>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="95">
+      <c r="G155" s="83" t="n"/>
+      <c r="H155" s="79" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="96">
       <c r="B156" s="3" t="n">
         <v>4</v>
       </c>
@@ -4614,18 +4621,18 @@
           <t>Насос 1Д630/90, Д630/125</t>
         </is>
       </c>
-      <c r="D156" s="81" t="n"/>
-      <c r="E156" s="81" t="n">
+      <c r="D156" s="83" t="n"/>
+      <c r="E156" s="83" t="n">
         <v>12708.86</v>
       </c>
       <c r="F156" s="18">
         <f>E156*D156</f>
         <v/>
       </c>
-      <c r="G156" s="81" t="n"/>
-      <c r="H156" s="77" t="n"/>
-    </row>
-    <row r="157" ht="44.25" customHeight="1" s="95">
+      <c r="G156" s="83" t="n"/>
+      <c r="H156" s="79" t="n"/>
+    </row>
+    <row r="157" ht="44.25" customHeight="1" s="96">
       <c r="B157" s="3" t="n">
         <v>5</v>
       </c>
@@ -4634,18 +4641,18 @@
           <t>Насос К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175, К 100-80-160;К 100-65-200, КМ 160-65-200, 3Т13Н; ЦВК 6,3/160;ВКС 2/26;</t>
         </is>
       </c>
-      <c r="D157" s="81" t="n"/>
-      <c r="E157" s="81" t="n">
+      <c r="D157" s="83" t="n"/>
+      <c r="E157" s="83" t="n">
         <v>2047.93</v>
       </c>
       <c r="F157" s="18">
         <f>E157*D157</f>
         <v/>
       </c>
-      <c r="G157" s="81" t="n"/>
-      <c r="H157" s="77" t="n"/>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="95">
+      <c r="G157" s="83" t="n"/>
+      <c r="H157" s="79" t="n"/>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="96">
       <c r="B158" s="3" t="n">
         <v>6</v>
       </c>
@@ -4654,18 +4661,18 @@
           <t>Насос НМШ 5/25; 8/25;</t>
         </is>
       </c>
-      <c r="D158" s="81" t="n"/>
-      <c r="E158" s="81" t="n">
+      <c r="D158" s="83" t="n"/>
+      <c r="E158" s="83" t="n">
         <v>1373.17</v>
       </c>
       <c r="F158" s="18">
         <f>E158*D158</f>
         <v/>
       </c>
-      <c r="G158" s="81" t="n"/>
-      <c r="H158" s="77" t="n"/>
-    </row>
-    <row r="159" ht="51" customHeight="1" s="95">
+      <c r="G158" s="83" t="n"/>
+      <c r="H158" s="79" t="n"/>
+    </row>
+    <row r="159" ht="51" customHeight="1" s="96">
       <c r="B159" s="3" t="n">
         <v>7</v>
       </c>
@@ -4674,18 +4681,18 @@
           <t>Насос ЦНС-105/98...490; ЦНС 180/170…425; ЦНС-180/1422…1900; ЦНС 180/240/1422...1900 (2ТМ, 3ТМ); ЦНС 180/240/1422...1900 ЗК; ЦНС 63/1800; ЦНС 40/1400;</t>
         </is>
       </c>
-      <c r="D159" s="81" t="n"/>
-      <c r="E159" s="81" t="n">
+      <c r="D159" s="83" t="n"/>
+      <c r="E159" s="83" t="n">
         <v>40029.98</v>
       </c>
       <c r="F159" s="18">
         <f>E159*D159</f>
         <v/>
       </c>
-      <c r="G159" s="81" t="n"/>
-      <c r="H159" s="77" t="n"/>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="95">
+      <c r="G159" s="83" t="n"/>
+      <c r="H159" s="79" t="n"/>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="96">
       <c r="B160" s="3" t="n">
         <v>8</v>
       </c>
@@ -4694,18 +4701,18 @@
           <t>Насос НПВ1250-60/90</t>
         </is>
       </c>
-      <c r="D160" s="81" t="n"/>
-      <c r="E160" s="81" t="n">
+      <c r="D160" s="83" t="n"/>
+      <c r="E160" s="83" t="n">
         <v>41116.26</v>
       </c>
       <c r="F160" s="18">
         <f>E160*D160</f>
         <v/>
       </c>
-      <c r="G160" s="81" t="n"/>
-      <c r="H160" s="77" t="n"/>
-    </row>
-    <row r="161" ht="25.5" customHeight="1" s="95">
+      <c r="G160" s="83" t="n"/>
+      <c r="H160" s="79" t="n"/>
+    </row>
+    <row r="161" ht="25.5" customHeight="1" s="96">
       <c r="B161" s="3" t="n">
         <v>9</v>
       </c>
@@ -4714,18 +4721,18 @@
           <t>Насос 1Д200/90, 1Д315/71, 4Д200/90, 1Д320/70, 1Д250/125</t>
         </is>
       </c>
-      <c r="D161" s="81" t="n"/>
-      <c r="E161" s="81" t="n">
+      <c r="D161" s="83" t="n"/>
+      <c r="E161" s="83" t="n">
         <v>6310.95</v>
       </c>
       <c r="F161" s="18">
         <f>E161*D161</f>
         <v/>
       </c>
-      <c r="G161" s="81" t="n"/>
-      <c r="H161" s="77" t="n"/>
-    </row>
-    <row r="162" ht="15" customHeight="1" s="95">
+      <c r="G161" s="83" t="n"/>
+      <c r="H161" s="79" t="n"/>
+    </row>
+    <row r="162" ht="15" customHeight="1" s="96">
       <c r="B162" s="3" t="n">
         <v>10</v>
       </c>
@@ -4734,18 +4741,18 @@
           <t>Насос ЦНС-60/66...330;</t>
         </is>
       </c>
-      <c r="D162" s="81" t="n"/>
-      <c r="E162" s="81" t="n">
+      <c r="D162" s="83" t="n"/>
+      <c r="E162" s="83" t="n">
         <v>17988.94</v>
       </c>
       <c r="F162" s="18">
         <f>E162*D162</f>
         <v/>
       </c>
-      <c r="G162" s="81" t="n"/>
-      <c r="H162" s="77" t="n"/>
-    </row>
-    <row r="163" ht="15" customHeight="1" s="95">
+      <c r="G162" s="83" t="n"/>
+      <c r="H162" s="79" t="n"/>
+    </row>
+    <row r="163" ht="15" customHeight="1" s="96">
       <c r="B163" s="3" t="n">
         <v>11</v>
       </c>
@@ -4754,18 +4761,18 @@
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D163" s="81" t="n"/>
-      <c r="E163" s="81" t="n">
+      <c r="D163" s="83" t="n"/>
+      <c r="E163" s="83" t="n">
         <v>42583.13</v>
       </c>
       <c r="F163" s="18">
         <f>E163*D163</f>
         <v/>
       </c>
-      <c r="G163" s="81" t="n"/>
-      <c r="H163" s="77" t="n"/>
-    </row>
-    <row r="164" ht="38.25" customHeight="1" s="95">
+      <c r="G163" s="83" t="n"/>
+      <c r="H163" s="79" t="n"/>
+    </row>
+    <row r="164" ht="38.25" customHeight="1" s="96">
       <c r="B164" s="3" t="n">
         <v>12</v>
       </c>
@@ -4774,18 +4781,18 @@
           <t>Насос АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D164" s="81" t="n"/>
-      <c r="E164" s="81" t="n">
+      <c r="D164" s="83" t="n"/>
+      <c r="E164" s="83" t="n">
         <v>5519.78</v>
       </c>
       <c r="F164" s="18">
         <f>E164*D164</f>
         <v/>
       </c>
-      <c r="G164" s="81" t="n"/>
-      <c r="H164" s="77" t="n"/>
-    </row>
-    <row r="165" ht="15" customHeight="1" s="95">
+      <c r="G164" s="83" t="n"/>
+      <c r="H164" s="79" t="n"/>
+    </row>
+    <row r="165" ht="15" customHeight="1" s="96">
       <c r="B165" s="3" t="n">
         <v>13</v>
       </c>
@@ -4794,18 +4801,18 @@
           <t>Насос 1Д1250/90-125</t>
         </is>
       </c>
-      <c r="D165" s="81" t="n"/>
-      <c r="E165" s="81" t="n">
+      <c r="D165" s="83" t="n"/>
+      <c r="E165" s="83" t="n">
         <v>15135.48</v>
       </c>
       <c r="F165" s="18">
         <f>E165*D165</f>
         <v/>
       </c>
-      <c r="G165" s="81" t="n"/>
-      <c r="H165" s="77" t="n"/>
-    </row>
-    <row r="166" ht="23.25" customHeight="1" s="95">
+      <c r="G165" s="83" t="n"/>
+      <c r="H165" s="79" t="n"/>
+    </row>
+    <row r="166" ht="23.25" customHeight="1" s="96">
       <c r="B166" s="3" t="n">
         <v>14</v>
       </c>
@@ -4814,18 +4821,18 @@
           <t>Насос KRGH 80/315,KRGH 200/500, KRGH 125/80/315</t>
         </is>
       </c>
-      <c r="D166" s="81" t="n"/>
-      <c r="E166" s="81" t="n">
+      <c r="D166" s="83" t="n"/>
+      <c r="E166" s="83" t="n">
         <v>21541.65</v>
       </c>
       <c r="F166" s="18">
         <f>E166*D166</f>
         <v/>
       </c>
-      <c r="G166" s="81" t="n"/>
-      <c r="H166" s="77" t="n"/>
-    </row>
-    <row r="167" ht="38.25" customHeight="1" s="95">
+      <c r="G166" s="83" t="n"/>
+      <c r="H166" s="79" t="n"/>
+    </row>
+    <row r="167" ht="38.25" customHeight="1" s="96">
       <c r="B167" s="3" t="n">
         <v>15</v>
       </c>
@@ -4834,18 +4841,18 @@
           <t>Насос  АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D167" s="81" t="n"/>
-      <c r="E167" s="81" t="n">
+      <c r="D167" s="83" t="n"/>
+      <c r="E167" s="83" t="n">
         <v>5519.78</v>
       </c>
       <c r="F167" s="18">
         <f>E167*D167</f>
         <v/>
       </c>
-      <c r="G167" s="81" t="n"/>
-      <c r="H167" s="77" t="n"/>
-    </row>
-    <row r="168" ht="15" customHeight="1" s="95">
+      <c r="G167" s="83" t="n"/>
+      <c r="H167" s="79" t="n"/>
+    </row>
+    <row r="168" ht="15" customHeight="1" s="96">
       <c r="B168" s="3" t="n">
         <v>16</v>
       </c>
@@ -4854,18 +4861,18 @@
           <t>Насос 1Д500/63б</t>
         </is>
       </c>
-      <c r="D168" s="81" t="n"/>
-      <c r="E168" s="81" t="n">
+      <c r="D168" s="83" t="n"/>
+      <c r="E168" s="83" t="n">
         <v>12708.89</v>
       </c>
       <c r="F168" s="18">
         <f>E168*D168</f>
         <v/>
       </c>
-      <c r="G168" s="81" t="n"/>
-      <c r="H168" s="77" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1" s="95">
+      <c r="G168" s="83" t="n"/>
+      <c r="H168" s="79" t="n"/>
+    </row>
+    <row r="169" ht="15" customHeight="1" s="96">
       <c r="B169" s="3" t="n">
         <v>17</v>
       </c>
@@ -4874,18 +4881,18 @@
           <t>Насос CRE20-01 G-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D169" s="81" t="n"/>
-      <c r="E169" s="81" t="n">
+      <c r="D169" s="83" t="n"/>
+      <c r="E169" s="83" t="n">
         <v>5519.78</v>
       </c>
       <c r="F169" s="18">
         <f>E169*D169</f>
         <v/>
       </c>
-      <c r="G169" s="81" t="n"/>
-      <c r="H169" s="77" t="n"/>
-    </row>
-    <row r="170" ht="15" customHeight="1" s="95">
+      <c r="G169" s="83" t="n"/>
+      <c r="H169" s="79" t="n"/>
+    </row>
+    <row r="170" ht="15" customHeight="1" s="96">
       <c r="B170" s="3" t="n">
         <v>18</v>
       </c>
@@ -4894,15 +4901,15 @@
           <t>Насос CR15-02 A-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D170" s="81" t="n"/>
-      <c r="E170" s="81" t="n">
+      <c r="D170" s="83" t="n"/>
+      <c r="E170" s="83" t="n">
         <v>5519.78</v>
       </c>
       <c r="F170" s="18" t="n"/>
-      <c r="G170" s="81" t="n"/>
-      <c r="H170" s="77" t="n"/>
-    </row>
-    <row r="171" ht="15" customHeight="1" s="95">
+      <c r="G170" s="83" t="n"/>
+      <c r="H170" s="79" t="n"/>
+    </row>
+    <row r="171" ht="15" customHeight="1" s="96">
       <c r="B171" s="3" t="n">
         <v>19</v>
       </c>
@@ -4911,15 +4918,15 @@
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D171" s="81" t="n"/>
-      <c r="E171" s="81" t="n">
+      <c r="D171" s="83" t="n"/>
+      <c r="E171" s="83" t="n">
         <v>37957.98</v>
       </c>
       <c r="F171" s="18" t="n"/>
-      <c r="G171" s="81" t="n"/>
-      <c r="H171" s="77" t="n"/>
-    </row>
-    <row r="172" ht="15" customHeight="1" s="95">
+      <c r="G171" s="83" t="n"/>
+      <c r="H171" s="79" t="n"/>
+    </row>
+    <row r="172" ht="15" customHeight="1" s="96">
       <c r="B172" s="3" t="n">
         <v>20</v>
       </c>
@@ -4928,15 +4935,15 @@
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D172" s="81" t="n"/>
-      <c r="E172" s="81" t="n">
+      <c r="D172" s="83" t="n"/>
+      <c r="E172" s="83" t="n">
         <v>37957.98</v>
       </c>
       <c r="F172" s="18" t="n"/>
-      <c r="G172" s="81" t="n"/>
-      <c r="H172" s="77" t="n"/>
-    </row>
-    <row r="173" ht="15" customHeight="1" s="95">
+      <c r="G172" s="83" t="n"/>
+      <c r="H172" s="79" t="n"/>
+    </row>
+    <row r="173" ht="15" customHeight="1" s="96">
       <c r="B173" s="3" t="n">
         <v>21</v>
       </c>
@@ -4945,18 +4952,18 @@
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D173" s="81" t="n"/>
-      <c r="E173" s="81" t="n">
+      <c r="D173" s="83" t="n"/>
+      <c r="E173" s="83" t="n">
         <v>17361.15</v>
       </c>
       <c r="F173" s="18">
         <f>E173*D173</f>
         <v/>
       </c>
-      <c r="G173" s="81" t="n"/>
-      <c r="H173" s="77" t="n"/>
-    </row>
-    <row r="174" ht="15" customHeight="1" s="95">
+      <c r="G173" s="83" t="n"/>
+      <c r="H173" s="79" t="n"/>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="96">
       <c r="B174" s="3" t="n">
         <v>22</v>
       </c>
@@ -4965,18 +4972,18 @@
           <t>Насос ЦНС 300/1422…1900</t>
         </is>
       </c>
-      <c r="D174" s="81" t="n"/>
-      <c r="E174" s="81" t="n">
+      <c r="D174" s="83" t="n"/>
+      <c r="E174" s="83" t="n">
         <v>37957.96</v>
       </c>
       <c r="F174" s="18">
         <f>E174*D174</f>
         <v/>
       </c>
-      <c r="G174" s="81" t="n"/>
-      <c r="H174" s="77" t="n"/>
-    </row>
-    <row r="175" ht="15" customHeight="1" s="95">
+      <c r="G174" s="83" t="n"/>
+      <c r="H174" s="79" t="n"/>
+    </row>
+    <row r="175" ht="15" customHeight="1" s="96">
       <c r="B175" s="3" t="n">
         <v>23</v>
       </c>
@@ -4993,630 +5000,630 @@
         <f>E175*D175</f>
         <v/>
       </c>
-      <c r="G175" s="81" t="n"/>
-      <c r="H175" s="77" t="n"/>
-    </row>
-    <row r="176" ht="15" customHeight="1" s="95">
-      <c r="B176" s="77" t="n"/>
-      <c r="C176" s="78" t="inlineStr">
+      <c r="G175" s="83" t="n"/>
+      <c r="H175" s="79" t="n"/>
+    </row>
+    <row r="176" ht="15" customHeight="1" s="96">
+      <c r="B176" s="79" t="n"/>
+      <c r="C176" s="80" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D176" s="81" t="n"/>
-      <c r="E176" s="81" t="n"/>
+      <c r="D176" s="83" t="n"/>
+      <c r="E176" s="83" t="n"/>
       <c r="F176" s="18">
         <f>SUM(F153:F175)</f>
         <v/>
       </c>
-      <c r="G176" s="81" t="n"/>
-      <c r="H176" s="77" t="n"/>
-    </row>
-    <row r="177" ht="15" customHeight="1" s="95">
-      <c r="B177" s="77" t="inlineStr">
+      <c r="G176" s="83" t="n"/>
+      <c r="H176" s="79" t="n"/>
+    </row>
+    <row r="177" ht="15" customHeight="1" s="96">
+      <c r="B177" s="79" t="inlineStr">
         <is>
           <t>Снятие оборудования</t>
         </is>
       </c>
-      <c r="C177" s="78" t="n"/>
-      <c r="D177" s="81" t="n"/>
-      <c r="E177" s="81" t="n"/>
+      <c r="C177" s="80" t="n"/>
+      <c r="D177" s="83" t="n"/>
+      <c r="E177" s="83" t="n"/>
       <c r="F177" s="3" t="n"/>
-      <c r="G177" s="81" t="n"/>
-      <c r="H177" s="77" t="n"/>
-    </row>
-    <row r="178" ht="38.25" customHeight="1" s="95">
+      <c r="G177" s="83" t="n"/>
+      <c r="H177" s="79" t="n"/>
+    </row>
+    <row r="178" ht="38.25" customHeight="1" s="96">
       <c r="B178" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C178" s="78" t="inlineStr">
+      <c r="C178" s="80" t="inlineStr">
         <is>
           <t>Насос 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D178" s="81" t="n"/>
-      <c r="E178" s="81" t="n">
+      <c r="D178" s="83" t="n"/>
+      <c r="E178" s="83" t="n">
         <v>1204.93</v>
       </c>
       <c r="F178" s="3">
         <f>E178*D178</f>
         <v/>
       </c>
-      <c r="G178" s="81" t="n"/>
-      <c r="H178" s="77" t="n"/>
-    </row>
-    <row r="179" ht="25.5" customHeight="1" s="95">
+      <c r="G178" s="83" t="n"/>
+      <c r="H178" s="79" t="n"/>
+    </row>
+    <row r="179" ht="25.5" customHeight="1" s="96">
       <c r="B179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C179" s="78" t="inlineStr">
+      <c r="C179" s="80" t="inlineStr">
         <is>
           <t>Насос дозировочный типа НД, ДП, PIAX 32/28; PAX 32/12; BUL 6,3/64</t>
         </is>
       </c>
-      <c r="D179" s="81" t="n"/>
-      <c r="E179" s="81" t="n">
+      <c r="D179" s="83" t="n"/>
+      <c r="E179" s="83" t="n">
         <v>204.01</v>
       </c>
       <c r="F179" s="3">
         <f>E179*D179</f>
         <v/>
       </c>
-      <c r="G179" s="81" t="n"/>
-      <c r="H179" s="77" t="n"/>
-    </row>
-    <row r="180" ht="15" customHeight="1" s="95">
+      <c r="G179" s="83" t="n"/>
+      <c r="H179" s="79" t="n"/>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="96">
       <c r="B180" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C180" s="78" t="inlineStr">
+      <c r="C180" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-300/120…600</t>
         </is>
       </c>
-      <c r="D180" s="81" t="n"/>
-      <c r="E180" s="81" t="n">
+      <c r="D180" s="83" t="n"/>
+      <c r="E180" s="83" t="n">
         <v>13670.84</v>
       </c>
       <c r="F180" s="3">
         <f>E180*D180</f>
         <v/>
       </c>
-      <c r="G180" s="81" t="n"/>
-      <c r="H180" s="77" t="n"/>
-    </row>
-    <row r="181" ht="21.75" customHeight="1" s="95">
+      <c r="G180" s="83" t="n"/>
+      <c r="H180" s="79" t="n"/>
+    </row>
+    <row r="181" ht="21.75" customHeight="1" s="96">
       <c r="B181" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C181" s="78" t="inlineStr">
+      <c r="C181" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-38/44…220; ЦНС 13/70…350;  ЦГ 6,3/32;</t>
         </is>
       </c>
-      <c r="D181" s="81" t="n"/>
-      <c r="E181" s="81" t="n">
+      <c r="D181" s="83" t="n"/>
+      <c r="E181" s="83" t="n">
         <v>4657.5</v>
       </c>
       <c r="F181" s="3">
         <f>E181*D181</f>
         <v/>
       </c>
-      <c r="G181" s="81" t="n"/>
-      <c r="H181" s="77" t="n"/>
-    </row>
-    <row r="182" ht="15" customHeight="1" s="95">
+      <c r="G181" s="83" t="n"/>
+      <c r="H181" s="79" t="n"/>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="96">
       <c r="B182" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C182" s="78" t="inlineStr">
+      <c r="C182" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д630/90, Д630/125</t>
         </is>
       </c>
-      <c r="D182" s="81" t="n"/>
-      <c r="E182" s="81" t="n">
+      <c r="D182" s="83" t="n"/>
+      <c r="E182" s="83" t="n">
         <v>4884.74</v>
       </c>
       <c r="F182" s="3">
         <f>E182*D182</f>
         <v/>
       </c>
-      <c r="G182" s="81" t="n"/>
-      <c r="H182" s="77" t="n"/>
-    </row>
-    <row r="183" ht="38.25" customHeight="1" s="95">
+      <c r="G182" s="83" t="n"/>
+      <c r="H182" s="79" t="n"/>
+    </row>
+    <row r="183" ht="38.25" customHeight="1" s="96">
       <c r="B183" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C183" s="78" t="inlineStr">
+      <c r="C183" s="80" t="inlineStr">
         <is>
           <t>Насос К 65-50-160; К 65-40-100; К 65-50-160; К 80-50-200; КМН 80-65-175, К 100-80-160;К 100-65-200, КМ 160-65-200, 3Т13Н; ЦВК 6,3/160;ВКС 2/26;</t>
         </is>
       </c>
-      <c r="D183" s="81" t="n"/>
-      <c r="E183" s="81" t="n">
+      <c r="D183" s="83" t="n"/>
+      <c r="E183" s="83" t="n">
         <v>357.91</v>
       </c>
       <c r="F183" s="3">
         <f>E183*D183</f>
         <v/>
       </c>
-      <c r="G183" s="81" t="n"/>
-      <c r="H183" s="77" t="n"/>
-    </row>
-    <row r="184" ht="15" customHeight="1" s="95">
+      <c r="G183" s="83" t="n"/>
+      <c r="H183" s="79" t="n"/>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="96">
       <c r="B184" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="78" t="inlineStr">
+      <c r="C184" s="80" t="inlineStr">
         <is>
           <t>Насос НМШ 5/25; 8/25;</t>
         </is>
       </c>
-      <c r="D184" s="81" t="n"/>
-      <c r="E184" s="81" t="n">
+      <c r="D184" s="83" t="n"/>
+      <c r="E184" s="83" t="n">
         <v>276.95</v>
       </c>
       <c r="F184" s="3">
         <f>E184*D184</f>
         <v/>
       </c>
-      <c r="G184" s="81" t="n"/>
-      <c r="H184" s="77" t="n"/>
-    </row>
-    <row r="185" ht="51" customHeight="1" s="95">
+      <c r="G184" s="83" t="n"/>
+      <c r="H184" s="79" t="n"/>
+    </row>
+    <row r="185" ht="51" customHeight="1" s="96">
       <c r="B185" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C185" s="78" t="inlineStr">
+      <c r="C185" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-105/98...490; ЦНС 180/170…425; ЦНС-180/1422…1900; ЦНС 180/240/1422...1900 (2ТМ, 3ТМ); ЦНС 180/240/1422...1900 ЗК; ЦНС 63/1800; ЦНС 40/1400;</t>
         </is>
       </c>
-      <c r="D185" s="81" t="n"/>
-      <c r="E185" s="81" t="n">
+      <c r="D185" s="83" t="n"/>
+      <c r="E185" s="83" t="n">
         <v>11253.38</v>
       </c>
       <c r="F185" s="3">
         <f>E185*D185</f>
         <v/>
       </c>
-      <c r="G185" s="81" t="n"/>
-      <c r="H185" s="77" t="n"/>
-    </row>
-    <row r="186" ht="15" customHeight="1" s="95">
+      <c r="G185" s="83" t="n"/>
+      <c r="H185" s="79" t="n"/>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="96">
       <c r="B186" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C186" s="78" t="inlineStr">
+      <c r="C186" s="80" t="inlineStr">
         <is>
           <t>Насос НПВ1250-60/90</t>
         </is>
       </c>
-      <c r="D186" s="81" t="n"/>
-      <c r="E186" s="81" t="n">
+      <c r="D186" s="83" t="n"/>
+      <c r="E186" s="83" t="n">
         <v>1226.32</v>
       </c>
       <c r="F186" s="3">
         <f>E186*D186</f>
         <v/>
       </c>
-      <c r="G186" s="81" t="n"/>
-      <c r="H186" s="77" t="n"/>
-    </row>
-    <row r="187" ht="25.5" customHeight="1" s="95">
+      <c r="G186" s="83" t="n"/>
+      <c r="H186" s="79" t="n"/>
+    </row>
+    <row r="187" ht="25.5" customHeight="1" s="96">
       <c r="B187" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C187" s="78" t="inlineStr">
+      <c r="C187" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д200/90, 1Д315/71, 4Д200/90, 1Д320/70, 1Д250/125</t>
         </is>
       </c>
-      <c r="D187" s="81" t="n"/>
-      <c r="E187" s="81" t="n">
+      <c r="D187" s="83" t="n"/>
+      <c r="E187" s="83" t="n">
         <v>1941.26</v>
       </c>
       <c r="F187" s="3">
         <f>E187*D187</f>
         <v/>
       </c>
-      <c r="G187" s="81" t="n"/>
-      <c r="H187" s="77" t="n"/>
-    </row>
-    <row r="188" ht="15" customHeight="1" s="95">
+      <c r="G187" s="83" t="n"/>
+      <c r="H187" s="79" t="n"/>
+    </row>
+    <row r="188" ht="15" customHeight="1" s="96">
       <c r="B188" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C188" s="78" t="inlineStr">
+      <c r="C188" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС-60/66...330;</t>
         </is>
       </c>
-      <c r="D188" s="81" t="n"/>
-      <c r="E188" s="81" t="n">
+      <c r="D188" s="83" t="n"/>
+      <c r="E188" s="83" t="n">
         <v>6396.48</v>
       </c>
       <c r="F188" s="3">
         <f>E188*D188</f>
         <v/>
       </c>
-      <c r="G188" s="81" t="n"/>
-      <c r="H188" s="77" t="n"/>
-    </row>
-    <row r="189" ht="38.25" customHeight="1" s="95">
+      <c r="G188" s="83" t="n"/>
+      <c r="H188" s="79" t="n"/>
+    </row>
+    <row r="189" ht="38.25" customHeight="1" s="96">
       <c r="B189" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C189" s="78" t="inlineStr">
+      <c r="C189" s="80" t="inlineStr">
         <is>
           <t>Насос АХП 45/31; 12НА9/4; 12НА 22/6; НВ 50/50; НВ 50/80; НВЕ 50/50; НВЕ 50/80; НВД50/50; НВД 50/80; НВД35/90; ГХИ 6,3/32;</t>
         </is>
       </c>
-      <c r="D189" s="81" t="n"/>
-      <c r="E189" s="81" t="n">
+      <c r="D189" s="83" t="n"/>
+      <c r="E189" s="83" t="n">
         <v>1204.93</v>
       </c>
       <c r="F189" s="3">
         <f>E189*D189</f>
         <v/>
       </c>
-      <c r="G189" s="81" t="n"/>
-      <c r="H189" s="77" t="n"/>
-    </row>
-    <row r="190" ht="15" customHeight="1" s="95">
+      <c r="G189" s="83" t="n"/>
+      <c r="H189" s="79" t="n"/>
+    </row>
+    <row r="190" ht="15" customHeight="1" s="96">
       <c r="B190" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C190" s="78" t="inlineStr">
+      <c r="C190" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д1250/90-125</t>
         </is>
       </c>
-      <c r="D190" s="81" t="n"/>
-      <c r="E190" s="81" t="n">
+      <c r="D190" s="83" t="n"/>
+      <c r="E190" s="83" t="n">
         <v>6164.09</v>
       </c>
       <c r="F190" s="3">
         <f>E190*D190</f>
         <v/>
       </c>
-      <c r="G190" s="81" t="n"/>
-      <c r="H190" s="77" t="n"/>
-    </row>
-    <row r="191" ht="19.5" customHeight="1" s="95">
+      <c r="G190" s="83" t="n"/>
+      <c r="H190" s="79" t="n"/>
+    </row>
+    <row r="191" ht="19.5" customHeight="1" s="96">
       <c r="B191" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C191" s="78" t="inlineStr">
+      <c r="C191" s="80" t="inlineStr">
         <is>
           <t>Насос KRGH 80/315,KRGH 200/500, KRGH 125/80/315</t>
         </is>
       </c>
-      <c r="D191" s="81" t="n"/>
-      <c r="E191" s="81" t="n">
+      <c r="D191" s="83" t="n"/>
+      <c r="E191" s="83" t="n">
         <v>9896.059999999999</v>
       </c>
       <c r="F191" s="3" t="n"/>
-      <c r="G191" s="81" t="n"/>
-      <c r="H191" s="77" t="n"/>
-    </row>
-    <row r="192" ht="15" customHeight="1" s="95">
+      <c r="G191" s="83" t="n"/>
+      <c r="H191" s="79" t="n"/>
+    </row>
+    <row r="192" ht="15" customHeight="1" s="96">
       <c r="B192" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C192" s="78" t="inlineStr">
+      <c r="C192" s="80" t="inlineStr">
         <is>
           <t>Станок-качалка (СК)</t>
         </is>
       </c>
-      <c r="D192" s="81" t="n"/>
-      <c r="E192" s="81" t="n">
+      <c r="D192" s="83" t="n"/>
+      <c r="E192" s="83" t="n">
         <v>14097.33</v>
       </c>
       <c r="F192" s="3" t="n"/>
-      <c r="G192" s="81" t="n"/>
-      <c r="H192" s="77" t="n"/>
-    </row>
-    <row r="193" ht="15" customHeight="1" s="95">
+      <c r="G192" s="83" t="n"/>
+      <c r="H192" s="79" t="n"/>
+    </row>
+    <row r="193" ht="15" customHeight="1" s="96">
       <c r="B193" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C193" s="78" t="inlineStr">
+      <c r="C193" s="80" t="inlineStr">
         <is>
           <t>Демонтаж балансира</t>
         </is>
       </c>
-      <c r="D193" s="81" t="n"/>
-      <c r="E193" s="81" t="n">
+      <c r="D193" s="83" t="n"/>
+      <c r="E193" s="83" t="n">
         <v>10520.32</v>
       </c>
       <c r="F193" s="3" t="n"/>
-      <c r="G193" s="81" t="n"/>
-      <c r="H193" s="77" t="n"/>
-    </row>
-    <row r="194" ht="15" customHeight="1" s="95">
+      <c r="G193" s="83" t="n"/>
+      <c r="H193" s="79" t="n"/>
+    </row>
+    <row r="194" ht="15" customHeight="1" s="96">
       <c r="B194" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C194" s="78" t="inlineStr">
+      <c r="C194" s="80" t="inlineStr">
         <is>
           <t>Основание СК (свайное поле)</t>
         </is>
       </c>
-      <c r="D194" s="81" t="n"/>
-      <c r="E194" s="81" t="n">
+      <c r="D194" s="83" t="n"/>
+      <c r="E194" s="83" t="n">
         <v>21359.93</v>
       </c>
       <c r="F194" s="3" t="n"/>
-      <c r="G194" s="81" t="n"/>
-      <c r="H194" s="77" t="n"/>
-    </row>
-    <row r="195" ht="15" customHeight="1" s="95">
+      <c r="G194" s="83" t="n"/>
+      <c r="H194" s="79" t="n"/>
+    </row>
+    <row r="195" ht="15" customHeight="1" s="96">
       <c r="B195" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C195" s="78" t="inlineStr">
+      <c r="C195" s="80" t="inlineStr">
         <is>
           <t>Насос 1Д500/63б</t>
         </is>
       </c>
-      <c r="D195" s="81" t="n"/>
-      <c r="E195" s="81" t="n">
+      <c r="D195" s="83" t="n"/>
+      <c r="E195" s="83" t="n">
         <v>4884.74</v>
       </c>
       <c r="F195" s="3" t="n"/>
-      <c r="G195" s="81" t="n"/>
-      <c r="H195" s="77" t="n"/>
-    </row>
-    <row r="196" ht="15" customHeight="1" s="95">
+      <c r="G195" s="83" t="n"/>
+      <c r="H195" s="79" t="n"/>
+    </row>
+    <row r="196" ht="15" customHeight="1" s="96">
       <c r="B196" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C196" s="78" t="inlineStr">
+      <c r="C196" s="80" t="inlineStr">
         <is>
           <t>Насос CRE20-01 G-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D196" s="81" t="n"/>
-      <c r="E196" s="81" t="n">
+      <c r="D196" s="83" t="n"/>
+      <c r="E196" s="83" t="n">
         <v>2240.93</v>
       </c>
       <c r="F196" s="3" t="n"/>
-      <c r="G196" s="81" t="n"/>
-      <c r="H196" s="77" t="n"/>
-    </row>
-    <row r="197" ht="15" customHeight="1" s="95">
+      <c r="G196" s="83" t="n"/>
+      <c r="H196" s="79" t="n"/>
+    </row>
+    <row r="197" ht="15" customHeight="1" s="96">
       <c r="B197" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C197" s="78" t="inlineStr">
+      <c r="C197" s="80" t="inlineStr">
         <is>
           <t>Насос CR15-02 A-F-A-E-HQQE</t>
         </is>
       </c>
-      <c r="D197" s="81" t="n"/>
-      <c r="E197" s="81" t="n">
+      <c r="D197" s="83" t="n"/>
+      <c r="E197" s="83" t="n">
         <v>2240.93</v>
       </c>
       <c r="F197" s="3">
         <f>E197*D197</f>
         <v/>
       </c>
-      <c r="G197" s="81" t="n"/>
-      <c r="H197" s="77" t="n"/>
-    </row>
-    <row r="198" ht="15" customHeight="1" s="95">
+      <c r="G197" s="83" t="n"/>
+      <c r="H197" s="79" t="n"/>
+    </row>
+    <row r="198" ht="15" customHeight="1" s="96">
       <c r="B198" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C198" s="78" t="inlineStr">
+      <c r="C198" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 180-1422...1900 3 ТМ</t>
         </is>
       </c>
-      <c r="D198" s="81" t="n"/>
-      <c r="E198" s="81" t="n">
+      <c r="D198" s="83" t="n"/>
+      <c r="E198" s="83" t="n">
         <v>11253.38</v>
       </c>
       <c r="F198" s="3">
         <f>E198*D198</f>
         <v/>
       </c>
-      <c r="G198" s="81" t="n"/>
-      <c r="H198" s="77" t="n"/>
-    </row>
-    <row r="199" ht="15" customHeight="1" s="95">
+      <c r="G198" s="83" t="n"/>
+      <c r="H198" s="79" t="n"/>
+    </row>
+    <row r="199" ht="15" customHeight="1" s="96">
       <c r="B199" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C199" s="78" t="inlineStr">
+      <c r="C199" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 63-1422...1900 2 ТМ</t>
         </is>
       </c>
-      <c r="D199" s="81" t="n"/>
-      <c r="E199" s="81" t="n">
+      <c r="D199" s="83" t="n"/>
+      <c r="E199" s="83" t="n">
         <v>11253.38</v>
       </c>
       <c r="F199" s="3">
         <f>E199*D199</f>
         <v/>
       </c>
-      <c r="G199" s="81" t="n"/>
-      <c r="H199" s="77" t="n"/>
-    </row>
-    <row r="200" ht="15" customHeight="1" s="95">
+      <c r="G199" s="83" t="n"/>
+      <c r="H199" s="79" t="n"/>
+    </row>
+    <row r="200" ht="15" customHeight="1" s="96">
       <c r="B200" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C200" s="78" t="inlineStr">
+      <c r="C200" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 13-70... 350</t>
         </is>
       </c>
-      <c r="D200" s="81" t="n"/>
-      <c r="E200" s="81" t="n">
+      <c r="D200" s="83" t="n"/>
+      <c r="E200" s="83" t="n">
         <v>4657.5</v>
       </c>
       <c r="F200" s="3">
         <f>E200*D200</f>
         <v/>
       </c>
-      <c r="G200" s="81" t="n"/>
-      <c r="H200" s="77" t="n"/>
-    </row>
-    <row r="201" ht="15" customHeight="1" s="95">
+      <c r="G200" s="83" t="n"/>
+      <c r="H200" s="79" t="n"/>
+    </row>
+    <row r="201" ht="15" customHeight="1" s="96">
       <c r="B201" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C201" s="78" t="inlineStr">
+      <c r="C201" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 300/1422…1900</t>
         </is>
       </c>
-      <c r="D201" s="81" t="n"/>
-      <c r="E201" s="81" t="n">
+      <c r="D201" s="83" t="n"/>
+      <c r="E201" s="83" t="n">
         <v>11253.38</v>
       </c>
       <c r="F201" s="3">
         <f>E201*D201</f>
         <v/>
       </c>
-      <c r="G201" s="81" t="n"/>
-      <c r="H201" s="77" t="n"/>
-    </row>
-    <row r="202" ht="15" customHeight="1" s="95">
+      <c r="G201" s="83" t="n"/>
+      <c r="H201" s="79" t="n"/>
+    </row>
+    <row r="202" ht="15" customHeight="1" s="96">
       <c r="B202" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C202" s="78" t="inlineStr">
+      <c r="C202" s="80" t="inlineStr">
         <is>
           <t>Насос ЦНС 310/1422…1900</t>
         </is>
       </c>
-      <c r="D202" s="81" t="n"/>
-      <c r="E202" s="81" t="n">
+      <c r="D202" s="83" t="n"/>
+      <c r="E202" s="83" t="n">
         <v>11253.38</v>
       </c>
       <c r="F202" s="3">
         <f>E202*D202</f>
         <v/>
       </c>
-      <c r="G202" s="81" t="n"/>
-      <c r="H202" s="77" t="n"/>
-    </row>
-    <row r="203" ht="14.25" customHeight="1" s="95">
+      <c r="G202" s="83" t="n"/>
+      <c r="H202" s="79" t="n"/>
+    </row>
+    <row r="203" ht="14.25" customHeight="1" s="96">
       <c r="B203" s="3" t="n"/>
-      <c r="C203" s="78" t="inlineStr">
+      <c r="C203" s="80" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D203" s="81" t="n"/>
-      <c r="E203" s="81" t="n"/>
+      <c r="D203" s="83" t="n"/>
+      <c r="E203" s="83" t="n"/>
       <c r="F203" s="3">
         <f>SUM(F178:F202)</f>
         <v/>
       </c>
-      <c r="G203" s="81" t="n"/>
-      <c r="H203" s="77" t="n"/>
-    </row>
-    <row r="204" ht="15" customHeight="1" s="95">
-      <c r="B204" s="77" t="inlineStr">
+      <c r="G203" s="83" t="n"/>
+      <c r="H203" s="79" t="n"/>
+    </row>
+    <row r="204" ht="15" customHeight="1" s="96">
+      <c r="B204" s="79" t="inlineStr">
         <is>
           <t>Прочие работы</t>
         </is>
       </c>
-      <c r="C204" s="78" t="n"/>
-      <c r="D204" s="81" t="n"/>
-      <c r="E204" s="81" t="n"/>
+      <c r="C204" s="80" t="n"/>
+      <c r="D204" s="83" t="n"/>
+      <c r="E204" s="83" t="n"/>
       <c r="F204" s="3" t="n"/>
-      <c r="G204" s="81" t="n"/>
-      <c r="H204" s="77" t="n"/>
-    </row>
-    <row r="205" ht="15" customHeight="1" s="95">
+      <c r="G204" s="83" t="n"/>
+      <c r="H204" s="79" t="n"/>
+    </row>
+    <row r="205" ht="15" customHeight="1" s="96">
       <c r="B205" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C205" s="78" t="inlineStr">
+      <c r="C205" s="80" t="inlineStr">
         <is>
           <t>Снятие, установка с обвзякой БГ</t>
         </is>
       </c>
-      <c r="D205" s="81" t="n"/>
-      <c r="E205" s="81" t="n">
+      <c r="D205" s="83" t="n"/>
+      <c r="E205" s="83" t="n">
         <v>325283.1</v>
       </c>
       <c r="F205" s="3">
         <f>E205*D205</f>
         <v/>
       </c>
-      <c r="G205" s="81" t="n"/>
-      <c r="H205" s="77" t="n"/>
-    </row>
-    <row r="206" ht="15" customHeight="1" s="95">
+      <c r="G205" s="83" t="n"/>
+      <c r="H205" s="79" t="n"/>
+    </row>
+    <row r="206" ht="15" customHeight="1" s="96">
       <c r="B206" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C206" s="78" t="inlineStr">
+      <c r="C206" s="80" t="inlineStr">
         <is>
           <t>Снятие, установка с обвзякой АГЗУ</t>
         </is>
       </c>
-      <c r="D206" s="81" t="n"/>
-      <c r="E206" s="81" t="n">
+      <c r="D206" s="83" t="n"/>
+      <c r="E206" s="83" t="n">
         <v>379231.49</v>
       </c>
       <c r="F206" s="3" t="n"/>
-      <c r="G206" s="81" t="n"/>
-      <c r="H206" s="77" t="n"/>
-    </row>
-    <row r="207" ht="21" customHeight="1" s="95">
+      <c r="G206" s="83" t="n"/>
+      <c r="H206" s="79" t="n"/>
+    </row>
+    <row r="207" ht="21" customHeight="1" s="96">
       <c r="B207" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C207" s="78" t="inlineStr">
+      <c r="C207" s="80" t="inlineStr">
         <is>
           <t>Установка площадки обслуживания скважин</t>
         </is>
       </c>
-      <c r="D207" s="81" t="n"/>
-      <c r="E207" s="81" t="n">
+      <c r="D207" s="83" t="n"/>
+      <c r="E207" s="83" t="n">
         <v>10115.25</v>
       </c>
       <c r="F207" s="3">
         <f>E207*D207</f>
         <v/>
       </c>
-      <c r="G207" s="81" t="n"/>
-      <c r="H207" s="77" t="n"/>
-    </row>
-    <row r="208" ht="14.25" customHeight="1" s="95">
+      <c r="G207" s="83" t="n"/>
+      <c r="H207" s="79" t="n"/>
+    </row>
+    <row r="208" ht="14.25" customHeight="1" s="96">
       <c r="B208" s="3" t="n"/>
-      <c r="C208" s="78" t="inlineStr">
+      <c r="C208" s="80" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D208" s="81" t="n"/>
-      <c r="E208" s="81" t="n"/>
+      <c r="D208" s="83" t="n"/>
+      <c r="E208" s="83" t="n"/>
       <c r="F208" s="3">
         <f>SUM(F205:F207)</f>
         <v/>
       </c>
-      <c r="G208" s="81" t="n"/>
-      <c r="H208" s="77" t="n"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1" s="95">
+      <c r="G208" s="83" t="n"/>
+      <c r="H208" s="79" t="n"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1" s="96">
       <c r="B209" s="13" t="inlineStr">
         <is>
           <t>Итого:</t>
         </is>
       </c>
-      <c r="D209" s="81" t="n"/>
-      <c r="E209" s="81" t="n"/>
+      <c r="D209" s="83" t="n"/>
+      <c r="E209" s="83" t="n"/>
       <c r="F209" s="18">
         <f>F208+F203+F176+F151+F112+F64</f>
         <v/>
@@ -5625,55 +5632,55 @@
         <f>F203+F176+F152+F151+F112+F64</f>
         <v/>
       </c>
-      <c r="I209" s="82">
+      <c r="I209" s="84">
         <f>F203+F176+F151+F112+F64</f>
         <v/>
       </c>
     </row>
-    <row r="210" ht="14.25" customHeight="1" s="95">
+    <row r="210" ht="14.25" customHeight="1" s="96">
       <c r="B210" s="13" t="inlineStr">
         <is>
           <t>НДС 18%</t>
         </is>
       </c>
-      <c r="D210" s="81" t="n"/>
-      <c r="E210" s="81" t="n"/>
+      <c r="D210" s="83" t="n"/>
+      <c r="E210" s="83" t="n"/>
       <c r="F210" s="18">
         <f>F209*0.18</f>
         <v/>
       </c>
-      <c r="G210" s="81" t="n"/>
-    </row>
-    <row r="211" ht="14.25" customHeight="1" s="95">
+      <c r="G210" s="83" t="n"/>
+    </row>
+    <row r="211" ht="14.25" customHeight="1" s="96">
       <c r="B211" s="13" t="inlineStr">
         <is>
           <t>Всего с НДС</t>
         </is>
       </c>
-      <c r="D211" s="81" t="n"/>
-      <c r="E211" s="81" t="n"/>
+      <c r="D211" s="83" t="n"/>
+      <c r="E211" s="83" t="n"/>
       <c r="F211" s="18">
         <f>F209+F210</f>
         <v/>
       </c>
-      <c r="G211" s="81" t="n"/>
-    </row>
-    <row r="212" ht="24.75" customHeight="1" s="95">
+      <c r="G211" s="83" t="n"/>
+    </row>
+    <row r="212" ht="24.75" customHeight="1" s="96">
       <c r="B212" s="13" t="n"/>
-      <c r="D212" s="81" t="n"/>
-      <c r="E212" s="81" t="n"/>
+      <c r="D212" s="83" t="n"/>
+      <c r="E212" s="83" t="n"/>
       <c r="F212" s="18" t="n"/>
       <c r="L212" s="3" t="n"/>
     </row>
-    <row r="213" ht="12.75" customFormat="1" customHeight="1" s="77">
-      <c r="B213" s="80" t="inlineStr">
+    <row r="213" ht="12.75" customFormat="1" customHeight="1" s="79">
+      <c r="B213" s="82" t="inlineStr">
         <is>
           <t>ИСПОЛНИТЕЛЬ:</t>
         </is>
       </c>
-      <c r="C213" s="82" t="n"/>
-      <c r="D213" s="80" t="n"/>
-      <c r="E213" s="80" t="inlineStr">
+      <c r="C213" s="84" t="n"/>
+      <c r="D213" s="82" t="n"/>
+      <c r="E213" s="82" t="inlineStr">
         <is>
           <t>ЗАКАЗЧИК:</t>
         </is>
@@ -5681,16 +5688,16 @@
       <c r="G213" s="3" t="n"/>
       <c r="L213" s="3" t="n"/>
     </row>
-    <row r="214" customFormat="1" s="77">
-      <c r="A214" s="82" t="inlineStr">
+    <row r="214" customFormat="1" s="79">
+      <c r="A214" s="84" t="inlineStr">
         <is>
           <t>Генеральный директор</t>
         </is>
       </c>
       <c r="B214" s="8" t="n"/>
       <c r="C214" s="8" t="n"/>
-      <c r="D214" s="80" t="n"/>
-      <c r="E214" s="77" t="inlineStr">
+      <c r="D214" s="82" t="n"/>
+      <c r="E214" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">И.О.Главного инженера – заместителя </t>
         </is>
@@ -5698,11 +5705,11 @@
       <c r="F214" s="44" t="n"/>
       <c r="H214" s="44" t="n"/>
     </row>
-    <row r="215" ht="20.25" customFormat="1" customHeight="1" s="77">
+    <row r="215" ht="20.25" customFormat="1" customHeight="1" s="79">
       <c r="B215" s="8" t="n"/>
       <c r="C215" s="8" t="n"/>
-      <c r="D215" s="80" t="n"/>
-      <c r="E215" s="77" t="inlineStr">
+      <c r="D215" s="82" t="n"/>
+      <c r="E215" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">генерального директора </t>
         </is>
@@ -5710,7 +5717,7 @@
       <c r="F215" s="44" t="n"/>
       <c r="H215" s="44" t="n"/>
     </row>
-    <row r="216" ht="24" customFormat="1" customHeight="1" s="77">
+    <row r="216" ht="24" customFormat="1" customHeight="1" s="79">
       <c r="A216" s="22" t="inlineStr">
         <is>
           <t>ООО "ЯмалСпецЦентр"</t>
@@ -5718,8 +5725,8 @@
       </c>
       <c r="B216" s="8" t="n"/>
       <c r="C216" s="8" t="n"/>
-      <c r="D216" s="80" t="n"/>
-      <c r="E216" s="77" t="inlineStr">
+      <c r="D216" s="82" t="n"/>
+      <c r="E216" s="79" t="inlineStr">
         <is>
           <t xml:space="preserve">АО "Газпромнефть-Ноябрьскнефтегаз"                                  </t>
         </is>
@@ -5727,40 +5734,40 @@
       <c r="F216" s="44" t="n"/>
       <c r="H216" s="44" t="n"/>
     </row>
-    <row r="217" ht="26.25" customFormat="1" customHeight="1" s="77">
-      <c r="A217" s="82" t="inlineStr">
+    <row r="217" ht="26.25" customFormat="1" customHeight="1" s="79">
+      <c r="A217" s="84" t="inlineStr">
         <is>
           <t>_________________А.Г. Воронин</t>
         </is>
       </c>
-      <c r="B217" s="86" t="n"/>
-      <c r="C217" s="86" t="n"/>
-      <c r="D217" s="78" t="n"/>
-      <c r="E217" s="82" t="inlineStr">
+      <c r="B217" s="88" t="n"/>
+      <c r="C217" s="88" t="n"/>
+      <c r="D217" s="80" t="n"/>
+      <c r="E217" s="84" t="inlineStr">
         <is>
           <t>_________________ В.В. Климанов</t>
         </is>
       </c>
-      <c r="G217" s="82" t="n"/>
-    </row>
-    <row r="218" customFormat="1" s="77">
-      <c r="A218" s="83" t="inlineStr">
+      <c r="G217" s="84" t="n"/>
+    </row>
+    <row r="218" customFormat="1" s="79">
+      <c r="A218" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">                        М.П.</t>
         </is>
       </c>
-      <c r="D218" s="80" t="n"/>
+      <c r="D218" s="82" t="n"/>
       <c r="E218" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">                        М.П.</t>
         </is>
       </c>
-      <c r="F218" s="84" t="n"/>
+      <c r="F218" s="86" t="n"/>
       <c r="G218" s="49" t="n"/>
-      <c r="H218" s="84" t="n"/>
-    </row>
-    <row r="219" ht="15" customFormat="1" customHeight="1" s="77">
-      <c r="A219" s="84" t="n"/>
+      <c r="H218" s="86" t="n"/>
+    </row>
+    <row r="219" ht="15" customFormat="1" customHeight="1" s="79">
+      <c r="A219" s="86" t="n"/>
       <c r="D219" s="10" t="n"/>
       <c r="E219" s="11" t="inlineStr">
         <is>
@@ -5771,16 +5778,16 @@
       <c r="G219" s="11" t="n"/>
       <c r="H219" s="11" t="n"/>
     </row>
-    <row r="220" ht="13.5" customFormat="1" customHeight="1" s="77">
+    <row r="220" ht="13.5" customFormat="1" customHeight="1" s="79">
       <c r="A220" s="30" t="n"/>
-      <c r="B220" s="83" t="n"/>
+      <c r="B220" s="85" t="n"/>
       <c r="C220" s="8" t="n"/>
       <c r="D220" s="20" t="n"/>
       <c r="E220" s="20" t="n"/>
       <c r="F220" s="20" t="n"/>
       <c r="G220" s="20" t="n"/>
     </row>
-    <row r="221" customFormat="1" s="77">
+    <row r="221" customFormat="1" s="79">
       <c r="A221" s="35" t="inlineStr">
         <is>
           <t>СОГЛАСОВАНО:</t>
@@ -5788,7 +5795,7 @@
       </c>
       <c r="B221" s="33" t="n"/>
       <c r="C221" s="8" t="n"/>
-      <c r="D221" s="80" t="n"/>
+      <c r="D221" s="82" t="n"/>
       <c r="E221" s="35" t="inlineStr">
         <is>
           <t>СОГЛАСОВАНО:</t>
@@ -5797,40 +5804,40 @@
       <c r="F221" s="36" t="n"/>
       <c r="G221" s="3" t="n"/>
     </row>
-    <row r="222" customFormat="1" s="77">
+    <row r="222" customFormat="1" s="79">
       <c r="A222" s="32" t="n"/>
       <c r="B222" s="33" t="n"/>
       <c r="C222" s="8" t="n"/>
-      <c r="D222" s="80" t="n"/>
+      <c r="D222" s="82" t="n"/>
       <c r="E222" s="35" t="n"/>
       <c r="F222" s="36" t="n"/>
       <c r="G222" s="3" t="n"/>
     </row>
-    <row r="223" ht="18" customFormat="1" customHeight="1" s="77">
-      <c r="A223" s="86" t="inlineStr">
+    <row r="223" ht="18" customFormat="1" customHeight="1" s="79">
+      <c r="A223" s="88" t="inlineStr">
         <is>
           <t>Начальник ПЭО</t>
         </is>
       </c>
-      <c r="D223" s="78" t="n"/>
+      <c r="D223" s="80" t="n"/>
       <c r="E223" s="37" t="inlineStr">
         <is>
           <t>Главный механик - начальник УОРНПО</t>
         </is>
       </c>
-      <c r="F223" s="82" t="n"/>
+      <c r="F223" s="84" t="n"/>
       <c r="G223" s="3" t="n"/>
     </row>
-    <row r="224" customFormat="1" s="77">
-      <c r="A224" s="76" t="n"/>
-      <c r="C224" s="78" t="n"/>
-      <c r="D224" s="80" t="n"/>
+    <row r="224" customFormat="1" s="79">
+      <c r="A224" s="78" t="n"/>
+      <c r="C224" s="80" t="n"/>
+      <c r="D224" s="82" t="n"/>
       <c r="E224" s="37" t="n"/>
       <c r="F224" s="34" t="n"/>
       <c r="G224" s="3" t="n"/>
     </row>
-    <row r="225" customFormat="1" s="77">
-      <c r="A225" s="82" t="n"/>
+    <row r="225" customFormat="1" s="79">
+      <c r="A225" s="84" t="n"/>
       <c r="B225" s="21" t="inlineStr">
         <is>
           <t>_________________А.С. Бойчук</t>
@@ -5847,7 +5854,7 @@
       <c r="G225" s="3" t="n"/>
       <c r="H225" s="19" t="n"/>
     </row>
-    <row r="226" customFormat="1" s="77">
+    <row r="226" customFormat="1" s="79">
       <c r="B226" s="39" t="n"/>
       <c r="C226" s="40" t="n"/>
       <c r="D226" s="12" t="n"/>
@@ -5856,10 +5863,10 @@
       <c r="G226" s="3" t="n"/>
       <c r="H226" s="19" t="n"/>
     </row>
-    <row r="227" ht="12.75" customFormat="1" customHeight="1" s="77">
+    <row r="227" ht="12.75" customFormat="1" customHeight="1" s="79">
       <c r="B227" s="11" t="n"/>
       <c r="C227" s="8" t="n"/>
-      <c r="D227" s="78" t="n"/>
+      <c r="D227" s="80" t="n"/>
       <c r="E227" s="38" t="inlineStr">
         <is>
           <t>Планово-бюджетное управление</t>
@@ -5868,9 +5875,9 @@
       <c r="F227" s="34" t="n"/>
       <c r="G227" s="3" t="n"/>
     </row>
-    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="77">
-      <c r="B228" s="82" t="n"/>
-      <c r="C228" s="82" t="n"/>
+    <row r="228" ht="15.75" customFormat="1" customHeight="1" s="79">
+      <c r="B228" s="84" t="n"/>
+      <c r="C228" s="84" t="n"/>
       <c r="D228" s="13" t="n"/>
       <c r="E228" s="14" t="inlineStr">
         <is>
@@ -5880,29 +5887,29 @@
       <c r="F228" s="34" t="n"/>
       <c r="G228" s="3" t="n"/>
     </row>
-    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="77">
-      <c r="B229" s="82" t="n"/>
-      <c r="C229" s="82" t="n"/>
+    <row r="229" ht="15.75" customFormat="1" customHeight="1" s="79">
+      <c r="B229" s="84" t="n"/>
+      <c r="C229" s="84" t="n"/>
       <c r="D229" s="14" t="n"/>
-      <c r="E229" s="81" t="n"/>
-      <c r="F229" s="81" t="n"/>
+      <c r="E229" s="83" t="n"/>
+      <c r="F229" s="83" t="n"/>
       <c r="G229" s="3" t="n"/>
     </row>
-    <row r="230" ht="6" customHeight="1" s="95">
+    <row r="230" ht="6" customHeight="1" s="96">
       <c r="B230" s="6" t="n"/>
-      <c r="C230" s="81" t="n"/>
-      <c r="D230" s="81" t="n"/>
-      <c r="E230" s="81" t="n"/>
-      <c r="F230" s="81" t="n"/>
-      <c r="G230" s="81" t="n"/>
-    </row>
-    <row r="231" ht="12.75" customHeight="1" s="95">
+      <c r="C230" s="83" t="n"/>
+      <c r="D230" s="83" t="n"/>
+      <c r="E230" s="83" t="n"/>
+      <c r="F230" s="83" t="n"/>
+      <c r="G230" s="83" t="n"/>
+    </row>
+    <row r="231" ht="12.75" customHeight="1" s="96">
       <c r="B231" s="6" t="n"/>
-      <c r="C231" s="81" t="n"/>
-      <c r="D231" s="81" t="n"/>
-      <c r="E231" s="81" t="n"/>
-      <c r="F231" s="81" t="n"/>
-      <c r="G231" s="81" t="n"/>
+      <c r="C231" s="83" t="n"/>
+      <c r="D231" s="83" t="n"/>
+      <c r="E231" s="83" t="n"/>
+      <c r="F231" s="83" t="n"/>
+      <c r="G231" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -5937,16 +5944,16 @@
   <dimension ref="A2:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.5703125" customWidth="1" style="95" min="1" max="1"/>
-    <col width="13.42578125" customWidth="1" style="95" min="2" max="2"/>
-    <col width="31.42578125" customWidth="1" style="95" min="3" max="3"/>
-    <col width="17.42578125" customWidth="1" style="95" min="4" max="4"/>
-    <col width="26.85546875" customWidth="1" style="95" min="5" max="5"/>
-    <col width="13.5703125" customWidth="1" style="95" min="6" max="6"/>
-    <col width="19" customWidth="1" style="95" min="7" max="7"/>
-    <col width="18.7109375" customWidth="1" style="95" min="8" max="8"/>
-    <col width="18.5703125" customWidth="1" style="95" min="9" max="9"/>
-    <col width="22.140625" customWidth="1" style="95" min="10" max="10"/>
+    <col width="9.5703125" customWidth="1" style="96" min="1" max="1"/>
+    <col width="13.42578125" customWidth="1" style="96" min="2" max="2"/>
+    <col width="31.42578125" customWidth="1" style="96" min="3" max="3"/>
+    <col width="17.42578125" customWidth="1" style="96" min="4" max="4"/>
+    <col width="26.85546875" customWidth="1" style="96" min="5" max="5"/>
+    <col width="13.5703125" customWidth="1" style="96" min="6" max="6"/>
+    <col width="19" customWidth="1" style="96" min="7" max="7"/>
+    <col width="18.7109375" customWidth="1" style="96" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="96" min="9" max="9"/>
+    <col width="22.140625" customWidth="1" style="96" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -5963,7 +5970,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="95">
+    <row r="4" ht="15.75" customHeight="1" s="96">
       <c r="E4" s="68" t="inlineStr">
         <is>
           <t>СПРАВКА №04</t>
@@ -5971,44 +5978,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="92" t="n">
+      <c r="C5" s="94" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="94" t="inlineStr">
         <is>
           <t>на объектах ЦППН-1 Акционерного Общества "Газпромнефть-Ноябрьскнефтегаз"(Ноябрьский регион)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B10" s="90" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C10" s="90" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">Работы по  сервисному обслуживанию </t>
         </is>
       </c>
-      <c r="H10" s="89" t="inlineStr">
+      <c r="H10" s="92" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I10" s="89" t="inlineStr">
+      <c r="I10" s="92" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J10" s="91" t="inlineStr">
+      <c r="J10" s="93" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
@@ -6016,38 +6023,38 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="C12" s="90" t="inlineStr">
+      <c r="C12" s="91" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D12" s="90" t="inlineStr">
+      <c r="D12" s="91" t="inlineStr">
         <is>
           <t>Оборудование</t>
         </is>
       </c>
-      <c r="E12" s="90" t="inlineStr">
+      <c r="E12" s="91" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F12" s="90" t="inlineStr">
+      <c r="F12" s="91" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="G12" s="90" t="inlineStr">
+      <c r="G12" s="91" t="inlineStr">
         <is>
           <t>Зав №</t>
         </is>
       </c>
     </row>
     <row r="13"/>
-    <row r="14" ht="42.75" customHeight="1" s="95">
-      <c r="A14" s="90" t="n">
+    <row r="14" ht="42.75" customHeight="1" s="96">
+      <c r="A14" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="93" t="inlineStr">
+      <c r="B14" s="95" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
@@ -6057,7 +6064,7 @@
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D14" s="90" t="inlineStr">
+      <c r="D14" s="91" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6067,37 +6074,37 @@
           <t xml:space="preserve">ЦНС 240-1650-2ТМ </t>
         </is>
       </c>
-      <c r="F14" s="90" t="inlineStr">
+      <c r="F14" s="91" t="inlineStr">
         <is>
           <t>НА-5</t>
         </is>
       </c>
-      <c r="G14" s="90" t="inlineStr">
+      <c r="G14" s="91" t="inlineStr">
         <is>
           <t>20093/002-2</t>
         </is>
       </c>
       <c r="H14" s="71" t="n"/>
       <c r="I14" s="71" t="n"/>
-      <c r="J14" s="92" t="n">
+      <c r="J14" s="94" t="n">
         <v>61000387815</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="90" t="n">
+      <c r="A15" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="90" t="inlineStr">
+      <c r="B15" s="91" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D15" s="90" t="inlineStr">
+      <c r="D15" s="91" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6122,20 +6129,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="90" t="n">
+      <c r="A16" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="90" t="inlineStr">
+      <c r="B16" s="91" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="60" t="inlineStr">
         <is>
           <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D16" s="90" t="inlineStr">
+      <c r="D16" s="91" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6162,20 +6169,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="90" t="n">
+      <c r="A17" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="90" t="inlineStr">
+      <c r="B17" s="91" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>КНС-1В Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D17" s="90" t="inlineStr">
+      <c r="D17" s="91" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6201,21 +6208,21 @@
         <v>61000313869</v>
       </c>
     </row>
-    <row r="18" ht="25.5" customHeight="1" s="95">
-      <c r="A18" s="90" t="n">
+    <row r="18" ht="25.5" customHeight="1" s="96">
+      <c r="A18" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="90" t="inlineStr">
+      <c r="B18" s="91" t="inlineStr">
         <is>
           <t>ЦППД-1</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="60" t="inlineStr">
         <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D18" s="90" t="inlineStr">
+      <c r="D18" s="91" t="inlineStr">
         <is>
           <t>насос</t>
         </is>
@@ -6240,461 +6247,466 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="92" t="n"/>
-      <c r="B19" s="92" t="n"/>
-      <c r="C19" s="94" t="n"/>
+      <c r="A19" s="94" t="n"/>
+      <c r="B19" s="94" t="n"/>
+      <c r="C19" s="60" t="n"/>
       <c r="E19" s="58" t="n"/>
       <c r="F19" s="62" t="n"/>
       <c r="G19" s="59" t="n"/>
       <c r="J19" s="61" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="92" t="inlineStr">
+      <c r="A20" s="91" t="n"/>
+      <c r="B20" s="91" t="n"/>
+      <c r="C20" s="75" t="n"/>
+      <c r="H20" s="71" t="n"/>
+      <c r="I20" s="71" t="n"/>
+      <c r="J20" s="60" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B20" s="92" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C22" s="94" t="inlineStr">
         <is>
           <t>Работы по текущему ремонту!!!</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J20" s="61" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Оборудование</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Марка оборудования</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Рег. №</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Зав №</t>
         </is>
       </c>
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="D24" s="92" t="n"/>
-      <c r="F24" s="62" t="n"/>
-      <c r="G24" s="59" t="n"/>
-      <c r="J24" s="94" t="n"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+      <c r="F24" s="76" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G24" s="77" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="92" t="n"/>
-      <c r="B25" s="92" t="n"/>
-      <c r="C25" s="94" t="n"/>
-      <c r="D25" s="92" t="n"/>
-      <c r="E25" s="58" t="n"/>
-      <c r="F25" s="62" t="n"/>
-      <c r="G25" s="59" t="n"/>
-      <c r="J25" s="94" t="n"/>
+      <c r="F25" s="97" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>КНС-3 Холмогорское м/р_ХМАО</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ЦНС 180-1422-2ИТ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>НА-8</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" t="n">
+        <v>61000329246</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>КНС-1А Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1660-2ТМ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>НА-6</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>61000313869</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>КНС-1А Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1650-2ИТ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>НА-7</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" t="n">
+        <v>61000235346</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>КНС-1Б Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1650-2ТМ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>НА-10</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>86</v>
+      </c>
+      <c r="J29" t="n">
+        <v>61000235329</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="91" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C30" s="94" t="inlineStr">
+        <is>
+          <t>КНС-1В Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1050-2ИТ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>НА-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H30" s="91" t="n"/>
+      <c r="I30" s="91" t="n"/>
+      <c r="J30" t="n">
+        <v>61000153881</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>НЦС К 310-1510-УХЛ4</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>НА-2</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J31" t="n">
+        <v>61000113163</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C32" s="91" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D32" s="91" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E32" s="91" t="inlineStr">
+        <is>
+          <t>ЦНС 310-1510-2И1Т</t>
+        </is>
+      </c>
+      <c r="F32" s="91" t="inlineStr">
+        <is>
+          <t>НА-4</t>
+        </is>
+      </c>
+      <c r="G32" s="91" t="inlineStr">
+        <is>
+          <t>240-28</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>61000313869</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="96">
+      <c r="A34" s="91" t="n"/>
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="75" t="n"/>
+      <c r="D34" s="73" t="n"/>
+      <c r="E34" s="73" t="n"/>
+      <c r="F34" s="62" t="n"/>
+      <c r="G34" s="73" t="n"/>
+      <c r="H34" s="91" t="n"/>
+      <c r="I34" s="91" t="n"/>
+      <c r="J34" s="75" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="n"/>
+      <c r="B35" s="91" t="n"/>
+      <c r="C35" s="75" t="n"/>
+      <c r="D35" s="73" t="n"/>
+      <c r="E35" s="73" t="n"/>
+      <c r="F35" s="62" t="n"/>
+      <c r="G35" s="73" t="n"/>
+      <c r="H35" s="91" t="n"/>
+      <c r="I35" s="91" t="n"/>
+      <c r="J35" s="75" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="n"/>
+      <c r="B36" s="91" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="91" t="n"/>
+      <c r="E36" s="73" t="n"/>
+      <c r="F36" s="62" t="n"/>
+      <c r="G36" s="73" t="n"/>
+      <c r="H36" s="91" t="n"/>
+      <c r="I36" s="91" t="n"/>
+      <c r="J36" s="75" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="n"/>
+      <c r="B37" s="91" t="n"/>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="91" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="62" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="91" t="n"/>
+      <c r="I37" s="91" t="n"/>
+      <c r="J37" s="75" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="91" t="n"/>
+      <c r="B38" s="91" t="n"/>
+      <c r="C38" s="91" t="n"/>
+      <c r="D38" s="91" t="n"/>
+      <c r="E38" s="91" t="n"/>
+      <c r="F38" s="91" t="n"/>
+      <c r="G38" s="91" t="n"/>
+      <c r="H38" s="91" t="n"/>
+      <c r="I38" s="91" t="n"/>
+      <c r="J38" s="91" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="91" t="n"/>
+      <c r="B39" s="91" t="n"/>
+      <c r="C39" s="91" t="n"/>
+      <c r="D39" s="91" t="n"/>
+      <c r="E39" s="91" t="n"/>
+      <c r="F39" s="91" t="n"/>
+      <c r="G39" s="91" t="n"/>
+      <c r="H39" s="91" t="n"/>
+      <c r="I39" s="91" t="n"/>
+      <c r="J39" s="91" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="91" t="n"/>
+      <c r="B40" s="91" t="n"/>
+      <c r="C40" s="91" t="n"/>
+      <c r="D40" s="91" t="n"/>
+      <c r="E40" s="91" t="n"/>
+      <c r="F40" s="91" t="n"/>
+      <c r="G40" s="91" t="n"/>
+      <c r="H40" s="91" t="n"/>
+      <c r="I40" s="91" t="n"/>
+      <c r="J40" s="91" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="91" t="n"/>
+      <c r="B41" s="91" t="n"/>
+      <c r="C41" s="91" t="n"/>
+      <c r="D41" s="91" t="n"/>
+      <c r="E41" s="91" t="n"/>
+      <c r="F41" s="91" t="n"/>
+      <c r="G41" s="91" t="n"/>
+      <c r="H41" s="91" t="n"/>
+      <c r="I41" s="91" t="n"/>
+      <c r="J41" s="91" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="91" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B30" s="90" t="inlineStr">
+      <c r="B45" s="91" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
-        <is>
-          <t>Работы по текущему ремонту</t>
-        </is>
-      </c>
-      <c r="H30" s="89" t="inlineStr">
+      <c r="C45" s="91" t="inlineStr">
+        <is>
+          <t>Работы по замене агрегатов</t>
+        </is>
+      </c>
+      <c r="H45" s="92" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I30" s="89" t="inlineStr">
+      <c r="I45" s="92" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>№ ЗАКАЗА САП ТОРО</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="C32" s="90" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="D32" s="90" t="inlineStr">
-        <is>
-          <t>Оборудование</t>
-        </is>
-      </c>
-      <c r="E32" s="90" t="inlineStr">
-        <is>
-          <t>Марка оборудования</t>
-        </is>
-      </c>
-      <c r="F32" s="90" t="inlineStr">
-        <is>
-          <t>Рег. №</t>
-        </is>
-      </c>
-      <c r="G32" s="90" t="inlineStr">
-        <is>
-          <t>Зав №</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34" ht="16.5" customHeight="1" s="95">
-      <c r="A34" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C34" s="75" t="inlineStr">
-        <is>
-          <t>КНС-3 Холмогорское м/р_ХМАО</t>
-        </is>
-      </c>
-      <c r="D34" s="73" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E34" s="73" t="inlineStr">
-        <is>
-          <t>ЦНС 180-1422-2ИТ</t>
-        </is>
-      </c>
-      <c r="F34" s="62" t="inlineStr">
-        <is>
-          <t>НА-8</t>
-        </is>
-      </c>
-      <c r="G34" s="73" t="n">
-        <v>17</v>
-      </c>
-      <c r="H34" s="90" t="n"/>
-      <c r="I34" s="90" t="n"/>
-      <c r="J34" s="75" t="n">
-        <v>61000329246</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C35" s="75" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D35" s="73" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E35" s="73" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="F35" s="62" t="inlineStr">
-        <is>
-          <t>НА-6</t>
-        </is>
-      </c>
-      <c r="G35" s="73" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="90" t="n"/>
-      <c r="I35" s="90" t="n"/>
-      <c r="J35" s="75" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C36" s="75" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D36" s="90" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E36" s="73" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ИТ</t>
-        </is>
-      </c>
-      <c r="F36" s="62" t="inlineStr">
-        <is>
-          <t>НА-7</t>
-        </is>
-      </c>
-      <c r="G36" s="73" t="n">
-        <v>26</v>
-      </c>
-      <c r="H36" s="90" t="n"/>
-      <c r="I36" s="90" t="n"/>
-      <c r="J36" s="75" t="n">
-        <v>61000235346</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C37" s="75" t="inlineStr">
-        <is>
-          <t>КНС-1Б Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D37" s="90" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E37" s="73" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ТМ</t>
-        </is>
-      </c>
-      <c r="F37" s="62" t="inlineStr">
-        <is>
-          <t>НА-10</t>
-        </is>
-      </c>
-      <c r="G37" s="73" t="n">
-        <v>86</v>
-      </c>
-      <c r="H37" s="90" t="n"/>
-      <c r="I37" s="90" t="n"/>
-      <c r="J37" s="75" t="n">
-        <v>61000235329</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C38" s="90" t="inlineStr">
-        <is>
-          <t>КНС-1В Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D38" s="90" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E38" s="90" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1050-2ИТ</t>
-        </is>
-      </c>
-      <c r="F38" s="90" t="inlineStr">
-        <is>
-          <t>НА-13</t>
-        </is>
-      </c>
-      <c r="G38" s="90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H38" s="90" t="n"/>
-      <c r="I38" s="90" t="n"/>
-      <c r="J38" s="90" t="n">
-        <v>61000153881</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C39" s="90" t="inlineStr">
-        <is>
-          <t>КНС-3 Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D39" s="90" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E39" s="90" t="inlineStr">
-        <is>
-          <t>НЦС К 310-1510-УХЛ4</t>
-        </is>
-      </c>
-      <c r="F39" s="90" t="inlineStr">
-        <is>
-          <t>НА-2</t>
-        </is>
-      </c>
-      <c r="G39" s="90" t="n">
-        <v>2070</v>
-      </c>
-      <c r="H39" s="90" t="n"/>
-      <c r="I39" s="90" t="n"/>
-      <c r="J39" s="90" t="n">
-        <v>61000113163</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="90" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C40" s="90" t="inlineStr">
-        <is>
-          <t>КНС-3 Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D40" s="90" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E40" s="90" t="inlineStr">
-        <is>
-          <t>ЦНС 310-1510-2И1Т</t>
-        </is>
-      </c>
-      <c r="F40" s="90" t="inlineStr">
-        <is>
-          <t>НА-4</t>
-        </is>
-      </c>
-      <c r="G40" s="90" t="inlineStr">
-        <is>
-          <t>240-28</t>
-        </is>
-      </c>
-      <c r="H40" s="90" t="n"/>
-      <c r="I40" s="90" t="n"/>
-      <c r="J40" s="90" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="90" t="n"/>
-      <c r="B41" s="90" t="n"/>
-      <c r="C41" s="90" t="n"/>
-      <c r="D41" s="90" t="n"/>
-      <c r="E41" s="90" t="n"/>
-      <c r="F41" s="90" t="n"/>
-      <c r="G41" s="90" t="n"/>
-      <c r="H41" s="90" t="n"/>
-      <c r="I41" s="90" t="n"/>
-      <c r="J41" s="90" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="90" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
-      </c>
-      <c r="B45" s="90" t="inlineStr">
-        <is>
-          <t>ЦЕХ</t>
-        </is>
-      </c>
-      <c r="C45" s="90" t="inlineStr">
-        <is>
-          <t>Работы по замене агрегатов</t>
-        </is>
-      </c>
-      <c r="H45" s="89" t="inlineStr">
-        <is>
-          <t>Дата выполнения работ</t>
-        </is>
-      </c>
-      <c r="I45" s="89" t="inlineStr">
-        <is>
-          <t>Подпись, ФИО механика (мастера)</t>
-        </is>
-      </c>
-      <c r="J45" s="91" t="inlineStr">
+      <c r="J45" s="93" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
@@ -6702,27 +6714,27 @@
     </row>
     <row r="46"/>
     <row r="47">
-      <c r="C47" s="90" t="inlineStr">
+      <c r="C47" s="91" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D47" s="90" t="inlineStr">
+      <c r="D47" s="91" t="inlineStr">
         <is>
           <t>Рег №</t>
         </is>
       </c>
-      <c r="E47" s="90" t="inlineStr">
+      <c r="E47" s="91" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="F47" s="90" t="inlineStr">
+      <c r="F47" s="91" t="inlineStr">
         <is>
           <t>Монтаж/ПНР</t>
         </is>
       </c>
-      <c r="G47" s="90" t="inlineStr">
+      <c r="G47" s="91" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
@@ -6886,7 +6898,7 @@
         <v>61000294385</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1" s="95" thickBot="1"/>
+    <row r="57" ht="15.75" customHeight="1" s="96" thickBot="1"/>
     <row r="58">
       <c r="A58" s="54" t="inlineStr">
         <is>
@@ -6935,7 +6947,7 @@
       <c r="I60" s="54" t="n"/>
       <c r="J60" s="54" t="n"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" s="95" thickBot="1">
+    <row r="61" ht="15.75" customHeight="1" s="96" thickBot="1">
       <c r="A61" s="54" t="n"/>
       <c r="B61" s="54" t="n"/>
       <c r="C61" s="54" t="n"/>
@@ -6947,7 +6959,7 @@
       <c r="I61" s="54" t="n"/>
       <c r="J61" s="54" t="n"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="95" thickBot="1">
+    <row r="62" ht="15.75" customHeight="1" s="96" thickBot="1">
       <c r="A62" s="54" t="n"/>
       <c r="B62" s="54" t="n"/>
       <c r="C62" s="54" t="n"/>
@@ -6959,23 +6971,23 @@
       <c r="I62" s="54" t="n"/>
       <c r="J62" s="54" t="n"/>
     </row>
-    <row r="63" ht="25.5" customHeight="1" s="95">
-      <c r="A63" s="87" t="inlineStr">
+    <row r="63" ht="25.5" customHeight="1" s="96">
+      <c r="A63" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">№ п/п </t>
         </is>
       </c>
-      <c r="B63" s="87" t="inlineStr">
+      <c r="B63" s="89" t="inlineStr">
         <is>
           <t>Цех</t>
         </is>
       </c>
-      <c r="C63" s="87" t="inlineStr">
+      <c r="C63" s="89" t="inlineStr">
         <is>
           <t>Прочие работы</t>
         </is>
       </c>
-      <c r="I63" s="93" t="inlineStr">
+      <c r="I63" s="95" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
@@ -6987,7 +6999,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="87" t="inlineStr">
+      <c r="C64" s="89" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
@@ -7002,7 +7014,7 @@
       <c r="H64" s="54" t="n"/>
       <c r="J64" s="54" t="n"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="95" thickBot="1">
+    <row r="65" ht="15.75" customHeight="1" s="96" thickBot="1">
       <c r="A65" s="54" t="n"/>
       <c r="B65" s="54" t="n"/>
       <c r="C65" s="56" t="n"/>
@@ -7011,7 +7023,7 @@
       <c r="F65" s="57" t="n"/>
       <c r="G65" s="57" t="n"/>
       <c r="H65" s="57" t="n"/>
-      <c r="I65" s="87" t="n"/>
+      <c r="I65" s="89" t="n"/>
       <c r="J65" s="54" t="n"/>
     </row>
     <row r="66">
@@ -7083,58 +7095,47 @@
       <c r="J70" s="54" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="40">
     <mergeCell ref="C63:H63"/>
-    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="H10:H13"/>
-    <mergeCell ref="A30:A33"/>
     <mergeCell ref="J10:J13"/>
     <mergeCell ref="A45:A48"/>
     <mergeCell ref="I45:I48"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="I22:I25"/>
     <mergeCell ref="C47:C48"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F22:F23"/>
     <mergeCell ref="D47:D48"/>
-    <mergeCell ref="J20:J23"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="D12:D13"/>
+    <mergeCell ref="G24:G25"/>
     <mergeCell ref="H45:H48"/>
-    <mergeCell ref="J30:J33"/>
     <mergeCell ref="J45:J48"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="J22:J25"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="I63:I64"/>
-    <mergeCell ref="G32:G33"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="C30:G31"/>
+    <mergeCell ref="A22:A25"/>
     <mergeCell ref="B63:B64"/>
-    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="I10:I13"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="I10:I13"/>
     <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C20:G21"/>
     <mergeCell ref="G47:G48"/>
-    <mergeCell ref="E12:E13"/>
     <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C45:G46"/>
     <mergeCell ref="C10:G11"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="C45:G46"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="H20:H23"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B45:B48"/>
-    <mergeCell ref="H30:H33"/>
-    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="C22:G23"/>
+    <mergeCell ref="F24:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="J15:J16">
     <cfRule type="duplicateValues" priority="21" dxfId="0"/>
